--- a/benchmarking/output/data.xlsx
+++ b/benchmarking/output/data.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1115E30E-BC6C-0740-A455-6FACFDE9769B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F2965AC-1B5C-1D42-A163-C6ACA340DDB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="basic" sheetId="1" r:id="rId1"/>
     <sheet name="special" sheetId="2" r:id="rId2"/>
     <sheet name="pretrained" sheetId="4" r:id="rId3"/>
+    <sheet name="checking bias" sheetId="5" r:id="rId4"/>
+    <sheet name="checking noise" sheetId="6" r:id="rId5"/>
+    <sheet name="family of models" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="106">
   <si>
     <t>Model</t>
   </si>
@@ -217,15 +220,169 @@
   <si>
     <t>Experiment: training on all nodes in the graph but evaluation only on relevant nodes with pretrained embeddings</t>
   </si>
+  <si>
+    <t>Average All</t>
+  </si>
+  <si>
+    <t>Average RP and RC</t>
+  </si>
+  <si>
+    <t>pretrained/</t>
+  </si>
+  <si>
+    <t>Relation Prediction HITS@2</t>
+  </si>
+  <si>
+    <t>Equivalent HITS@1</t>
+  </si>
+  <si>
+    <t>Attack HITS@1</t>
+  </si>
+  <si>
+    <t>Support HITS@1</t>
+  </si>
+  <si>
+    <t>Are the models good or just biased?</t>
+  </si>
+  <si>
+    <t>Are the models robust to noise?</t>
+  </si>
+  <si>
+    <t>Noise</t>
+  </si>
+  <si>
+    <t>Do models in the same family behave the same?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semantic Matching </t>
+  </si>
+  <si>
+    <t>Deep Scoring Function</t>
+  </si>
+  <si>
+    <t>TransH</t>
+  </si>
+  <si>
+    <t>TransD</t>
+  </si>
+  <si>
+    <t>RESCAL</t>
+  </si>
+  <si>
+    <t>HolE</t>
+  </si>
+  <si>
+    <t>ConvKB</t>
+  </si>
+  <si>
+    <t>Standard Dev</t>
+  </si>
+  <si>
+    <t>Weighted Average</t>
+  </si>
+  <si>
+    <t>Average REL HITS@1</t>
+  </si>
+  <si>
+    <t>pretrained/text</t>
+  </si>
+  <si>
+    <t>pretrained/text-year</t>
+  </si>
+  <si>
+    <t>pretrained/text-speaker</t>
+  </si>
+  <si>
+    <t>pretrained/text-claim+premise</t>
+  </si>
+  <si>
+    <t>pretrained/text-claim-year</t>
+  </si>
+  <si>
+    <t>pretrained/text-claim-speaker</t>
+  </si>
+  <si>
+    <t>pretrained/text-speaker-year</t>
+  </si>
+  <si>
+    <t>pretrained/text-claim+premise-speaker-year</t>
+  </si>
+  <si>
+    <t>pretrained/text+type</t>
+  </si>
+  <si>
+    <t>pretrained/text+type-year</t>
+  </si>
+  <si>
+    <t>pretrained/text+type-speaker</t>
+  </si>
+  <si>
+    <t>pretrained/text+type-speaker-year</t>
+  </si>
+  <si>
+    <t>MIN=</t>
+  </si>
+  <si>
+    <t>Average LP, LD, TC</t>
+  </si>
+  <si>
+    <t>TRIAL 1</t>
+  </si>
+  <si>
+    <t>SUPPORT</t>
+  </si>
+  <si>
+    <t>ATTACK</t>
+  </si>
+  <si>
+    <t>EQUIVALENT</t>
+  </si>
+  <si>
+    <t>COEFF</t>
+  </si>
+  <si>
+    <t>TRIAL 2</t>
+  </si>
+  <si>
+    <t>TRIAL 3</t>
+  </si>
+  <si>
+    <t>Composition</t>
+  </si>
+  <si>
+    <t>year: 53%, support:38%, attack: 6,8%, equivalent:1,2%</t>
+  </si>
+  <si>
+    <t>year: 59%, support: 34%, attack: 6%, equivalent: 1%</t>
+  </si>
+  <si>
+    <t>says: 38%, year:36%, support: 21%, attack:4%, equivalent:1%</t>
+  </si>
+  <si>
+    <t>MAX=</t>
+  </si>
+  <si>
+    <t>MEAN=</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Weighted Average REL hits@1</t>
+  </si>
+  <si>
+    <t>Relation classification + prediction f1_macro</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000000"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -263,8 +420,52 @@
       <color theme="1"/>
       <name val="Calibri (Corpo)"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri (Corpo)"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -295,8 +496,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE9D9"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FF75"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -313,11 +544,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -364,18 +619,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -385,19 +628,144 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -406,6 +774,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFF3FF75"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -705,16 +1078,16 @@
   <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="44.83203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.83203125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="50.1640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="17.6640625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="32.83203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="39" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="42.5" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="38.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.5" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33.1640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35" style="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="38.1640625" style="12" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="8.83203125" style="5"/>
   </cols>
   <sheetData>
@@ -751,13 +1124,13 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="52" t="s">
         <v>29</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -783,9 +1156,9 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A3" s="18"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="17"/>
+      <c r="A3" s="51"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="53"/>
       <c r="D3" s="5" t="s">
         <v>24</v>
       </c>
@@ -809,9 +1182,9 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="18"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="17"/>
+      <c r="A4" s="51"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="53"/>
       <c r="D4" s="5" t="s">
         <v>25</v>
       </c>
@@ -836,7 +1209,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
-      <c r="B5" s="19"/>
+      <c r="B5" s="54"/>
       <c r="C5" s="7"/>
       <c r="E5" s="4"/>
       <c r="F5" s="6"/>
@@ -846,11 +1219,11 @@
       <c r="J5" s="6"/>
     </row>
     <row r="6" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="16" t="s">
+      <c r="B6" s="54"/>
+      <c r="C6" s="52" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="5" t="s">
@@ -876,9 +1249,9 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="18"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="17"/>
+      <c r="A7" s="51"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="53"/>
       <c r="D7" s="5" t="s">
         <v>24</v>
       </c>
@@ -902,9 +1275,9 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A8" s="18"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="17"/>
+      <c r="A8" s="51"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="53"/>
       <c r="D8" s="5" t="s">
         <v>25</v>
       </c>
@@ -929,7 +1302,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
-      <c r="B9" s="19"/>
+      <c r="B9" s="54"/>
       <c r="C9" s="7"/>
       <c r="E9" s="4"/>
       <c r="F9" s="6"/>
@@ -939,11 +1312,11 @@
       <c r="J9" s="6"/>
     </row>
     <row r="10" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="16" t="s">
+      <c r="B10" s="54"/>
+      <c r="C10" s="52" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="5" t="s">
@@ -969,9 +1342,9 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="18"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="17"/>
+      <c r="A11" s="51"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="53"/>
       <c r="D11" s="5" t="s">
         <v>24</v>
       </c>
@@ -995,9 +1368,9 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="18"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="17"/>
+      <c r="A12" s="51"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="53"/>
       <c r="D12" s="5" t="s">
         <v>25</v>
       </c>
@@ -1022,7 +1395,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="4"/>
-      <c r="B13" s="19"/>
+      <c r="B13" s="54"/>
       <c r="C13" s="7"/>
       <c r="E13" s="4"/>
       <c r="F13" s="6"/>
@@ -1032,11 +1405,11 @@
       <c r="J13" s="6"/>
     </row>
     <row r="14" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="16" t="s">
+      <c r="B14" s="54"/>
+      <c r="C14" s="52" t="s">
         <v>32</v>
       </c>
       <c r="D14" s="5" t="s">
@@ -1062,9 +1435,9 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A15" s="18"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="17"/>
+      <c r="A15" s="51"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="53"/>
       <c r="D15" s="5" t="s">
         <v>24</v>
       </c>
@@ -1088,9 +1461,9 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A16" s="18"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="17"/>
+      <c r="A16" s="51"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="53"/>
       <c r="D16" s="5" t="s">
         <v>25</v>
       </c>
@@ -1115,7 +1488,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
-      <c r="B17" s="19"/>
+      <c r="B17" s="54"/>
       <c r="C17" s="7"/>
       <c r="E17" s="4"/>
       <c r="F17" s="6"/>
@@ -1125,11 +1498,11 @@
       <c r="J17" s="6"/>
     </row>
     <row r="18" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="16" t="s">
+      <c r="B18" s="54"/>
+      <c r="C18" s="52" t="s">
         <v>33</v>
       </c>
       <c r="D18" s="5" t="s">
@@ -1155,9 +1528,9 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A19" s="18"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="17"/>
+      <c r="A19" s="51"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="53"/>
       <c r="D19" s="5" t="s">
         <v>24</v>
       </c>
@@ -1181,9 +1554,9 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A20" s="18"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="17"/>
+      <c r="A20" s="51"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="53"/>
       <c r="D20" s="5" t="s">
         <v>25</v>
       </c>
@@ -1208,7 +1581,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
-      <c r="B21" s="19"/>
+      <c r="B21" s="54"/>
       <c r="C21" s="7"/>
       <c r="E21" s="4"/>
       <c r="F21" s="6"/>
@@ -1218,11 +1591,11 @@
       <c r="J21" s="6"/>
     </row>
     <row r="22" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="19"/>
-      <c r="C22" s="16" t="s">
+      <c r="B22" s="54"/>
+      <c r="C22" s="52" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="5" t="s">
@@ -1248,9 +1621,9 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A23" s="18"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="17"/>
+      <c r="A23" s="51"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="53"/>
       <c r="D23" s="5" t="s">
         <v>24</v>
       </c>
@@ -1274,9 +1647,9 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A24" s="18"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="17"/>
+      <c r="A24" s="51"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="53"/>
       <c r="D24" s="5" t="s">
         <v>25</v>
       </c>
@@ -1301,7 +1674,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="4"/>
-      <c r="B25" s="19"/>
+      <c r="B25" s="54"/>
       <c r="C25" s="7"/>
       <c r="E25" s="4"/>
       <c r="F25" s="6"/>
@@ -1311,11 +1684,11 @@
       <c r="J25" s="6"/>
     </row>
     <row r="26" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="51" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="16" t="s">
+      <c r="B26" s="54"/>
+      <c r="C26" s="52" t="s">
         <v>35</v>
       </c>
       <c r="D26" s="8" t="s">
@@ -1341,9 +1714,9 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A27" s="18"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="17"/>
+      <c r="A27" s="51"/>
+      <c r="B27" s="54"/>
+      <c r="C27" s="53"/>
       <c r="D27" s="5" t="s">
         <v>24</v>
       </c>
@@ -1367,9 +1740,9 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A28" s="18"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="17"/>
+      <c r="A28" s="51"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="53"/>
       <c r="D28" s="5" t="s">
         <v>25</v>
       </c>
@@ -1394,7 +1767,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
-      <c r="B29" s="19"/>
+      <c r="B29" s="54"/>
       <c r="C29" s="7"/>
       <c r="E29" s="4"/>
       <c r="F29" s="6"/>
@@ -1404,11 +1777,11 @@
       <c r="J29" s="6"/>
     </row>
     <row r="30" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="16" t="s">
+      <c r="B30" s="54"/>
+      <c r="C30" s="52" t="s">
         <v>36</v>
       </c>
       <c r="D30" s="8" t="s">
@@ -1434,9 +1807,9 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A31" s="18"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="17"/>
+      <c r="A31" s="51"/>
+      <c r="B31" s="54"/>
+      <c r="C31" s="53"/>
       <c r="D31" s="5" t="s">
         <v>24</v>
       </c>
@@ -1460,9 +1833,9 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A32" s="18"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="17"/>
+      <c r="A32" s="51"/>
+      <c r="B32" s="54"/>
+      <c r="C32" s="53"/>
       <c r="D32" s="8" t="s">
         <v>25</v>
       </c>
@@ -1497,13 +1870,13 @@
       <c r="J33" s="6"/>
     </row>
     <row r="34" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="18" t="s">
+      <c r="B34" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="52" t="s">
         <v>29</v>
       </c>
       <c r="D34" s="5" t="s">
@@ -1529,9 +1902,9 @@
       </c>
     </row>
     <row r="35" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A35" s="18"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="17"/>
+      <c r="A35" s="51"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="53"/>
       <c r="D35" s="5" t="s">
         <v>24</v>
       </c>
@@ -1555,9 +1928,9 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A36" s="18"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="17"/>
+      <c r="A36" s="51"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="53"/>
       <c r="D36" s="5" t="s">
         <v>25</v>
       </c>
@@ -1582,7 +1955,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
-      <c r="B37" s="18"/>
+      <c r="B37" s="51"/>
       <c r="C37" s="7"/>
       <c r="E37" s="4"/>
       <c r="F37" s="6"/>
@@ -1592,11 +1965,11 @@
       <c r="J37" s="6"/>
     </row>
     <row r="38" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A38" s="18" t="s">
+      <c r="A38" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="B38" s="18"/>
-      <c r="C38" s="16" t="s">
+      <c r="B38" s="51"/>
+      <c r="C38" s="52" t="s">
         <v>30</v>
       </c>
       <c r="D38" s="5" t="s">
@@ -1622,9 +1995,9 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A39" s="18"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="17"/>
+      <c r="A39" s="51"/>
+      <c r="B39" s="51"/>
+      <c r="C39" s="53"/>
       <c r="D39" s="8" t="s">
         <v>24</v>
       </c>
@@ -1648,9 +2021,9 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A40" s="18"/>
-      <c r="B40" s="18"/>
-      <c r="C40" s="17"/>
+      <c r="A40" s="51"/>
+      <c r="B40" s="51"/>
+      <c r="C40" s="53"/>
       <c r="D40" s="5" t="s">
         <v>25</v>
       </c>
@@ -1675,7 +2048,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
-      <c r="B41" s="18"/>
+      <c r="B41" s="51"/>
       <c r="C41" s="7"/>
       <c r="E41" s="4"/>
       <c r="F41" s="6"/>
@@ -1685,11 +2058,11 @@
       <c r="J41" s="6"/>
     </row>
     <row r="42" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A42" s="18" t="s">
+      <c r="A42" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="B42" s="18"/>
-      <c r="C42" s="16" t="s">
+      <c r="B42" s="51"/>
+      <c r="C42" s="52" t="s">
         <v>31</v>
       </c>
       <c r="D42" s="5" t="s">
@@ -1715,9 +2088,9 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A43" s="18"/>
-      <c r="B43" s="18"/>
-      <c r="C43" s="17"/>
+      <c r="A43" s="51"/>
+      <c r="B43" s="51"/>
+      <c r="C43" s="53"/>
       <c r="D43" s="5" t="s">
         <v>24</v>
       </c>
@@ -1741,9 +2114,9 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A44" s="18"/>
-      <c r="B44" s="18"/>
-      <c r="C44" s="17"/>
+      <c r="A44" s="51"/>
+      <c r="B44" s="51"/>
+      <c r="C44" s="53"/>
       <c r="D44" s="5" t="s">
         <v>25</v>
       </c>
@@ -1768,7 +2141,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
-      <c r="B45" s="18"/>
+      <c r="B45" s="51"/>
       <c r="C45" s="7"/>
       <c r="E45" s="4"/>
       <c r="F45" s="6"/>
@@ -1778,11 +2151,11 @@
       <c r="J45" s="6"/>
     </row>
     <row r="46" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A46" s="18" t="s">
+      <c r="A46" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="B46" s="18"/>
-      <c r="C46" s="16" t="s">
+      <c r="B46" s="51"/>
+      <c r="C46" s="52" t="s">
         <v>35</v>
       </c>
       <c r="D46" s="5" t="s">
@@ -1808,9 +2181,9 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A47" s="18"/>
-      <c r="B47" s="18"/>
-      <c r="C47" s="17"/>
+      <c r="A47" s="51"/>
+      <c r="B47" s="51"/>
+      <c r="C47" s="53"/>
       <c r="D47" s="5" t="s">
         <v>24</v>
       </c>
@@ -1834,9 +2207,9 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A48" s="18"/>
-      <c r="B48" s="18"/>
-      <c r="C48" s="17"/>
+      <c r="A48" s="51"/>
+      <c r="B48" s="51"/>
+      <c r="C48" s="53"/>
       <c r="D48" s="5" t="s">
         <v>25</v>
       </c>
@@ -1950,16 +2323,16 @@
   <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="44.83203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.1640625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="46" style="5" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="17.6640625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="32.83203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="39" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="42.5" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.1640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29.5" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33.1640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35" style="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="38.1640625" style="12" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="8.83203125" style="5"/>
   </cols>
   <sheetData>
@@ -1996,95 +2369,94 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="E2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="26">
+      <c r="F2" s="19">
         <v>8.9244851299999997E-2</v>
       </c>
-      <c r="G2" s="26">
+      <c r="G2" s="19">
         <v>4.0045766999999999E-3</v>
       </c>
-      <c r="H2" s="26">
+      <c r="H2" s="19">
         <v>0.52135774219999997</v>
       </c>
-      <c r="I2" s="26">
+      <c r="I2" s="19">
         <v>0.61007338850000004</v>
       </c>
-      <c r="J2" s="26">
+      <c r="J2" s="19">
         <v>0.55770218569999996</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A3" s="18"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="23" t="s">
+      <c r="A3" s="51"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="24" t="s">
+      <c r="E3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="26">
+      <c r="F3" s="19">
         <v>9.7254005000000001E-3</v>
       </c>
-      <c r="G3" s="26">
+      <c r="G3" s="19">
         <v>4.9580472999999998E-3</v>
       </c>
-      <c r="H3" s="26">
+      <c r="H3" s="19">
         <v>0.27765064839999998</v>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="19">
         <v>0.28339461329999999</v>
       </c>
-      <c r="J3" s="26">
+      <c r="J3" s="19">
         <v>0.22860687900000001</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="18"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="23" t="s">
+      <c r="A4" s="51"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="19">
         <v>2.6315789499999999E-2</v>
       </c>
-      <c r="G4" s="26">
+      <c r="G4" s="19">
         <v>2.2883295000000001E-3</v>
       </c>
-      <c r="H4" s="26">
+      <c r="H4" s="19">
         <v>0.26201373</v>
       </c>
-      <c r="I4" s="26">
+      <c r="I4" s="19">
         <v>0.4021947038</v>
       </c>
-      <c r="J4" s="26">
+      <c r="J4" s="19">
         <v>0.41155579170000001</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
-      <c r="B5" s="19"/>
+      <c r="B5" s="54"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="24"/>
+      <c r="E5" s="4"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
@@ -2092,93 +2464,92 @@
       <c r="J5" s="6"/>
     </row>
     <row r="6" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="51" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="16" t="s">
+      <c r="B6" s="54"/>
+      <c r="C6" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="19">
         <v>2.9176201400000001E-2</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="19">
         <v>1.1823035900000001E-2</v>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="19">
         <v>0.35278413419999999</v>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="19">
         <v>0.90289591940000002</v>
       </c>
-      <c r="J6" s="26">
+      <c r="J6" s="19">
         <v>0.38437252039999997</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="18"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="23" t="s">
+      <c r="A7" s="51"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F7" s="19">
         <v>4.78642258E-2</v>
       </c>
-      <c r="G7" s="26">
+      <c r="G7" s="19">
         <v>5.7208238000000002E-3</v>
       </c>
-      <c r="H7" s="26">
+      <c r="H7" s="19">
         <v>0.56445461480000003</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="19">
         <v>0.86838170120000002</v>
       </c>
-      <c r="J7" s="26">
+      <c r="J7" s="19">
         <v>0.43012224199999999</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A8" s="18"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="17"/>
+      <c r="A8" s="51"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="53"/>
       <c r="D8" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="20">
         <v>3.8138830000000002E-4</v>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="20">
         <v>3.4324943E-3</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="20">
         <v>1</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="20">
         <v>0.4664562666</v>
       </c>
-      <c r="J8" s="27">
+      <c r="J8" s="20">
         <v>0.47061019659999997</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
-      <c r="B9" s="19"/>
+      <c r="B9" s="54"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="24"/>
+      <c r="E9" s="4"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
@@ -2186,93 +2557,92 @@
       <c r="J9" s="6"/>
     </row>
     <row r="10" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="16" t="s">
+      <c r="B10" s="54"/>
+      <c r="C10" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="E10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="19">
         <v>6.9031273800000001E-2</v>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="19">
         <v>1.25858124E-2</v>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="19">
         <v>0.4755911518</v>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="19">
         <v>0.78189336310000002</v>
       </c>
-      <c r="J10" s="26">
+      <c r="J10" s="19">
         <v>0.45351961439999999</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="18"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="23" t="s">
+      <c r="A11" s="51"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="19">
         <v>3.8138830000000002E-4</v>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="19">
         <v>4.5766590000000003E-3</v>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="19">
         <v>0.28794813120000001</v>
       </c>
-      <c r="I11" s="26">
+      <c r="I11" s="19">
         <v>0.50441556720000003</v>
       </c>
-      <c r="J11" s="26">
+      <c r="J11" s="19">
         <v>0.49009279519999999</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="18"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="17"/>
+      <c r="A12" s="51"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="53"/>
       <c r="D12" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="20">
         <v>3.8138830000000002E-4</v>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="20">
         <v>4.0045766999999999E-3</v>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="20">
         <v>1</v>
       </c>
-      <c r="I12" s="27">
+      <c r="I12" s="20">
         <v>0.47810245969999998</v>
       </c>
-      <c r="J12" s="27">
+      <c r="J12" s="20">
         <v>0.48136801289999998</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="4"/>
-      <c r="B13" s="19"/>
+      <c r="B13" s="54"/>
       <c r="C13" s="7"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="24"/>
+      <c r="E13" s="4"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
@@ -2280,93 +2650,92 @@
       <c r="J13" s="6"/>
     </row>
     <row r="14" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="51" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="16" t="s">
+      <c r="B14" s="54"/>
+      <c r="C14" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="19">
         <v>6.9984744500000001E-2</v>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="19">
         <v>1.2395118199999999E-2</v>
       </c>
-      <c r="H14" s="26">
+      <c r="H14" s="19">
         <v>0.38062547670000002</v>
       </c>
-      <c r="I14" s="26">
+      <c r="I14" s="19">
         <v>0.57288055419999995</v>
       </c>
-      <c r="J14" s="26">
+      <c r="J14" s="19">
         <v>0.49366858590000001</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A15" s="18"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="23" t="s">
+      <c r="A15" s="51"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="26">
+      <c r="F15" s="19">
         <v>6.2929062000000001E-3</v>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="19">
         <v>8.7719298999999994E-3</v>
       </c>
-      <c r="H15" s="26">
+      <c r="H15" s="19">
         <v>0.26620900079999998</v>
       </c>
-      <c r="I15" s="26">
+      <c r="I15" s="19">
         <v>0.49963703459999997</v>
       </c>
-      <c r="J15" s="26">
+      <c r="J15" s="19">
         <v>0.46533840399999998</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A16" s="18"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="17"/>
+      <c r="A16" s="51"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="53"/>
       <c r="D16" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="20">
         <v>0</v>
       </c>
-      <c r="G16" s="27">
+      <c r="G16" s="20">
         <v>1.1441648000000001E-3</v>
       </c>
-      <c r="H16" s="27">
+      <c r="H16" s="20">
         <v>0.82646834479999998</v>
       </c>
-      <c r="I16" s="27">
+      <c r="I16" s="20">
         <v>0.73931582289999997</v>
       </c>
-      <c r="J16" s="27">
+      <c r="J16" s="20">
         <v>0.86156660770000004</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
-      <c r="B17" s="19"/>
+      <c r="B17" s="54"/>
       <c r="C17" s="7"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="24"/>
+      <c r="E17" s="4"/>
       <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="H17" s="6"/>
@@ -2374,93 +2743,92 @@
       <c r="J17" s="6"/>
     </row>
     <row r="18" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="16" t="s">
+      <c r="B18" s="54"/>
+      <c r="C18" s="52" t="s">
         <v>33</v>
       </c>
-      <c r="D18" s="23" t="s">
+      <c r="D18" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F18" s="26">
+      <c r="F18" s="19">
         <v>1.8115941999999999E-2</v>
       </c>
-      <c r="G18" s="26">
+      <c r="G18" s="19">
         <v>3.2418002E-3</v>
       </c>
-      <c r="H18" s="26">
+      <c r="H18" s="19">
         <v>0.47673531660000001</v>
       </c>
-      <c r="I18" s="26">
+      <c r="I18" s="19">
         <v>0.90828805290000003</v>
       </c>
-      <c r="J18" s="26">
+      <c r="J18" s="19">
         <v>0.38241380689999999</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A19" s="18"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="23" t="s">
+      <c r="A19" s="51"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="19">
         <v>1.4683447699999999E-2</v>
       </c>
-      <c r="G19" s="26">
+      <c r="G19" s="19">
         <v>1.6781083200000001E-2</v>
       </c>
-      <c r="H19" s="26">
+      <c r="H19" s="19">
         <v>0.33028222730000001</v>
       </c>
-      <c r="I19" s="26">
+      <c r="I19" s="19">
         <v>0.6932949316</v>
       </c>
-      <c r="J19" s="26">
+      <c r="J19" s="19">
         <v>0.46851075240000001</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A20" s="18"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="17"/>
+      <c r="A20" s="51"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="53"/>
       <c r="D20" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F20" s="27">
+      <c r="F20" s="20">
         <v>5.7208240000000004E-4</v>
       </c>
-      <c r="G20" s="27">
+      <c r="G20" s="20">
         <v>1.9069412E-3</v>
       </c>
-      <c r="H20" s="27">
+      <c r="H20" s="20">
         <v>1</v>
       </c>
-      <c r="I20" s="27">
+      <c r="I20" s="20">
         <v>0.48074983929999998</v>
       </c>
-      <c r="J20" s="27">
+      <c r="J20" s="20">
         <v>0.47820880100000002</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
-      <c r="B21" s="19"/>
+      <c r="B21" s="54"/>
       <c r="C21" s="7"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="24"/>
+      <c r="E21" s="4"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
@@ -2468,93 +2836,92 @@
       <c r="J21" s="6"/>
     </row>
     <row r="22" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="19"/>
-      <c r="C22" s="16" t="s">
+      <c r="B22" s="54"/>
+      <c r="C22" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="D22" s="23" t="s">
+      <c r="D22" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E22" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="19">
         <v>6.1022120499999999E-2</v>
       </c>
-      <c r="G22" s="26">
+      <c r="G22" s="19">
         <v>1.9641494999999998E-2</v>
       </c>
-      <c r="H22" s="26">
+      <c r="H22" s="19">
         <v>0.50457665900000004</v>
       </c>
-      <c r="I22" s="26">
+      <c r="I22" s="19">
         <v>0.79997379280000003</v>
       </c>
-      <c r="J22" s="26">
+      <c r="J22" s="19">
         <v>0.4494335834</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A23" s="18"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="23" t="s">
+      <c r="A23" s="51"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="53"/>
+      <c r="D23" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E23" s="24" t="s">
+      <c r="E23" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F23" s="26">
+      <c r="F23" s="19">
         <v>1.1441648000000001E-3</v>
       </c>
-      <c r="G23" s="26">
+      <c r="G23" s="19">
         <v>4.3859648999999999E-3</v>
       </c>
-      <c r="H23" s="26">
+      <c r="H23" s="19">
         <v>0.29824561399999999</v>
       </c>
-      <c r="I23" s="26">
+      <c r="I23" s="19">
         <v>0.50951249160000001</v>
       </c>
-      <c r="J23" s="26">
+      <c r="J23" s="19">
         <v>0.48493636159999998</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A24" s="18"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="23" t="s">
+      <c r="A24" s="51"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F24" s="26">
+      <c r="F24" s="19">
         <v>0</v>
       </c>
-      <c r="G24" s="26">
+      <c r="G24" s="19">
         <v>3.4324943E-3</v>
       </c>
-      <c r="H24" s="26">
+      <c r="H24" s="19">
         <v>0.1468344775</v>
       </c>
-      <c r="I24" s="26">
+      <c r="I24" s="19">
         <v>0.48289788459999999</v>
       </c>
-      <c r="J24" s="26">
+      <c r="J24" s="19">
         <v>0.47928901419999997</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="4"/>
-      <c r="B25" s="19"/>
+      <c r="B25" s="54"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="24"/>
+      <c r="E25" s="4"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
@@ -2562,11 +2929,11 @@
       <c r="J25" s="6"/>
     </row>
     <row r="26" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="51" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="16" t="s">
+      <c r="B26" s="54"/>
+      <c r="C26" s="52" t="s">
         <v>35</v>
       </c>
       <c r="D26" s="8" t="s">
@@ -2575,80 +2942,79 @@
       <c r="E26" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="F26" s="27">
+      <c r="F26" s="20">
         <v>0.1186117468</v>
       </c>
-      <c r="G26" s="27">
+      <c r="G26" s="20">
         <v>6.1022120000000001E-3</v>
       </c>
-      <c r="H26" s="27">
+      <c r="H26" s="20">
         <v>0.41075514870000002</v>
       </c>
-      <c r="I26" s="27">
+      <c r="I26" s="20">
         <v>0.76521998459999996</v>
       </c>
-      <c r="J26" s="27">
+      <c r="J26" s="20">
         <v>0.42785365250000001</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A27" s="18"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="23" t="s">
+      <c r="A27" s="51"/>
+      <c r="B27" s="54"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E27" s="24" t="s">
+      <c r="E27" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F27" s="26">
+      <c r="F27" s="19">
         <v>5.7208240000000004E-4</v>
       </c>
-      <c r="G27" s="26">
+      <c r="G27" s="19">
         <v>2.0976354000000002E-3</v>
       </c>
-      <c r="H27" s="26">
+      <c r="H27" s="19">
         <v>0.26430205950000002</v>
       </c>
-      <c r="I27" s="26">
+      <c r="I27" s="19">
         <v>0.4885343251</v>
       </c>
-      <c r="J27" s="26">
+      <c r="J27" s="19">
         <v>0.47971979549999999</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A28" s="18"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="17"/>
+      <c r="A28" s="51"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="53"/>
       <c r="D28" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F28" s="27">
+      <c r="F28" s="20">
         <v>0</v>
       </c>
-      <c r="G28" s="27">
+      <c r="G28" s="20">
         <v>2.8604119000000001E-3</v>
       </c>
-      <c r="H28" s="27">
+      <c r="H28" s="20">
         <v>1</v>
       </c>
-      <c r="I28" s="27">
+      <c r="I28" s="20">
         <v>0.481477506</v>
       </c>
-      <c r="J28" s="27">
+      <c r="J28" s="20">
         <v>0.48250741460000002</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
-      <c r="B29" s="19"/>
+      <c r="B29" s="54"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="24"/>
+      <c r="E29" s="4"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="6"/>
@@ -2656,84 +3022,84 @@
       <c r="J29" s="6"/>
     </row>
     <row r="30" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="16" t="s">
+      <c r="B30" s="54"/>
+      <c r="C30" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="23" t="s">
+      <c r="D30" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E30" s="24" t="s">
+      <c r="E30" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F30" s="26">
+      <c r="F30" s="19">
         <v>8.6956521699999997E-2</v>
       </c>
-      <c r="G30" s="26">
+      <c r="G30" s="19">
         <v>5.4919908400000002E-2</v>
       </c>
-      <c r="H30" s="26">
+      <c r="H30" s="19">
         <v>0.55034324940000001</v>
       </c>
-      <c r="I30" s="26">
+      <c r="I30" s="19">
         <v>0.88981843729999999</v>
       </c>
-      <c r="J30" s="26">
+      <c r="J30" s="19">
         <v>0.41754147930000002</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A31" s="18"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="23" t="s">
+      <c r="A31" s="51"/>
+      <c r="B31" s="54"/>
+      <c r="C31" s="53"/>
+      <c r="D31" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E31" s="24" t="s">
+      <c r="E31" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F31" s="26">
+      <c r="F31" s="19">
         <v>1.1441648000000001E-3</v>
       </c>
-      <c r="G31" s="26">
+      <c r="G31" s="19">
         <v>4.9771166999999998E-2</v>
       </c>
-      <c r="H31" s="26">
+      <c r="H31" s="19">
         <v>0.18039664380000001</v>
       </c>
-      <c r="I31" s="26">
+      <c r="I31" s="19">
         <v>0.61880202399999995</v>
       </c>
-      <c r="J31" s="26">
+      <c r="J31" s="19">
         <v>0.44863267369999998</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A32" s="18"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="23" t="s">
+      <c r="A32" s="51"/>
+      <c r="B32" s="54"/>
+      <c r="C32" s="53"/>
+      <c r="D32" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E32" s="24" t="s">
+      <c r="E32" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F32" s="26">
+      <c r="F32" s="19">
         <v>5.7208240000000004E-4</v>
       </c>
-      <c r="G32" s="26">
+      <c r="G32" s="19">
         <v>4.3859648999999999E-3</v>
       </c>
-      <c r="H32" s="26">
+      <c r="H32" s="19">
         <v>0.28985507249999998</v>
       </c>
-      <c r="I32" s="26">
+      <c r="I32" s="19">
         <v>0.48726395379999998</v>
       </c>
-      <c r="J32" s="26">
+      <c r="J32" s="19">
         <v>0.48167254500000001</v>
       </c>
     </row>
@@ -2741,8 +3107,7 @@
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="24"/>
+      <c r="E33" s="4"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
       <c r="H33" s="6"/>
@@ -2750,95 +3115,94 @@
       <c r="J33" s="6"/>
     </row>
     <row r="34" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="18" t="s">
+      <c r="B34" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="D34" s="23" t="s">
+      <c r="D34" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E34" s="24" t="s">
+      <c r="E34" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F34" s="26">
+      <c r="F34" s="19">
         <v>6.2690548799999996E-2</v>
       </c>
-      <c r="G34" s="26">
+      <c r="G34" s="19">
         <v>3.6204268999999998E-3</v>
       </c>
-      <c r="H34" s="26">
+      <c r="H34" s="19">
         <v>0.42263719509999997</v>
       </c>
-      <c r="I34" s="26">
+      <c r="I34" s="19">
         <v>0.58112046120000005</v>
       </c>
-      <c r="J34" s="26">
+      <c r="J34" s="19">
         <v>0.51529468329999994</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A35" s="18"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="23" t="s">
+      <c r="A35" s="51"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="53"/>
+      <c r="D35" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E35" s="24" t="s">
+      <c r="E35" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F35" s="26">
+      <c r="F35" s="19">
         <v>7.8125E-3</v>
       </c>
-      <c r="G35" s="26">
+      <c r="G35" s="19">
         <v>4.1920730999999998E-3</v>
       </c>
-      <c r="H35" s="26">
+      <c r="H35" s="19">
         <v>0.331554878</v>
       </c>
-      <c r="I35" s="26">
+      <c r="I35" s="19">
         <v>0.50855967150000003</v>
       </c>
-      <c r="J35" s="26">
+      <c r="J35" s="19">
         <v>0.49168733549999999</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A36" s="18"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="23" t="s">
+      <c r="A36" s="51"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="53"/>
+      <c r="D36" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E36" s="24" t="s">
+      <c r="E36" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F36" s="26">
+      <c r="F36" s="19">
         <v>3.4298780500000001E-2</v>
       </c>
-      <c r="G36" s="26">
+      <c r="G36" s="19">
         <v>7.6219510000000005E-4</v>
       </c>
-      <c r="H36" s="26">
+      <c r="H36" s="19">
         <v>0.34184451220000001</v>
       </c>
-      <c r="I36" s="26">
+      <c r="I36" s="19">
         <v>0.24379135830000001</v>
       </c>
-      <c r="J36" s="26">
+      <c r="J36" s="19">
         <v>0.4980104071</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
-      <c r="B37" s="18"/>
+      <c r="B37" s="51"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="24"/>
+      <c r="E37" s="4"/>
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
@@ -2846,93 +3210,92 @@
       <c r="J37" s="6"/>
     </row>
     <row r="38" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A38" s="18" t="s">
+      <c r="A38" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="B38" s="18"/>
-      <c r="C38" s="16" t="s">
+      <c r="B38" s="51"/>
+      <c r="C38" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="D38" s="23" t="s">
+      <c r="D38" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E38" s="24" t="s">
+      <c r="E38" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F38" s="26">
+      <c r="F38" s="19">
         <v>7.3742377999999997E-2</v>
       </c>
-      <c r="G38" s="26">
+      <c r="G38" s="19">
         <v>1.77210366E-2</v>
       </c>
-      <c r="H38" s="26">
+      <c r="H38" s="19">
         <v>0.33727134149999999</v>
       </c>
-      <c r="I38" s="26">
+      <c r="I38" s="19">
         <v>0.84133180860000001</v>
       </c>
-      <c r="J38" s="26">
+      <c r="J38" s="19">
         <v>0.421498506</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A39" s="18"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="23" t="s">
+      <c r="A39" s="51"/>
+      <c r="B39" s="51"/>
+      <c r="C39" s="53"/>
+      <c r="D39" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E39" s="24" t="s">
+      <c r="E39" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F39" s="26">
+      <c r="F39" s="19">
         <v>3.6013719499999999E-2</v>
       </c>
-      <c r="G39" s="26">
+      <c r="G39" s="19">
         <v>2.2675304899999998E-2</v>
       </c>
-      <c r="H39" s="26">
+      <c r="H39" s="19">
         <v>0.34603658539999999</v>
       </c>
-      <c r="I39" s="26">
+      <c r="I39" s="19">
         <v>0.78530530659999997</v>
       </c>
-      <c r="J39" s="26">
+      <c r="J39" s="19">
         <v>0.43452962410000001</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A40" s="18"/>
-      <c r="B40" s="18"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="23" t="s">
+      <c r="A40" s="51"/>
+      <c r="B40" s="51"/>
+      <c r="C40" s="53"/>
+      <c r="D40" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E40" s="24" t="s">
+      <c r="E40" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F40" s="26">
+      <c r="F40" s="19">
         <v>0</v>
       </c>
-      <c r="G40" s="26">
+      <c r="G40" s="19">
         <v>1.9054878E-3</v>
       </c>
-      <c r="H40" s="26">
+      <c r="H40" s="19">
         <v>0.64900914629999995</v>
       </c>
-      <c r="I40" s="26">
+      <c r="I40" s="19">
         <v>0.41518582999999998</v>
       </c>
-      <c r="J40" s="26">
+      <c r="J40" s="19">
         <v>0.4477787178</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
-      <c r="B41" s="18"/>
+      <c r="B41" s="51"/>
       <c r="C41" s="7"/>
-      <c r="D41" s="23"/>
-      <c r="E41" s="24"/>
+      <c r="E41" s="4"/>
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
@@ -2940,93 +3303,92 @@
       <c r="J41" s="6"/>
     </row>
     <row r="42" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A42" s="18" t="s">
+      <c r="A42" s="51" t="s">
         <v>48</v>
       </c>
-      <c r="B42" s="18"/>
-      <c r="C42" s="16" t="s">
+      <c r="B42" s="51"/>
+      <c r="C42" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="D42" s="23" t="s">
+      <c r="D42" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E42" s="24" t="s">
+      <c r="E42" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F42" s="26">
+      <c r="F42" s="19">
         <v>5.6402438999999999E-2</v>
       </c>
-      <c r="G42" s="26">
+      <c r="G42" s="19">
         <v>1.3910061E-2</v>
       </c>
-      <c r="H42" s="26">
+      <c r="H42" s="19">
         <v>0.25647865850000001</v>
       </c>
-      <c r="I42" s="26">
+      <c r="I42" s="19">
         <v>0.78706769850000002</v>
       </c>
-      <c r="J42" s="26">
+      <c r="J42" s="19">
         <v>0.42004035560000003</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A43" s="18"/>
-      <c r="B43" s="18"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="23" t="s">
+      <c r="A43" s="51"/>
+      <c r="B43" s="51"/>
+      <c r="C43" s="53"/>
+      <c r="D43" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E43" s="24" t="s">
+      <c r="E43" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="26">
+      <c r="F43" s="19">
         <v>5.7164629999999998E-4</v>
       </c>
-      <c r="G43" s="26">
+      <c r="G43" s="19">
         <v>5.3353658000000002E-3</v>
       </c>
-      <c r="H43" s="26">
+      <c r="H43" s="19">
         <v>0.26981707319999998</v>
       </c>
-      <c r="I43" s="26">
+      <c r="I43" s="19">
         <v>0.48663375619999999</v>
       </c>
-      <c r="J43" s="26">
+      <c r="J43" s="19">
         <v>0.48601019839999998</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A44" s="18"/>
-      <c r="B44" s="18"/>
-      <c r="C44" s="17"/>
-      <c r="D44" s="23" t="s">
+      <c r="A44" s="51"/>
+      <c r="B44" s="51"/>
+      <c r="C44" s="53"/>
+      <c r="D44" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E44" s="24" t="s">
+      <c r="E44" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="26">
+      <c r="F44" s="19">
         <v>0</v>
       </c>
-      <c r="G44" s="26">
+      <c r="G44" s="19">
         <v>1.3338415000000001E-3</v>
       </c>
-      <c r="H44" s="26">
+      <c r="H44" s="19">
         <v>0.1211890244</v>
       </c>
-      <c r="I44" s="26">
+      <c r="I44" s="19">
         <v>0.26047697260000002</v>
       </c>
-      <c r="J44" s="26">
+      <c r="J44" s="19">
         <v>0.1173744025</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
-      <c r="B45" s="18"/>
+      <c r="B45" s="51"/>
       <c r="C45" s="7"/>
-      <c r="D45" s="23"/>
-      <c r="E45" s="24"/>
+      <c r="E45" s="4"/>
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
@@ -3034,11 +3396,11 @@
       <c r="J45" s="6"/>
     </row>
     <row r="46" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A46" s="18" t="s">
+      <c r="A46" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="18"/>
-      <c r="C46" s="16" t="s">
+      <c r="B46" s="51"/>
+      <c r="C46" s="52" t="s">
         <v>35</v>
       </c>
       <c r="D46" s="8" t="s">
@@ -3047,71 +3409,71 @@
       <c r="E46" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="F46" s="27">
+      <c r="F46" s="20">
         <v>6.6882622000000003E-2</v>
       </c>
-      <c r="G46" s="27">
+      <c r="G46" s="20">
         <v>4.1730182900000003E-2</v>
       </c>
-      <c r="H46" s="27">
+      <c r="H46" s="20">
         <v>0.3525152439</v>
       </c>
-      <c r="I46" s="27">
+      <c r="I46" s="20">
         <v>0.91800077579999995</v>
       </c>
-      <c r="J46" s="27">
+      <c r="J46" s="20">
         <v>0.3527158145</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A47" s="18"/>
-      <c r="B47" s="18"/>
-      <c r="C47" s="17"/>
+      <c r="A47" s="51"/>
+      <c r="B47" s="51"/>
+      <c r="C47" s="53"/>
       <c r="D47" s="8" t="s">
         <v>24</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="27">
+      <c r="F47" s="20">
         <v>6.0213414600000001E-2</v>
       </c>
-      <c r="G47" s="27">
+      <c r="G47" s="20">
         <v>0.14100609750000001</v>
       </c>
-      <c r="H47" s="27">
+      <c r="H47" s="20">
         <v>0.51181402440000001</v>
       </c>
-      <c r="I47" s="27">
+      <c r="I47" s="20">
         <v>0.85295546509999998</v>
       </c>
-      <c r="J47" s="27">
+      <c r="J47" s="20">
         <v>0.40423080890000002</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A48" s="18"/>
-      <c r="B48" s="18"/>
-      <c r="C48" s="17"/>
+      <c r="A48" s="51"/>
+      <c r="B48" s="51"/>
+      <c r="C48" s="53"/>
       <c r="D48" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F48" s="26">
+      <c r="F48" s="19">
         <v>0</v>
       </c>
-      <c r="G48" s="26">
+      <c r="G48" s="19">
         <v>3.4298779999999999E-3</v>
       </c>
-      <c r="H48" s="26">
+      <c r="H48" s="19">
         <v>1</v>
       </c>
-      <c r="I48" s="26">
+      <c r="I48" s="19">
         <v>0.47132286420000002</v>
       </c>
-      <c r="J48" s="26">
+      <c r="J48" s="19">
         <v>0.47686803360000002</v>
       </c>
     </row>
@@ -3170,8 +3532,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="C30:C32"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B32"/>
     <mergeCell ref="C2:C4"/>
@@ -3187,6 +3547,8 @@
     <mergeCell ref="C22:C24"/>
     <mergeCell ref="A26:A28"/>
     <mergeCell ref="C26:C28"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="C30:C32"/>
     <mergeCell ref="A34:A36"/>
     <mergeCell ref="B34:B48"/>
     <mergeCell ref="C34:C36"/>
@@ -3203,62 +3565,74 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBA0BED1-E6AE-6440-9DA8-C62C40C218E4}">
-  <dimension ref="A1:K52"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="44.83203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.83203125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="50.1640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.6640625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="17.6640625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="32.83203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="30.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="36.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="39" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="42.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.83203125" style="5"/>
+    <col min="1" max="1" width="37.83203125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="22.1640625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="36.5" style="5" customWidth="1"/>
+    <col min="4" max="4" width="21.83203125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="15" style="5" customWidth="1"/>
+    <col min="6" max="6" width="18.5" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.83203125" style="12" customWidth="1"/>
+    <col min="9" max="9" width="20.1640625" style="12" customWidth="1"/>
+    <col min="10" max="10" width="24.33203125" style="12" customWidth="1"/>
+    <col min="11" max="11" width="14.5" style="12" customWidth="1"/>
+    <col min="12" max="12" width="17.6640625" style="12" customWidth="1"/>
+    <col min="13" max="13" width="17" style="12" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="22" customFormat="1" ht="89" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:13" s="18" customFormat="1" ht="111" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="J1" s="17" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A2" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="19" t="s">
+      <c r="K1" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="L1" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="M1" s="39" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A2" s="51" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="52" t="s">
         <v>29</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -3267,47 +3641,113 @@
       <c r="E2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-    </row>
-    <row r="3" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A3" s="18"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="17"/>
+      <c r="F2" s="12">
+        <v>3.8901601799999998E-2</v>
+      </c>
+      <c r="G2" s="12">
+        <v>6.1022120000000001E-3</v>
+      </c>
+      <c r="H2" s="12">
+        <v>0.63958810070000005</v>
+      </c>
+      <c r="I2" s="12">
+        <v>0.6580912753</v>
+      </c>
+      <c r="J2" s="12">
+        <v>0.68471369510000002</v>
+      </c>
+      <c r="K2" s="12">
+        <f>F2*1/5 +G2*1/5+H2*1/5+I2*1/5+J2*1/5</f>
+        <v>0.40547937698000003</v>
+      </c>
+      <c r="L2" s="12">
+        <f>H2*1/2+J2*1/2</f>
+        <v>0.66215089790000004</v>
+      </c>
+      <c r="M2" s="12">
+        <f>F2*1/3+G2*1/3+I2*1/3</f>
+        <v>0.2343650297</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A3" s="51"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="53"/>
       <c r="D3" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-    </row>
-    <row r="4" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="18"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="17"/>
+      <c r="F3" s="12">
+        <v>1.75438596E-2</v>
+      </c>
+      <c r="G3" s="12">
+        <v>3.6231884E-3</v>
+      </c>
+      <c r="H3" s="12">
+        <v>0.26926010680000001</v>
+      </c>
+      <c r="I3" s="12">
+        <v>0.50990095319999995</v>
+      </c>
+      <c r="J3" s="12">
+        <v>0.49317243570000002</v>
+      </c>
+      <c r="K3" s="12">
+        <f t="shared" ref="K3:K48" si="0">F3*1/5 +G3*1/5+H3*1/5+I3*1/5+J3*1/5</f>
+        <v>0.25870010873999999</v>
+      </c>
+      <c r="L3" s="12">
+        <f>H3*1/2+J3*1/2</f>
+        <v>0.38121627125000002</v>
+      </c>
+      <c r="M3" s="12">
+        <f t="shared" ref="M3:M4" si="1">F3*1/3+G3*1/3+I3*1/3</f>
+        <v>0.17702266706666667</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A4" s="51"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="53"/>
       <c r="D4" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="F4" s="12">
+        <v>3.8138830000000002E-4</v>
+      </c>
+      <c r="G4" s="12">
+        <v>2.6697177000000001E-3</v>
+      </c>
+      <c r="H4" s="12">
+        <v>0.79366895500000001</v>
+      </c>
+      <c r="I4" s="12">
+        <v>0.57090215860000004</v>
+      </c>
+      <c r="J4" s="12">
+        <v>0.58510193919999998</v>
+      </c>
+      <c r="K4" s="12">
+        <f t="shared" si="0"/>
+        <v>0.39054483175999999</v>
+      </c>
+      <c r="L4" s="12">
+        <f>H4*1/2+J4*1/2</f>
+        <v>0.68938544710000005</v>
+      </c>
+      <c r="M4" s="12">
+        <f t="shared" si="1"/>
+        <v>0.19131775486666669</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
-      <c r="B5" s="19"/>
+      <c r="B5" s="54"/>
       <c r="C5" s="7"/>
       <c r="E5" s="4"/>
       <c r="F5" s="6"/>
@@ -3316,12 +3756,12 @@
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
     </row>
-    <row r="6" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="16" t="s">
+    <row r="6" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A6" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="B6" s="54"/>
+      <c r="C6" s="52" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="5" t="s">
@@ -3330,47 +3770,113 @@
       <c r="E6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-    </row>
-    <row r="7" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="18"/>
-      <c r="B7" s="19"/>
-      <c r="C7" s="17"/>
+      <c r="F6" s="12">
+        <v>3.56598017E-2</v>
+      </c>
+      <c r="G6" s="12">
+        <v>1.14416476E-2</v>
+      </c>
+      <c r="H6" s="12">
+        <v>0.65484363079999997</v>
+      </c>
+      <c r="I6" s="12">
+        <v>0.75059192720000001</v>
+      </c>
+      <c r="J6" s="12">
+        <v>0.59952031800000005</v>
+      </c>
+      <c r="K6" s="12">
+        <f t="shared" si="0"/>
+        <v>0.41041146505999998</v>
+      </c>
+      <c r="L6" s="12">
+        <f t="shared" ref="L6:L8" si="2">H6*1/2+J6*1/2</f>
+        <v>0.62718197440000001</v>
+      </c>
+      <c r="M6" s="12">
+        <f>F6*1/3+G6*1/3+I6*1/3</f>
+        <v>0.26589779216666665</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A7" s="51"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="53"/>
       <c r="D7" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-    </row>
-    <row r="8" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A8" s="18"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="5" t="s">
+      <c r="F7" s="12">
+        <v>0</v>
+      </c>
+      <c r="G7" s="12">
+        <v>2.6697178000000001E-3</v>
+      </c>
+      <c r="H7" s="12">
+        <v>0.31807780320000001</v>
+      </c>
+      <c r="I7" s="12">
+        <v>0.49853525259999998</v>
+      </c>
+      <c r="J7" s="12">
+        <v>0.49760901740000002</v>
+      </c>
+      <c r="K7" s="12">
+        <f t="shared" si="0"/>
+        <v>0.2633783582</v>
+      </c>
+      <c r="L7" s="12">
+        <f t="shared" si="2"/>
+        <v>0.40784341030000004</v>
+      </c>
+      <c r="M7" s="12">
+        <f t="shared" ref="M7:M8" si="3">F7*1/3+G7*1/3+I7*1/3</f>
+        <v>0.16706832346666664</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A8" s="51"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="F8" s="11">
+        <v>0</v>
+      </c>
+      <c r="G8" s="11">
+        <v>5.3394356000000002E-3</v>
+      </c>
+      <c r="H8" s="11">
+        <v>0.96948893970000005</v>
+      </c>
+      <c r="I8" s="11">
+        <v>0.54854145649999997</v>
+      </c>
+      <c r="J8" s="11">
+        <v>0.61895662200000001</v>
+      </c>
+      <c r="K8" s="12">
+        <f t="shared" si="0"/>
+        <v>0.42846529076000001</v>
+      </c>
+      <c r="L8" s="12">
+        <f t="shared" si="2"/>
+        <v>0.79422278084999998</v>
+      </c>
+      <c r="M8" s="12">
+        <f t="shared" si="3"/>
+        <v>0.18462696403333334</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
-      <c r="B9" s="19"/>
+      <c r="B9" s="54"/>
       <c r="C9" s="7"/>
       <c r="E9" s="4"/>
       <c r="F9" s="6"/>
@@ -3379,12 +3885,12 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="16" t="s">
+    <row r="10" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A10" s="51" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="54"/>
+      <c r="C10" s="52" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="5" t="s">
@@ -3393,47 +3899,113 @@
       <c r="E10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-    </row>
-    <row r="11" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="18"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="17"/>
+      <c r="F10" s="12">
+        <v>1.3539282999999999E-2</v>
+      </c>
+      <c r="G10" s="12">
+        <v>7.437071E-3</v>
+      </c>
+      <c r="H10" s="12">
+        <v>0.68192219679999999</v>
+      </c>
+      <c r="I10" s="12">
+        <v>0.76195930150000002</v>
+      </c>
+      <c r="J10" s="12">
+        <v>0.65195960269999997</v>
+      </c>
+      <c r="K10" s="12">
+        <f t="shared" si="0"/>
+        <v>0.42336349099999998</v>
+      </c>
+      <c r="L10" s="12">
+        <f t="shared" ref="L10:L12" si="4">H10*1/2+J10*1/2</f>
+        <v>0.66694089974999993</v>
+      </c>
+      <c r="M10" s="12">
+        <f>F10*1/3+G10*1/3+I10*1/3</f>
+        <v>0.26097855183333335</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A11" s="51"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="53"/>
       <c r="D11" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-    </row>
-    <row r="12" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="18"/>
-      <c r="B12" s="19"/>
-      <c r="C12" s="17"/>
+      <c r="F11" s="12">
+        <v>4.3859648999999999E-3</v>
+      </c>
+      <c r="G11" s="12">
+        <v>3.8138830000000002E-4</v>
+      </c>
+      <c r="H11" s="12">
+        <v>0.81388253239999997</v>
+      </c>
+      <c r="I11" s="12">
+        <v>0.62862944050000003</v>
+      </c>
+      <c r="J11" s="12">
+        <v>0.64003247760000004</v>
+      </c>
+      <c r="K11" s="12">
+        <f t="shared" si="0"/>
+        <v>0.41746236073999998</v>
+      </c>
+      <c r="L11" s="12">
+        <f t="shared" si="4"/>
+        <v>0.726957505</v>
+      </c>
+      <c r="M11" s="12">
+        <f t="shared" ref="M11:M12" si="5">F11*1/3+G11*1/3+I11*1/3</f>
+        <v>0.21113226456666667</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A12" s="51"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="53"/>
       <c r="D12" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="F12" s="12">
+        <v>0</v>
+      </c>
+      <c r="G12" s="12">
+        <v>2.2883295000000001E-3</v>
+      </c>
+      <c r="H12" s="12">
+        <v>2.93668955E-2</v>
+      </c>
+      <c r="I12" s="12">
+        <v>0.47452555019999998</v>
+      </c>
+      <c r="J12" s="12">
+        <v>0.47974364320000001</v>
+      </c>
+      <c r="K12" s="12">
+        <f t="shared" si="0"/>
+        <v>0.19718488368000001</v>
+      </c>
+      <c r="L12" s="12">
+        <f t="shared" si="4"/>
+        <v>0.25455526935</v>
+      </c>
+      <c r="M12" s="12">
+        <f t="shared" si="5"/>
+        <v>0.15893795990000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13" s="4"/>
-      <c r="B13" s="19"/>
+      <c r="B13" s="54"/>
       <c r="C13" s="7"/>
       <c r="E13" s="4"/>
       <c r="F13" s="6"/>
@@ -3442,12 +4014,12 @@
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A14" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="16" t="s">
+    <row r="14" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A14" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="54"/>
+      <c r="C14" s="52" t="s">
         <v>32</v>
       </c>
       <c r="D14" s="5" t="s">
@@ -3456,47 +4028,113 @@
       <c r="E14" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-    </row>
-    <row r="15" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A15" s="18"/>
-      <c r="B15" s="19"/>
-      <c r="C15" s="17"/>
+      <c r="F14" s="12">
+        <v>2.7841342500000001E-2</v>
+      </c>
+      <c r="G14" s="12">
+        <v>9.3440121999999997E-3</v>
+      </c>
+      <c r="H14" s="12">
+        <v>0.66628527839999996</v>
+      </c>
+      <c r="I14" s="12">
+        <v>0.68165094780000002</v>
+      </c>
+      <c r="J14" s="12">
+        <v>0.656536805</v>
+      </c>
+      <c r="K14" s="12">
+        <f t="shared" si="0"/>
+        <v>0.40833167718000002</v>
+      </c>
+      <c r="L14" s="12">
+        <f t="shared" ref="L14:L16" si="6">H14*1/2+J14*1/2</f>
+        <v>0.66141104169999998</v>
+      </c>
+      <c r="M14" s="12">
+        <f>F14*1/3+G14*1/3+I14*1/3</f>
+        <v>0.23961210083333334</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A15" s="51"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="53"/>
       <c r="D15" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-    </row>
-    <row r="16" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A16" s="18"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="17"/>
+      <c r="F15" s="12">
+        <v>1.9069409999999999E-4</v>
+      </c>
+      <c r="G15" s="12">
+        <v>2.4790237000000001E-3</v>
+      </c>
+      <c r="H15" s="12">
+        <v>0.26735316549999999</v>
+      </c>
+      <c r="I15" s="12">
+        <v>0.51288884690000003</v>
+      </c>
+      <c r="J15" s="12">
+        <v>0.4966505316</v>
+      </c>
+      <c r="K15" s="12">
+        <f t="shared" si="0"/>
+        <v>0.25591245235999999</v>
+      </c>
+      <c r="L15" s="12">
+        <f t="shared" si="6"/>
+        <v>0.38200184854999997</v>
+      </c>
+      <c r="M15" s="12">
+        <f t="shared" ref="M15:M16" si="7">F15*1/3+G15*1/3+I15*1/3</f>
+        <v>0.17185285489999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A16" s="51"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="53"/>
       <c r="D16" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="F16" s="12">
+        <v>3.8138830000000002E-4</v>
+      </c>
+      <c r="G16" s="12">
+        <v>3.2418001E-3</v>
+      </c>
+      <c r="H16" s="12">
+        <v>2.8604119000000001E-2</v>
+      </c>
+      <c r="I16" s="12">
+        <v>0.30229342920000002</v>
+      </c>
+      <c r="J16" s="12">
+        <v>0.19462933560000001</v>
+      </c>
+      <c r="K16" s="12">
+        <f t="shared" si="0"/>
+        <v>0.10583001444000001</v>
+      </c>
+      <c r="L16" s="12">
+        <f t="shared" si="6"/>
+        <v>0.11161672730000001</v>
+      </c>
+      <c r="M16" s="12">
+        <f t="shared" si="7"/>
+        <v>0.10197220586666668</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
-      <c r="B17" s="19"/>
+      <c r="B17" s="54"/>
       <c r="C17" s="7"/>
       <c r="E17" s="4"/>
       <c r="F17" s="6"/>
@@ -3505,12 +4143,12 @@
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
     </row>
-    <row r="18" spans="1:11" ht="20" x14ac:dyDescent="0.2">
-      <c r="A18" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="16" t="s">
+    <row r="18" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A18" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="54"/>
+      <c r="C18" s="52" t="s">
         <v>33</v>
       </c>
       <c r="D18" s="5" t="s">
@@ -3519,47 +4157,113 @@
       <c r="E18" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-    </row>
-    <row r="19" spans="1:11" ht="20" x14ac:dyDescent="0.2">
-      <c r="A19" s="18"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="17"/>
+      <c r="F18" s="12">
+        <v>1.5636918400000002E-2</v>
+      </c>
+      <c r="G18" s="12">
+        <v>6.2929062000000001E-3</v>
+      </c>
+      <c r="H18" s="12">
+        <v>0.77612509529999996</v>
+      </c>
+      <c r="I18" s="12">
+        <v>0.74139800369999997</v>
+      </c>
+      <c r="J18" s="12">
+        <v>0.74694543889999998</v>
+      </c>
+      <c r="K18" s="12">
+        <f t="shared" si="0"/>
+        <v>0.45727967249999996</v>
+      </c>
+      <c r="L18" s="12">
+        <f t="shared" ref="L18:L20" si="8">H18*1/2+J18*1/2</f>
+        <v>0.76153526709999997</v>
+      </c>
+      <c r="M18" s="12">
+        <f>F18*1/3+G18*1/3+I18*1/3</f>
+        <v>0.2544426094333333</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A19" s="51"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="53"/>
       <c r="D19" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-    </row>
-    <row r="20" spans="1:11" ht="20" x14ac:dyDescent="0.2">
-      <c r="A20" s="18"/>
-      <c r="B20" s="19"/>
-      <c r="C20" s="17"/>
+      <c r="F19" s="12">
+        <v>1.9069409999999999E-4</v>
+      </c>
+      <c r="G19" s="12">
+        <v>3.2418001E-3</v>
+      </c>
+      <c r="H19" s="12">
+        <v>0.29099923719999998</v>
+      </c>
+      <c r="I19" s="12">
+        <v>0.48040252360000002</v>
+      </c>
+      <c r="J19" s="12">
+        <v>0.47678633349999999</v>
+      </c>
+      <c r="K19" s="12">
+        <f t="shared" si="0"/>
+        <v>0.25032411769999996</v>
+      </c>
+      <c r="L19" s="12">
+        <f t="shared" si="8"/>
+        <v>0.38389278534999999</v>
+      </c>
+      <c r="M19" s="12">
+        <f t="shared" ref="M19:M20" si="9">F19*1/3+G19*1/3+I19*1/3</f>
+        <v>0.16127833926666668</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A20" s="51"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="53"/>
       <c r="D20" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="F20" s="12">
+        <v>3.8138830000000002E-4</v>
+      </c>
+      <c r="G20" s="12">
+        <v>4.1952708000000003E-3</v>
+      </c>
+      <c r="H20" s="12">
+        <v>2.7078565999999998E-2</v>
+      </c>
+      <c r="I20" s="12">
+        <v>0.40992652470000002</v>
+      </c>
+      <c r="J20" s="12">
+        <v>0.38954129339999999</v>
+      </c>
+      <c r="K20" s="12">
+        <f t="shared" si="0"/>
+        <v>0.16622460863999999</v>
+      </c>
+      <c r="L20" s="12">
+        <f t="shared" si="8"/>
+        <v>0.20830992970000001</v>
+      </c>
+      <c r="M20" s="12">
+        <f t="shared" si="9"/>
+        <v>0.13816772793333332</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
-      <c r="B21" s="19"/>
+      <c r="B21" s="54"/>
       <c r="C21" s="7"/>
       <c r="E21" s="4"/>
       <c r="F21" s="6"/>
@@ -3568,12 +4272,12 @@
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
     </row>
-    <row r="22" spans="1:11" ht="20" x14ac:dyDescent="0.2">
-      <c r="A22" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B22" s="19"/>
-      <c r="C22" s="16" t="s">
+    <row r="22" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A22" s="51" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" s="54"/>
+      <c r="C22" s="52" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="5" t="s">
@@ -3582,47 +4286,113 @@
       <c r="E22" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-    </row>
-    <row r="23" spans="1:11" ht="20" x14ac:dyDescent="0.2">
-      <c r="A23" s="18"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="17"/>
+      <c r="F22" s="12">
+        <v>1.8688024399999999E-2</v>
+      </c>
+      <c r="G22" s="12">
+        <v>1.6209000800000001E-2</v>
+      </c>
+      <c r="H22" s="12">
+        <v>0.64340198319999997</v>
+      </c>
+      <c r="I22" s="12">
+        <v>0.73541693649999995</v>
+      </c>
+      <c r="J22" s="12">
+        <v>0.57155276239999997</v>
+      </c>
+      <c r="K22" s="12">
+        <f t="shared" si="0"/>
+        <v>0.39705374145999994</v>
+      </c>
+      <c r="L22" s="12">
+        <f t="shared" ref="L22:L24" si="10">H22*1/2+J22*1/2</f>
+        <v>0.60747737280000003</v>
+      </c>
+      <c r="M22" s="12">
+        <f>F22*1/3+G22*1/3+I22*1/3</f>
+        <v>0.25677132056666668</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A23" s="51"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="53"/>
       <c r="D23" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F23" s="6"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-    </row>
-    <row r="24" spans="1:11" ht="20" x14ac:dyDescent="0.2">
-      <c r="A24" s="18"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="17"/>
+      <c r="F23" s="12">
+        <v>5.7208240000000004E-4</v>
+      </c>
+      <c r="G23" s="12">
+        <v>2.4790237000000001E-3</v>
+      </c>
+      <c r="H23" s="12">
+        <v>0.14492753620000001</v>
+      </c>
+      <c r="I23" s="12">
+        <v>0.36882205509999999</v>
+      </c>
+      <c r="J23" s="12">
+        <v>0.36333761959999999</v>
+      </c>
+      <c r="K23" s="12">
+        <f t="shared" si="0"/>
+        <v>0.17602766340000001</v>
+      </c>
+      <c r="L23" s="12">
+        <f t="shared" si="10"/>
+        <v>0.25413257789999999</v>
+      </c>
+      <c r="M23" s="12">
+        <f t="shared" ref="M23:M24" si="11">F23*1/3+G23*1/3+I23*1/3</f>
+        <v>0.1239577204</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A24" s="51"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="53"/>
       <c r="D24" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="F24" s="12">
+        <v>5.7208240000000004E-4</v>
+      </c>
+      <c r="G24" s="12">
+        <v>2.8604119000000001E-3</v>
+      </c>
+      <c r="H24" s="12">
+        <v>0.408085431</v>
+      </c>
+      <c r="I24" s="12">
+        <v>0.61558054129999995</v>
+      </c>
+      <c r="J24" s="12">
+        <v>0.64331702260000001</v>
+      </c>
+      <c r="K24" s="12">
+        <f t="shared" si="0"/>
+        <v>0.33408309784000001</v>
+      </c>
+      <c r="L24" s="12">
+        <f t="shared" si="10"/>
+        <v>0.52570122679999998</v>
+      </c>
+      <c r="M24" s="12">
+        <f t="shared" si="11"/>
+        <v>0.20633767853333332</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25" s="4"/>
-      <c r="B25" s="19"/>
+      <c r="B25" s="54"/>
       <c r="C25" s="7"/>
       <c r="E25" s="4"/>
       <c r="F25" s="6"/>
@@ -3631,254 +4401,469 @@
       <c r="I25" s="6"/>
       <c r="J25" s="6"/>
     </row>
-    <row r="26" spans="1:11" ht="20" x14ac:dyDescent="0.2">
-      <c r="A26" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="16" t="s">
+    <row r="26" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A26" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="54"/>
+      <c r="C26" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="D26" s="23" t="s">
+      <c r="D26" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E26" s="24" t="s">
+      <c r="E26" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F26" s="25"/>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="25"/>
-      <c r="J26" s="25"/>
-      <c r="K26" s="23"/>
-    </row>
-    <row r="27" spans="1:11" ht="20" x14ac:dyDescent="0.2">
-      <c r="A27" s="18"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="23" t="s">
+      <c r="F26" s="12">
+        <v>1.83066362E-2</v>
+      </c>
+      <c r="G26" s="12">
+        <v>9.1533181000000002E-3</v>
+      </c>
+      <c r="H26" s="12">
+        <v>0.74713958810000003</v>
+      </c>
+      <c r="I26" s="12">
+        <v>0.84097820459999995</v>
+      </c>
+      <c r="J26" s="12">
+        <v>0.65728491980000003</v>
+      </c>
+      <c r="K26" s="12">
+        <f t="shared" si="0"/>
+        <v>0.45457253335999998</v>
+      </c>
+      <c r="L26" s="12">
+        <f>H26*1/2+J26*1/2</f>
+        <v>0.70221225394999998</v>
+      </c>
+      <c r="M26" s="12">
+        <f>F26*1/3+G26*1/3+I26*1/3</f>
+        <v>0.28947938629999997</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A27" s="51"/>
+      <c r="B27" s="54"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E27" s="24" t="s">
+      <c r="E27" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="25"/>
-      <c r="J27" s="25"/>
-      <c r="K27" s="23"/>
-    </row>
-    <row r="28" spans="1:11" ht="20" x14ac:dyDescent="0.2">
-      <c r="A28" s="18"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="23" t="s">
+      <c r="F27" s="12">
+        <v>6.2929062000000001E-3</v>
+      </c>
+      <c r="G27" s="12">
+        <v>1.5064836E-2</v>
+      </c>
+      <c r="H27" s="12">
+        <v>0.65980167810000001</v>
+      </c>
+      <c r="I27" s="12">
+        <v>0.75336811260000003</v>
+      </c>
+      <c r="J27" s="12">
+        <v>0.59480806279999998</v>
+      </c>
+      <c r="K27" s="12">
+        <f t="shared" si="0"/>
+        <v>0.40586711914000001</v>
+      </c>
+      <c r="L27" s="12">
+        <f>H27*1/2+J27*1/2</f>
+        <v>0.62730487044999994</v>
+      </c>
+      <c r="M27" s="12">
+        <f t="shared" ref="M27:M28" si="12">F27*1/3+G27*1/3+I27*1/3</f>
+        <v>0.25824195159999996</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A28" s="51"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="53"/>
+      <c r="D28" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E28" s="24" t="s">
+      <c r="E28" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-      <c r="H28" s="25"/>
-      <c r="I28" s="25"/>
-      <c r="J28" s="25"/>
-      <c r="K28" s="23"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="F28" s="12">
+        <v>3.8138830000000002E-4</v>
+      </c>
+      <c r="G28" s="12">
+        <v>3.8138824999999999E-3</v>
+      </c>
+      <c r="H28" s="12">
+        <v>0.25896262399999997</v>
+      </c>
+      <c r="I28" s="12">
+        <v>0.58112698119999995</v>
+      </c>
+      <c r="J28" s="12">
+        <v>0.61473724439999999</v>
+      </c>
+      <c r="K28" s="12">
+        <f t="shared" si="0"/>
+        <v>0.29180442407999996</v>
+      </c>
+      <c r="L28" s="12">
+        <f>H28*1/2+J28*1/2</f>
+        <v>0.43684993419999996</v>
+      </c>
+      <c r="M28" s="12">
+        <f t="shared" si="12"/>
+        <v>0.19510741733333331</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
-      <c r="B29" s="19"/>
+      <c r="B29" s="54"/>
       <c r="C29" s="7"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="24"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-      <c r="H29" s="25"/>
-      <c r="I29" s="25"/>
-      <c r="J29" s="25"/>
-      <c r="K29" s="23"/>
-    </row>
-    <row r="30" spans="1:11" ht="20" x14ac:dyDescent="0.2">
-      <c r="A30" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="16" t="s">
+      <c r="E29" s="4"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+    </row>
+    <row r="30" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A30" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" s="54"/>
+      <c r="C30" s="52" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="23" t="s">
+      <c r="D30" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E30" s="24" t="s">
+      <c r="E30" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
-      <c r="H30" s="25"/>
-      <c r="I30" s="25"/>
-      <c r="J30" s="25"/>
-      <c r="K30" s="23"/>
-    </row>
-    <row r="31" spans="1:11" ht="20" x14ac:dyDescent="0.2">
-      <c r="A31" s="18"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="23" t="s">
+      <c r="F30" s="11">
+        <v>4.5385202100000001E-2</v>
+      </c>
+      <c r="G30" s="11">
+        <v>2.5171624699999999E-2</v>
+      </c>
+      <c r="H30" s="11">
+        <v>0.74942791760000005</v>
+      </c>
+      <c r="I30" s="11">
+        <v>0.85230850219999998</v>
+      </c>
+      <c r="J30" s="11">
+        <v>0.64946929639999995</v>
+      </c>
+      <c r="K30" s="12">
+        <f t="shared" si="0"/>
+        <v>0.46435250859999999</v>
+      </c>
+      <c r="L30" s="12">
+        <f t="shared" ref="L30:L48" si="13">H30*1/2+J30*1/2</f>
+        <v>0.699448607</v>
+      </c>
+      <c r="M30" s="12">
+        <f>F30*1/3+G30*1/3+I30*1/3</f>
+        <v>0.30762177633333332</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A31" s="51"/>
+      <c r="B31" s="54"/>
+      <c r="C31" s="53"/>
+      <c r="D31" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E31" s="24" t="s">
+      <c r="E31" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F31" s="25"/>
-      <c r="G31" s="25"/>
-      <c r="H31" s="25"/>
-      <c r="I31" s="25"/>
-      <c r="J31" s="25"/>
-      <c r="K31" s="23"/>
-    </row>
-    <row r="32" spans="1:11" ht="20" x14ac:dyDescent="0.2">
-      <c r="A32" s="18"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="23" t="s">
+      <c r="F31" s="12">
+        <v>9.5347059999999998E-4</v>
+      </c>
+      <c r="G31" s="12">
+        <v>4.5766590999999999E-3</v>
+      </c>
+      <c r="H31" s="12">
+        <v>0.15331807780000001</v>
+      </c>
+      <c r="I31" s="12">
+        <v>0.37985365679999999</v>
+      </c>
+      <c r="J31" s="12">
+        <v>0.36610513039999998</v>
+      </c>
+      <c r="K31" s="12">
+        <f t="shared" si="0"/>
+        <v>0.18096139894000002</v>
+      </c>
+      <c r="L31" s="12">
+        <f t="shared" si="13"/>
+        <v>0.25971160409999999</v>
+      </c>
+      <c r="M31" s="12">
+        <f t="shared" ref="M31:M32" si="14">F31*1/3+G31*1/3+I31*1/3</f>
+        <v>0.12846126216666667</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A32" s="51"/>
+      <c r="B32" s="54"/>
+      <c r="C32" s="53"/>
+      <c r="D32" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E32" s="24" t="s">
+      <c r="E32" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F32" s="25"/>
-      <c r="G32" s="25"/>
-      <c r="H32" s="25"/>
-      <c r="I32" s="25"/>
-      <c r="J32" s="25"/>
-      <c r="K32" s="23"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="12">
+        <f>F32*1/5 +G32*1/5+H32*1/5+I32*1/5+J32*1/5</f>
+        <v>0</v>
+      </c>
+      <c r="L32" s="12">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M32" s="12">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="25"/>
-      <c r="G33" s="25"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="25"/>
-      <c r="J33" s="25"/>
-      <c r="K33" s="23"/>
-    </row>
-    <row r="34" spans="1:11" ht="20" x14ac:dyDescent="0.2">
-      <c r="A34" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B34" s="18" t="s">
+      <c r="E33" s="4"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+    </row>
+    <row r="34" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A34" s="51" t="s">
+        <v>84</v>
+      </c>
+      <c r="B34" s="51" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="D34" s="23" t="s">
+      <c r="D34" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E34" s="24" t="s">
+      <c r="E34" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F34" s="25"/>
-      <c r="G34" s="25"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
-      <c r="J34" s="25"/>
-      <c r="K34" s="23"/>
-    </row>
-    <row r="35" spans="1:11" ht="20" x14ac:dyDescent="0.2">
-      <c r="A35" s="18"/>
-      <c r="B35" s="18"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="23" t="s">
+      <c r="F34" s="12">
+        <v>1.1814024399999999E-2</v>
+      </c>
+      <c r="G34" s="12">
+        <v>2.6676829000000001E-3</v>
+      </c>
+      <c r="H34" s="12">
+        <v>0.62461890239999995</v>
+      </c>
+      <c r="I34" s="12">
+        <v>0.61594775769999999</v>
+      </c>
+      <c r="J34" s="12">
+        <v>0.66839133620000002</v>
+      </c>
+      <c r="K34" s="12">
+        <f t="shared" si="0"/>
+        <v>0.38468794072000001</v>
+      </c>
+      <c r="L34" s="12">
+        <f t="shared" si="13"/>
+        <v>0.64650511929999999</v>
+      </c>
+      <c r="M34" s="12">
+        <f>F34*1/3+G34*1/3+I34*1/3</f>
+        <v>0.210143155</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A35" s="51"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="53"/>
+      <c r="D35" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E35" s="24" t="s">
+      <c r="E35" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F35" s="25"/>
-      <c r="G35" s="25"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="25"/>
-      <c r="J35" s="25"/>
-      <c r="K35" s="23"/>
-    </row>
-    <row r="36" spans="1:11" ht="20" x14ac:dyDescent="0.2">
-      <c r="A36" s="18"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="23" t="s">
+      <c r="F35" s="12">
+        <v>2.4009146299999999E-2</v>
+      </c>
+      <c r="G35" s="12">
+        <v>5.7164633999999999E-3</v>
+      </c>
+      <c r="H35" s="12">
+        <v>0.36547256099999997</v>
+      </c>
+      <c r="I35" s="12">
+        <v>0.49941951550000002</v>
+      </c>
+      <c r="J35" s="12">
+        <v>0.49771204279999998</v>
+      </c>
+      <c r="K35" s="12">
+        <f t="shared" si="0"/>
+        <v>0.27846594579999995</v>
+      </c>
+      <c r="L35" s="12">
+        <f t="shared" si="13"/>
+        <v>0.43159230189999997</v>
+      </c>
+      <c r="M35" s="12">
+        <f t="shared" ref="M35:M36" si="15">F35*1/3+G35*1/3+I35*1/3</f>
+        <v>0.1763817084</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A36" s="51"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="53"/>
+      <c r="D36" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E36" s="24" t="s">
+      <c r="E36" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F36" s="25"/>
-      <c r="G36" s="25"/>
-      <c r="H36" s="25"/>
-      <c r="I36" s="25"/>
-      <c r="J36" s="25"/>
-      <c r="K36" s="23"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="F36" s="12">
+        <v>0</v>
+      </c>
+      <c r="G36" s="12">
+        <v>1.06707317E-2</v>
+      </c>
+      <c r="H36" s="12">
+        <v>0.19740853659999999</v>
+      </c>
+      <c r="I36" s="12">
+        <v>0.44089801090000003</v>
+      </c>
+      <c r="J36" s="12">
+        <v>0.35974137750000001</v>
+      </c>
+      <c r="K36" s="12">
+        <f t="shared" si="0"/>
+        <v>0.20174373134000001</v>
+      </c>
+      <c r="L36" s="12">
+        <f t="shared" si="13"/>
+        <v>0.27857495705000002</v>
+      </c>
+      <c r="M36" s="12">
+        <f t="shared" si="15"/>
+        <v>0.1505229142</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
-      <c r="B37" s="18"/>
+      <c r="B37" s="51"/>
       <c r="C37" s="7"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="25"/>
-      <c r="G37" s="25"/>
-      <c r="H37" s="25"/>
-      <c r="I37" s="25"/>
-      <c r="J37" s="25"/>
-      <c r="K37" s="23"/>
-    </row>
-    <row r="38" spans="1:11" ht="20" x14ac:dyDescent="0.2">
-      <c r="A38" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="B38" s="18"/>
-      <c r="C38" s="16" t="s">
+      <c r="E37" s="4"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+    </row>
+    <row r="38" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A38" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" s="51"/>
+      <c r="C38" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="D38" s="23" t="s">
+      <c r="D38" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E38" s="24" t="s">
+      <c r="E38" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F38" s="25"/>
-      <c r="G38" s="25"/>
-      <c r="H38" s="25"/>
-      <c r="I38" s="25"/>
-      <c r="J38" s="25"/>
-      <c r="K38" s="23"/>
-    </row>
-    <row r="39" spans="1:11" ht="20" x14ac:dyDescent="0.2">
-      <c r="A39" s="18"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="23" t="s">
+      <c r="F38" s="12">
+        <v>5.7164629999999998E-4</v>
+      </c>
+      <c r="G38" s="12">
+        <v>3.8109756000000001E-3</v>
+      </c>
+      <c r="H38" s="12">
+        <v>0.60518292679999997</v>
+      </c>
+      <c r="I38" s="12">
+        <v>0.62701617990000003</v>
+      </c>
+      <c r="J38" s="12">
+        <v>0.68544860669999996</v>
+      </c>
+      <c r="K38" s="12">
+        <f t="shared" si="0"/>
+        <v>0.38440606706000002</v>
+      </c>
+      <c r="L38" s="12">
+        <f t="shared" si="13"/>
+        <v>0.64531576675000002</v>
+      </c>
+      <c r="M38" s="12">
+        <f>F38*1/3+G38*1/3+I38*1/3</f>
+        <v>0.21046626726666667</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A39" s="51"/>
+      <c r="B39" s="51"/>
+      <c r="C39" s="53"/>
+      <c r="D39" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E39" s="24" t="s">
+      <c r="E39" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="F39" s="25"/>
-      <c r="G39" s="25"/>
-      <c r="H39" s="25"/>
-      <c r="I39" s="25"/>
-      <c r="J39" s="25"/>
-      <c r="K39" s="23"/>
-    </row>
-    <row r="40" spans="1:11" ht="20" x14ac:dyDescent="0.2">
-      <c r="A40" s="18"/>
-      <c r="B40" s="18"/>
-      <c r="C40" s="17"/>
+      <c r="F39" s="11">
+        <v>4.9161585399999999E-2</v>
+      </c>
+      <c r="G39" s="11">
+        <v>1.2576219499999999E-2</v>
+      </c>
+      <c r="H39" s="11">
+        <v>0.71532012199999995</v>
+      </c>
+      <c r="I39" s="11">
+        <v>0.86194404820000003</v>
+      </c>
+      <c r="J39" s="11">
+        <v>0.73983099360000004</v>
+      </c>
+      <c r="K39" s="47">
+        <f t="shared" si="0"/>
+        <v>0.47576659374000002</v>
+      </c>
+      <c r="L39" s="12">
+        <f t="shared" si="13"/>
+        <v>0.72757555780000005</v>
+      </c>
+      <c r="M39" s="47">
+        <f t="shared" ref="M39:M40" si="16">F39*1/3+G39*1/3+I39*1/3</f>
+        <v>0.30789395103333334</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A40" s="51"/>
+      <c r="B40" s="51"/>
+      <c r="C40" s="53"/>
       <c r="D40" s="5" t="s">
         <v>25</v>
       </c>
@@ -3890,10 +4875,22 @@
       <c r="H40" s="6"/>
       <c r="I40" s="6"/>
       <c r="J40" s="6"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="K40" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L40" s="12">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M40" s="12">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
-      <c r="B41" s="18"/>
+      <c r="B41" s="51"/>
       <c r="C41" s="7"/>
       <c r="E41" s="4"/>
       <c r="F41" s="6"/>
@@ -3902,12 +4899,12 @@
       <c r="I41" s="6"/>
       <c r="J41" s="6"/>
     </row>
-    <row r="42" spans="1:11" ht="20" x14ac:dyDescent="0.2">
-      <c r="A42" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B42" s="18"/>
-      <c r="C42" s="16" t="s">
+    <row r="42" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A42" s="51" t="s">
+        <v>86</v>
+      </c>
+      <c r="B42" s="51"/>
+      <c r="C42" s="52" t="s">
         <v>31</v>
       </c>
       <c r="D42" s="5" t="s">
@@ -3916,47 +4913,113 @@
       <c r="E42" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
-      <c r="H42" s="6"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
-    </row>
-    <row r="43" spans="1:11" ht="20" x14ac:dyDescent="0.2">
-      <c r="A43" s="18"/>
-      <c r="B43" s="18"/>
-      <c r="C43" s="17"/>
+      <c r="F42" s="12">
+        <v>7.2408537E-3</v>
+      </c>
+      <c r="G42" s="12">
+        <v>9.3368902999999993E-3</v>
+      </c>
+      <c r="H42" s="12">
+        <v>0.72789634150000004</v>
+      </c>
+      <c r="I42" s="12">
+        <v>0.72569261240000005</v>
+      </c>
+      <c r="J42" s="12">
+        <v>0.68594619649999999</v>
+      </c>
+      <c r="K42" s="12">
+        <f t="shared" si="0"/>
+        <v>0.43122257887999998</v>
+      </c>
+      <c r="L42" s="12">
+        <f t="shared" si="13"/>
+        <v>0.70692126899999996</v>
+      </c>
+      <c r="M42" s="12">
+        <f>F42*1/3+G42*1/3+I42*1/3</f>
+        <v>0.24742345213333333</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A43" s="51"/>
+      <c r="B43" s="51"/>
+      <c r="C43" s="53"/>
       <c r="D43" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F43" s="6"/>
-      <c r="G43" s="6"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-    </row>
-    <row r="44" spans="1:11" ht="20" x14ac:dyDescent="0.2">
-      <c r="A44" s="18"/>
-      <c r="B44" s="18"/>
-      <c r="C44" s="17"/>
+      <c r="F43" s="12">
+        <v>7.6219510000000005E-4</v>
+      </c>
+      <c r="G43" s="12">
+        <v>4.3826220000000001E-3</v>
+      </c>
+      <c r="H43" s="12">
+        <v>0.25609756099999997</v>
+      </c>
+      <c r="I43" s="12">
+        <v>0.3903245058</v>
+      </c>
+      <c r="J43" s="12">
+        <v>0.35050324440000002</v>
+      </c>
+      <c r="K43" s="12">
+        <f t="shared" si="0"/>
+        <v>0.20041402565999999</v>
+      </c>
+      <c r="L43" s="12">
+        <f t="shared" si="13"/>
+        <v>0.30330040270000003</v>
+      </c>
+      <c r="M43" s="12">
+        <f t="shared" ref="M43:M44" si="17">F43*1/3+G43*1/3+I43*1/3</f>
+        <v>0.13182310763333333</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A44" s="51"/>
+      <c r="B44" s="51"/>
+      <c r="C44" s="53"/>
       <c r="D44" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F44" s="6"/>
-      <c r="G44" s="6"/>
-      <c r="H44" s="6"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="F44" s="12">
+        <v>5.7164629999999998E-4</v>
+      </c>
+      <c r="G44" s="12">
+        <v>2.0960366000000001E-3</v>
+      </c>
+      <c r="H44" s="12">
+        <v>0.16768292679999999</v>
+      </c>
+      <c r="I44" s="12">
+        <v>0.52153423170000002</v>
+      </c>
+      <c r="J44" s="12">
+        <v>0.53800463509999996</v>
+      </c>
+      <c r="K44" s="12">
+        <f t="shared" si="0"/>
+        <v>0.2459778953</v>
+      </c>
+      <c r="L44" s="12">
+        <f t="shared" si="13"/>
+        <v>0.35284378094999996</v>
+      </c>
+      <c r="M44" s="12">
+        <f t="shared" si="17"/>
+        <v>0.17473397153333334</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
-      <c r="B45" s="18"/>
+      <c r="B45" s="51"/>
       <c r="C45" s="7"/>
       <c r="E45" s="4"/>
       <c r="F45" s="6"/>
@@ -3965,46 +5028,90 @@
       <c r="I45" s="6"/>
       <c r="J45" s="6"/>
     </row>
-    <row r="46" spans="1:11" ht="20" x14ac:dyDescent="0.2">
-      <c r="A46" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B46" s="18"/>
-      <c r="C46" s="16" t="s">
+    <row r="46" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A46" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="B46" s="51"/>
+      <c r="C46" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="D46" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
-    </row>
-    <row r="47" spans="1:11" ht="20" x14ac:dyDescent="0.2">
-      <c r="A47" s="18"/>
-      <c r="B47" s="18"/>
-      <c r="C47" s="17"/>
+      <c r="F46" s="11">
+        <v>5.7164629999999998E-4</v>
+      </c>
+      <c r="G46" s="11">
+        <v>5.1448170999999999E-3</v>
+      </c>
+      <c r="H46" s="11">
+        <v>0.77019817069999996</v>
+      </c>
+      <c r="I46" s="11">
+        <v>0.68990504159999999</v>
+      </c>
+      <c r="J46" s="11">
+        <v>0.82907810169999996</v>
+      </c>
+      <c r="K46" s="12">
+        <f t="shared" si="0"/>
+        <v>0.45897955547999991</v>
+      </c>
+      <c r="L46" s="47">
+        <f t="shared" si="13"/>
+        <v>0.79963813620000002</v>
+      </c>
+      <c r="M46" s="12">
+        <f>F46*1/3+G46*1/3+I46*1/3</f>
+        <v>0.231873835</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A47" s="51"/>
+      <c r="B47" s="51"/>
+      <c r="C47" s="53"/>
       <c r="D47" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-    </row>
-    <row r="48" spans="1:11" ht="20" x14ac:dyDescent="0.2">
-      <c r="A48" s="18"/>
-      <c r="B48" s="18"/>
-      <c r="C48" s="17"/>
+      <c r="F47" s="12">
+        <v>3.8109759999999999E-4</v>
+      </c>
+      <c r="G47" s="12">
+        <v>3.4298781E-3</v>
+      </c>
+      <c r="H47" s="12">
+        <v>0.36775914630000001</v>
+      </c>
+      <c r="I47" s="12">
+        <v>0.47550582689999998</v>
+      </c>
+      <c r="J47" s="12">
+        <v>0.47833423320000001</v>
+      </c>
+      <c r="K47" s="12">
+        <f t="shared" si="0"/>
+        <v>0.26508203642</v>
+      </c>
+      <c r="L47" s="12">
+        <f t="shared" si="13"/>
+        <v>0.42304668975000004</v>
+      </c>
+      <c r="M47" s="12">
+        <f t="shared" ref="M47:M48" si="18">F47*1/3+G47*1/3+I47*1/3</f>
+        <v>0.15977226753333335</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="20" x14ac:dyDescent="0.2">
+      <c r="A48" s="51"/>
+      <c r="B48" s="51"/>
+      <c r="C48" s="53"/>
       <c r="D48" s="5" t="s">
         <v>25</v>
       </c>
@@ -4016,62 +5123,136 @@
       <c r="H48" s="6"/>
       <c r="I48" s="6"/>
       <c r="J48" s="6"/>
-    </row>
-    <row r="51" spans="4:10" x14ac:dyDescent="0.2">
+      <c r="K48" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L48" s="12">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="M48" s="12">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:13" x14ac:dyDescent="0.2">
       <c r="E51" s="8" t="s">
         <v>39</v>
       </c>
       <c r="F51" s="11">
         <f>MAX(F2:F48)</f>
-        <v>0</v>
+        <v>4.9161585399999999E-2</v>
       </c>
       <c r="G51" s="11">
         <f>MAX(G2:G48)</f>
-        <v>0</v>
+        <v>2.5171624699999999E-2</v>
       </c>
       <c r="H51" s="11">
         <f>MAX(H2:H48)</f>
-        <v>0</v>
+        <v>0.96948893970000005</v>
       </c>
       <c r="I51" s="11">
         <f>MAX(I2:I48)</f>
-        <v>0</v>
+        <v>0.86194404820000003</v>
       </c>
       <c r="J51" s="11">
         <f>MAX(J2:J48)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="4:10" x14ac:dyDescent="0.2">
+        <v>0.82907810169999996</v>
+      </c>
+      <c r="K51" s="47">
+        <f t="shared" ref="K51:L51" si="19">MAX(K2:K48)</f>
+        <v>0.47576659374000002</v>
+      </c>
+      <c r="L51" s="47">
+        <f t="shared" si="19"/>
+        <v>0.79963813620000002</v>
+      </c>
+      <c r="M51" s="47">
+        <f t="shared" ref="M51" si="20">MAX(M2:M48)</f>
+        <v>0.30789395103333334</v>
+      </c>
+    </row>
+    <row r="52" spans="4:13" x14ac:dyDescent="0.2">
       <c r="D52" s="5" t="s">
         <v>37</v>
       </c>
       <c r="E52" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="F52" s="11" t="e">
+      <c r="F52" s="11">
         <f>AVERAGE(F2:F48)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G52" s="11" t="e">
+        <v>1.034151390909091E-2</v>
+      </c>
+      <c r="G52" s="11">
         <f>AVERAGE(G2:G48)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H52" s="11" t="e">
+        <v>6.3608665151515141E-3</v>
+      </c>
+      <c r="H52" s="11">
         <f>AVERAGE(H2:H48)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I52" s="11" t="e">
+        <v>0.47846201980000003</v>
+      </c>
+      <c r="I52" s="11">
         <f>AVERAGE(I2:I48)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J52" s="11" t="e">
+        <v>0.59108728219393936</v>
+      </c>
+      <c r="J52" s="11">
         <f>AVERAGE(J2:J48)</f>
-        <v>#DIV/0!</v>
+        <v>0.56077279742424224</v>
+      </c>
+      <c r="K52" s="47">
+        <f t="shared" ref="K52:L52" si="21">AVERAGE(K2:K48)</f>
+        <v>0.30195448797111113</v>
+      </c>
+      <c r="L52" s="47">
+        <f t="shared" si="21"/>
+        <v>0.47631595789444453</v>
+      </c>
+      <c r="M52" s="47">
+        <f t="shared" ref="M52" si="22">AVERAGE(M2:M48)</f>
+        <v>0.1857135080222222</v>
+      </c>
+    </row>
+    <row r="53" spans="4:13" x14ac:dyDescent="0.2">
+      <c r="E53" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="F53" s="11">
+        <f t="shared" ref="F53:L53" si="23">MIN(F2:F48)</f>
+        <v>0</v>
+      </c>
+      <c r="G53" s="11">
+        <f t="shared" si="23"/>
+        <v>3.8138830000000002E-4</v>
+      </c>
+      <c r="H53" s="11">
+        <f t="shared" si="23"/>
+        <v>2.7078565999999998E-2</v>
+      </c>
+      <c r="I53" s="11">
+        <f t="shared" si="23"/>
+        <v>0.30229342920000002</v>
+      </c>
+      <c r="J53" s="11">
+        <f t="shared" si="23"/>
+        <v>0.19462933560000001</v>
+      </c>
+      <c r="K53" s="47">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="L53" s="47">
+        <f t="shared" si="23"/>
+        <v>0</v>
+      </c>
+      <c r="M53" s="47">
+        <f t="shared" ref="M53" si="24">MIN(M2:M48)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C30:C32"/>
     <mergeCell ref="A34:A36"/>
     <mergeCell ref="B34:B48"/>
     <mergeCell ref="C34:C36"/>
@@ -4081,13 +5262,6 @@
     <mergeCell ref="C42:C44"/>
     <mergeCell ref="A46:A48"/>
     <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="C30:C32"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B32"/>
     <mergeCell ref="C2:C4"/>
@@ -4098,6 +5272,2897 @@
     <mergeCell ref="A14:A16"/>
     <mergeCell ref="C14:C16"/>
     <mergeCell ref="A18:A20"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="A30:A32"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E75D5ADF-282B-7143-A056-3E023A2AE323}">
+  <dimension ref="A1:N44"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="42.83203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.83203125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="22" style="5" customWidth="1"/>
+    <col min="4" max="4" width="12.5" style="5" customWidth="1"/>
+    <col min="5" max="5" width="19" style="12" customWidth="1"/>
+    <col min="6" max="6" width="20" style="12" customWidth="1"/>
+    <col min="7" max="7" width="20" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.1640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.1640625" style="12" customWidth="1"/>
+    <col min="10" max="10" width="18.33203125" style="12" customWidth="1"/>
+    <col min="11" max="11" width="20.5" style="12" customWidth="1"/>
+    <col min="12" max="12" width="23" style="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.83203125" style="12" customWidth="1"/>
+    <col min="14" max="14" width="24.1640625" style="12" customWidth="1"/>
+    <col min="15" max="16384" width="8.83203125" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="18" customFormat="1" ht="67" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="50" t="s">
+        <v>103</v>
+      </c>
+      <c r="L1" s="50" t="s">
+        <v>73</v>
+      </c>
+      <c r="M1" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="N1" s="39" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="20" x14ac:dyDescent="0.2">
+      <c r="A2" s="51" t="s">
+        <v>77</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="6">
+        <v>0.65484363079999997</v>
+      </c>
+      <c r="F2" s="6">
+        <v>0.83790999239999997</v>
+      </c>
+      <c r="G2" s="6">
+        <v>0.71204430090000004</v>
+      </c>
+      <c r="H2" s="6">
+        <v>0.40625</v>
+      </c>
+      <c r="I2" s="6">
+        <v>0.2535211268</v>
+      </c>
+      <c r="J2" s="6">
+        <v>0.59952031800000005</v>
+      </c>
+      <c r="K2" s="29">
+        <f>SUM(E2:J2)/6</f>
+        <v>0.57734822815000009</v>
+      </c>
+      <c r="L2" s="29">
+        <f>STDEV(E2:J2)</f>
+        <v>0.21291838776787708</v>
+      </c>
+      <c r="M2" s="12">
+        <f>SUMPRODUCT(G2:I2,$C$16:$E$16)/SUM($C$16:$E$16)</f>
+        <v>0.28781759565756021</v>
+      </c>
+      <c r="N2" s="12">
+        <v>0.35202662579999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="20" x14ac:dyDescent="0.2">
+      <c r="A3" s="51"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0.31807780320000001</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0.70289855069999996</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0.31379787720000002</v>
+      </c>
+      <c r="H3" s="6">
+        <v>0.32552083329999998</v>
+      </c>
+      <c r="I3" s="6">
+        <v>0.40845070420000001</v>
+      </c>
+      <c r="J3" s="6">
+        <v>0.49760901740000002</v>
+      </c>
+      <c r="K3" s="29">
+        <f t="shared" ref="K3:K12" si="0">SUM(E3:J3)/6</f>
+        <v>0.42772579766666663</v>
+      </c>
+      <c r="L3" s="29">
+        <f>STDEV(E3:J3)</f>
+        <v>0.15259314934426299</v>
+      </c>
+      <c r="M3" s="12">
+        <f>SUMPRODUCT(G3:I3,$C$16:$E$16)/SUM($C$16:$E$16)</f>
+        <v>0.39386213045140961</v>
+      </c>
+      <c r="N3" s="12">
+        <v>0.30946887969999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="20" x14ac:dyDescent="0.2">
+      <c r="A4" s="51"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0.96948893970000005</v>
+      </c>
+      <c r="F4" s="6">
+        <v>0.97330282229999998</v>
+      </c>
+      <c r="G4" s="6">
+        <v>0.99584679279999999</v>
+      </c>
+      <c r="H4" s="6">
+        <v>0.99739583330000003</v>
+      </c>
+      <c r="I4" s="6">
+        <v>1.4084507E-2</v>
+      </c>
+      <c r="J4" s="6">
+        <v>0.61895662200000001</v>
+      </c>
+      <c r="K4" s="29">
+        <f t="shared" si="0"/>
+        <v>0.76151258618333351</v>
+      </c>
+      <c r="L4" s="29">
+        <f>STDEV(E4:J4)</f>
+        <v>0.39436876926890008</v>
+      </c>
+      <c r="M4" s="12">
+        <f>SUMPRODUCT(G4:I4,$C$16:$E$16)/SUM($C$16:$E$16)</f>
+        <v>0.18338927612931832</v>
+      </c>
+      <c r="N4" s="12">
+        <v>0.21538406309999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+    </row>
+    <row r="6" spans="1:14" ht="20" x14ac:dyDescent="0.2">
+      <c r="A6" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0.60518292679999997</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0.89824695119999998</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0.65191332410000002</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0.43489583329999998</v>
+      </c>
+      <c r="I6" s="6">
+        <v>9.8591549299999998E-2</v>
+      </c>
+      <c r="J6" s="6">
+        <v>0.68544860669999996</v>
+      </c>
+      <c r="K6" s="29">
+        <f t="shared" si="0"/>
+        <v>0.56237986523333339</v>
+      </c>
+      <c r="L6" s="29">
+        <f>STDEV(E6:J6)</f>
+        <v>0.27171777170155592</v>
+      </c>
+      <c r="M6" s="12">
+        <f>SUMPRODUCT(G6:I6,$C$19:$E$19)/SUM($C$19:$E$19)</f>
+        <v>0.15905989481147539</v>
+      </c>
+      <c r="N6" s="12">
+        <v>0.29145481309999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="20" x14ac:dyDescent="0.2">
+      <c r="A7" s="51"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="62" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="63" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="64">
+        <v>0.71532012199999995</v>
+      </c>
+      <c r="F7" s="64">
+        <v>0.88452743899999997</v>
+      </c>
+      <c r="G7" s="64">
+        <v>0.82664822500000001</v>
+      </c>
+      <c r="H7" s="64">
+        <v>0.20572916669999999</v>
+      </c>
+      <c r="I7" s="64">
+        <v>7.0422535199999997E-2</v>
+      </c>
+      <c r="J7" s="64">
+        <v>0.73983099360000004</v>
+      </c>
+      <c r="K7" s="65">
+        <f>SUM(E7:J7)/6</f>
+        <v>0.57374641358333334</v>
+      </c>
+      <c r="L7" s="65">
+        <f>STDEV(E7:J7)</f>
+        <v>0.34552655329669091</v>
+      </c>
+      <c r="M7" s="66">
+        <f>SUMPRODUCT(G7:I7,$C$19:$E$19)/SUM($C$19:$E$19)</f>
+        <v>0.10787245163360654</v>
+      </c>
+      <c r="N7" s="66">
+        <v>0.60415152729999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="20" x14ac:dyDescent="0.2">
+      <c r="A8" s="51"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="29">
+        <f>SUM(E8:J8)/6</f>
+        <v>0</v>
+      </c>
+      <c r="L8" s="29" t="e">
+        <f>STDEV(E8:J8)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M8" s="12">
+        <f>SUMPRODUCT(G8:I8,$C$19:$E$19)/SUM($C$19:$E$19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="29"/>
+      <c r="L9" s="29"/>
+    </row>
+    <row r="10" spans="1:14" ht="20" x14ac:dyDescent="0.2">
+      <c r="A10" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.77019817069999996</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0.96989329270000002</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0.91240202859999997</v>
+      </c>
+      <c r="H10" s="6">
+        <v>0.109375</v>
+      </c>
+      <c r="I10" s="6">
+        <v>0</v>
+      </c>
+      <c r="J10" s="6">
+        <v>0.82907810169999996</v>
+      </c>
+      <c r="K10" s="29">
+        <f t="shared" si="0"/>
+        <v>0.59849109894999997</v>
+      </c>
+      <c r="L10" s="29">
+        <f>STDEV(E10:J10)</f>
+        <v>0.42814938967063176</v>
+      </c>
+      <c r="M10" s="12">
+        <f>SUMPRODUCT(G10:I10, $C$22:$E$22)/SUM($C$22:$E$22)</f>
+        <v>5.4554890957798155E-2</v>
+      </c>
+      <c r="N10" s="12">
+        <v>0.27578664860000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="20" x14ac:dyDescent="0.2">
+      <c r="A11" s="51"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="6">
+        <v>0.36775914630000001</v>
+      </c>
+      <c r="F11" s="6">
+        <v>0.64481707320000003</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0.3785154449</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0.31510416670000002</v>
+      </c>
+      <c r="I11" s="6">
+        <v>0.32394366200000002</v>
+      </c>
+      <c r="J11" s="6">
+        <v>0.47833423320000001</v>
+      </c>
+      <c r="K11" s="29">
+        <f t="shared" si="0"/>
+        <v>0.41807895438333337</v>
+      </c>
+      <c r="L11" s="29">
+        <f>STDEV(E11:J11)</f>
+        <v>0.12538220582562706</v>
+      </c>
+      <c r="M11" s="12">
+        <f>SUMPRODUCT(G11:I11, $C$22:$E$22)/SUM($C$22:$E$22)</f>
+        <v>0.32424327420458715</v>
+      </c>
+      <c r="N11" s="12">
+        <v>0.30020344319999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="20" x14ac:dyDescent="0.2">
+      <c r="A12" s="51"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L12" s="29" t="e">
+        <f>STDEV(E12:J12)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M12" s="12">
+        <f>SUMPRODUCT(G12:I12, $C$22:$E$22)/SUM($C$22:$E$22)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" s="23"/>
+      <c r="B14" s="23"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="K14" s="61">
+        <f>MAX(K2:K12)</f>
+        <v>0.76151258618333351</v>
+      </c>
+      <c r="L14" s="61" t="e">
+        <f t="shared" ref="L14:M14" si="1">MAX(L2:L12)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M14" s="61">
+        <f t="shared" si="1"/>
+        <v>0.39386213045140961</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" s="23"/>
+      <c r="B15" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="E15" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="K15" s="61">
+        <f>MIN(K2:K12)</f>
+        <v>0</v>
+      </c>
+      <c r="L15" s="61" t="e">
+        <f t="shared" ref="L15:M15" si="2">MIN(L2:L12)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M15" s="61">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" s="23"/>
+      <c r="B16" s="42" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="48">
+        <f>1/38</f>
+        <v>2.6315789473684209E-2</v>
+      </c>
+      <c r="D16" s="49">
+        <f>1/6.8</f>
+        <v>0.14705882352941177</v>
+      </c>
+      <c r="E16" s="49">
+        <f>1/1.2</f>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="K16" s="61">
+        <f>AVERAGE(K2:K12)</f>
+        <v>0.43547588268333332</v>
+      </c>
+      <c r="L16" s="61" t="e">
+        <f t="shared" ref="L16:M16" si="3">AVERAGE(L2:L12)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M16" s="61">
+        <f t="shared" si="3"/>
+        <v>0.16786661264952837</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17" s="25"/>
+      <c r="B17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18" s="23"/>
+      <c r="B18" s="42" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A19" s="23"/>
+      <c r="B19" s="42" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="48">
+        <f>1/34</f>
+        <v>2.9411764705882353E-2</v>
+      </c>
+      <c r="D19" s="49">
+        <f>1/6</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="E19" s="49">
+        <f>1/1</f>
+        <v>1</v>
+      </c>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="29"/>
+      <c r="L19" s="29"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A20" s="23"/>
+      <c r="B20" s="23"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A21" s="25"/>
+      <c r="B21" s="42" t="s">
+        <v>96</v>
+      </c>
+      <c r="C21" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="D21" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="E21" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="29"/>
+      <c r="L21" s="29"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A22" s="23"/>
+      <c r="B22" s="42" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" s="48">
+        <f>1/21</f>
+        <v>4.7619047619047616E-2</v>
+      </c>
+      <c r="D22" s="49">
+        <f>1/4</f>
+        <v>0.25</v>
+      </c>
+      <c r="E22" s="49">
+        <f>1/1</f>
+        <v>1</v>
+      </c>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="29"/>
+      <c r="L22" s="29"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23" s="23"/>
+      <c r="B23" s="23"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A24" s="23"/>
+      <c r="B24" s="23"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A25" s="25"/>
+      <c r="B25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A26" s="23"/>
+      <c r="B26" s="23"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A27" s="23"/>
+      <c r="B27" s="23"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="29"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A28" s="23"/>
+      <c r="B28" s="23"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="29"/>
+      <c r="L28" s="29"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A29" s="25"/>
+      <c r="B29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A30" s="23"/>
+      <c r="B30" s="23"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="29"/>
+      <c r="L30" s="29"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A31" s="23"/>
+      <c r="B31" s="23"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="19"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="29"/>
+      <c r="L31" s="29"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A32" s="23"/>
+      <c r="B32" s="23"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A33" s="25"/>
+      <c r="B33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="19"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="29"/>
+      <c r="L33" s="29"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A34" s="23"/>
+      <c r="B34" s="23"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="29"/>
+      <c r="L34" s="29"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A35" s="23"/>
+      <c r="B35" s="23"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="29"/>
+      <c r="L35" s="29"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A36" s="23"/>
+      <c r="B36" s="23"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="19"/>
+      <c r="K36" s="29"/>
+      <c r="L36" s="29"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A37" s="25"/>
+      <c r="B37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="19"/>
+      <c r="K37" s="29"/>
+      <c r="L37" s="29"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A38" s="23"/>
+      <c r="B38" s="23"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="29"/>
+      <c r="L38" s="29"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A39" s="23"/>
+      <c r="B39" s="23"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="29"/>
+      <c r="L39" s="29"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A40" s="23"/>
+      <c r="B40" s="23"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="19"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="29"/>
+      <c r="L40" s="29"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K41" s="29"/>
+      <c r="L41" s="29"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K42" s="29"/>
+      <c r="L42" s="29"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="D43" s="8"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="29"/>
+      <c r="L43" s="29"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="D44" s="8"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="29"/>
+      <c r="L44" s="29"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="B10:B12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB030C74-5D3D-4140-98C1-A6779936EBBB}">
+  <dimension ref="A1:N52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="42.83203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28" style="5" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="22" style="5" customWidth="1"/>
+    <col min="5" max="5" width="12.5" style="5" customWidth="1"/>
+    <col min="6" max="6" width="19" style="12" customWidth="1"/>
+    <col min="7" max="7" width="20" style="12" customWidth="1"/>
+    <col min="8" max="8" width="20" style="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.1640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.33203125" style="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.83203125" style="12" customWidth="1"/>
+    <col min="12" max="12" width="20.5" style="33" customWidth="1"/>
+    <col min="13" max="13" width="23" style="33" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.83203125" style="33" customWidth="1"/>
+    <col min="15" max="16384" width="8.83203125" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="18" customFormat="1" ht="67" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="I1" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="J1" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="K1" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="M1" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="N1" s="21" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="20" x14ac:dyDescent="0.25">
+      <c r="A2" s="55" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="56">
+        <v>0</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="28">
+        <f>H2*1/3+I2*1/3+J2*1/3</f>
+        <v>0</v>
+      </c>
+      <c r="M2" s="28" t="e">
+        <f>STDEV(H2:J2)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N2" s="33" t="e">
+        <f>SUMPRODUCT(H2:J2,$D$26:$F$26)/SUM($D$26:$F$26)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="20" x14ac:dyDescent="0.25">
+      <c r="A3" s="51"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="28">
+        <f>H3*1/3+I3*1/3+J3*1/3</f>
+        <v>0</v>
+      </c>
+      <c r="M3" s="28" t="e">
+        <f t="shared" ref="M3:M4" si="0">STDEV(H3:J3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N3" s="33" t="e">
+        <f>SUMPRODUCT(H3:J3,$D$26:$F$26)/SUM($D$26:$F$26)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="20" x14ac:dyDescent="0.25">
+      <c r="A4" s="51"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="28">
+        <f>H4*1/3+I4*1/3+J4*1/3</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="28" t="e">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N4" s="33" t="e">
+        <f>SUMPRODUCT(H4:J4,$D$26:$F$26)/SUM($D$26:$F$26)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="51"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="22"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+    </row>
+    <row r="6" spans="1:14" ht="20" x14ac:dyDescent="0.25">
+      <c r="A6" s="51"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="54">
+        <v>10</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="28">
+        <f>H6*1/3+I6*1/3+J6*1/3</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="28" t="e">
+        <f>STDEV(H6:J6)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N6" s="33" t="e">
+        <f>SUMPRODUCT(H6:J6,$D$26:$F$26)/SUM($D$26:$F$26)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="20" x14ac:dyDescent="0.25">
+      <c r="A7" s="51"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="28">
+        <f>H7*1/3+I7*1/3+J7*1/3</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="28" t="e">
+        <f t="shared" ref="M7:M8" si="1">STDEV(H7:J7)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N7" s="33" t="e">
+        <f>SUMPRODUCT(H7:J7,$D$26:$F$26)/SUM($D$26:$F$26)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="20" x14ac:dyDescent="0.25">
+      <c r="A8" s="51"/>
+      <c r="B8" s="51"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="28">
+        <f>H8*1/3+I8*1/3+J8*1/3</f>
+        <v>0</v>
+      </c>
+      <c r="M8" s="28" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N8" s="33" t="e">
+        <f>SUMPRODUCT(H8:J8,$D$26:$F$26)/SUM($D$26:$F$26)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="51"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="22"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+    </row>
+    <row r="10" spans="1:14" ht="20" x14ac:dyDescent="0.25">
+      <c r="A10" s="51"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="54">
+        <v>20</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="28">
+        <f>H10*1/3+I10*1/3+J10*1/3</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="28" t="e">
+        <f t="shared" ref="M10:M20" si="2">STDEV(H10:J10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N10" s="33" t="e">
+        <f>SUMPRODUCT(H10:J10,$D$26:$F$26)/SUM($D$26:$F$26)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="20" x14ac:dyDescent="0.25">
+      <c r="A11" s="51"/>
+      <c r="B11" s="51"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="28">
+        <f>H11*1/3+I11*1/3+J11*1/3</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="28" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N11" s="33" t="e">
+        <f>SUMPRODUCT(H11:J11,$D$26:$F$26)/SUM($D$26:$F$26)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="20" x14ac:dyDescent="0.25">
+      <c r="A12" s="51"/>
+      <c r="B12" s="51"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="28">
+        <f>H12*1/3+I12*1/3+J12*1/3</f>
+        <v>0</v>
+      </c>
+      <c r="M12" s="28" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N12" s="33" t="e">
+        <f>SUMPRODUCT(H12:J12,$D$26:$F$26)/SUM($D$26:$F$26)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="51"/>
+      <c r="B13" s="51"/>
+      <c r="C13" s="22"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="28"/>
+    </row>
+    <row r="14" spans="1:14" ht="20" x14ac:dyDescent="0.25">
+      <c r="A14" s="51"/>
+      <c r="B14" s="51"/>
+      <c r="C14" s="54">
+        <v>30</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="28">
+        <f>H14*1/3+I14*1/3+J14*1/3</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="28" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N14" s="33" t="e">
+        <f>SUMPRODUCT(H14:J14,$D$26:$F$26)/SUM($D$26:$F$26)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="20" x14ac:dyDescent="0.25">
+      <c r="A15" s="51"/>
+      <c r="B15" s="51"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="28">
+        <f>H15*1/3+I15*1/3+J15*1/3</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="28" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N15" s="33" t="e">
+        <f>SUMPRODUCT(H15:J15,$D$26:$F$26)/SUM($D$26:$F$26)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="20" x14ac:dyDescent="0.25">
+      <c r="A16" s="51"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="28">
+        <f>H16*1/3+I16*1/3+J16*1/3</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="28" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N16" s="33" t="e">
+        <f>SUMPRODUCT(H16:J16,$D$26:$F$26)/SUM($D$26:$F$26)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="51"/>
+      <c r="B17" s="51"/>
+      <c r="C17" s="24"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="28"/>
+    </row>
+    <row r="18" spans="1:14" ht="20" x14ac:dyDescent="0.25">
+      <c r="A18" s="51"/>
+      <c r="B18" s="51"/>
+      <c r="C18" s="54">
+        <v>100</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="28">
+        <f>H18*1/3+I18*1/3+J18*1/3</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="28" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N18" s="33" t="e">
+        <f>SUMPRODUCT(H18:J18,$D$26:$F$26)/SUM($D$26:$F$26)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="20" x14ac:dyDescent="0.25">
+      <c r="A19" s="51"/>
+      <c r="B19" s="51"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="28">
+        <f>H19*1/3+I19*1/3+J19*1/3</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="28" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N19" s="33" t="e">
+        <f>SUMPRODUCT(H19:J19,$D$26:$F$26)/SUM($D$26:$F$26)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="20" x14ac:dyDescent="0.25">
+      <c r="A20" s="51"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="28">
+        <f>H20*1/3+I20*1/3+J20*1/3</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="28" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N20" s="33" t="e">
+        <f>SUMPRODUCT(H20:J20,$D$26:$F$26)/SUM($D$26:$F$26)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="25"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="24"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="28"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="23"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="24"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="28"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="23"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="24"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="28"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="23"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="24"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="28"/>
+      <c r="M24" s="28"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="25"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="D25" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="E25" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="F25" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="28"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26" s="23"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="42" t="s">
+        <v>94</v>
+      </c>
+      <c r="D26" s="41"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="28"/>
+      <c r="M26" s="28"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A27" s="23"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="24"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="28"/>
+      <c r="M27" s="28"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A28" s="23"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="24"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="28"/>
+      <c r="M28" s="28"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A29" s="25"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="24"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19"/>
+      <c r="K29" s="19"/>
+      <c r="L29" s="28"/>
+      <c r="M29" s="28"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A30" s="23"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="24"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="19"/>
+      <c r="L30" s="28"/>
+      <c r="M30" s="28"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A31" s="23"/>
+      <c r="B31" s="23"/>
+      <c r="C31" s="24"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="19"/>
+      <c r="G31" s="19"/>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19"/>
+      <c r="K31" s="19"/>
+      <c r="L31" s="28"/>
+      <c r="M31" s="28"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A32" s="23"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="24"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19"/>
+      <c r="K32" s="19"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="25"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="19"/>
+      <c r="G33" s="19"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19"/>
+      <c r="K33" s="19"/>
+      <c r="L33" s="28"/>
+      <c r="M33" s="28"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="23"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="23"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+      <c r="H34" s="19"/>
+      <c r="I34" s="19"/>
+      <c r="J34" s="19"/>
+      <c r="K34" s="19"/>
+      <c r="L34" s="28"/>
+      <c r="M34" s="28"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="23"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="23"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="28"/>
+      <c r="M35" s="28"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="23"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="19"/>
+      <c r="J36" s="19"/>
+      <c r="K36" s="19"/>
+      <c r="L36" s="28"/>
+      <c r="M36" s="28"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="25"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="23"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="19"/>
+      <c r="G37" s="19"/>
+      <c r="H37" s="19"/>
+      <c r="I37" s="19"/>
+      <c r="J37" s="19"/>
+      <c r="K37" s="19"/>
+      <c r="L37" s="28"/>
+      <c r="M37" s="28"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="23"/>
+      <c r="B38" s="23"/>
+      <c r="C38" s="23"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
+      <c r="H38" s="19"/>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19"/>
+      <c r="K38" s="19"/>
+      <c r="L38" s="28"/>
+      <c r="M38" s="28"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="23"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="28"/>
+      <c r="M39" s="28"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" s="23"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="19"/>
+      <c r="G40" s="19"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19"/>
+      <c r="K40" s="19"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="28"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="25"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="23"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="28"/>
+      <c r="M41" s="28"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" s="23"/>
+      <c r="B42" s="23"/>
+      <c r="C42" s="23"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="19"/>
+      <c r="K42" s="19"/>
+      <c r="L42" s="28"/>
+      <c r="M42" s="28"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" s="23"/>
+      <c r="B43" s="23"/>
+      <c r="C43" s="23"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="19"/>
+      <c r="K43" s="19"/>
+      <c r="L43" s="28"/>
+      <c r="M43" s="28"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" s="23"/>
+      <c r="B44" s="23"/>
+      <c r="C44" s="23"/>
+      <c r="E44" s="25"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="19"/>
+      <c r="K44" s="19"/>
+      <c r="L44" s="28"/>
+      <c r="M44" s="28"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" s="25"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="23"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="19"/>
+      <c r="L45" s="28"/>
+      <c r="M45" s="28"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="23"/>
+      <c r="B46" s="23"/>
+      <c r="C46" s="23"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="19"/>
+      <c r="G46" s="19"/>
+      <c r="H46" s="19"/>
+      <c r="I46" s="19"/>
+      <c r="J46" s="19"/>
+      <c r="K46" s="19"/>
+      <c r="L46" s="28"/>
+      <c r="M46" s="28"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="23"/>
+      <c r="B47" s="23"/>
+      <c r="C47" s="23"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="19"/>
+      <c r="G47" s="19"/>
+      <c r="H47" s="19"/>
+      <c r="I47" s="19"/>
+      <c r="J47" s="19"/>
+      <c r="K47" s="19"/>
+      <c r="L47" s="28"/>
+      <c r="M47" s="28"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="23"/>
+      <c r="B48" s="23"/>
+      <c r="C48" s="23"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="19"/>
+      <c r="G48" s="19"/>
+      <c r="H48" s="19"/>
+      <c r="I48" s="19"/>
+      <c r="J48" s="19"/>
+      <c r="K48" s="19"/>
+      <c r="L48" s="28"/>
+      <c r="M48" s="28"/>
+    </row>
+    <row r="49" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="L49" s="28"/>
+      <c r="M49" s="28"/>
+    </row>
+    <row r="50" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="L50" s="28"/>
+      <c r="M50" s="28"/>
+    </row>
+    <row r="51" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E51" s="8"/>
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+      <c r="H51" s="11"/>
+      <c r="I51" s="11"/>
+      <c r="J51" s="11"/>
+      <c r="K51" s="11"/>
+      <c r="L51" s="28"/>
+      <c r="M51" s="28"/>
+    </row>
+    <row r="52" spans="5:13" x14ac:dyDescent="0.25">
+      <c r="E52" s="8"/>
+      <c r="F52" s="11"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="11"/>
+      <c r="I52" s="11"/>
+      <c r="J52" s="11"/>
+      <c r="K52" s="11"/>
+      <c r="L52" s="28"/>
+      <c r="M52" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="C10:C12"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="A2:A20"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="B2:B20"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C64FDBF-6E58-8148-821B-47274FA4A935}">
+  <dimension ref="A1:M52"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="32.1640625" style="33" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" style="33" customWidth="1"/>
+    <col min="4" max="4" width="15.5" style="33" customWidth="1"/>
+    <col min="5" max="5" width="23.33203125" style="33" customWidth="1"/>
+    <col min="6" max="6" width="26.1640625" style="33" customWidth="1"/>
+    <col min="7" max="7" width="19.83203125" style="33" customWidth="1"/>
+    <col min="8" max="8" width="18.1640625" style="33" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="23" style="33" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.33203125" style="33" customWidth="1"/>
+    <col min="11" max="11" width="20.5" style="33" customWidth="1"/>
+    <col min="12" max="12" width="23" style="33" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.83203125" style="33" customWidth="1"/>
+    <col min="14" max="16384" width="10.83203125" style="33"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" s="38" customFormat="1" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="C1" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="35" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="36" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1" s="36" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="L1" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="M1" s="21" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="58" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="28">
+        <f>G2*1/3+H2*1/3+I2*1/3</f>
+        <v>0</v>
+      </c>
+      <c r="L2" s="28" t="e">
+        <f>STDEV(G2:I2)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M2" s="33" t="e">
+        <f>SUMPRODUCT(G2:I2,$D$14:$F$14)/SUM($D$14:$F$14)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="59"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
+      <c r="J3" s="29"/>
+      <c r="K3" s="28">
+        <f t="shared" ref="K3:K4" si="0">G3*1/3+H3*1/3+I3*1/3</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="28" t="e">
+        <f t="shared" ref="L3:L4" si="1">STDEV(G3:I3)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M3" s="33" t="e">
+        <f>SUMPRODUCT(G3:I3,$D$14:$F$14)/SUM($D$14:$F$14)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="59"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L4" s="28" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M4" s="33" t="e">
+        <f>SUMPRODUCT(G4:I4,$D$14:$F$14)/SUM($D$14:$F$14)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="59"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="59"/>
+      <c r="B6" s="59"/>
+      <c r="C6" s="60" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="29"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="29"/>
+      <c r="K6" s="28">
+        <f>G6*1/3+H6*1/3+I6*1/3</f>
+        <v>0</v>
+      </c>
+      <c r="L6" s="28" t="e">
+        <f>STDEV(G6:I6)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M6" s="33" t="e">
+        <f>SUMPRODUCT(G6:I6,$D$14:$F$14)/SUM($D$14:$F$14)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="59"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="29"/>
+      <c r="K7" s="28">
+        <f t="shared" ref="K7:K8" si="2">G7*1/3+H7*1/3+I7*1/3</f>
+        <v>0</v>
+      </c>
+      <c r="L7" s="28" t="e">
+        <f t="shared" ref="L7:L8" si="3">STDEV(G7:I7)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M7" s="33" t="e">
+        <f>SUMPRODUCT(G7:I7,$D$14:$F$14)/SUM($D$14:$F$14)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="59"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="27" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="29"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="29"/>
+      <c r="K8" s="28">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L8" s="28" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M8" s="33" t="e">
+        <f>SUMPRODUCT(G8:I8,$D$14:$F$14)/SUM($D$14:$F$14)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="59"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="59"/>
+      <c r="B10" s="59"/>
+      <c r="C10" s="57" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="29"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="29"/>
+      <c r="K10" s="28">
+        <f>G10*1/3+H10*1/3+I10*1/3</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="28" t="e">
+        <f t="shared" ref="L10:L11" si="4">STDEV(G10:I10)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M10" s="33" t="e">
+        <f>SUMPRODUCT(G10:I10,$D$14:$F$14)/SUM($D$14:$F$14)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="59"/>
+      <c r="B11" s="59"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="29"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="28">
+        <f t="shared" ref="K11" si="5">G11*1/3+H11*1/3+I11*1/3</f>
+        <v>0</v>
+      </c>
+      <c r="L11" s="28" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M11" s="33" t="e">
+        <f>SUMPRODUCT(G11:I11,$D$14:$F$14)/SUM($D$14:$F$14)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="30"/>
+      <c r="B12" s="30"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="29"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="28"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="27"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="G13" s="29"/>
+      <c r="H13" s="29"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="30"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="42" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" s="41"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="29"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="30"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="27"/>
+      <c r="D15" s="27"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="30"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="29"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="29"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A17" s="27"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="29"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="29"/>
+      <c r="H17" s="29"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="29"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="30"/>
+      <c r="B18" s="30"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="27"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="29"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="29"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A19" s="30"/>
+      <c r="B19" s="30"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="27"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A20" s="30"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="27"/>
+      <c r="D20" s="27"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A21" s="27"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="29"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="29"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A22" s="30"/>
+      <c r="B22" s="30"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="30"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="30"/>
+      <c r="B24" s="30"/>
+      <c r="C24" s="27"/>
+      <c r="D24" s="27"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="27"/>
+      <c r="B25" s="27"/>
+      <c r="C25" s="27"/>
+      <c r="D25" s="27"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="30"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="27"/>
+      <c r="D26" s="27"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="30"/>
+      <c r="B27" s="30"/>
+      <c r="C27" s="27"/>
+      <c r="D27" s="27"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="30"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="27"/>
+      <c r="D28" s="27"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="27"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="27"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="30"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="28"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="30"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="30"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="27"/>
+      <c r="B33" s="27"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="27"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="29"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="29"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="30"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="27"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="29"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="30"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="27"/>
+      <c r="E35" s="29"/>
+      <c r="F35" s="29"/>
+      <c r="G35" s="29"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29"/>
+      <c r="J35" s="29"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="30"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="27"/>
+      <c r="D36" s="27"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="29"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="27"/>
+      <c r="B37" s="27"/>
+      <c r="C37" s="27"/>
+      <c r="D37" s="27"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="30"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="27"/>
+      <c r="D38" s="27"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="29"/>
+      <c r="G38" s="29"/>
+      <c r="H38" s="29"/>
+      <c r="I38" s="29"/>
+      <c r="J38" s="29"/>
+      <c r="K38" s="28"/>
+      <c r="L38" s="28"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="30"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="27"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="29"/>
+      <c r="J39" s="29"/>
+      <c r="K39" s="28"/>
+      <c r="L39" s="28"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" s="30"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="27"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="28"/>
+      <c r="L40" s="28"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" s="27"/>
+      <c r="B41" s="27"/>
+      <c r="C41" s="27"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="29"/>
+      <c r="I41" s="29"/>
+      <c r="J41" s="29"/>
+      <c r="K41" s="28"/>
+      <c r="L41" s="28"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" s="30"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="27"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
+      <c r="I42" s="29"/>
+      <c r="J42" s="29"/>
+      <c r="K42" s="28"/>
+      <c r="L42" s="28"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" s="30"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="27"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29"/>
+      <c r="I43" s="29"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="28"/>
+      <c r="L43" s="28"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" s="30"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="27"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
+      <c r="H44" s="29"/>
+      <c r="I44" s="29"/>
+      <c r="J44" s="29"/>
+      <c r="K44" s="28"/>
+      <c r="L44" s="28"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" s="27"/>
+      <c r="B45" s="27"/>
+      <c r="C45" s="27"/>
+      <c r="D45" s="27"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="29"/>
+      <c r="H45" s="29"/>
+      <c r="I45" s="29"/>
+      <c r="J45" s="29"/>
+      <c r="K45" s="28"/>
+      <c r="L45" s="28"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" s="30"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="27"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="29"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="28"/>
+      <c r="L46" s="28"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" s="30"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="29"/>
+      <c r="I47" s="29"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="28"/>
+      <c r="L47" s="28"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" s="30"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="27"/>
+      <c r="D48" s="27"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
+      <c r="G48" s="29"/>
+      <c r="H48" s="29"/>
+      <c r="I48" s="29"/>
+      <c r="J48" s="29"/>
+      <c r="K48" s="28"/>
+      <c r="L48" s="28"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="27"/>
+      <c r="B49" s="27"/>
+      <c r="C49" s="27"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="29"/>
+      <c r="H49" s="29"/>
+      <c r="I49" s="29"/>
+      <c r="J49" s="29"/>
+      <c r="K49" s="28"/>
+      <c r="L49" s="28"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="27"/>
+      <c r="B50" s="27"/>
+      <c r="C50" s="27"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="29"/>
+      <c r="F50" s="29"/>
+      <c r="G50" s="29"/>
+      <c r="H50" s="29"/>
+      <c r="I50" s="29"/>
+      <c r="J50" s="29"/>
+      <c r="K50" s="28"/>
+      <c r="L50" s="28"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" s="27"/>
+      <c r="B51" s="27"/>
+      <c r="C51" s="27"/>
+      <c r="D51" s="31"/>
+      <c r="E51" s="32"/>
+      <c r="F51" s="32"/>
+      <c r="G51" s="32"/>
+      <c r="H51" s="32"/>
+      <c r="I51" s="32"/>
+      <c r="J51" s="32"/>
+      <c r="K51" s="28"/>
+      <c r="L51" s="28"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" s="27"/>
+      <c r="B52" s="27"/>
+      <c r="C52" s="27"/>
+      <c r="D52" s="31"/>
+      <c r="E52" s="32"/>
+      <c r="F52" s="32"/>
+      <c r="G52" s="32"/>
+      <c r="H52" s="32"/>
+      <c r="I52" s="32"/>
+      <c r="J52" s="32"/>
+      <c r="K52" s="28"/>
+      <c r="L52" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="A2:A11"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="B2:B11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/benchmarking/output/data.xlsx
+++ b/benchmarking/output/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F2965AC-1B5C-1D42-A163-C6ACA340DDB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49F3ABE-5490-2440-869B-0F47643259FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4280" yWindow="500" windowWidth="46920" windowHeight="26600" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="basic" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="105">
   <si>
     <t>Model</t>
   </si>
@@ -227,9 +227,6 @@
     <t>Average RP and RC</t>
   </si>
   <si>
-    <t>pretrained/</t>
-  </si>
-  <si>
     <t>Relation Prediction HITS@2</t>
   </si>
   <si>
@@ -378,11 +375,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000000"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -464,8 +460,44 @@
       <color theme="1"/>
       <name val="Calibri (Corpo)"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri (Corpo)"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri (Corpo)"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -498,24 +530,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFDE9D9"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -526,8 +540,44 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -568,11 +618,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -634,9 +721,6 @@
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -649,13 +733,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -664,33 +742,11 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -702,13 +758,7 @@
     <xf numFmtId="164" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -717,7 +767,125 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -750,23 +918,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1076,22 +1229,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="22.33203125" defaultRowHeight="19" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="38.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33.1640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="38.1640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.83203125" style="5"/>
+    <col min="1" max="1" width="29.83203125" style="5" customWidth="1"/>
+    <col min="2" max="5" width="22.33203125" style="5"/>
+    <col min="6" max="10" width="21.1640625" style="12" customWidth="1"/>
+    <col min="11" max="16384" width="22.33203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="3" customFormat="1" ht="45" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="3" customFormat="1" ht="74" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -1124,13 +1270,13 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="78" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="52" t="s">
+      <c r="C2" s="79" t="s">
         <v>29</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -1156,9 +1302,9 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A3" s="51"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="53"/>
+      <c r="A3" s="78"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="80"/>
       <c r="D3" s="5" t="s">
         <v>24</v>
       </c>
@@ -1182,9 +1328,9 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="51"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="53"/>
+      <c r="A4" s="78"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="80"/>
       <c r="D4" s="5" t="s">
         <v>25</v>
       </c>
@@ -1209,7 +1355,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
-      <c r="B5" s="54"/>
+      <c r="B5" s="81"/>
       <c r="C5" s="7"/>
       <c r="E5" s="4"/>
       <c r="F5" s="6"/>
@@ -1219,11 +1365,11 @@
       <c r="J5" s="6"/>
     </row>
     <row r="6" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="52" t="s">
+      <c r="B6" s="81"/>
+      <c r="C6" s="79" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="5" t="s">
@@ -1249,9 +1395,9 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="51"/>
-      <c r="B7" s="54"/>
-      <c r="C7" s="53"/>
+      <c r="A7" s="78"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="80"/>
       <c r="D7" s="5" t="s">
         <v>24</v>
       </c>
@@ -1275,9 +1421,9 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A8" s="51"/>
-      <c r="B8" s="54"/>
-      <c r="C8" s="53"/>
+      <c r="A8" s="78"/>
+      <c r="B8" s="81"/>
+      <c r="C8" s="80"/>
       <c r="D8" s="5" t="s">
         <v>25</v>
       </c>
@@ -1302,7 +1448,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
-      <c r="B9" s="54"/>
+      <c r="B9" s="81"/>
       <c r="C9" s="7"/>
       <c r="E9" s="4"/>
       <c r="F9" s="6"/>
@@ -1312,11 +1458,11 @@
       <c r="J9" s="6"/>
     </row>
     <row r="10" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="51" t="s">
+      <c r="A10" s="78" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="54"/>
-      <c r="C10" s="52" t="s">
+      <c r="B10" s="81"/>
+      <c r="C10" s="79" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="5" t="s">
@@ -1342,9 +1488,9 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="51"/>
-      <c r="B11" s="54"/>
-      <c r="C11" s="53"/>
+      <c r="A11" s="78"/>
+      <c r="B11" s="81"/>
+      <c r="C11" s="80"/>
       <c r="D11" s="5" t="s">
         <v>24</v>
       </c>
@@ -1368,9 +1514,9 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="51"/>
-      <c r="B12" s="54"/>
-      <c r="C12" s="53"/>
+      <c r="A12" s="78"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="80"/>
       <c r="D12" s="5" t="s">
         <v>25</v>
       </c>
@@ -1395,7 +1541,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="4"/>
-      <c r="B13" s="54"/>
+      <c r="B13" s="81"/>
       <c r="C13" s="7"/>
       <c r="E13" s="4"/>
       <c r="F13" s="6"/>
@@ -1405,11 +1551,11 @@
       <c r="J13" s="6"/>
     </row>
     <row r="14" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A14" s="51" t="s">
+      <c r="A14" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="54"/>
-      <c r="C14" s="52" t="s">
+      <c r="B14" s="81"/>
+      <c r="C14" s="79" t="s">
         <v>32</v>
       </c>
       <c r="D14" s="5" t="s">
@@ -1435,9 +1581,9 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A15" s="51"/>
-      <c r="B15" s="54"/>
-      <c r="C15" s="53"/>
+      <c r="A15" s="78"/>
+      <c r="B15" s="81"/>
+      <c r="C15" s="80"/>
       <c r="D15" s="5" t="s">
         <v>24</v>
       </c>
@@ -1461,9 +1607,9 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A16" s="51"/>
-      <c r="B16" s="54"/>
-      <c r="C16" s="53"/>
+      <c r="A16" s="78"/>
+      <c r="B16" s="81"/>
+      <c r="C16" s="80"/>
       <c r="D16" s="5" t="s">
         <v>25</v>
       </c>
@@ -1488,7 +1634,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
-      <c r="B17" s="54"/>
+      <c r="B17" s="81"/>
       <c r="C17" s="7"/>
       <c r="E17" s="4"/>
       <c r="F17" s="6"/>
@@ -1498,11 +1644,11 @@
       <c r="J17" s="6"/>
     </row>
     <row r="18" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A18" s="51" t="s">
+      <c r="A18" s="78" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="54"/>
-      <c r="C18" s="52" t="s">
+      <c r="B18" s="81"/>
+      <c r="C18" s="79" t="s">
         <v>33</v>
       </c>
       <c r="D18" s="5" t="s">
@@ -1528,9 +1674,9 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A19" s="51"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="53"/>
+      <c r="A19" s="78"/>
+      <c r="B19" s="81"/>
+      <c r="C19" s="80"/>
       <c r="D19" s="5" t="s">
         <v>24</v>
       </c>
@@ -1554,9 +1700,9 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A20" s="51"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="53"/>
+      <c r="A20" s="78"/>
+      <c r="B20" s="81"/>
+      <c r="C20" s="80"/>
       <c r="D20" s="5" t="s">
         <v>25</v>
       </c>
@@ -1581,7 +1727,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
-      <c r="B21" s="54"/>
+      <c r="B21" s="81"/>
       <c r="C21" s="7"/>
       <c r="E21" s="4"/>
       <c r="F21" s="6"/>
@@ -1591,11 +1737,11 @@
       <c r="J21" s="6"/>
     </row>
     <row r="22" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A22" s="51" t="s">
+      <c r="A22" s="78" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="54"/>
-      <c r="C22" s="52" t="s">
+      <c r="B22" s="81"/>
+      <c r="C22" s="79" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="5" t="s">
@@ -1621,9 +1767,9 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A23" s="51"/>
-      <c r="B23" s="54"/>
-      <c r="C23" s="53"/>
+      <c r="A23" s="78"/>
+      <c r="B23" s="81"/>
+      <c r="C23" s="80"/>
       <c r="D23" s="5" t="s">
         <v>24</v>
       </c>
@@ -1647,9 +1793,9 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A24" s="51"/>
-      <c r="B24" s="54"/>
-      <c r="C24" s="53"/>
+      <c r="A24" s="78"/>
+      <c r="B24" s="81"/>
+      <c r="C24" s="80"/>
       <c r="D24" s="5" t="s">
         <v>25</v>
       </c>
@@ -1674,7 +1820,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="4"/>
-      <c r="B25" s="54"/>
+      <c r="B25" s="81"/>
       <c r="C25" s="7"/>
       <c r="E25" s="4"/>
       <c r="F25" s="6"/>
@@ -1684,11 +1830,11 @@
       <c r="J25" s="6"/>
     </row>
     <row r="26" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A26" s="51" t="s">
+      <c r="A26" s="78" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="54"/>
-      <c r="C26" s="52" t="s">
+      <c r="B26" s="81"/>
+      <c r="C26" s="79" t="s">
         <v>35</v>
       </c>
       <c r="D26" s="8" t="s">
@@ -1714,9 +1860,9 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A27" s="51"/>
-      <c r="B27" s="54"/>
-      <c r="C27" s="53"/>
+      <c r="A27" s="78"/>
+      <c r="B27" s="81"/>
+      <c r="C27" s="80"/>
       <c r="D27" s="5" t="s">
         <v>24</v>
       </c>
@@ -1740,9 +1886,9 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A28" s="51"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="53"/>
+      <c r="A28" s="78"/>
+      <c r="B28" s="81"/>
+      <c r="C28" s="80"/>
       <c r="D28" s="5" t="s">
         <v>25</v>
       </c>
@@ -1767,7 +1913,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
-      <c r="B29" s="54"/>
+      <c r="B29" s="81"/>
       <c r="C29" s="7"/>
       <c r="E29" s="4"/>
       <c r="F29" s="6"/>
@@ -1777,11 +1923,11 @@
       <c r="J29" s="6"/>
     </row>
     <row r="30" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A30" s="51" t="s">
+      <c r="A30" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="B30" s="54"/>
-      <c r="C30" s="52" t="s">
+      <c r="B30" s="81"/>
+      <c r="C30" s="79" t="s">
         <v>36</v>
       </c>
       <c r="D30" s="8" t="s">
@@ -1807,9 +1953,9 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A31" s="51"/>
-      <c r="B31" s="54"/>
-      <c r="C31" s="53"/>
+      <c r="A31" s="78"/>
+      <c r="B31" s="81"/>
+      <c r="C31" s="80"/>
       <c r="D31" s="5" t="s">
         <v>24</v>
       </c>
@@ -1833,9 +1979,9 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A32" s="51"/>
-      <c r="B32" s="54"/>
-      <c r="C32" s="53"/>
+      <c r="A32" s="78"/>
+      <c r="B32" s="81"/>
+      <c r="C32" s="80"/>
       <c r="D32" s="8" t="s">
         <v>25</v>
       </c>
@@ -1870,13 +2016,13 @@
       <c r="J33" s="6"/>
     </row>
     <row r="34" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A34" s="51" t="s">
+      <c r="A34" s="78" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="51" t="s">
+      <c r="B34" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="52" t="s">
+      <c r="C34" s="79" t="s">
         <v>29</v>
       </c>
       <c r="D34" s="5" t="s">
@@ -1902,9 +2048,9 @@
       </c>
     </row>
     <row r="35" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A35" s="51"/>
-      <c r="B35" s="51"/>
-      <c r="C35" s="53"/>
+      <c r="A35" s="78"/>
+      <c r="B35" s="78"/>
+      <c r="C35" s="80"/>
       <c r="D35" s="5" t="s">
         <v>24</v>
       </c>
@@ -1928,9 +2074,9 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A36" s="51"/>
-      <c r="B36" s="51"/>
-      <c r="C36" s="53"/>
+      <c r="A36" s="78"/>
+      <c r="B36" s="78"/>
+      <c r="C36" s="80"/>
       <c r="D36" s="5" t="s">
         <v>25</v>
       </c>
@@ -1955,7 +2101,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
-      <c r="B37" s="51"/>
+      <c r="B37" s="78"/>
       <c r="C37" s="7"/>
       <c r="E37" s="4"/>
       <c r="F37" s="6"/>
@@ -1965,11 +2111,11 @@
       <c r="J37" s="6"/>
     </row>
     <row r="38" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A38" s="51" t="s">
+      <c r="A38" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="B38" s="51"/>
-      <c r="C38" s="52" t="s">
+      <c r="B38" s="78"/>
+      <c r="C38" s="79" t="s">
         <v>30</v>
       </c>
       <c r="D38" s="5" t="s">
@@ -1995,9 +2141,9 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A39" s="51"/>
-      <c r="B39" s="51"/>
-      <c r="C39" s="53"/>
+      <c r="A39" s="78"/>
+      <c r="B39" s="78"/>
+      <c r="C39" s="80"/>
       <c r="D39" s="8" t="s">
         <v>24</v>
       </c>
@@ -2021,9 +2167,9 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A40" s="51"/>
-      <c r="B40" s="51"/>
-      <c r="C40" s="53"/>
+      <c r="A40" s="78"/>
+      <c r="B40" s="78"/>
+      <c r="C40" s="80"/>
       <c r="D40" s="5" t="s">
         <v>25</v>
       </c>
@@ -2048,7 +2194,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
-      <c r="B41" s="51"/>
+      <c r="B41" s="78"/>
       <c r="C41" s="7"/>
       <c r="E41" s="4"/>
       <c r="F41" s="6"/>
@@ -2058,11 +2204,11 @@
       <c r="J41" s="6"/>
     </row>
     <row r="42" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A42" s="51" t="s">
+      <c r="A42" s="78" t="s">
         <v>6</v>
       </c>
-      <c r="B42" s="51"/>
-      <c r="C42" s="52" t="s">
+      <c r="B42" s="78"/>
+      <c r="C42" s="79" t="s">
         <v>31</v>
       </c>
       <c r="D42" s="5" t="s">
@@ -2088,9 +2234,9 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A43" s="51"/>
-      <c r="B43" s="51"/>
-      <c r="C43" s="53"/>
+      <c r="A43" s="78"/>
+      <c r="B43" s="78"/>
+      <c r="C43" s="80"/>
       <c r="D43" s="5" t="s">
         <v>24</v>
       </c>
@@ -2114,9 +2260,9 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A44" s="51"/>
-      <c r="B44" s="51"/>
-      <c r="C44" s="53"/>
+      <c r="A44" s="78"/>
+      <c r="B44" s="78"/>
+      <c r="C44" s="80"/>
       <c r="D44" s="5" t="s">
         <v>25</v>
       </c>
@@ -2141,7 +2287,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
-      <c r="B45" s="51"/>
+      <c r="B45" s="78"/>
       <c r="C45" s="7"/>
       <c r="E45" s="4"/>
       <c r="F45" s="6"/>
@@ -2151,11 +2297,11 @@
       <c r="J45" s="6"/>
     </row>
     <row r="46" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A46" s="51" t="s">
+      <c r="A46" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="B46" s="51"/>
-      <c r="C46" s="52" t="s">
+      <c r="B46" s="78"/>
+      <c r="C46" s="79" t="s">
         <v>35</v>
       </c>
       <c r="D46" s="5" t="s">
@@ -2181,9 +2327,9 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A47" s="51"/>
-      <c r="B47" s="51"/>
-      <c r="C47" s="53"/>
+      <c r="A47" s="78"/>
+      <c r="B47" s="78"/>
+      <c r="C47" s="80"/>
       <c r="D47" s="5" t="s">
         <v>24</v>
       </c>
@@ -2207,9 +2353,9 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A48" s="51"/>
-      <c r="B48" s="51"/>
-      <c r="C48" s="53"/>
+      <c r="A48" s="78"/>
+      <c r="B48" s="78"/>
+      <c r="C48" s="80"/>
       <c r="D48" s="5" t="s">
         <v>25</v>
       </c>
@@ -2324,15 +2470,11 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.1640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" style="5" customWidth="1"/>
     <col min="3" max="3" width="43.33203125" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="29.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33.1640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="38.1640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" style="5" customWidth="1"/>
+    <col min="6" max="10" width="21.33203125" style="12" customWidth="1"/>
     <col min="11" max="16384" width="8.83203125" style="5"/>
   </cols>
   <sheetData>
@@ -2369,13 +2511,13 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="52" t="s">
+      <c r="C2" s="79" t="s">
         <v>29</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -2401,9 +2543,9 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A3" s="51"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="53"/>
+      <c r="A3" s="78"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="80"/>
       <c r="D3" s="5" t="s">
         <v>24</v>
       </c>
@@ -2427,9 +2569,9 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="51"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="53"/>
+      <c r="A4" s="78"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="80"/>
       <c r="D4" s="5" t="s">
         <v>25</v>
       </c>
@@ -2454,7 +2596,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
-      <c r="B5" s="54"/>
+      <c r="B5" s="81"/>
       <c r="C5" s="7"/>
       <c r="E5" s="4"/>
       <c r="F5" s="6"/>
@@ -2464,11 +2606,11 @@
       <c r="J5" s="6"/>
     </row>
     <row r="6" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="51" t="s">
+      <c r="A6" s="78" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="52" t="s">
+      <c r="B6" s="81"/>
+      <c r="C6" s="79" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="5" t="s">
@@ -2494,9 +2636,9 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="51"/>
-      <c r="B7" s="54"/>
-      <c r="C7" s="53"/>
+      <c r="A7" s="78"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="80"/>
       <c r="D7" s="5" t="s">
         <v>24</v>
       </c>
@@ -2520,9 +2662,9 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A8" s="51"/>
-      <c r="B8" s="54"/>
-      <c r="C8" s="53"/>
+      <c r="A8" s="78"/>
+      <c r="B8" s="81"/>
+      <c r="C8" s="80"/>
       <c r="D8" s="8" t="s">
         <v>25</v>
       </c>
@@ -2547,7 +2689,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
-      <c r="B9" s="54"/>
+      <c r="B9" s="81"/>
       <c r="C9" s="7"/>
       <c r="E9" s="4"/>
       <c r="F9" s="6"/>
@@ -2557,11 +2699,11 @@
       <c r="J9" s="6"/>
     </row>
     <row r="10" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="51" t="s">
+      <c r="A10" s="78" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="54"/>
-      <c r="C10" s="52" t="s">
+      <c r="B10" s="81"/>
+      <c r="C10" s="79" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="5" t="s">
@@ -2587,9 +2729,9 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="51"/>
-      <c r="B11" s="54"/>
-      <c r="C11" s="53"/>
+      <c r="A11" s="78"/>
+      <c r="B11" s="81"/>
+      <c r="C11" s="80"/>
       <c r="D11" s="5" t="s">
         <v>24</v>
       </c>
@@ -2613,9 +2755,9 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="51"/>
-      <c r="B12" s="54"/>
-      <c r="C12" s="53"/>
+      <c r="A12" s="78"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="80"/>
       <c r="D12" s="8" t="s">
         <v>25</v>
       </c>
@@ -2640,7 +2782,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="4"/>
-      <c r="B13" s="54"/>
+      <c r="B13" s="81"/>
       <c r="C13" s="7"/>
       <c r="E13" s="4"/>
       <c r="F13" s="6"/>
@@ -2650,11 +2792,11 @@
       <c r="J13" s="6"/>
     </row>
     <row r="14" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A14" s="51" t="s">
+      <c r="A14" s="78" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="54"/>
-      <c r="C14" s="52" t="s">
+      <c r="B14" s="81"/>
+      <c r="C14" s="79" t="s">
         <v>32</v>
       </c>
       <c r="D14" s="5" t="s">
@@ -2680,9 +2822,9 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A15" s="51"/>
-      <c r="B15" s="54"/>
-      <c r="C15" s="53"/>
+      <c r="A15" s="78"/>
+      <c r="B15" s="81"/>
+      <c r="C15" s="80"/>
       <c r="D15" s="5" t="s">
         <v>24</v>
       </c>
@@ -2706,9 +2848,9 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A16" s="51"/>
-      <c r="B16" s="54"/>
-      <c r="C16" s="53"/>
+      <c r="A16" s="78"/>
+      <c r="B16" s="81"/>
+      <c r="C16" s="80"/>
       <c r="D16" s="8" t="s">
         <v>25</v>
       </c>
@@ -2733,7 +2875,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
-      <c r="B17" s="54"/>
+      <c r="B17" s="81"/>
       <c r="C17" s="7"/>
       <c r="E17" s="4"/>
       <c r="F17" s="6"/>
@@ -2743,11 +2885,11 @@
       <c r="J17" s="6"/>
     </row>
     <row r="18" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A18" s="51" t="s">
+      <c r="A18" s="78" t="s">
         <v>53</v>
       </c>
-      <c r="B18" s="54"/>
-      <c r="C18" s="52" t="s">
+      <c r="B18" s="81"/>
+      <c r="C18" s="79" t="s">
         <v>33</v>
       </c>
       <c r="D18" s="5" t="s">
@@ -2773,9 +2915,9 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A19" s="51"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="53"/>
+      <c r="A19" s="78"/>
+      <c r="B19" s="81"/>
+      <c r="C19" s="80"/>
       <c r="D19" s="5" t="s">
         <v>24</v>
       </c>
@@ -2799,9 +2941,9 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A20" s="51"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="53"/>
+      <c r="A20" s="78"/>
+      <c r="B20" s="81"/>
+      <c r="C20" s="80"/>
       <c r="D20" s="8" t="s">
         <v>25</v>
       </c>
@@ -2826,7 +2968,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
-      <c r="B21" s="54"/>
+      <c r="B21" s="81"/>
       <c r="C21" s="7"/>
       <c r="E21" s="4"/>
       <c r="F21" s="6"/>
@@ -2836,11 +2978,11 @@
       <c r="J21" s="6"/>
     </row>
     <row r="22" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A22" s="51" t="s">
+      <c r="A22" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="B22" s="54"/>
-      <c r="C22" s="52" t="s">
+      <c r="B22" s="81"/>
+      <c r="C22" s="79" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="5" t="s">
@@ -2866,9 +3008,9 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A23" s="51"/>
-      <c r="B23" s="54"/>
-      <c r="C23" s="53"/>
+      <c r="A23" s="78"/>
+      <c r="B23" s="81"/>
+      <c r="C23" s="80"/>
       <c r="D23" s="5" t="s">
         <v>24</v>
       </c>
@@ -2892,9 +3034,9 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A24" s="51"/>
-      <c r="B24" s="54"/>
-      <c r="C24" s="53"/>
+      <c r="A24" s="78"/>
+      <c r="B24" s="81"/>
+      <c r="C24" s="80"/>
       <c r="D24" s="5" t="s">
         <v>25</v>
       </c>
@@ -2919,7 +3061,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="4"/>
-      <c r="B25" s="54"/>
+      <c r="B25" s="81"/>
       <c r="C25" s="7"/>
       <c r="E25" s="4"/>
       <c r="F25" s="6"/>
@@ -2929,11 +3071,11 @@
       <c r="J25" s="6"/>
     </row>
     <row r="26" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A26" s="51" t="s">
+      <c r="A26" s="78" t="s">
         <v>44</v>
       </c>
-      <c r="B26" s="54"/>
-      <c r="C26" s="52" t="s">
+      <c r="B26" s="81"/>
+      <c r="C26" s="79" t="s">
         <v>35</v>
       </c>
       <c r="D26" s="8" t="s">
@@ -2959,9 +3101,9 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A27" s="51"/>
-      <c r="B27" s="54"/>
-      <c r="C27" s="53"/>
+      <c r="A27" s="78"/>
+      <c r="B27" s="81"/>
+      <c r="C27" s="80"/>
       <c r="D27" s="5" t="s">
         <v>24</v>
       </c>
@@ -2985,9 +3127,9 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A28" s="51"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="53"/>
+      <c r="A28" s="78"/>
+      <c r="B28" s="81"/>
+      <c r="C28" s="80"/>
       <c r="D28" s="8" t="s">
         <v>25</v>
       </c>
@@ -3012,7 +3154,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
-      <c r="B29" s="54"/>
+      <c r="B29" s="81"/>
       <c r="C29" s="7"/>
       <c r="E29" s="4"/>
       <c r="F29" s="6"/>
@@ -3022,11 +3164,11 @@
       <c r="J29" s="6"/>
     </row>
     <row r="30" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A30" s="51" t="s">
+      <c r="A30" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="B30" s="54"/>
-      <c r="C30" s="52" t="s">
+      <c r="B30" s="81"/>
+      <c r="C30" s="79" t="s">
         <v>36</v>
       </c>
       <c r="D30" s="5" t="s">
@@ -3052,9 +3194,9 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A31" s="51"/>
-      <c r="B31" s="54"/>
-      <c r="C31" s="53"/>
+      <c r="A31" s="78"/>
+      <c r="B31" s="81"/>
+      <c r="C31" s="80"/>
       <c r="D31" s="5" t="s">
         <v>24</v>
       </c>
@@ -3078,9 +3220,9 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A32" s="51"/>
-      <c r="B32" s="54"/>
-      <c r="C32" s="53"/>
+      <c r="A32" s="78"/>
+      <c r="B32" s="81"/>
+      <c r="C32" s="80"/>
       <c r="D32" s="5" t="s">
         <v>25</v>
       </c>
@@ -3115,13 +3257,13 @@
       <c r="J33" s="6"/>
     </row>
     <row r="34" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A34" s="51" t="s">
+      <c r="A34" s="78" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="51" t="s">
+      <c r="B34" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="52" t="s">
+      <c r="C34" s="79" t="s">
         <v>29</v>
       </c>
       <c r="D34" s="5" t="s">
@@ -3147,9 +3289,9 @@
       </c>
     </row>
     <row r="35" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A35" s="51"/>
-      <c r="B35" s="51"/>
-      <c r="C35" s="53"/>
+      <c r="A35" s="78"/>
+      <c r="B35" s="78"/>
+      <c r="C35" s="80"/>
       <c r="D35" s="5" t="s">
         <v>24</v>
       </c>
@@ -3173,9 +3315,9 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A36" s="51"/>
-      <c r="B36" s="51"/>
-      <c r="C36" s="53"/>
+      <c r="A36" s="78"/>
+      <c r="B36" s="78"/>
+      <c r="C36" s="80"/>
       <c r="D36" s="5" t="s">
         <v>25</v>
       </c>
@@ -3200,7 +3342,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
-      <c r="B37" s="51"/>
+      <c r="B37" s="78"/>
       <c r="C37" s="7"/>
       <c r="E37" s="4"/>
       <c r="F37" s="6"/>
@@ -3210,11 +3352,11 @@
       <c r="J37" s="6"/>
     </row>
     <row r="38" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A38" s="51" t="s">
+      <c r="A38" s="78" t="s">
         <v>47</v>
       </c>
-      <c r="B38" s="51"/>
-      <c r="C38" s="52" t="s">
+      <c r="B38" s="78"/>
+      <c r="C38" s="79" t="s">
         <v>30</v>
       </c>
       <c r="D38" s="5" t="s">
@@ -3240,9 +3382,9 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A39" s="51"/>
-      <c r="B39" s="51"/>
-      <c r="C39" s="53"/>
+      <c r="A39" s="78"/>
+      <c r="B39" s="78"/>
+      <c r="C39" s="80"/>
       <c r="D39" s="5" t="s">
         <v>24</v>
       </c>
@@ -3266,9 +3408,9 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A40" s="51"/>
-      <c r="B40" s="51"/>
-      <c r="C40" s="53"/>
+      <c r="A40" s="78"/>
+      <c r="B40" s="78"/>
+      <c r="C40" s="80"/>
       <c r="D40" s="5" t="s">
         <v>25</v>
       </c>
@@ -3293,7 +3435,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
-      <c r="B41" s="51"/>
+      <c r="B41" s="78"/>
       <c r="C41" s="7"/>
       <c r="E41" s="4"/>
       <c r="F41" s="6"/>
@@ -3303,11 +3445,11 @@
       <c r="J41" s="6"/>
     </row>
     <row r="42" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A42" s="51" t="s">
+      <c r="A42" s="78" t="s">
         <v>48</v>
       </c>
-      <c r="B42" s="51"/>
-      <c r="C42" s="52" t="s">
+      <c r="B42" s="78"/>
+      <c r="C42" s="79" t="s">
         <v>31</v>
       </c>
       <c r="D42" s="5" t="s">
@@ -3333,9 +3475,9 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A43" s="51"/>
-      <c r="B43" s="51"/>
-      <c r="C43" s="53"/>
+      <c r="A43" s="78"/>
+      <c r="B43" s="78"/>
+      <c r="C43" s="80"/>
       <c r="D43" s="5" t="s">
         <v>24</v>
       </c>
@@ -3359,9 +3501,9 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A44" s="51"/>
-      <c r="B44" s="51"/>
-      <c r="C44" s="53"/>
+      <c r="A44" s="78"/>
+      <c r="B44" s="78"/>
+      <c r="C44" s="80"/>
       <c r="D44" s="5" t="s">
         <v>25</v>
       </c>
@@ -3386,7 +3528,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
-      <c r="B45" s="51"/>
+      <c r="B45" s="78"/>
       <c r="C45" s="7"/>
       <c r="E45" s="4"/>
       <c r="F45" s="6"/>
@@ -3396,11 +3538,11 @@
       <c r="J45" s="6"/>
     </row>
     <row r="46" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A46" s="51" t="s">
+      <c r="A46" s="78" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="51"/>
-      <c r="C46" s="52" t="s">
+      <c r="B46" s="78"/>
+      <c r="C46" s="79" t="s">
         <v>35</v>
       </c>
       <c r="D46" s="8" t="s">
@@ -3426,9 +3568,9 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A47" s="51"/>
-      <c r="B47" s="51"/>
-      <c r="C47" s="53"/>
+      <c r="A47" s="78"/>
+      <c r="B47" s="78"/>
+      <c r="C47" s="80"/>
       <c r="D47" s="8" t="s">
         <v>24</v>
       </c>
@@ -3452,9 +3594,9 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A48" s="51"/>
-      <c r="B48" s="51"/>
-      <c r="C48" s="53"/>
+      <c r="A48" s="78"/>
+      <c r="B48" s="78"/>
+      <c r="C48" s="80"/>
       <c r="D48" s="5" t="s">
         <v>25</v>
       </c>
@@ -3568,28 +3710,21 @@
   <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="37.83203125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="22.1640625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="22.1640625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="37.83203125" style="5" customWidth="1"/>
     <col min="3" max="3" width="36.5" style="5" customWidth="1"/>
     <col min="4" max="4" width="21.83203125" style="5" customWidth="1"/>
     <col min="5" max="5" width="15" style="5" customWidth="1"/>
-    <col min="6" max="6" width="18.5" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.83203125" style="12" customWidth="1"/>
-    <col min="9" max="9" width="20.1640625" style="12" customWidth="1"/>
-    <col min="10" max="10" width="24.33203125" style="12" customWidth="1"/>
-    <col min="11" max="11" width="14.5" style="12" customWidth="1"/>
-    <col min="12" max="12" width="17.6640625" style="12" customWidth="1"/>
-    <col min="13" max="13" width="17" style="12" customWidth="1"/>
+    <col min="6" max="13" width="17.5" style="12" customWidth="1"/>
     <col min="14" max="16384" width="8.83203125" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="18" customFormat="1" ht="111" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>54</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>26</v>
       </c>
       <c r="C1" s="16" t="s">
         <v>27</v>
@@ -3615,24 +3750,24 @@
       <c r="J1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="39" t="s">
+      <c r="K1" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="L1" s="39" t="s">
+      <c r="L1" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="M1" s="39" t="s">
-        <v>89</v>
+      <c r="M1" s="29" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A2" s="51" t="s">
-        <v>76</v>
-      </c>
-      <c r="B2" s="54" t="s">
+      <c r="A2" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="52" t="s">
+      <c r="B2" s="78" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="79" t="s">
         <v>29</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -3670,9 +3805,9 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A3" s="51"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="53"/>
+      <c r="A3" s="81"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="80"/>
       <c r="D3" s="5" t="s">
         <v>24</v>
       </c>
@@ -3708,9 +3843,9 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="51"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="53"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="80"/>
       <c r="D4" s="5" t="s">
         <v>25</v>
       </c>
@@ -3746,8 +3881,8 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="4"/>
-      <c r="B5" s="54"/>
+      <c r="A5" s="81"/>
+      <c r="B5" s="4"/>
       <c r="C5" s="7"/>
       <c r="E5" s="4"/>
       <c r="F5" s="6"/>
@@ -3757,11 +3892,11 @@
       <c r="J5" s="6"/>
     </row>
     <row r="6" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="51" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="52" t="s">
+      <c r="A6" s="81"/>
+      <c r="B6" s="78" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="79" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="5" t="s">
@@ -3799,9 +3934,9 @@
       </c>
     </row>
     <row r="7" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="51"/>
-      <c r="B7" s="54"/>
-      <c r="C7" s="53"/>
+      <c r="A7" s="81"/>
+      <c r="B7" s="78"/>
+      <c r="C7" s="80"/>
       <c r="D7" s="5" t="s">
         <v>24</v>
       </c>
@@ -3837,9 +3972,9 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A8" s="51"/>
-      <c r="B8" s="54"/>
-      <c r="C8" s="53"/>
+      <c r="A8" s="81"/>
+      <c r="B8" s="78"/>
+      <c r="C8" s="80"/>
       <c r="D8" s="8" t="s">
         <v>25</v>
       </c>
@@ -3875,8 +4010,8 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="4"/>
-      <c r="B9" s="54"/>
+      <c r="A9" s="81"/>
+      <c r="B9" s="4"/>
       <c r="C9" s="7"/>
       <c r="E9" s="4"/>
       <c r="F9" s="6"/>
@@ -3886,11 +4021,11 @@
       <c r="J9" s="6"/>
     </row>
     <row r="10" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="51" t="s">
-        <v>78</v>
-      </c>
-      <c r="B10" s="54"/>
-      <c r="C10" s="52" t="s">
+      <c r="A10" s="81"/>
+      <c r="B10" s="78" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="79" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="5" t="s">
@@ -3928,9 +4063,9 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="51"/>
-      <c r="B11" s="54"/>
-      <c r="C11" s="53"/>
+      <c r="A11" s="81"/>
+      <c r="B11" s="78"/>
+      <c r="C11" s="80"/>
       <c r="D11" s="5" t="s">
         <v>24</v>
       </c>
@@ -3966,9 +4101,9 @@
       </c>
     </row>
     <row r="12" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="51"/>
-      <c r="B12" s="54"/>
-      <c r="C12" s="53"/>
+      <c r="A12" s="81"/>
+      <c r="B12" s="78"/>
+      <c r="C12" s="80"/>
       <c r="D12" s="5" t="s">
         <v>25</v>
       </c>
@@ -4004,8 +4139,8 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="4"/>
-      <c r="B13" s="54"/>
+      <c r="A13" s="81"/>
+      <c r="B13" s="4"/>
       <c r="C13" s="7"/>
       <c r="E13" s="4"/>
       <c r="F13" s="6"/>
@@ -4015,11 +4150,11 @@
       <c r="J13" s="6"/>
     </row>
     <row r="14" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A14" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="B14" s="54"/>
-      <c r="C14" s="52" t="s">
+      <c r="A14" s="81"/>
+      <c r="B14" s="78" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="79" t="s">
         <v>32</v>
       </c>
       <c r="D14" s="5" t="s">
@@ -4057,9 +4192,9 @@
       </c>
     </row>
     <row r="15" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A15" s="51"/>
-      <c r="B15" s="54"/>
-      <c r="C15" s="53"/>
+      <c r="A15" s="81"/>
+      <c r="B15" s="78"/>
+      <c r="C15" s="80"/>
       <c r="D15" s="5" t="s">
         <v>24</v>
       </c>
@@ -4095,9 +4230,9 @@
       </c>
     </row>
     <row r="16" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A16" s="51"/>
-      <c r="B16" s="54"/>
-      <c r="C16" s="53"/>
+      <c r="A16" s="81"/>
+      <c r="B16" s="78"/>
+      <c r="C16" s="80"/>
       <c r="D16" s="5" t="s">
         <v>25</v>
       </c>
@@ -4133,8 +4268,8 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="4"/>
-      <c r="B17" s="54"/>
+      <c r="A17" s="81"/>
+      <c r="B17" s="4"/>
       <c r="C17" s="7"/>
       <c r="E17" s="4"/>
       <c r="F17" s="6"/>
@@ -4144,11 +4279,11 @@
       <c r="J17" s="6"/>
     </row>
     <row r="18" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A18" s="51" t="s">
-        <v>80</v>
-      </c>
-      <c r="B18" s="54"/>
-      <c r="C18" s="52" t="s">
+      <c r="A18" s="81"/>
+      <c r="B18" s="78" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" s="79" t="s">
         <v>33</v>
       </c>
       <c r="D18" s="5" t="s">
@@ -4186,9 +4321,9 @@
       </c>
     </row>
     <row r="19" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A19" s="51"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="53"/>
+      <c r="A19" s="81"/>
+      <c r="B19" s="78"/>
+      <c r="C19" s="80"/>
       <c r="D19" s="5" t="s">
         <v>24</v>
       </c>
@@ -4224,9 +4359,9 @@
       </c>
     </row>
     <row r="20" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A20" s="51"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="53"/>
+      <c r="A20" s="81"/>
+      <c r="B20" s="78"/>
+      <c r="C20" s="80"/>
       <c r="D20" s="5" t="s">
         <v>25</v>
       </c>
@@ -4262,8 +4397,8 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="4"/>
-      <c r="B21" s="54"/>
+      <c r="A21" s="81"/>
+      <c r="B21" s="4"/>
       <c r="C21" s="7"/>
       <c r="E21" s="4"/>
       <c r="F21" s="6"/>
@@ -4273,11 +4408,11 @@
       <c r="J21" s="6"/>
     </row>
     <row r="22" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A22" s="51" t="s">
-        <v>81</v>
-      </c>
-      <c r="B22" s="54"/>
-      <c r="C22" s="52" t="s">
+      <c r="A22" s="81"/>
+      <c r="B22" s="78" t="s">
+        <v>80</v>
+      </c>
+      <c r="C22" s="79" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="5" t="s">
@@ -4315,9 +4450,9 @@
       </c>
     </row>
     <row r="23" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A23" s="51"/>
-      <c r="B23" s="54"/>
-      <c r="C23" s="53"/>
+      <c r="A23" s="81"/>
+      <c r="B23" s="78"/>
+      <c r="C23" s="80"/>
       <c r="D23" s="5" t="s">
         <v>24</v>
       </c>
@@ -4353,9 +4488,9 @@
       </c>
     </row>
     <row r="24" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A24" s="51"/>
-      <c r="B24" s="54"/>
-      <c r="C24" s="53"/>
+      <c r="A24" s="81"/>
+      <c r="B24" s="78"/>
+      <c r="C24" s="80"/>
       <c r="D24" s="5" t="s">
         <v>25</v>
       </c>
@@ -4391,8 +4526,8 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="4"/>
-      <c r="B25" s="54"/>
+      <c r="A25" s="81"/>
+      <c r="B25" s="4"/>
       <c r="C25" s="7"/>
       <c r="E25" s="4"/>
       <c r="F25" s="6"/>
@@ -4402,11 +4537,11 @@
       <c r="J25" s="6"/>
     </row>
     <row r="26" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A26" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="B26" s="54"/>
-      <c r="C26" s="52" t="s">
+      <c r="A26" s="81"/>
+      <c r="B26" s="78" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="79" t="s">
         <v>35</v>
       </c>
       <c r="D26" s="5" t="s">
@@ -4444,9 +4579,9 @@
       </c>
     </row>
     <row r="27" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A27" s="51"/>
-      <c r="B27" s="54"/>
-      <c r="C27" s="53"/>
+      <c r="A27" s="81"/>
+      <c r="B27" s="78"/>
+      <c r="C27" s="80"/>
       <c r="D27" s="5" t="s">
         <v>24</v>
       </c>
@@ -4482,9 +4617,9 @@
       </c>
     </row>
     <row r="28" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A28" s="51"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="53"/>
+      <c r="A28" s="81"/>
+      <c r="B28" s="78"/>
+      <c r="C28" s="80"/>
       <c r="D28" s="5" t="s">
         <v>25</v>
       </c>
@@ -4520,8 +4655,8 @@
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="4"/>
-      <c r="B29" s="54"/>
+      <c r="A29" s="81"/>
+      <c r="B29" s="4"/>
       <c r="C29" s="7"/>
       <c r="E29" s="4"/>
       <c r="F29" s="6"/>
@@ -4531,11 +4666,11 @@
       <c r="J29" s="6"/>
     </row>
     <row r="30" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A30" s="51" t="s">
-        <v>83</v>
-      </c>
-      <c r="B30" s="54"/>
-      <c r="C30" s="52" t="s">
+      <c r="A30" s="81"/>
+      <c r="B30" s="78" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="79" t="s">
         <v>36</v>
       </c>
       <c r="D30" s="8" t="s">
@@ -4573,9 +4708,9 @@
       </c>
     </row>
     <row r="31" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A31" s="51"/>
-      <c r="B31" s="54"/>
-      <c r="C31" s="53"/>
+      <c r="A31" s="81"/>
+      <c r="B31" s="78"/>
+      <c r="C31" s="80"/>
       <c r="D31" s="5" t="s">
         <v>24</v>
       </c>
@@ -4611,31 +4746,41 @@
       </c>
     </row>
     <row r="32" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A32" s="51"/>
-      <c r="B32" s="54"/>
-      <c r="C32" s="53"/>
+      <c r="A32" s="81"/>
+      <c r="B32" s="78"/>
+      <c r="C32" s="80"/>
       <c r="D32" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
+      <c r="F32" s="6">
+        <v>3.8138830000000002E-4</v>
+      </c>
+      <c r="G32" s="6">
+        <v>5.3394356000000002E-3</v>
+      </c>
+      <c r="H32" s="6">
+        <v>0.1487414188</v>
+      </c>
+      <c r="I32" s="6">
+        <v>0.53002011719999997</v>
+      </c>
+      <c r="J32" s="6">
+        <v>0.59878249289999996</v>
+      </c>
       <c r="K32" s="12">
         <f>F32*1/5 +G32*1/5+H32*1/5+I32*1/5+J32*1/5</f>
-        <v>0</v>
+        <v>0.25665297055999997</v>
       </c>
       <c r="L32" s="12">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>0.37376195584999999</v>
       </c>
       <c r="M32" s="12">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>0.17858031369999999</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.2">
@@ -4650,13 +4795,13 @@
       <c r="J33" s="6"/>
     </row>
     <row r="34" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A34" s="51" t="s">
-        <v>84</v>
-      </c>
-      <c r="B34" s="51" t="s">
+      <c r="A34" s="78" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="52" t="s">
+      <c r="B34" s="78" t="s">
+        <v>83</v>
+      </c>
+      <c r="C34" s="79" t="s">
         <v>29</v>
       </c>
       <c r="D34" s="5" t="s">
@@ -4694,9 +4839,9 @@
       </c>
     </row>
     <row r="35" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A35" s="51"/>
-      <c r="B35" s="51"/>
-      <c r="C35" s="53"/>
+      <c r="A35" s="78"/>
+      <c r="B35" s="78"/>
+      <c r="C35" s="80"/>
       <c r="D35" s="5" t="s">
         <v>24</v>
       </c>
@@ -4732,9 +4877,9 @@
       </c>
     </row>
     <row r="36" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A36" s="51"/>
-      <c r="B36" s="51"/>
-      <c r="C36" s="53"/>
+      <c r="A36" s="78"/>
+      <c r="B36" s="78"/>
+      <c r="C36" s="80"/>
       <c r="D36" s="5" t="s">
         <v>25</v>
       </c>
@@ -4770,8 +4915,8 @@
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A37" s="4"/>
-      <c r="B37" s="51"/>
+      <c r="A37" s="78"/>
+      <c r="B37" s="4"/>
       <c r="C37" s="7"/>
       <c r="E37" s="4"/>
       <c r="F37" s="6"/>
@@ -4781,11 +4926,11 @@
       <c r="J37" s="6"/>
     </row>
     <row r="38" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A38" s="51" t="s">
-        <v>85</v>
-      </c>
-      <c r="B38" s="51"/>
-      <c r="C38" s="52" t="s">
+      <c r="A38" s="78"/>
+      <c r="B38" s="78" t="s">
+        <v>84</v>
+      </c>
+      <c r="C38" s="79" t="s">
         <v>30</v>
       </c>
       <c r="D38" s="5" t="s">
@@ -4798,7 +4943,7 @@
         <v>5.7164629999999998E-4</v>
       </c>
       <c r="G38" s="12">
-        <v>3.8109756000000001E-3</v>
+        <v>4.7637195000000002E-3</v>
       </c>
       <c r="H38" s="12">
         <v>0.60518292679999997</v>
@@ -4811,7 +4956,7 @@
       </c>
       <c r="K38" s="12">
         <f t="shared" si="0"/>
-        <v>0.38440606706000002</v>
+        <v>0.38459661583999999</v>
       </c>
       <c r="L38" s="12">
         <f t="shared" si="13"/>
@@ -4819,13 +4964,13 @@
       </c>
       <c r="M38" s="12">
         <f>F38*1/3+G38*1/3+I38*1/3</f>
-        <v>0.21046626726666667</v>
+        <v>0.21078384856666668</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A39" s="51"/>
-      <c r="B39" s="51"/>
-      <c r="C39" s="53"/>
+      <c r="A39" s="78"/>
+      <c r="B39" s="78"/>
+      <c r="C39" s="80"/>
       <c r="D39" s="8" t="s">
         <v>24</v>
       </c>
@@ -4836,7 +4981,7 @@
         <v>4.9161585399999999E-2</v>
       </c>
       <c r="G39" s="11">
-        <v>1.2576219499999999E-2</v>
+        <v>1.31478658E-2</v>
       </c>
       <c r="H39" s="11">
         <v>0.71532012199999995</v>
@@ -4847,50 +4992,60 @@
       <c r="J39" s="11">
         <v>0.73983099360000004</v>
       </c>
-      <c r="K39" s="47">
+      <c r="K39" s="34">
         <f t="shared" si="0"/>
-        <v>0.47576659374000002</v>
+        <v>0.47588092300000001</v>
       </c>
       <c r="L39" s="12">
         <f t="shared" si="13"/>
         <v>0.72757555780000005</v>
       </c>
-      <c r="M39" s="47">
+      <c r="M39" s="34">
         <f t="shared" ref="M39:M40" si="16">F39*1/3+G39*1/3+I39*1/3</f>
-        <v>0.30789395103333334</v>
+        <v>0.30808449979999997</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A40" s="51"/>
-      <c r="B40" s="51"/>
-      <c r="C40" s="53"/>
+      <c r="A40" s="78"/>
+      <c r="B40" s="78"/>
+      <c r="C40" s="80"/>
       <c r="D40" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F40" s="6"/>
-      <c r="G40" s="6"/>
-      <c r="H40" s="6"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
+      <c r="F40" s="6">
+        <v>7.6219510000000005E-4</v>
+      </c>
+      <c r="G40" s="6">
+        <v>3.2393293000000001E-3</v>
+      </c>
+      <c r="H40" s="6">
+        <v>0.78048780490000003</v>
+      </c>
+      <c r="I40" s="6">
+        <v>0.47766805309999999</v>
+      </c>
+      <c r="J40" s="6">
+        <v>0.50378384080000005</v>
+      </c>
       <c r="K40" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.35318824463999998</v>
       </c>
       <c r="L40" s="12">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>0.64213582285000004</v>
       </c>
       <c r="M40" s="12">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>0.16055652583333335</v>
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A41" s="4"/>
-      <c r="B41" s="51"/>
+      <c r="A41" s="78"/>
+      <c r="B41" s="4"/>
       <c r="C41" s="7"/>
       <c r="E41" s="4"/>
       <c r="F41" s="6"/>
@@ -4900,11 +5055,11 @@
       <c r="J41" s="6"/>
     </row>
     <row r="42" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A42" s="51" t="s">
-        <v>86</v>
-      </c>
-      <c r="B42" s="51"/>
-      <c r="C42" s="52" t="s">
+      <c r="A42" s="78"/>
+      <c r="B42" s="78" t="s">
+        <v>85</v>
+      </c>
+      <c r="C42" s="79" t="s">
         <v>31</v>
       </c>
       <c r="D42" s="5" t="s">
@@ -4942,9 +5097,9 @@
       </c>
     </row>
     <row r="43" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A43" s="51"/>
-      <c r="B43" s="51"/>
-      <c r="C43" s="53"/>
+      <c r="A43" s="78"/>
+      <c r="B43" s="78"/>
+      <c r="C43" s="80"/>
       <c r="D43" s="5" t="s">
         <v>24</v>
       </c>
@@ -4980,9 +5135,9 @@
       </c>
     </row>
     <row r="44" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A44" s="51"/>
-      <c r="B44" s="51"/>
-      <c r="C44" s="53"/>
+      <c r="A44" s="78"/>
+      <c r="B44" s="78"/>
+      <c r="C44" s="80"/>
       <c r="D44" s="5" t="s">
         <v>25</v>
       </c>
@@ -5018,8 +5173,8 @@
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A45" s="4"/>
-      <c r="B45" s="51"/>
+      <c r="A45" s="78"/>
+      <c r="B45" s="4"/>
       <c r="C45" s="7"/>
       <c r="E45" s="4"/>
       <c r="F45" s="6"/>
@@ -5029,11 +5184,11 @@
       <c r="J45" s="6"/>
     </row>
     <row r="46" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A46" s="51" t="s">
-        <v>87</v>
-      </c>
-      <c r="B46" s="51"/>
-      <c r="C46" s="52" t="s">
+      <c r="A46" s="78"/>
+      <c r="B46" s="78" t="s">
+        <v>86</v>
+      </c>
+      <c r="C46" s="79" t="s">
         <v>35</v>
       </c>
       <c r="D46" s="8" t="s">
@@ -5061,7 +5216,7 @@
         <f t="shared" si="0"/>
         <v>0.45897955547999991</v>
       </c>
-      <c r="L46" s="47">
+      <c r="L46" s="34">
         <f t="shared" si="13"/>
         <v>0.79963813620000002</v>
       </c>
@@ -5071,9 +5226,9 @@
       </c>
     </row>
     <row r="47" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A47" s="51"/>
-      <c r="B47" s="51"/>
-      <c r="C47" s="53"/>
+      <c r="A47" s="78"/>
+      <c r="B47" s="78"/>
+      <c r="C47" s="80"/>
       <c r="D47" s="5" t="s">
         <v>24</v>
       </c>
@@ -5109,31 +5264,41 @@
       </c>
     </row>
     <row r="48" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A48" s="51"/>
-      <c r="B48" s="51"/>
-      <c r="C48" s="53"/>
+      <c r="A48" s="78"/>
+      <c r="B48" s="78"/>
+      <c r="C48" s="80"/>
       <c r="D48" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
+      <c r="F48" s="6">
+        <v>0</v>
+      </c>
+      <c r="G48" s="6">
+        <v>2.2865854E-3</v>
+      </c>
+      <c r="H48" s="6">
+        <v>1</v>
+      </c>
+      <c r="I48" s="6">
+        <v>0.448357271</v>
+      </c>
+      <c r="J48" s="6">
+        <v>0.4793704064</v>
+      </c>
       <c r="K48" s="12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.38600285256</v>
       </c>
       <c r="L48" s="12">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>0.73968520319999997</v>
       </c>
       <c r="M48" s="12">
         <f t="shared" si="18"/>
-        <v>0</v>
+        <v>0.1502146188</v>
       </c>
     </row>
     <row r="51" spans="4:13" x14ac:dyDescent="0.2">
@@ -5150,7 +5315,7 @@
       </c>
       <c r="H51" s="11">
         <f>MAX(H2:H48)</f>
-        <v>0.96948893970000005</v>
+        <v>1</v>
       </c>
       <c r="I51" s="11">
         <f>MAX(I2:I48)</f>
@@ -5160,17 +5325,17 @@
         <f>MAX(J2:J48)</f>
         <v>0.82907810169999996</v>
       </c>
-      <c r="K51" s="47">
+      <c r="K51" s="34">
         <f t="shared" ref="K51:L51" si="19">MAX(K2:K48)</f>
-        <v>0.47576659374000002</v>
-      </c>
-      <c r="L51" s="47">
+        <v>0.47588092300000001</v>
+      </c>
+      <c r="L51" s="34">
         <f t="shared" si="19"/>
         <v>0.79963813620000002</v>
       </c>
-      <c r="M51" s="47">
+      <c r="M51" s="34">
         <f t="shared" ref="M51" si="20">MAX(M2:M48)</f>
-        <v>0.30789395103333334</v>
+        <v>0.30808449979999997</v>
       </c>
     </row>
     <row r="52" spans="4:13" x14ac:dyDescent="0.2">
@@ -5182,40 +5347,40 @@
       </c>
       <c r="F52" s="11">
         <f>AVERAGE(F2:F48)</f>
-        <v>1.034151390909091E-2</v>
+        <v>9.5114872888888893E-3</v>
       </c>
       <c r="G52" s="11">
         <f>AVERAGE(G2:G48)</f>
-        <v>6.3608665151515141E-3</v>
+        <v>6.17495376388889E-3</v>
       </c>
       <c r="H52" s="11">
         <f>AVERAGE(H2:H48)</f>
-        <v>0.47846201980000003</v>
+        <v>0.49217988547500002</v>
       </c>
       <c r="I52" s="11">
         <f>AVERAGE(I2:I48)</f>
-        <v>0.59108728219393936</v>
+        <v>0.58227571538055545</v>
       </c>
       <c r="J52" s="11">
         <f>AVERAGE(J2:J48)</f>
-        <v>0.56077279742424224</v>
-      </c>
-      <c r="K52" s="47">
+        <v>0.55798441819722222</v>
+      </c>
+      <c r="K52" s="34">
         <f t="shared" ref="K52:L52" si="21">AVERAGE(K2:K48)</f>
-        <v>0.30195448797111113</v>
-      </c>
-      <c r="L52" s="47">
+        <v>0.32962529202111118</v>
+      </c>
+      <c r="L52" s="34">
         <f t="shared" si="21"/>
-        <v>0.47631595789444453</v>
-      </c>
-      <c r="M52" s="47">
+        <v>0.52508215183611118</v>
+      </c>
+      <c r="M52" s="34">
         <f t="shared" ref="M52" si="22">AVERAGE(M2:M48)</f>
-        <v>0.1857135080222222</v>
+        <v>0.1993207188111111</v>
       </c>
     </row>
     <row r="53" spans="4:13" x14ac:dyDescent="0.2">
       <c r="E53" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F53" s="11">
         <f t="shared" ref="F53:L53" si="23">MIN(F2:F48)</f>
@@ -5237,47 +5402,47 @@
         <f t="shared" si="23"/>
         <v>0.19462933560000001</v>
       </c>
-      <c r="K53" s="47">
+      <c r="K53" s="34">
         <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="L53" s="47">
+        <v>0.10583001444000001</v>
+      </c>
+      <c r="L53" s="34">
         <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="M53" s="47">
+        <v>0.11161672730000001</v>
+      </c>
+      <c r="M53" s="34">
         <f t="shared" ref="M53" si="24">MIN(M2:M48)</f>
-        <v>0</v>
+        <v>0.10197220586666668</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="26">
     <mergeCell ref="C30:C32"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="B34:B48"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="A34:A48"/>
     <mergeCell ref="C34:C36"/>
-    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="B38:B40"/>
     <mergeCell ref="C38:C40"/>
-    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="B42:B44"/>
     <mergeCell ref="C42:C44"/>
-    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="B46:B48"/>
     <mergeCell ref="C46:C48"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B32"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="A2:A32"/>
     <mergeCell ref="C2:C4"/>
-    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="B6:B8"/>
     <mergeCell ref="C6:C8"/>
-    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B10:B12"/>
     <mergeCell ref="C10:C12"/>
-    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="B14:B16"/>
     <mergeCell ref="C14:C16"/>
-    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="B18:B20"/>
     <mergeCell ref="C18:C20"/>
-    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="B22:B24"/>
     <mergeCell ref="C22:C24"/>
-    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="B26:B28"/>
     <mergeCell ref="C26:C28"/>
-    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="B30:B32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5292,69 +5457,62 @@
     <col min="2" max="2" width="42.83203125" style="5" customWidth="1"/>
     <col min="3" max="3" width="22" style="5" customWidth="1"/>
     <col min="4" max="4" width="12.5" style="5" customWidth="1"/>
-    <col min="5" max="5" width="19" style="12" customWidth="1"/>
-    <col min="6" max="6" width="20" style="12" customWidth="1"/>
-    <col min="7" max="7" width="20" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.1640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.1640625" style="12" customWidth="1"/>
-    <col min="10" max="10" width="18.33203125" style="12" customWidth="1"/>
-    <col min="11" max="11" width="20.5" style="12" customWidth="1"/>
-    <col min="12" max="12" width="23" style="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.83203125" style="12" customWidth="1"/>
-    <col min="14" max="14" width="24.1640625" style="12" customWidth="1"/>
+    <col min="5" max="10" width="18" style="12" customWidth="1"/>
+    <col min="11" max="11" width="18" style="48" customWidth="1"/>
+    <col min="12" max="14" width="18" style="12" customWidth="1"/>
     <col min="15" max="16384" width="8.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="18" customFormat="1" ht="67" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="B1" s="16" t="s">
+    <row r="1" spans="1:14" s="74" customFormat="1" ht="89" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="68" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" s="68" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="68" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="69" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="69" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="70" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="70" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="70" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1" s="69" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="71" t="s">
+        <v>104</v>
+      </c>
+      <c r="L1" s="72" t="s">
+        <v>102</v>
+      </c>
+      <c r="M1" s="72" t="s">
+        <v>72</v>
+      </c>
+      <c r="N1" s="73" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="20" x14ac:dyDescent="0.2">
+      <c r="A2" s="78" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="82" t="s">
         <v>97</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="J1" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="50" t="s">
-        <v>103</v>
-      </c>
-      <c r="L1" s="50" t="s">
-        <v>73</v>
-      </c>
-      <c r="M1" s="39" t="s">
-        <v>104</v>
-      </c>
-      <c r="N1" s="39" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A2" s="51" t="s">
-        <v>77</v>
-      </c>
-      <c r="B2" s="55" t="s">
-        <v>98</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>23</v>
@@ -5380,25 +5538,25 @@
       <c r="J2" s="6">
         <v>0.59952031800000005</v>
       </c>
-      <c r="K2" s="29">
+      <c r="K2" s="48">
+        <v>0.35202662579999999</v>
+      </c>
+      <c r="L2" s="26">
         <f>SUM(E2:J2)/6</f>
         <v>0.57734822815000009</v>
       </c>
-      <c r="L2" s="29">
+      <c r="M2" s="26">
         <f>STDEV(E2:J2)</f>
         <v>0.21291838776787708</v>
       </c>
-      <c r="M2" s="12">
+      <c r="N2" s="12">
         <f>SUMPRODUCT(G2:I2,$C$16:$E$16)/SUM($C$16:$E$16)</f>
         <v>0.28781759565756021</v>
       </c>
-      <c r="N2" s="12">
-        <v>0.35202662579999999</v>
-      </c>
     </row>
     <row r="3" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A3" s="51"/>
-      <c r="B3" s="51"/>
+      <c r="A3" s="78"/>
+      <c r="B3" s="78"/>
       <c r="C3" s="5" t="s">
         <v>24</v>
       </c>
@@ -5423,25 +5581,25 @@
       <c r="J3" s="6">
         <v>0.49760901740000002</v>
       </c>
-      <c r="K3" s="29">
-        <f t="shared" ref="K3:K12" si="0">SUM(E3:J3)/6</f>
+      <c r="K3" s="48">
+        <v>0.30946887969999998</v>
+      </c>
+      <c r="L3" s="26">
+        <f t="shared" ref="L3:L12" si="0">SUM(E3:J3)/6</f>
         <v>0.42772579766666663</v>
       </c>
-      <c r="L3" s="29">
+      <c r="M3" s="26">
         <f>STDEV(E3:J3)</f>
         <v>0.15259314934426299</v>
       </c>
-      <c r="M3" s="12">
+      <c r="N3" s="12">
         <f>SUMPRODUCT(G3:I3,$C$16:$E$16)/SUM($C$16:$E$16)</f>
         <v>0.39386213045140961</v>
       </c>
-      <c r="N3" s="12">
-        <v>0.30946887969999998</v>
-      </c>
     </row>
     <row r="4" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="51"/>
-      <c r="B4" s="51"/>
+      <c r="A4" s="78"/>
+      <c r="B4" s="78"/>
       <c r="C4" s="5" t="s">
         <v>25</v>
       </c>
@@ -5466,20 +5624,20 @@
       <c r="J4" s="6">
         <v>0.61895662200000001</v>
       </c>
-      <c r="K4" s="29">
+      <c r="K4" s="48">
+        <v>0.21538406309999999</v>
+      </c>
+      <c r="L4" s="26">
         <f t="shared" si="0"/>
         <v>0.76151258618333351</v>
       </c>
-      <c r="L4" s="29">
+      <c r="M4" s="26">
         <f>STDEV(E4:J4)</f>
         <v>0.39436876926890008</v>
       </c>
-      <c r="M4" s="12">
+      <c r="N4" s="12">
         <f>SUMPRODUCT(G4:I4,$C$16:$E$16)/SUM($C$16:$E$16)</f>
         <v>0.18338927612931832</v>
-      </c>
-      <c r="N4" s="12">
-        <v>0.21538406309999999</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -5492,15 +5650,15 @@
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
     </row>
     <row r="6" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="51" t="s">
-        <v>85</v>
-      </c>
-      <c r="B6" s="51" t="s">
-        <v>99</v>
+      <c r="A6" s="78" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="78" t="s">
+        <v>98</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>23</v>
@@ -5526,91 +5684,106 @@
       <c r="J6" s="6">
         <v>0.68544860669999996</v>
       </c>
-      <c r="K6" s="29">
+      <c r="K6" s="48">
+        <v>0.29145481309999999</v>
+      </c>
+      <c r="L6" s="26">
         <f t="shared" si="0"/>
         <v>0.56237986523333339</v>
       </c>
-      <c r="L6" s="29">
+      <c r="M6" s="26">
         <f>STDEV(E6:J6)</f>
         <v>0.27171777170155592</v>
       </c>
-      <c r="M6" s="12">
+      <c r="N6" s="12">
         <f>SUMPRODUCT(G6:I6,$C$19:$E$19)/SUM($C$19:$E$19)</f>
         <v>0.15905989481147539</v>
       </c>
-      <c r="N6" s="12">
-        <v>0.29145481309999999</v>
-      </c>
     </row>
     <row r="7" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="51"/>
-      <c r="B7" s="51"/>
-      <c r="C7" s="62" t="s">
+      <c r="A7" s="78"/>
+      <c r="B7" s="78"/>
+      <c r="C7" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="63" t="s">
+      <c r="D7" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="64">
+      <c r="E7" s="40">
         <v>0.71532012199999995</v>
       </c>
-      <c r="F7" s="64">
+      <c r="F7" s="40">
         <v>0.88452743899999997</v>
       </c>
-      <c r="G7" s="64">
+      <c r="G7" s="40">
         <v>0.82664822500000001</v>
       </c>
-      <c r="H7" s="64">
+      <c r="H7" s="40">
         <v>0.20572916669999999</v>
       </c>
-      <c r="I7" s="64">
+      <c r="I7" s="40">
         <v>7.0422535199999997E-2</v>
       </c>
-      <c r="J7" s="64">
+      <c r="J7" s="40">
         <v>0.73983099360000004</v>
       </c>
-      <c r="K7" s="65">
+      <c r="K7" s="49">
+        <v>0.60415152729999999</v>
+      </c>
+      <c r="L7" s="41">
         <f>SUM(E7:J7)/6</f>
         <v>0.57374641358333334</v>
       </c>
-      <c r="L7" s="65">
+      <c r="M7" s="41">
         <f>STDEV(E7:J7)</f>
         <v>0.34552655329669091</v>
       </c>
-      <c r="M7" s="66">
+      <c r="N7" s="42">
         <f>SUMPRODUCT(G7:I7,$C$19:$E$19)/SUM($C$19:$E$19)</f>
         <v>0.10787245163360654</v>
       </c>
-      <c r="N7" s="66">
-        <v>0.60415152729999999</v>
-      </c>
     </row>
     <row r="8" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A8" s="51"/>
-      <c r="B8" s="51"/>
+      <c r="A8" s="78"/>
+      <c r="B8" s="78"/>
       <c r="C8" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="29">
+      <c r="E8" s="6">
+        <v>0.78048780490000003</v>
+      </c>
+      <c r="F8" s="6">
+        <v>0.85670731710000003</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.94006454589999999</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0.1267605634</v>
+      </c>
+      <c r="J8" s="6">
+        <v>0.50378384080000005</v>
+      </c>
+      <c r="K8" s="48">
+        <v>0.322335392</v>
+      </c>
+      <c r="L8" s="26">
         <f>SUM(E8:J8)/6</f>
-        <v>0</v>
-      </c>
-      <c r="L8" s="29" t="e">
+        <v>0.53463401201666672</v>
+      </c>
+      <c r="M8" s="26">
         <f>STDEV(E8:J8)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M8" s="12">
+        <v>0.39539732651674198</v>
+      </c>
+      <c r="N8" s="12">
         <f>SUMPRODUCT(G8:I8,$C$19:$E$19)/SUM($C$19:$E$19)</f>
-        <v>0</v>
+        <v>0.12909648446311475</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -5623,15 +5796,15 @@
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
     </row>
     <row r="10" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="51" t="s">
-        <v>87</v>
-      </c>
-      <c r="B10" s="51" t="s">
-        <v>100</v>
+      <c r="A10" s="78" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" s="78" t="s">
+        <v>99</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>23</v>
@@ -5657,25 +5830,25 @@
       <c r="J10" s="6">
         <v>0.82907810169999996</v>
       </c>
-      <c r="K10" s="29">
+      <c r="K10" s="48">
+        <v>0.27578664860000002</v>
+      </c>
+      <c r="L10" s="26">
         <f t="shared" si="0"/>
         <v>0.59849109894999997</v>
       </c>
-      <c r="L10" s="29">
+      <c r="M10" s="26">
         <f>STDEV(E10:J10)</f>
         <v>0.42814938967063176</v>
       </c>
-      <c r="M10" s="12">
+      <c r="N10" s="12">
         <f>SUMPRODUCT(G10:I10, $C$22:$E$22)/SUM($C$22:$E$22)</f>
         <v>5.4554890957798155E-2</v>
       </c>
-      <c r="N10" s="12">
-        <v>0.27578664860000002</v>
-      </c>
     </row>
     <row r="11" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="51"/>
-      <c r="B11" s="51"/>
+      <c r="A11" s="78"/>
+      <c r="B11" s="78"/>
       <c r="C11" s="5" t="s">
         <v>24</v>
       </c>
@@ -5700,48 +5873,63 @@
       <c r="J11" s="6">
         <v>0.47833423320000001</v>
       </c>
-      <c r="K11" s="29">
+      <c r="K11" s="48">
+        <v>0.30020344319999998</v>
+      </c>
+      <c r="L11" s="26">
         <f t="shared" si="0"/>
         <v>0.41807895438333337</v>
       </c>
-      <c r="L11" s="29">
+      <c r="M11" s="26">
         <f>STDEV(E11:J11)</f>
         <v>0.12538220582562706</v>
       </c>
-      <c r="M11" s="12">
+      <c r="N11" s="12">
         <f>SUMPRODUCT(G11:I11, $C$22:$E$22)/SUM($C$22:$E$22)</f>
         <v>0.32424327420458715</v>
       </c>
-      <c r="N11" s="12">
-        <v>0.30020344319999998</v>
-      </c>
     </row>
     <row r="12" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="51"/>
-      <c r="B12" s="51"/>
+      <c r="A12" s="78"/>
+      <c r="B12" s="78"/>
       <c r="C12" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="29">
+      <c r="E12" s="6">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6">
+        <v>1</v>
+      </c>
+      <c r="G12" s="6">
+        <v>1</v>
+      </c>
+      <c r="H12" s="6">
+        <v>1</v>
+      </c>
+      <c r="I12" s="6">
+        <v>1</v>
+      </c>
+      <c r="J12" s="6">
+        <v>0.4793704064</v>
+      </c>
+      <c r="K12" s="48">
+        <v>0.29891920059999999</v>
+      </c>
+      <c r="L12" s="26">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L12" s="29" t="e">
+        <v>0.9132284010666667</v>
+      </c>
+      <c r="M12" s="26">
         <f>STDEV(E12:J12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M12" s="12">
+        <v>0.21254614155209578</v>
+      </c>
+      <c r="N12" s="12">
         <f>SUMPRODUCT(G12:I12, $C$22:$E$22)/SUM($C$22:$E$22)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
@@ -5754,82 +5942,90 @@
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="26"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="23"/>
-      <c r="B14" s="23"/>
-      <c r="D14" s="25"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
+      <c r="D14" s="24"/>
       <c r="E14" s="19"/>
       <c r="F14" s="19"/>
       <c r="G14" s="19"/>
       <c r="H14" s="19"/>
       <c r="I14" s="19"/>
       <c r="J14" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="K14" s="61">
-        <f>MAX(K2:K12)</f>
-        <v>0.76151258618333351</v>
-      </c>
-      <c r="L14" s="61" t="e">
-        <f t="shared" ref="L14:M14" si="1">MAX(L2:L12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M14" s="61">
-        <f t="shared" si="1"/>
-        <v>0.39386213045140961</v>
+        <v>100</v>
+      </c>
+      <c r="K14" s="50">
+        <f t="shared" ref="K14" si="1">MAX(K2:K12)</f>
+        <v>0.60415152729999999</v>
+      </c>
+      <c r="L14" s="37">
+        <f>MAX(L2:L12)</f>
+        <v>0.9132284010666667</v>
+      </c>
+      <c r="M14" s="37">
+        <f t="shared" ref="M14:N14" si="2">MAX(M2:M12)</f>
+        <v>0.42814938967063176</v>
+      </c>
+      <c r="N14" s="37">
+        <f t="shared" si="2"/>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="23"/>
-      <c r="B15" s="42" t="s">
+      <c r="A15" s="22"/>
+      <c r="B15" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="C15" s="40" t="s">
+      <c r="D15" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="D15" s="43" t="s">
+      <c r="E15" s="33" t="s">
         <v>92</v>
-      </c>
-      <c r="E15" s="44" t="s">
-        <v>93</v>
       </c>
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
       <c r="H15" s="19"/>
       <c r="I15" s="19"/>
       <c r="J15" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="K15" s="61">
-        <f>MIN(K2:K12)</f>
-        <v>0</v>
-      </c>
-      <c r="L15" s="61" t="e">
-        <f t="shared" ref="L15:M15" si="2">MIN(L2:L12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M15" s="61">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>87</v>
+      </c>
+      <c r="K15" s="50">
+        <f t="shared" ref="K15" si="3">MIN(K2:K12)</f>
+        <v>0.21538406309999999</v>
+      </c>
+      <c r="L15" s="37">
+        <f>MIN(L2:L12)</f>
+        <v>0.41807895438333337</v>
+      </c>
+      <c r="M15" s="37">
+        <f t="shared" ref="M15:N15" si="4">MIN(M2:M12)</f>
+        <v>0.12538220582562706</v>
+      </c>
+      <c r="N15" s="37">
+        <f t="shared" si="4"/>
+        <v>5.4554890957798155E-2</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="23"/>
-      <c r="B16" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="C16" s="48">
+      <c r="A16" s="22"/>
+      <c r="B16" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="35">
         <f>1/38</f>
         <v>2.6315789473684209E-2</v>
       </c>
-      <c r="D16" s="49">
+      <c r="D16" s="36">
         <f>1/6.8</f>
         <v>0.14705882352941177</v>
       </c>
-      <c r="E16" s="49">
+      <c r="E16" s="36">
         <f>1/1.2</f>
         <v>0.83333333333333337</v>
       </c>
@@ -5838,70 +6034,74 @@
       <c r="H16" s="19"/>
       <c r="I16" s="19"/>
       <c r="J16" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="K16" s="61">
-        <f>AVERAGE(K2:K12)</f>
-        <v>0.43547588268333332</v>
-      </c>
-      <c r="L16" s="61" t="e">
-        <f t="shared" ref="L16:M16" si="3">AVERAGE(L2:L12)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M16" s="61">
-        <f t="shared" si="3"/>
-        <v>0.16786661264952837</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="25"/>
-      <c r="B17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="19"/>
+        <v>101</v>
+      </c>
+      <c r="K16" s="50">
+        <f t="shared" ref="K16" si="5">AVERAGE(K2:K12)</f>
+        <v>0.32997006593333333</v>
+      </c>
+      <c r="L16" s="37">
+        <f>AVERAGE(L2:L12)</f>
+        <v>0.59634948413703703</v>
+      </c>
+      <c r="M16" s="37">
+        <f t="shared" ref="M16:N16" si="6">AVERAGE(M2:M12)</f>
+        <v>0.28206663277159816</v>
+      </c>
+      <c r="N16" s="37">
+        <f t="shared" si="6"/>
+        <v>0.29332177758987449</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17" s="24"/>
+      <c r="B17" s="24"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="52"/>
       <c r="F17" s="19"/>
       <c r="G17" s="19"/>
       <c r="H17" s="19"/>
       <c r="I17" s="19"/>
       <c r="J17" s="19"/>
-      <c r="K17" s="29"/>
-      <c r="L17" s="29"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="23"/>
-      <c r="B18" s="42" t="s">
-        <v>95</v>
-      </c>
-      <c r="C18" s="40" t="s">
+      <c r="L17" s="26"/>
+      <c r="M17" s="26"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A18" s="22"/>
+      <c r="B18" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="D18" s="43" t="s">
+      <c r="E18" s="53" t="s">
         <v>92</v>
-      </c>
-      <c r="E18" s="44" t="s">
-        <v>93</v>
       </c>
       <c r="F18" s="19"/>
       <c r="G18" s="19"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
       <c r="J18" s="19"/>
-      <c r="K18" s="29"/>
-      <c r="L18" s="29"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="23"/>
-      <c r="B19" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" s="48">
+      <c r="L18" s="26"/>
+      <c r="M18" s="26"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A19" s="22"/>
+      <c r="B19" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="35">
         <f>1/34</f>
         <v>2.9411764705882353E-2</v>
       </c>
-      <c r="D19" s="49">
+      <c r="D19" s="36">
         <f>1/6</f>
         <v>0.16666666666666666</v>
       </c>
-      <c r="E19" s="49">
+      <c r="E19" s="36">
         <f>1/1</f>
         <v>1</v>
       </c>
@@ -5910,58 +6110,58 @@
       <c r="H19" s="19"/>
       <c r="I19" s="19"/>
       <c r="J19" s="19"/>
-      <c r="K19" s="29"/>
-      <c r="L19" s="29"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="23"/>
-      <c r="B20" s="23"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="19"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="26"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A20" s="22"/>
+      <c r="B20" s="22"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="52"/>
       <c r="F20" s="19"/>
       <c r="G20" s="19"/>
       <c r="H20" s="19"/>
       <c r="I20" s="19"/>
       <c r="J20" s="19"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="25"/>
-      <c r="B21" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="C21" s="40" t="s">
+      <c r="L20" s="26"/>
+      <c r="M20" s="26"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A21" s="24"/>
+      <c r="B21" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="D21" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="D21" s="43" t="s">
+      <c r="E21" s="53" t="s">
         <v>92</v>
-      </c>
-      <c r="E21" s="44" t="s">
-        <v>93</v>
       </c>
       <c r="F21" s="19"/>
       <c r="G21" s="19"/>
       <c r="H21" s="19"/>
       <c r="I21" s="19"/>
       <c r="J21" s="19"/>
-      <c r="K21" s="29"/>
-      <c r="L21" s="29"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="23"/>
-      <c r="B22" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="C22" s="48">
+      <c r="L21" s="26"/>
+      <c r="M21" s="26"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A22" s="22"/>
+      <c r="B22" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C22" s="35">
         <f>1/21</f>
         <v>4.7619047619047616E-2</v>
       </c>
-      <c r="D22" s="49">
+      <c r="D22" s="36">
         <f>1/4</f>
         <v>0.25</v>
       </c>
-      <c r="E22" s="49">
+      <c r="E22" s="36">
         <f>1/1</f>
         <v>1</v>
       </c>
@@ -5970,272 +6170,258 @@
       <c r="H22" s="19"/>
       <c r="I22" s="19"/>
       <c r="J22" s="19"/>
-      <c r="K22" s="29"/>
-      <c r="L22" s="29"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="23"/>
-      <c r="B23" s="23"/>
-      <c r="D23" s="25"/>
+      <c r="L22" s="26"/>
+      <c r="M22" s="26"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="D23" s="24"/>
       <c r="E23" s="19"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
       <c r="H23" s="19"/>
       <c r="I23" s="19"/>
       <c r="J23" s="19"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="23"/>
-      <c r="B24" s="23"/>
-      <c r="D24" s="25"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A24" s="22"/>
+      <c r="B24" s="22"/>
+      <c r="D24" s="24"/>
       <c r="E24" s="19"/>
       <c r="F24" s="19"/>
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
       <c r="I24" s="19"/>
       <c r="J24" s="19"/>
-      <c r="K24" s="29"/>
-      <c r="L24" s="29"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A25" s="25"/>
-      <c r="B25" s="25"/>
-      <c r="D25" s="25"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="26"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A25" s="24"/>
+      <c r="B25" s="24"/>
+      <c r="D25" s="24"/>
       <c r="E25" s="19"/>
       <c r="F25" s="19"/>
       <c r="G25" s="19"/>
       <c r="H25" s="19"/>
       <c r="I25" s="19"/>
       <c r="J25" s="19"/>
-      <c r="K25" s="29"/>
-      <c r="L25" s="29"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="23"/>
-      <c r="B26" s="23"/>
-      <c r="D26" s="25"/>
+      <c r="L25" s="26"/>
+      <c r="M25" s="26"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22"/>
+      <c r="D26" s="24"/>
       <c r="E26" s="19"/>
       <c r="F26" s="19"/>
       <c r="G26" s="19"/>
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
       <c r="J26" s="19"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="23"/>
-      <c r="B27" s="23"/>
-      <c r="D27" s="25"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="D27" s="24"/>
       <c r="E27" s="19"/>
       <c r="F27" s="19"/>
       <c r="G27" s="19"/>
       <c r="H27" s="19"/>
       <c r="I27" s="19"/>
       <c r="J27" s="19"/>
-      <c r="K27" s="29"/>
-      <c r="L27" s="29"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A28" s="23"/>
-      <c r="B28" s="23"/>
-      <c r="D28" s="25"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22"/>
+      <c r="D28" s="24"/>
       <c r="E28" s="19"/>
       <c r="F28" s="19"/>
       <c r="G28" s="19"/>
       <c r="H28" s="19"/>
       <c r="I28" s="19"/>
       <c r="J28" s="19"/>
-      <c r="K28" s="29"/>
-      <c r="L28" s="29"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A29" s="25"/>
-      <c r="B29" s="25"/>
-      <c r="D29" s="25"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A29" s="24"/>
+      <c r="B29" s="24"/>
+      <c r="D29" s="24"/>
       <c r="E29" s="19"/>
       <c r="F29" s="19"/>
       <c r="G29" s="19"/>
       <c r="H29" s="19"/>
       <c r="I29" s="19"/>
       <c r="J29" s="19"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="29"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" s="23"/>
-      <c r="B30" s="23"/>
-      <c r="D30" s="25"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="26"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A30" s="22"/>
+      <c r="B30" s="22"/>
+      <c r="D30" s="24"/>
       <c r="E30" s="19"/>
       <c r="F30" s="19"/>
       <c r="G30" s="19"/>
       <c r="H30" s="19"/>
       <c r="I30" s="19"/>
       <c r="J30" s="19"/>
-      <c r="K30" s="29"/>
-      <c r="L30" s="29"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" s="23"/>
-      <c r="B31" s="23"/>
-      <c r="D31" s="25"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="26"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A31" s="22"/>
+      <c r="B31" s="22"/>
+      <c r="D31" s="24"/>
       <c r="E31" s="19"/>
       <c r="F31" s="19"/>
       <c r="G31" s="19"/>
       <c r="H31" s="19"/>
       <c r="I31" s="19"/>
       <c r="J31" s="19"/>
-      <c r="K31" s="29"/>
-      <c r="L31" s="29"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="23"/>
-      <c r="B32" s="23"/>
-      <c r="D32" s="25"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="26"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="D32" s="24"/>
       <c r="E32" s="19"/>
       <c r="F32" s="19"/>
       <c r="G32" s="19"/>
       <c r="H32" s="19"/>
       <c r="I32" s="19"/>
       <c r="J32" s="19"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="25"/>
-      <c r="B33" s="25"/>
-      <c r="D33" s="25"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="26"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A33" s="24"/>
+      <c r="B33" s="24"/>
+      <c r="D33" s="24"/>
       <c r="E33" s="19"/>
       <c r="F33" s="19"/>
       <c r="G33" s="19"/>
       <c r="H33" s="19"/>
       <c r="I33" s="19"/>
       <c r="J33" s="19"/>
-      <c r="K33" s="29"/>
-      <c r="L33" s="29"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" s="23"/>
-      <c r="B34" s="23"/>
-      <c r="D34" s="25"/>
+      <c r="L33" s="26"/>
+      <c r="M33" s="26"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
+      <c r="D34" s="24"/>
       <c r="E34" s="19"/>
       <c r="F34" s="19"/>
       <c r="G34" s="19"/>
       <c r="H34" s="19"/>
       <c r="I34" s="19"/>
       <c r="J34" s="19"/>
-      <c r="K34" s="29"/>
-      <c r="L34" s="29"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A35" s="23"/>
-      <c r="B35" s="23"/>
-      <c r="D35" s="25"/>
+      <c r="L34" s="26"/>
+      <c r="M34" s="26"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A35" s="22"/>
+      <c r="B35" s="22"/>
+      <c r="D35" s="24"/>
       <c r="E35" s="19"/>
       <c r="F35" s="19"/>
       <c r="G35" s="19"/>
       <c r="H35" s="19"/>
       <c r="I35" s="19"/>
       <c r="J35" s="19"/>
-      <c r="K35" s="29"/>
-      <c r="L35" s="29"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A36" s="23"/>
-      <c r="B36" s="23"/>
-      <c r="D36" s="25"/>
+      <c r="L35" s="26"/>
+      <c r="M35" s="26"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A36" s="22"/>
+      <c r="B36" s="22"/>
+      <c r="D36" s="24"/>
       <c r="E36" s="19"/>
       <c r="F36" s="19"/>
       <c r="G36" s="19"/>
       <c r="H36" s="19"/>
       <c r="I36" s="19"/>
       <c r="J36" s="19"/>
-      <c r="K36" s="29"/>
-      <c r="L36" s="29"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A37" s="25"/>
-      <c r="B37" s="25"/>
-      <c r="D37" s="25"/>
+      <c r="L36" s="26"/>
+      <c r="M36" s="26"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A37" s="24"/>
+      <c r="B37" s="24"/>
+      <c r="D37" s="24"/>
       <c r="E37" s="19"/>
       <c r="F37" s="19"/>
       <c r="G37" s="19"/>
       <c r="H37" s="19"/>
       <c r="I37" s="19"/>
       <c r="J37" s="19"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A38" s="23"/>
-      <c r="B38" s="23"/>
-      <c r="D38" s="25"/>
+      <c r="L37" s="26"/>
+      <c r="M37" s="26"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A38" s="22"/>
+      <c r="B38" s="22"/>
+      <c r="D38" s="24"/>
       <c r="E38" s="19"/>
       <c r="F38" s="19"/>
       <c r="G38" s="19"/>
       <c r="H38" s="19"/>
       <c r="I38" s="19"/>
       <c r="J38" s="19"/>
-      <c r="K38" s="29"/>
-      <c r="L38" s="29"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A39" s="23"/>
-      <c r="B39" s="23"/>
-      <c r="D39" s="25"/>
+      <c r="L38" s="26"/>
+      <c r="M38" s="26"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A39" s="22"/>
+      <c r="B39" s="22"/>
+      <c r="D39" s="24"/>
       <c r="E39" s="19"/>
       <c r="F39" s="19"/>
       <c r="G39" s="19"/>
       <c r="H39" s="19"/>
       <c r="I39" s="19"/>
       <c r="J39" s="19"/>
-      <c r="K39" s="29"/>
-      <c r="L39" s="29"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A40" s="23"/>
-      <c r="B40" s="23"/>
-      <c r="D40" s="25"/>
+      <c r="L39" s="26"/>
+      <c r="M39" s="26"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A40" s="22"/>
+      <c r="B40" s="22"/>
+      <c r="D40" s="24"/>
       <c r="E40" s="19"/>
       <c r="F40" s="19"/>
       <c r="G40" s="19"/>
       <c r="H40" s="19"/>
       <c r="I40" s="19"/>
       <c r="J40" s="19"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="K41" s="29"/>
-      <c r="L41" s="29"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="K42" s="29"/>
-      <c r="L42" s="29"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="D43" s="8"/>
-      <c r="E43" s="11"/>
-      <c r="F43" s="11"/>
-      <c r="G43" s="11"/>
-      <c r="H43" s="11"/>
-      <c r="I43" s="11"/>
-      <c r="J43" s="11"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="29"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="D44" s="8"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-      <c r="G44" s="11"/>
-      <c r="H44" s="11"/>
-      <c r="I44" s="11"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="29"/>
-      <c r="L44" s="29"/>
+      <c r="L40" s="26"/>
+      <c r="M40" s="26"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="L41" s="26"/>
+      <c r="M41" s="26"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="L42" s="26"/>
+      <c r="M42" s="26"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="L43" s="26"/>
+      <c r="M43" s="26"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="L44" s="26"/>
+      <c r="M44" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -6252,76 +6438,75 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB030C74-5D3D-4140-98C1-A6779936EBBB}">
-  <dimension ref="A1:N52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="42.83203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28" style="5" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="5" customWidth="1"/>
-    <col min="4" max="4" width="22" style="5" customWidth="1"/>
-    <col min="5" max="5" width="12.5" style="5" customWidth="1"/>
-    <col min="6" max="6" width="19" style="12" customWidth="1"/>
-    <col min="7" max="7" width="20" style="12" customWidth="1"/>
-    <col min="8" max="8" width="20" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.1640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.83203125" style="12" customWidth="1"/>
-    <col min="12" max="12" width="20.5" style="33" customWidth="1"/>
-    <col min="13" max="13" width="23" style="33" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.83203125" style="33" customWidth="1"/>
-    <col min="15" max="16384" width="8.83203125" style="5"/>
+    <col min="1" max="1" width="28.6640625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="31" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.1640625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="19.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" style="5" customWidth="1"/>
+    <col min="6" max="11" width="19.1640625" style="12" customWidth="1"/>
+    <col min="12" max="12" width="19.1640625" style="48" customWidth="1"/>
+    <col min="13" max="15" width="19.1640625" style="12" customWidth="1"/>
+    <col min="16" max="16384" width="8.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="18" customFormat="1" ht="67" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:15" s="67" customFormat="1" ht="89" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="61" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="61" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" s="61" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="H1" s="63" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="J1" s="63" t="s">
         <v>58</v>
       </c>
-      <c r="H1" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="J1" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="K1" s="17" t="s">
+      <c r="K1" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="M1" s="37" t="s">
+      <c r="L1" s="64" t="s">
+        <v>104</v>
+      </c>
+      <c r="M1" s="65" t="s">
+        <v>74</v>
+      </c>
+      <c r="N1" s="65" t="s">
+        <v>72</v>
+      </c>
+      <c r="O1" s="66" t="s">
         <v>73</v>
       </c>
-      <c r="N1" s="21" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="20" x14ac:dyDescent="0.25">
-      <c r="A2" s="55" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="56">
+    </row>
+    <row r="2" spans="1:15" ht="20" x14ac:dyDescent="0.2">
+      <c r="A2" s="82" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="82" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" s="83">
         <v>0</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -6330,87 +6515,132 @@
       <c r="E2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="28">
+      <c r="F2" s="6">
+        <v>0.60518292679999997</v>
+      </c>
+      <c r="G2" s="6">
+        <v>0.89824695119999998</v>
+      </c>
+      <c r="H2" s="6">
+        <v>0.65191332410000002</v>
+      </c>
+      <c r="I2" s="6">
+        <v>0.43489583329999998</v>
+      </c>
+      <c r="J2" s="6">
+        <v>9.8591549299999998E-2</v>
+      </c>
+      <c r="K2" s="6">
+        <v>0.68544860669999996</v>
+      </c>
+      <c r="L2" s="48">
+        <v>0.29145481309999999</v>
+      </c>
+      <c r="M2" s="26">
         <f>H2*1/3+I2*1/3+J2*1/3</f>
-        <v>0</v>
-      </c>
-      <c r="M2" s="28" t="e">
+        <v>0.39513356890000001</v>
+      </c>
+      <c r="N2" s="26">
         <f>STDEV(H2:J2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N2" s="33" t="e">
+        <v>0.27879566867083339</v>
+      </c>
+      <c r="O2" s="12">
         <f>SUMPRODUCT(H2:J2,$D$26:$F$26)/SUM($D$26:$F$26)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="20" x14ac:dyDescent="0.25">
-      <c r="A3" s="51"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="54"/>
+        <v>0.15905989481147539</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="20" x14ac:dyDescent="0.2">
+      <c r="A3" s="78"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="81"/>
       <c r="D3" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="28">
+      <c r="F3" s="19">
+        <v>0.71532012199999995</v>
+      </c>
+      <c r="G3" s="19">
+        <v>0.88452743899999997</v>
+      </c>
+      <c r="H3" s="19">
+        <v>0.82664822500000001</v>
+      </c>
+      <c r="I3" s="19">
+        <v>0.20572916669999999</v>
+      </c>
+      <c r="J3" s="19">
+        <v>7.0422535199999997E-2</v>
+      </c>
+      <c r="K3" s="19">
+        <v>0.73983099360000004</v>
+      </c>
+      <c r="L3" s="76">
+        <v>0.60415152729999999</v>
+      </c>
+      <c r="M3" s="26">
         <f>H3*1/3+I3*1/3+J3*1/3</f>
-        <v>0</v>
-      </c>
-      <c r="M3" s="28" t="e">
-        <f t="shared" ref="M3:M4" si="0">STDEV(H3:J3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N3" s="33" t="e">
+        <v>0.36759997563333335</v>
+      </c>
+      <c r="N3" s="26">
+        <f t="shared" ref="N3:N4" si="0">STDEV(H3:J3)</f>
+        <v>0.40326287030536323</v>
+      </c>
+      <c r="O3" s="12">
         <f>SUMPRODUCT(H3:J3,$D$26:$F$26)/SUM($D$26:$F$26)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="20" x14ac:dyDescent="0.25">
-      <c r="A4" s="51"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="54"/>
+        <v>0.10787245163360654</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="20" x14ac:dyDescent="0.2">
+      <c r="A4" s="78"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="81"/>
       <c r="D4" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="28">
+      <c r="F4" s="26">
+        <v>0.78048780490000003</v>
+      </c>
+      <c r="G4" s="26">
+        <v>0.85670731710000003</v>
+      </c>
+      <c r="H4" s="26">
+        <v>0.94006454589999999</v>
+      </c>
+      <c r="I4" s="26">
+        <v>0</v>
+      </c>
+      <c r="J4" s="26">
+        <v>0.1267605634</v>
+      </c>
+      <c r="K4" s="26">
+        <v>0.50378384080000005</v>
+      </c>
+      <c r="L4" s="48">
+        <v>0.322335392</v>
+      </c>
+      <c r="M4" s="26">
         <f>H4*1/3+I4*1/3+J4*1/3</f>
-        <v>0</v>
-      </c>
-      <c r="M4" s="28" t="e">
+        <v>0.35560836976666665</v>
+      </c>
+      <c r="N4" s="26">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N4" s="33" t="e">
+        <v>0.51010668146346583</v>
+      </c>
+      <c r="O4" s="12">
         <f>SUMPRODUCT(H4:J4,$D$26:$F$26)/SUM($D$26:$F$26)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="51"/>
-      <c r="B5" s="51"/>
-      <c r="C5" s="22"/>
+        <v>0.12909648446311475</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5" s="78"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="21"/>
       <c r="E5" s="4"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
@@ -6418,13 +6648,14 @@
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
-    </row>
-    <row r="6" spans="1:14" ht="20" x14ac:dyDescent="0.25">
-      <c r="A6" s="51"/>
-      <c r="B6" s="51"/>
-      <c r="C6" s="54">
+      <c r="L5" s="75"/>
+      <c r="M5" s="26"/>
+      <c r="N5" s="26"/>
+    </row>
+    <row r="6" spans="1:15" ht="20" x14ac:dyDescent="0.2">
+      <c r="A6" s="78"/>
+      <c r="B6" s="78"/>
+      <c r="C6" s="81">
         <v>10</v>
       </c>
       <c r="D6" s="5" t="s">
@@ -6433,87 +6664,132 @@
       <c r="E6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="28">
+      <c r="F6" s="19">
+        <v>0.67149390239999995</v>
+      </c>
+      <c r="G6" s="19">
+        <v>0.87309451220000001</v>
+      </c>
+      <c r="H6" s="19">
+        <v>0.75472567999999995</v>
+      </c>
+      <c r="I6" s="19">
+        <v>0.3046875</v>
+      </c>
+      <c r="J6" s="19">
+        <v>0.11267605629999999</v>
+      </c>
+      <c r="K6" s="19">
+        <v>0.73476295459999996</v>
+      </c>
+      <c r="L6" s="76">
+        <v>0.31354534789999999</v>
+      </c>
+      <c r="M6" s="26">
         <f>H6*1/3+I6*1/3+J6*1/3</f>
-        <v>0</v>
-      </c>
-      <c r="M6" s="28" t="e">
+        <v>0.3906964121</v>
+      </c>
+      <c r="N6" s="26">
         <f>STDEV(H6:J6)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N6" s="33" t="e">
+        <v>0.32955284787693312</v>
+      </c>
+      <c r="O6" s="12">
         <f>SUMPRODUCT(H6:J6,$D$26:$F$26)/SUM($D$26:$F$26)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="20" x14ac:dyDescent="0.25">
-      <c r="A7" s="51"/>
-      <c r="B7" s="51"/>
-      <c r="C7" s="54"/>
+        <v>0.15521985477540981</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="20" x14ac:dyDescent="0.2">
+      <c r="A7" s="78"/>
+      <c r="B7" s="78"/>
+      <c r="C7" s="81"/>
       <c r="D7" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
-      <c r="L7" s="28">
+      <c r="F7" s="26">
+        <v>0.70388719509999997</v>
+      </c>
+      <c r="G7" s="26">
+        <v>0.89176829270000002</v>
+      </c>
+      <c r="H7" s="26">
+        <v>0.8045182112</v>
+      </c>
+      <c r="I7" s="26">
+        <v>0.20833333330000001</v>
+      </c>
+      <c r="J7" s="26">
+        <v>0.30985915489999999</v>
+      </c>
+      <c r="K7" s="26">
+        <v>0.70778481859999998</v>
+      </c>
+      <c r="L7" s="48">
+        <v>0.60222457630000004</v>
+      </c>
+      <c r="M7" s="26">
         <f>H7*1/3+I7*1/3+J7*1/3</f>
-        <v>0</v>
-      </c>
-      <c r="M7" s="28" t="e">
-        <f t="shared" ref="M7:M8" si="1">STDEV(H7:J7)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N7" s="33" t="e">
+        <v>0.44090356646666662</v>
+      </c>
+      <c r="N7" s="26">
+        <f t="shared" ref="N7:N8" si="1">STDEV(H7:J7)</f>
+        <v>0.31896485779988359</v>
+      </c>
+      <c r="O7" s="12">
         <f>SUMPRODUCT(H7:J7,$D$26:$F$26)/SUM($D$26:$F$26)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="20" x14ac:dyDescent="0.25">
-      <c r="A8" s="51"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="54"/>
+        <v>0.30787586147131152</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="20" x14ac:dyDescent="0.2">
+      <c r="A8" s="78"/>
+      <c r="B8" s="78"/>
+      <c r="C8" s="81"/>
       <c r="D8" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
-      <c r="L8" s="28">
+      <c r="F8" s="6">
+        <v>0.23246951220000001</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0.46112804880000002</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0.1853388658</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0.49479166670000002</v>
+      </c>
+      <c r="J8" s="6">
+        <v>0.2535211268</v>
+      </c>
+      <c r="K8" s="6">
+        <v>0.46718656149999999</v>
+      </c>
+      <c r="L8" s="75">
+        <v>0.27905481360000001</v>
+      </c>
+      <c r="M8" s="26">
         <f>H8*1/3+I8*1/3+J8*1/3</f>
-        <v>0</v>
-      </c>
-      <c r="M8" s="28" t="e">
+        <v>0.31121721976666666</v>
+      </c>
+      <c r="N8" s="26">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N8" s="33" t="e">
+        <v>0.1625942445289115</v>
+      </c>
+      <c r="O8" s="12">
         <f>SUMPRODUCT(H8:J8,$D$26:$F$26)/SUM($D$26:$F$26)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="51"/>
-      <c r="B9" s="51"/>
-      <c r="C9" s="22"/>
+        <v>0.28546417922049183</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A9" s="78"/>
+      <c r="B9" s="78"/>
+      <c r="C9" s="21"/>
       <c r="E9" s="4"/>
       <c r="F9" s="6"/>
       <c r="G9" s="6"/>
@@ -6521,13 +6797,14 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
-      <c r="L9" s="28"/>
-      <c r="M9" s="28"/>
-    </row>
-    <row r="10" spans="1:14" ht="20" x14ac:dyDescent="0.25">
-      <c r="A10" s="51"/>
-      <c r="B10" s="51"/>
-      <c r="C10" s="54">
+      <c r="L9" s="75"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
+    </row>
+    <row r="10" spans="1:15" ht="20" x14ac:dyDescent="0.2">
+      <c r="A10" s="78"/>
+      <c r="B10" s="78"/>
+      <c r="C10" s="81">
         <v>20</v>
       </c>
       <c r="D10" s="5" t="s">
@@ -6536,87 +6813,132 @@
       <c r="E10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
-      <c r="L10" s="28">
+      <c r="F10" s="77">
+        <v>0.59908536590000006</v>
+      </c>
+      <c r="G10" s="26">
+        <v>0.91692073169999999</v>
+      </c>
+      <c r="H10" s="26">
+        <v>0.65836791149999996</v>
+      </c>
+      <c r="I10" s="26">
+        <v>0.3671875</v>
+      </c>
+      <c r="J10" s="26">
+        <v>4.2253521099999997E-2</v>
+      </c>
+      <c r="K10" s="26">
+        <v>0.68091049619999999</v>
+      </c>
+      <c r="L10" s="48">
+        <v>0.26234870690000001</v>
+      </c>
+      <c r="M10" s="26">
         <f>H10*1/3+I10*1/3+J10*1/3</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="28" t="e">
-        <f t="shared" ref="M10:M20" si="2">STDEV(H10:J10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N10" s="33" t="e">
+        <v>0.35593631086666666</v>
+      </c>
+      <c r="N10" s="26">
+        <f t="shared" ref="N10:N20" si="2">STDEV(H10:J10)</f>
+        <v>0.30821125459200288</v>
+      </c>
+      <c r="O10" s="12">
         <f>SUMPRODUCT(H10:J10,$D$26:$F$26)/SUM($D$26:$F$26)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="20" x14ac:dyDescent="0.25">
-      <c r="A11" s="51"/>
-      <c r="B11" s="51"/>
-      <c r="C11" s="54"/>
+        <v>0.10268156054672131</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="20" x14ac:dyDescent="0.2">
+      <c r="A11" s="78"/>
+      <c r="B11" s="78"/>
+      <c r="C11" s="81"/>
       <c r="D11" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
-      <c r="L11" s="28">
+      <c r="F11" s="6">
+        <v>0.7118902439</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0.87881097559999999</v>
+      </c>
+      <c r="H11" s="6">
+        <v>0.81834946980000001</v>
+      </c>
+      <c r="I11" s="6">
+        <v>0.21354166669999999</v>
+      </c>
+      <c r="J11" s="6">
+        <v>0.1549295775</v>
+      </c>
+      <c r="K11" s="6">
+        <v>0.77931160200000005</v>
+      </c>
+      <c r="L11" s="75">
+        <v>0.59928654589999997</v>
+      </c>
+      <c r="M11" s="26">
         <f>H11*1/3+I11*1/3+J11*1/3</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="28" t="e">
+        <v>0.39560690466666665</v>
+      </c>
+      <c r="N11" s="26">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N11" s="33" t="e">
+        <v>0.36727687312398277</v>
+      </c>
+      <c r="O11" s="12">
         <f>SUMPRODUCT(H11:J11,$D$26:$F$26)/SUM($D$26:$F$26)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="20" x14ac:dyDescent="0.25">
-      <c r="A12" s="51"/>
-      <c r="B12" s="51"/>
-      <c r="C12" s="54"/>
+        <v>0.17941043974016394</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="20" x14ac:dyDescent="0.2">
+      <c r="A12" s="78"/>
+      <c r="B12" s="78"/>
+      <c r="C12" s="81"/>
       <c r="D12" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="28">
+      <c r="F12" s="19">
+        <v>0.42111280490000003</v>
+      </c>
+      <c r="G12" s="19">
+        <v>0.58079268289999997</v>
+      </c>
+      <c r="H12" s="19">
+        <v>0.42784693410000002</v>
+      </c>
+      <c r="I12" s="19">
+        <v>0.4296875</v>
+      </c>
+      <c r="J12" s="19">
+        <v>0.16901408449999999</v>
+      </c>
+      <c r="K12" s="19">
+        <v>0.49644469029999999</v>
+      </c>
+      <c r="L12" s="76">
+        <v>0.30310681719999999</v>
+      </c>
+      <c r="M12" s="26">
         <f>H12*1/3+I12*1/3+J12*1/3</f>
-        <v>0</v>
-      </c>
-      <c r="M12" s="28" t="e">
+        <v>0.34218283953333334</v>
+      </c>
+      <c r="N12" s="26">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N12" s="33" t="e">
+        <v>0.14997136463523317</v>
+      </c>
+      <c r="O12" s="12">
         <f>SUMPRODUCT(H12:J12,$D$26:$F$26)/SUM($D$26:$F$26)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="51"/>
-      <c r="B13" s="51"/>
-      <c r="C13" s="22"/>
+        <v>0.21170217148606557</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A13" s="78"/>
+      <c r="B13" s="78"/>
+      <c r="C13" s="21"/>
       <c r="E13" s="4"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
@@ -6624,13 +6946,14 @@
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
-      <c r="L13" s="28"/>
-      <c r="M13" s="28"/>
-    </row>
-    <row r="14" spans="1:14" ht="20" x14ac:dyDescent="0.25">
-      <c r="A14" s="51"/>
-      <c r="B14" s="51"/>
-      <c r="C14" s="54">
+      <c r="L13" s="75"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="26"/>
+    </row>
+    <row r="14" spans="1:15" ht="20" x14ac:dyDescent="0.2">
+      <c r="A14" s="78"/>
+      <c r="B14" s="78"/>
+      <c r="C14" s="81">
         <v>30</v>
       </c>
       <c r="D14" s="5" t="s">
@@ -6639,101 +6962,147 @@
       <c r="E14" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
-      <c r="L14" s="28">
+      <c r="F14" s="26">
+        <v>0.61775914629999995</v>
+      </c>
+      <c r="G14" s="26">
+        <v>0.82736280490000003</v>
+      </c>
+      <c r="H14" s="26">
+        <v>0.70032272939999995</v>
+      </c>
+      <c r="I14" s="26">
+        <v>0.234375</v>
+      </c>
+      <c r="J14" s="26">
+        <v>0.16901408449999999</v>
+      </c>
+      <c r="K14" s="26">
+        <v>0.71088839550000005</v>
+      </c>
+      <c r="L14" s="48">
+        <v>0.31843601970000002</v>
+      </c>
+      <c r="M14" s="26">
         <f>H14*1/3+I14*1/3+J14*1/3</f>
-        <v>0</v>
-      </c>
-      <c r="M14" s="28" t="e">
+        <v>0.36790393796666665</v>
+      </c>
+      <c r="N14" s="26">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N14" s="33" t="e">
+        <v>0.289732121091618</v>
+      </c>
+      <c r="O14" s="12">
         <f>SUMPRODUCT(H14:J14,$D$26:$F$26)/SUM($D$26:$F$26)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="20" x14ac:dyDescent="0.25">
-      <c r="A15" s="51"/>
-      <c r="B15" s="51"/>
-      <c r="C15" s="54"/>
+        <v>0.19118671973114754</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="20" x14ac:dyDescent="0.2">
+      <c r="A15" s="78"/>
+      <c r="B15" s="78"/>
+      <c r="C15" s="81"/>
       <c r="D15" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="28">
+      <c r="F15" s="26">
+        <v>0.70388719509999997</v>
+      </c>
+      <c r="G15" s="26">
+        <v>0.83803353660000002</v>
+      </c>
+      <c r="H15" s="26">
+        <v>0.83863531579999995</v>
+      </c>
+      <c r="I15" s="26">
+        <v>5.72916667E-2</v>
+      </c>
+      <c r="J15" s="26">
+        <v>8.4507042300000002E-2</v>
+      </c>
+      <c r="K15" s="26">
+        <v>0.7951218136</v>
+      </c>
+      <c r="L15" s="48">
+        <v>0.55517741580000002</v>
+      </c>
+      <c r="M15" s="26">
         <f>H15*1/3+I15*1/3+J15*1/3</f>
-        <v>0</v>
-      </c>
-      <c r="M15" s="28" t="e">
+        <v>0.32681134159999997</v>
+      </c>
+      <c r="N15" s="26">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N15" s="33" t="e">
+        <v>0.44346139019273595</v>
+      </c>
+      <c r="O15" s="12">
         <f>SUMPRODUCT(H15:J15,$D$26:$F$26)/SUM($D$26:$F$26)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="20" x14ac:dyDescent="0.25">
-      <c r="A16" s="51"/>
-      <c r="B16" s="51"/>
-      <c r="C16" s="54"/>
+        <v>9.9258873736885245E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="20" x14ac:dyDescent="0.2">
+      <c r="A16" s="78"/>
+      <c r="B16" s="78"/>
+      <c r="C16" s="81"/>
       <c r="D16" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6"/>
-      <c r="L16" s="28">
+      <c r="F16" s="26">
+        <v>0.144054878</v>
+      </c>
+      <c r="G16" s="26">
+        <v>0.17568597559999999</v>
+      </c>
+      <c r="H16" s="26">
+        <v>9.2208389999999996E-4</v>
+      </c>
+      <c r="I16" s="26">
+        <v>0.9765625</v>
+      </c>
+      <c r="J16" s="26">
+        <v>1.4084507E-2</v>
+      </c>
+      <c r="K16" s="26">
+        <v>0.36442804410000001</v>
+      </c>
+      <c r="L16" s="48">
+        <v>0.15361280429999999</v>
+      </c>
+      <c r="M16" s="26">
         <f>H16*1/3+I16*1/3+J16*1/3</f>
-        <v>0</v>
-      </c>
-      <c r="M16" s="28" t="e">
+        <v>0.33052303029999996</v>
+      </c>
+      <c r="N16" s="26">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N16" s="33" t="e">
+        <v>0.55952529849253352</v>
+      </c>
+      <c r="O16" s="12">
         <f>SUMPRODUCT(H16:J16,$D$26:$F$26)/SUM($D$26:$F$26)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="51"/>
-      <c r="B17" s="51"/>
-      <c r="C17" s="24"/>
-      <c r="E17" s="25"/>
+        <v>0.14787662676803279</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A17" s="78"/>
+      <c r="B17" s="78"/>
+      <c r="C17" s="23"/>
+      <c r="E17" s="24"/>
       <c r="F17" s="19"/>
       <c r="G17" s="19"/>
       <c r="H17" s="19"/>
       <c r="I17" s="19"/>
       <c r="J17" s="19"/>
       <c r="K17" s="19"/>
-      <c r="L17" s="28"/>
-      <c r="M17" s="28"/>
-    </row>
-    <row r="18" spans="1:14" ht="20" x14ac:dyDescent="0.25">
-      <c r="A18" s="51"/>
-      <c r="B18" s="51"/>
-      <c r="C18" s="54">
+      <c r="L17" s="76"/>
+      <c r="M17" s="26"/>
+      <c r="N17" s="26"/>
+    </row>
+    <row r="18" spans="1:15" ht="20" x14ac:dyDescent="0.2">
+      <c r="A18" s="78"/>
+      <c r="B18" s="78"/>
+      <c r="C18" s="81">
         <v>100</v>
       </c>
       <c r="D18" s="5" t="s">
@@ -6742,58 +7111,88 @@
       <c r="E18" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
-      <c r="K18" s="6"/>
-      <c r="L18" s="28">
+      <c r="F18" s="6">
+        <v>0.42835365850000001</v>
+      </c>
+      <c r="G18" s="6">
+        <v>0.76295731710000003</v>
+      </c>
+      <c r="H18" s="6">
+        <v>0.44306131859999998</v>
+      </c>
+      <c r="I18" s="6">
+        <v>0.39583333329999998</v>
+      </c>
+      <c r="J18" s="6">
+        <v>0.1549295775</v>
+      </c>
+      <c r="K18" s="6">
+        <v>0.56211542520000002</v>
+      </c>
+      <c r="L18" s="75">
+        <v>0.27215055560000001</v>
+      </c>
+      <c r="M18" s="26">
         <f>H18*1/3+I18*1/3+J18*1/3</f>
-        <v>0</v>
-      </c>
-      <c r="M18" s="28" t="e">
+        <v>0.33127474313333333</v>
+      </c>
+      <c r="N18" s="26">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N18" s="33" t="e">
+        <v>0.15453424775938834</v>
+      </c>
+      <c r="O18" s="12">
         <f>SUMPRODUCT(H18:J18,$D$26:$F$26)/SUM($D$26:$F$26)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" ht="20" x14ac:dyDescent="0.25">
-      <c r="A19" s="51"/>
-      <c r="B19" s="51"/>
-      <c r="C19" s="54"/>
+        <v>0.19558334038442624</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="20" x14ac:dyDescent="0.2">
+      <c r="A19" s="78"/>
+      <c r="B19" s="78"/>
+      <c r="C19" s="81"/>
       <c r="D19" s="5" t="s">
         <v>24</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="28">
+      <c r="F19" s="6">
+        <v>0.75800304880000002</v>
+      </c>
+      <c r="G19" s="6">
+        <v>0.80945121949999999</v>
+      </c>
+      <c r="H19" s="6">
+        <v>0.90871369290000004</v>
+      </c>
+      <c r="I19" s="6">
+        <v>4.6875E-2</v>
+      </c>
+      <c r="J19" s="6">
+        <v>0</v>
+      </c>
+      <c r="K19" s="6">
+        <v>0.70333462499999999</v>
+      </c>
+      <c r="L19" s="75">
+        <v>0.44629329410000002</v>
+      </c>
+      <c r="M19" s="26">
         <f>H19*1/3+I19*1/3+J19*1/3</f>
-        <v>0</v>
-      </c>
-      <c r="M19" s="28" t="e">
+        <v>0.31852956430000001</v>
+      </c>
+      <c r="N19" s="26">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N19" s="33" t="e">
+        <v>0.51165153732277202</v>
+      </c>
+      <c r="O19" s="12">
         <f>SUMPRODUCT(H19:J19,$D$26:$F$26)/SUM($D$26:$F$26)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" ht="20" x14ac:dyDescent="0.25">
-      <c r="A20" s="51"/>
-      <c r="B20" s="51"/>
-      <c r="C20" s="54"/>
+        <v>2.8877180972950819E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="20" x14ac:dyDescent="0.2">
+      <c r="A20" s="78"/>
+      <c r="B20" s="78"/>
+      <c r="C20" s="81"/>
       <c r="D20" s="5" t="s">
         <v>25</v>
       </c>
@@ -6806,452 +7205,521 @@
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
       <c r="K20" s="6"/>
-      <c r="L20" s="28">
+      <c r="L20" s="75"/>
+      <c r="M20" s="26">
         <f>H20*1/3+I20*1/3+J20*1/3</f>
         <v>0</v>
       </c>
-      <c r="M20" s="28" t="e">
+      <c r="N20" s="26" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N20" s="33" t="e">
+      <c r="O20" s="12">
         <f>SUMPRODUCT(H20:J20,$D$26:$F$26)/SUM($D$26:$F$26)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="25"/>
-      <c r="B21" s="25"/>
-      <c r="C21" s="24"/>
-      <c r="E21" s="25"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A21" s="24"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="23"/>
+      <c r="E21" s="24"/>
       <c r="F21" s="19"/>
       <c r="G21" s="19"/>
       <c r="H21" s="19"/>
       <c r="I21" s="19"/>
       <c r="J21" s="19"/>
       <c r="K21" s="19"/>
-      <c r="L21" s="28"/>
-      <c r="M21" s="28"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="23"/>
-      <c r="B22" s="23"/>
-      <c r="C22" s="24"/>
-      <c r="E22" s="25"/>
+      <c r="L21" s="76"/>
+      <c r="M21" s="26"/>
+      <c r="N21" s="26"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="23"/>
+      <c r="E22" s="24"/>
       <c r="F22" s="19"/>
       <c r="G22" s="19"/>
       <c r="H22" s="19"/>
       <c r="I22" s="19"/>
       <c r="J22" s="19"/>
       <c r="K22" s="19"/>
-      <c r="L22" s="28"/>
-      <c r="M22" s="28"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="23"/>
-      <c r="B23" s="23"/>
-      <c r="C23" s="24"/>
-      <c r="E23" s="25"/>
+      <c r="L22" s="76"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="26"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A23" s="22"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="23"/>
+      <c r="E23" s="24"/>
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
       <c r="H23" s="19"/>
       <c r="I23" s="19"/>
       <c r="J23" s="19"/>
       <c r="K23" s="19"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="28"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="23"/>
-      <c r="B24" s="23"/>
-      <c r="C24" s="24"/>
-      <c r="E24" s="25"/>
+      <c r="L23" s="76"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A24" s="22"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="23"/>
+      <c r="E24" s="24"/>
       <c r="F24" s="19"/>
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
       <c r="I24" s="19"/>
       <c r="J24" s="19"/>
       <c r="K24" s="19"/>
-      <c r="L24" s="28"/>
-      <c r="M24" s="28"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="25"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="42" t="s">
+      <c r="L24" s="76"/>
+      <c r="M24" s="26"/>
+      <c r="N24" s="26"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A25" s="24"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="D25" s="40" t="s">
+      <c r="E25" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="E25" s="43" t="s">
+      <c r="F25" s="33" t="s">
         <v>92</v>
-      </c>
-      <c r="F25" s="44" t="s">
-        <v>93</v>
       </c>
       <c r="G25" s="19"/>
       <c r="H25" s="19"/>
       <c r="I25" s="19"/>
       <c r="J25" s="19"/>
-      <c r="K25" s="19"/>
-      <c r="L25" s="28"/>
-      <c r="M25" s="28"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="23"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="D26" s="41"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="46"/>
+      <c r="K25" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="L25" s="50">
+        <f>MAX(L2:L23)</f>
+        <v>0.60415152729999999</v>
+      </c>
+      <c r="M25" s="51">
+        <f>MAX(M2:M23)</f>
+        <v>0.44090356646666662</v>
+      </c>
+      <c r="N25" s="51" t="e">
+        <f>MAX(N2:N23)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O25" s="51">
+        <f>MAX(O2:O23)</f>
+        <v>0.30787586147131152</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A26" s="22"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="D26" s="35">
+        <f>1/34</f>
+        <v>2.9411764705882353E-2</v>
+      </c>
+      <c r="E26" s="36">
+        <f>1/6</f>
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="F26" s="36">
+        <f>1/1</f>
+        <v>1</v>
+      </c>
       <c r="G26" s="19"/>
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
       <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="28"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="23"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="24"/>
-      <c r="E27" s="25"/>
+      <c r="K26" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="L26" s="50">
+        <f>MIN(L2:L20)</f>
+        <v>0.15361280429999999</v>
+      </c>
+      <c r="M26" s="51">
+        <f>MIN(M2:M20)</f>
+        <v>0</v>
+      </c>
+      <c r="N26" s="51" t="e">
+        <f>MIN(N2:N20)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O26" s="51">
+        <f>MIN(O2:O20)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="23"/>
+      <c r="E27" s="24"/>
       <c r="F27" s="19"/>
       <c r="G27" s="19"/>
       <c r="H27" s="19"/>
       <c r="I27" s="19"/>
       <c r="J27" s="19"/>
-      <c r="K27" s="19"/>
-      <c r="L27" s="28"/>
-      <c r="M27" s="28"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A28" s="23"/>
-      <c r="B28" s="23"/>
-      <c r="C28" s="24"/>
-      <c r="E28" s="25"/>
+      <c r="K27" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="L27" s="50">
+        <f>AVERAGE(L2:L23)</f>
+        <v>0.38022704497857146</v>
+      </c>
+      <c r="M27" s="51">
+        <f>AVERAGE(M2:M23)</f>
+        <v>0.33532851900000005</v>
+      </c>
+      <c r="N27" s="51" t="e">
+        <f>AVERAGE(N2:N23)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O27" s="51">
+        <f>AVERAGE(O2:O23)</f>
+        <v>0.15341104264945354</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="23"/>
+      <c r="E28" s="24"/>
       <c r="F28" s="19"/>
       <c r="G28" s="19"/>
       <c r="H28" s="19"/>
       <c r="I28" s="19"/>
       <c r="J28" s="19"/>
       <c r="K28" s="19"/>
-      <c r="L28" s="28"/>
-      <c r="M28" s="28"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A29" s="25"/>
-      <c r="B29" s="25"/>
-      <c r="C29" s="24"/>
-      <c r="E29" s="25"/>
+      <c r="L28" s="76"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="26"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A29" s="24"/>
+      <c r="B29" s="24"/>
+      <c r="C29" s="23"/>
+      <c r="E29" s="24"/>
       <c r="F29" s="19"/>
       <c r="G29" s="19"/>
       <c r="H29" s="19"/>
       <c r="I29" s="19"/>
       <c r="J29" s="19"/>
       <c r="K29" s="19"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="28"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A30" s="23"/>
-      <c r="B30" s="23"/>
-      <c r="C30" s="24"/>
-      <c r="E30" s="25"/>
+      <c r="L29" s="76"/>
+      <c r="M29" s="26"/>
+      <c r="N29" s="26"/>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A30" s="22"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="23"/>
+      <c r="E30" s="24"/>
       <c r="F30" s="19"/>
       <c r="G30" s="19"/>
       <c r="H30" s="19"/>
       <c r="I30" s="19"/>
       <c r="J30" s="19"/>
       <c r="K30" s="19"/>
-      <c r="L30" s="28"/>
-      <c r="M30" s="28"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A31" s="23"/>
-      <c r="B31" s="23"/>
-      <c r="C31" s="24"/>
-      <c r="E31" s="25"/>
+      <c r="L30" s="76"/>
+      <c r="M30" s="26"/>
+      <c r="N30" s="26"/>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A31" s="22"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="23"/>
+      <c r="E31" s="24"/>
       <c r="F31" s="19"/>
       <c r="G31" s="19"/>
       <c r="H31" s="19"/>
       <c r="I31" s="19"/>
       <c r="J31" s="19"/>
       <c r="K31" s="19"/>
-      <c r="L31" s="28"/>
-      <c r="M31" s="28"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A32" s="23"/>
-      <c r="B32" s="23"/>
-      <c r="C32" s="24"/>
-      <c r="E32" s="25"/>
+      <c r="L31" s="76"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="26"/>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="23"/>
+      <c r="E32" s="24"/>
       <c r="F32" s="19"/>
       <c r="G32" s="19"/>
       <c r="H32" s="19"/>
       <c r="I32" s="19"/>
       <c r="J32" s="19"/>
       <c r="K32" s="19"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" s="25"/>
-      <c r="B33" s="25"/>
-      <c r="C33" s="25"/>
-      <c r="E33" s="25"/>
+      <c r="L32" s="76"/>
+      <c r="M32" s="26"/>
+      <c r="N32" s="26"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A33" s="24"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="E33" s="24"/>
       <c r="F33" s="19"/>
       <c r="G33" s="19"/>
       <c r="H33" s="19"/>
       <c r="I33" s="19"/>
       <c r="J33" s="19"/>
       <c r="K33" s="19"/>
-      <c r="L33" s="28"/>
-      <c r="M33" s="28"/>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A34" s="23"/>
-      <c r="B34" s="23"/>
-      <c r="C34" s="23"/>
-      <c r="E34" s="25"/>
+      <c r="L33" s="76"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="26"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="E34" s="24"/>
       <c r="F34" s="19"/>
       <c r="G34" s="19"/>
       <c r="H34" s="19"/>
       <c r="I34" s="19"/>
       <c r="J34" s="19"/>
       <c r="K34" s="19"/>
-      <c r="L34" s="28"/>
-      <c r="M34" s="28"/>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" s="23"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="23"/>
-      <c r="E35" s="25"/>
+      <c r="L34" s="76"/>
+      <c r="M34" s="26"/>
+      <c r="N34" s="26"/>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A35" s="22"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="E35" s="24"/>
       <c r="F35" s="19"/>
       <c r="G35" s="19"/>
       <c r="H35" s="19"/>
       <c r="I35" s="19"/>
       <c r="J35" s="19"/>
       <c r="K35" s="19"/>
-      <c r="L35" s="28"/>
-      <c r="M35" s="28"/>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A36" s="23"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="23"/>
-      <c r="E36" s="25"/>
+      <c r="L35" s="76"/>
+      <c r="M35" s="26"/>
+      <c r="N35" s="26"/>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A36" s="22"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="E36" s="24"/>
       <c r="F36" s="19"/>
       <c r="G36" s="19"/>
       <c r="H36" s="19"/>
       <c r="I36" s="19"/>
       <c r="J36" s="19"/>
       <c r="K36" s="19"/>
-      <c r="L36" s="28"/>
-      <c r="M36" s="28"/>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A37" s="25"/>
-      <c r="B37" s="25"/>
-      <c r="C37" s="23"/>
-      <c r="E37" s="25"/>
+      <c r="L36" s="76"/>
+      <c r="M36" s="26"/>
+      <c r="N36" s="26"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A37" s="24"/>
+      <c r="B37" s="24"/>
+      <c r="C37" s="22"/>
+      <c r="E37" s="24"/>
       <c r="F37" s="19"/>
       <c r="G37" s="19"/>
       <c r="H37" s="19"/>
       <c r="I37" s="19"/>
       <c r="J37" s="19"/>
       <c r="K37" s="19"/>
-      <c r="L37" s="28"/>
-      <c r="M37" s="28"/>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A38" s="23"/>
-      <c r="B38" s="23"/>
-      <c r="C38" s="23"/>
-      <c r="E38" s="25"/>
+      <c r="L37" s="76"/>
+      <c r="M37" s="26"/>
+      <c r="N37" s="26"/>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A38" s="22"/>
+      <c r="B38" s="22"/>
+      <c r="C38" s="22"/>
+      <c r="E38" s="24"/>
       <c r="F38" s="19"/>
       <c r="G38" s="19"/>
       <c r="H38" s="19"/>
       <c r="I38" s="19"/>
       <c r="J38" s="19"/>
       <c r="K38" s="19"/>
-      <c r="L38" s="28"/>
-      <c r="M38" s="28"/>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" s="23"/>
-      <c r="B39" s="23"/>
-      <c r="C39" s="23"/>
-      <c r="E39" s="25"/>
+      <c r="L38" s="76"/>
+      <c r="M38" s="26"/>
+      <c r="N38" s="26"/>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A39" s="22"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="22"/>
+      <c r="E39" s="24"/>
       <c r="F39" s="19"/>
       <c r="G39" s="19"/>
       <c r="H39" s="19"/>
       <c r="I39" s="19"/>
       <c r="J39" s="19"/>
       <c r="K39" s="19"/>
-      <c r="L39" s="28"/>
-      <c r="M39" s="28"/>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="23"/>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23"/>
-      <c r="E40" s="25"/>
+      <c r="L39" s="76"/>
+      <c r="M39" s="26"/>
+      <c r="N39" s="26"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A40" s="22"/>
+      <c r="B40" s="22"/>
+      <c r="C40" s="22"/>
+      <c r="E40" s="24"/>
       <c r="F40" s="19"/>
       <c r="G40" s="19"/>
       <c r="H40" s="19"/>
       <c r="I40" s="19"/>
       <c r="J40" s="19"/>
       <c r="K40" s="19"/>
-      <c r="L40" s="28"/>
-      <c r="M40" s="28"/>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A41" s="25"/>
-      <c r="B41" s="25"/>
-      <c r="C41" s="23"/>
-      <c r="E41" s="25"/>
+      <c r="L40" s="76"/>
+      <c r="M40" s="26"/>
+      <c r="N40" s="26"/>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A41" s="24"/>
+      <c r="B41" s="24"/>
+      <c r="C41" s="22"/>
+      <c r="E41" s="24"/>
       <c r="F41" s="19"/>
       <c r="G41" s="19"/>
       <c r="H41" s="19"/>
       <c r="I41" s="19"/>
       <c r="J41" s="19"/>
       <c r="K41" s="19"/>
-      <c r="L41" s="28"/>
-      <c r="M41" s="28"/>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A42" s="23"/>
-      <c r="B42" s="23"/>
-      <c r="C42" s="23"/>
-      <c r="E42" s="25"/>
+      <c r="L41" s="76"/>
+      <c r="M41" s="26"/>
+      <c r="N41" s="26"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A42" s="22"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
+      <c r="E42" s="24"/>
       <c r="F42" s="19"/>
       <c r="G42" s="19"/>
       <c r="H42" s="19"/>
       <c r="I42" s="19"/>
       <c r="J42" s="19"/>
       <c r="K42" s="19"/>
-      <c r="L42" s="28"/>
-      <c r="M42" s="28"/>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A43" s="23"/>
-      <c r="B43" s="23"/>
-      <c r="C43" s="23"/>
-      <c r="E43" s="25"/>
+      <c r="L42" s="76"/>
+      <c r="M42" s="26"/>
+      <c r="N42" s="26"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A43" s="22"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="22"/>
+      <c r="E43" s="24"/>
       <c r="F43" s="19"/>
       <c r="G43" s="19"/>
       <c r="H43" s="19"/>
       <c r="I43" s="19"/>
       <c r="J43" s="19"/>
       <c r="K43" s="19"/>
-      <c r="L43" s="28"/>
-      <c r="M43" s="28"/>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A44" s="23"/>
-      <c r="B44" s="23"/>
-      <c r="C44" s="23"/>
-      <c r="E44" s="25"/>
+      <c r="L43" s="76"/>
+      <c r="M43" s="26"/>
+      <c r="N43" s="26"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A44" s="22"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="E44" s="24"/>
       <c r="F44" s="19"/>
       <c r="G44" s="19"/>
       <c r="H44" s="19"/>
       <c r="I44" s="19"/>
       <c r="J44" s="19"/>
       <c r="K44" s="19"/>
-      <c r="L44" s="28"/>
-      <c r="M44" s="28"/>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A45" s="25"/>
-      <c r="B45" s="25"/>
-      <c r="C45" s="23"/>
-      <c r="E45" s="25"/>
+      <c r="L44" s="76"/>
+      <c r="M44" s="26"/>
+      <c r="N44" s="26"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A45" s="24"/>
+      <c r="B45" s="24"/>
+      <c r="C45" s="22"/>
+      <c r="E45" s="24"/>
       <c r="F45" s="19"/>
       <c r="G45" s="19"/>
       <c r="H45" s="19"/>
       <c r="I45" s="19"/>
       <c r="J45" s="19"/>
       <c r="K45" s="19"/>
-      <c r="L45" s="28"/>
-      <c r="M45" s="28"/>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A46" s="23"/>
-      <c r="B46" s="23"/>
-      <c r="C46" s="23"/>
-      <c r="E46" s="25"/>
+      <c r="L45" s="76"/>
+      <c r="M45" s="26"/>
+      <c r="N45" s="26"/>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A46" s="22"/>
+      <c r="B46" s="22"/>
+      <c r="C46" s="22"/>
+      <c r="E46" s="24"/>
       <c r="F46" s="19"/>
       <c r="G46" s="19"/>
       <c r="H46" s="19"/>
       <c r="I46" s="19"/>
       <c r="J46" s="19"/>
       <c r="K46" s="19"/>
-      <c r="L46" s="28"/>
-      <c r="M46" s="28"/>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A47" s="23"/>
-      <c r="B47" s="23"/>
-      <c r="C47" s="23"/>
-      <c r="E47" s="25"/>
+      <c r="L46" s="76"/>
+      <c r="M46" s="26"/>
+      <c r="N46" s="26"/>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A47" s="22"/>
+      <c r="B47" s="22"/>
+      <c r="C47" s="22"/>
+      <c r="E47" s="24"/>
       <c r="F47" s="19"/>
       <c r="G47" s="19"/>
       <c r="H47" s="19"/>
       <c r="I47" s="19"/>
       <c r="J47" s="19"/>
       <c r="K47" s="19"/>
-      <c r="L47" s="28"/>
-      <c r="M47" s="28"/>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A48" s="23"/>
-      <c r="B48" s="23"/>
-      <c r="C48" s="23"/>
-      <c r="E48" s="25"/>
+      <c r="L47" s="76"/>
+      <c r="M47" s="26"/>
+      <c r="N47" s="26"/>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A48" s="22"/>
+      <c r="B48" s="22"/>
+      <c r="C48" s="22"/>
+      <c r="E48" s="24"/>
       <c r="F48" s="19"/>
       <c r="G48" s="19"/>
       <c r="H48" s="19"/>
       <c r="I48" s="19"/>
       <c r="J48" s="19"/>
       <c r="K48" s="19"/>
-      <c r="L48" s="28"/>
-      <c r="M48" s="28"/>
-    </row>
-    <row r="49" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="L49" s="28"/>
-      <c r="M49" s="28"/>
-    </row>
-    <row r="50" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="L50" s="28"/>
-      <c r="M50" s="28"/>
-    </row>
-    <row r="51" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E51" s="8"/>
-      <c r="F51" s="11"/>
-      <c r="G51" s="11"/>
-      <c r="H51" s="11"/>
-      <c r="I51" s="11"/>
-      <c r="J51" s="11"/>
-      <c r="K51" s="11"/>
-      <c r="L51" s="28"/>
-      <c r="M51" s="28"/>
-    </row>
-    <row r="52" spans="5:13" x14ac:dyDescent="0.25">
-      <c r="E52" s="8"/>
-      <c r="F52" s="11"/>
-      <c r="G52" s="11"/>
-      <c r="H52" s="11"/>
-      <c r="I52" s="11"/>
-      <c r="J52" s="11"/>
-      <c r="K52" s="11"/>
-      <c r="L52" s="28"/>
-      <c r="M52" s="28"/>
+      <c r="L48" s="76"/>
+      <c r="M48" s="26"/>
+      <c r="N48" s="26"/>
+    </row>
+    <row r="49" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M49" s="26"/>
+      <c r="N49" s="26"/>
+    </row>
+    <row r="50" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M50" s="26"/>
+      <c r="N50" s="26"/>
+    </row>
+    <row r="51" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M51" s="26"/>
+      <c r="N51" s="26"/>
+    </row>
+    <row r="52" spans="13:14" x14ac:dyDescent="0.2">
+      <c r="M52" s="26"/>
+      <c r="N52" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -7269,892 +7737,1043 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C64FDBF-6E58-8148-821B-47274FA4A935}">
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="32.1640625" style="33" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" style="33" customWidth="1"/>
-    <col min="4" max="4" width="15.5" style="33" customWidth="1"/>
-    <col min="5" max="5" width="23.33203125" style="33" customWidth="1"/>
-    <col min="6" max="6" width="26.1640625" style="33" customWidth="1"/>
-    <col min="7" max="7" width="19.83203125" style="33" customWidth="1"/>
-    <col min="8" max="8" width="18.1640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23" style="33" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.33203125" style="33" customWidth="1"/>
-    <col min="11" max="11" width="20.5" style="33" customWidth="1"/>
-    <col min="12" max="12" width="23" style="33" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.83203125" style="33" customWidth="1"/>
-    <col min="14" max="16384" width="10.83203125" style="33"/>
+    <col min="1" max="1" width="25.6640625" style="28" customWidth="1"/>
+    <col min="2" max="2" width="23" style="28" customWidth="1"/>
+    <col min="3" max="3" width="21.5" style="28" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" style="28" customWidth="1"/>
+    <col min="5" max="10" width="17.5" style="12" customWidth="1"/>
+    <col min="11" max="11" width="17.5" style="48" customWidth="1"/>
+    <col min="12" max="14" width="17.5" style="12" customWidth="1"/>
+    <col min="15" max="16384" width="10.83203125" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="38" customFormat="1" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="34" t="s">
+    <row r="1" spans="1:14" s="60" customFormat="1" ht="89" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="54" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="54" t="s">
+        <v>96</v>
+      </c>
+      <c r="C1" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="55" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="56" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="56" t="s">
+        <v>60</v>
+      </c>
+      <c r="H1" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1" s="56" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" s="57" t="s">
+        <v>104</v>
+      </c>
+      <c r="L1" s="58" t="s">
+        <v>74</v>
+      </c>
+      <c r="M1" s="58" t="s">
+        <v>72</v>
+      </c>
+      <c r="N1" s="59" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="85" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="88" t="s">
+        <v>98</v>
+      </c>
+      <c r="C2" s="85" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="6">
+        <v>0.60518292679999997</v>
+      </c>
+      <c r="F2" s="6">
+        <v>0.89824695119999998</v>
+      </c>
+      <c r="G2" s="6">
+        <v>0.65191332410000002</v>
+      </c>
+      <c r="H2" s="6">
+        <v>0.43489583329999998</v>
+      </c>
+      <c r="I2" s="6">
+        <v>9.8591549299999998E-2</v>
+      </c>
+      <c r="J2" s="6">
+        <v>0.68544860669999996</v>
+      </c>
+      <c r="K2" s="48">
+        <v>0.29145481309999999</v>
+      </c>
+      <c r="L2" s="26">
+        <f>G2*1/3+H2*1/3+I2*1/3</f>
+        <v>0.39513356890000001</v>
+      </c>
+      <c r="M2" s="26">
+        <f>STDEV(G2:I2)</f>
+        <v>0.27879566867083339</v>
+      </c>
+      <c r="N2" s="12">
+        <f>SUMPRODUCT(G2:I2,$D$14:$F$14)/SUM($D$14:$F$14)</f>
+        <v>0.16006770057000003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="86"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="86"/>
+      <c r="D3" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="26">
+        <v>0.82660060980000005</v>
+      </c>
+      <c r="F3" s="26">
+        <v>0.97294207320000003</v>
+      </c>
+      <c r="G3" s="26">
+        <v>1</v>
+      </c>
+      <c r="H3" s="26">
+        <v>0</v>
+      </c>
+      <c r="I3" s="26">
+        <v>0</v>
+      </c>
+      <c r="J3" s="26">
+        <v>0.86995045729999998</v>
+      </c>
+      <c r="K3" s="48">
+        <v>0.19871618520000001</v>
+      </c>
+      <c r="L3" s="26">
+        <f t="shared" ref="L3:L4" si="0">G3*1/3+H3*1/3+I3*1/3</f>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="M3" s="26">
+        <f t="shared" ref="M3:M4" si="1">STDEV(G3:I3)</f>
+        <v>0.57735026918962584</v>
+      </c>
+      <c r="N3" s="12">
+        <f>SUMPRODUCT(G3:I3,$D$14:$F$14)/SUM($D$14:$F$14)</f>
+        <v>2.5000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="86"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="86"/>
+      <c r="D4" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="26">
+        <v>0.61128048779999999</v>
+      </c>
+      <c r="F4" s="26">
+        <v>0.85632621949999999</v>
+      </c>
+      <c r="G4" s="26">
+        <v>0.67634854769999997</v>
+      </c>
+      <c r="H4" s="26">
+        <v>0.29947916670000002</v>
+      </c>
+      <c r="I4" s="26">
+        <v>0.30985915489999999</v>
+      </c>
+      <c r="J4" s="26">
+        <v>0.50006826780000002</v>
+      </c>
+      <c r="K4" s="48">
+        <v>0.42822100460000001</v>
+      </c>
+      <c r="L4" s="26">
+        <f t="shared" si="0"/>
+        <v>0.42856228976666666</v>
+      </c>
+      <c r="M4" s="26">
+        <f t="shared" si="1"/>
+        <v>0.21465194677479932</v>
+      </c>
+      <c r="N4" s="12">
+        <f>SUMPRODUCT(G4:I4,$D$14:$F$14)/SUM($D$14:$F$14)</f>
+        <v>0.31755089139166665</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="86"/>
+      <c r="B5" s="84"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="75"/>
+      <c r="L5" s="26"/>
+      <c r="M5" s="26"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="86"/>
+      <c r="B6" s="84"/>
+      <c r="C6" s="87" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="34" t="s">
-        <v>97</v>
-      </c>
-      <c r="C1" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="35" t="s">
+      <c r="D6" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="6">
+        <v>0.71532012199999995</v>
+      </c>
+      <c r="F6" s="6">
+        <v>0.88452743899999997</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0.82664822500000001</v>
+      </c>
+      <c r="H6" s="6">
+        <v>0.20572916669999999</v>
+      </c>
+      <c r="I6" s="6">
+        <v>7.0422535199999997E-2</v>
+      </c>
+      <c r="J6" s="6">
+        <v>0.73983099360000004</v>
+      </c>
+      <c r="K6" s="48">
+        <v>0.60415152729999999</v>
+      </c>
+      <c r="L6" s="26">
+        <f>G6*1/3+H6*1/3+I6*1/3</f>
+        <v>0.36759997563333335</v>
+      </c>
+      <c r="M6" s="26">
+        <f>STDEV(G6:I6)</f>
+        <v>0.40326287030536323</v>
+      </c>
+      <c r="N6" s="12">
+        <f>SUMPRODUCT(G6:I6,$D$14:$F$14)/SUM($D$14:$F$14)</f>
+        <v>0.10849661690750001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="86"/>
+      <c r="B7" s="84"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="26">
+        <v>0.62080792679999997</v>
+      </c>
+      <c r="F7" s="26">
+        <v>0.87347560980000005</v>
+      </c>
+      <c r="G7" s="26">
+        <v>0.67819271550000004</v>
+      </c>
+      <c r="H7" s="26">
+        <v>0.3828125</v>
+      </c>
+      <c r="I7" s="26">
+        <v>0.1549295775</v>
+      </c>
+      <c r="J7" s="26">
+        <v>0.64483064459999995</v>
+      </c>
+      <c r="K7" s="75">
+        <v>0.48987603270000002</v>
+      </c>
+      <c r="L7" s="26">
+        <f t="shared" ref="L7:L8" si="2">G7*1/3+H7*1/3+I7*1/3</f>
+        <v>0.40531159766666663</v>
+      </c>
+      <c r="M7" s="26">
+        <f t="shared" ref="M7:M8" si="3">STDEV(G7:I7)</f>
+        <v>0.26235612236855171</v>
+      </c>
+      <c r="N7" s="12">
+        <f>SUMPRODUCT(G7:I7,$D$14:$F$14)/SUM($D$14:$F$14)</f>
+        <v>0.20029456997083334</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="86"/>
+      <c r="B8" s="84"/>
+      <c r="C8" s="87"/>
+      <c r="D8" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="26">
+        <v>0.61242378050000001</v>
+      </c>
+      <c r="F8" s="26">
+        <v>0.84984756100000003</v>
+      </c>
+      <c r="G8" s="26">
+        <v>0.67127708620000004</v>
+      </c>
+      <c r="H8" s="26">
+        <v>0.3203125</v>
+      </c>
+      <c r="I8" s="26">
+        <v>0.39436619719999999</v>
+      </c>
+      <c r="J8" s="26">
+        <v>0.63692361819999999</v>
+      </c>
+      <c r="K8" s="75">
+        <v>0.52219947680000001</v>
+      </c>
+      <c r="L8" s="26">
+        <f t="shared" si="2"/>
+        <v>0.46198526113333338</v>
+      </c>
+      <c r="M8" s="26">
+        <f t="shared" si="3"/>
+        <v>0.18499537439365743</v>
+      </c>
+      <c r="N8" s="12">
+        <f>SUMPRODUCT(G8:I8,$D$14:$F$14)/SUM($D$14:$F$14)</f>
+        <v>0.39079802898833332</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="86"/>
+      <c r="B9" s="84"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="75"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="86"/>
+      <c r="B10" s="84"/>
+      <c r="C10" s="84" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="6">
+        <v>0.78048780490000003</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0.85670731710000003</v>
+      </c>
+      <c r="G10" s="6">
+        <v>0.94006454589999999</v>
+      </c>
+      <c r="H10" s="6">
         <v>0</v>
       </c>
-      <c r="E1" s="36" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="H1" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="J1" s="36" t="s">
-        <v>5</v>
-      </c>
-      <c r="K1" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="L1" s="37" t="s">
-        <v>73</v>
-      </c>
-      <c r="M1" s="21" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" s="58" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="28">
-        <f>G2*1/3+H2*1/3+I2*1/3</f>
+      <c r="I10" s="6">
+        <v>0.1267605634</v>
+      </c>
+      <c r="J10" s="6">
+        <v>0.50378384080000005</v>
+      </c>
+      <c r="K10" s="48">
+        <v>0.322335392</v>
+      </c>
+      <c r="L10" s="26">
+        <f>G10*1/3+H10*1/3+I10*1/3</f>
+        <v>0.35560836976666665</v>
+      </c>
+      <c r="M10" s="26">
+        <f t="shared" ref="M10:M11" si="4">STDEV(G10:I10)</f>
+        <v>0.51010668146346583</v>
+      </c>
+      <c r="N10" s="12">
+        <f>SUMPRODUCT(G10:I10,$D$14:$F$14)/SUM($D$14:$F$14)</f>
+        <v>0.12913541648083335</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="86"/>
+      <c r="B11" s="84"/>
+      <c r="C11" s="84"/>
+      <c r="D11" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="75"/>
+      <c r="L11" s="26">
+        <f t="shared" ref="L11" si="5">G11*1/3+H11*1/3+I11*1/3</f>
         <v>0</v>
       </c>
-      <c r="L2" s="28" t="e">
-        <f>STDEV(G2:I2)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M2" s="33" t="e">
-        <f>SUMPRODUCT(G2:I2,$D$14:$F$14)/SUM($D$14:$F$14)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" s="59"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="28">
-        <f t="shared" ref="K3:K4" si="0">G3*1/3+H3*1/3+I3*1/3</f>
-        <v>0</v>
-      </c>
-      <c r="L3" s="28" t="e">
-        <f t="shared" ref="L3:L4" si="1">STDEV(G3:I3)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M3" s="33" t="e">
-        <f>SUMPRODUCT(G3:I3,$D$14:$F$14)/SUM($D$14:$F$14)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="59"/>
-      <c r="B4" s="59"/>
-      <c r="C4" s="59"/>
-      <c r="D4" s="27" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" s="29"/>
-      <c r="F4" s="29"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="28">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L4" s="28" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M4" s="33" t="e">
-        <f>SUMPRODUCT(G4:I4,$D$14:$F$14)/SUM($D$14:$F$14)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="59"/>
-      <c r="B5" s="59"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" s="59"/>
-      <c r="B6" s="59"/>
-      <c r="C6" s="60" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="28">
-        <f>G6*1/3+H6*1/3+I6*1/3</f>
-        <v>0</v>
-      </c>
-      <c r="L6" s="28" t="e">
-        <f>STDEV(G6:I6)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M6" s="33" t="e">
-        <f>SUMPRODUCT(G6:I6,$D$14:$F$14)/SUM($D$14:$F$14)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="59"/>
-      <c r="B7" s="59"/>
-      <c r="C7" s="60"/>
-      <c r="D7" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="28">
-        <f t="shared" ref="K7:K8" si="2">G7*1/3+H7*1/3+I7*1/3</f>
-        <v>0</v>
-      </c>
-      <c r="L7" s="28" t="e">
-        <f t="shared" ref="L7:L8" si="3">STDEV(G7:I7)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M7" s="33" t="e">
-        <f>SUMPRODUCT(G7:I7,$D$14:$F$14)/SUM($D$14:$F$14)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" s="59"/>
-      <c r="B8" s="59"/>
-      <c r="C8" s="60"/>
-      <c r="D8" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="29"/>
-      <c r="I8" s="29"/>
-      <c r="J8" s="29"/>
-      <c r="K8" s="28">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L8" s="28" t="e">
-        <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M8" s="33" t="e">
-        <f>SUMPRODUCT(G8:I8,$D$14:$F$14)/SUM($D$14:$F$14)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A9" s="59"/>
-      <c r="B9" s="59"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="29"/>
-      <c r="J9" s="29"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A10" s="59"/>
-      <c r="B10" s="59"/>
-      <c r="C10" s="57" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="28">
-        <f>G10*1/3+H10*1/3+I10*1/3</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="28" t="e">
-        <f t="shared" ref="L10:L11" si="4">STDEV(G10:I10)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M10" s="33" t="e">
-        <f>SUMPRODUCT(G10:I10,$D$14:$F$14)/SUM($D$14:$F$14)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A11" s="59"/>
-      <c r="B11" s="59"/>
-      <c r="C11" s="57"/>
-      <c r="D11" s="27" t="s">
-        <v>72</v>
-      </c>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="28">
-        <f t="shared" ref="K11" si="5">G11*1/3+H11*1/3+I11*1/3</f>
-        <v>0</v>
-      </c>
-      <c r="L11" s="28" t="e">
+      <c r="M11" s="26" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M11" s="33" t="e">
+      <c r="N11" s="12">
         <f>SUMPRODUCT(G11:I11,$D$14:$F$14)/SUM($D$14:$F$14)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="30"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="28"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="27"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="42" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="27"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="75"/>
+      <c r="L12" s="26"/>
+      <c r="M12" s="26"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="25"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="D13" s="40" t="s">
+      <c r="E13" s="45" t="s">
         <v>91</v>
       </c>
-      <c r="E13" s="43" t="s">
+      <c r="F13" s="45" t="s">
         <v>92</v>
       </c>
-      <c r="F13" s="44" t="s">
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="75"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="26"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="27"/>
+      <c r="B14" s="27"/>
+      <c r="C14" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="29"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="28"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A14" s="30"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="D14" s="41"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="28"/>
-      <c r="L14" s="28"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A15" s="30"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="29"/>
-      <c r="K15" s="28"/>
-      <c r="L15" s="28"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A16" s="30"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="29"/>
-      <c r="K16" s="28"/>
-      <c r="L16" s="28"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" s="27"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="27"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="29"/>
-      <c r="J17" s="29"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="28"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="30"/>
-      <c r="B18" s="30"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="29"/>
-      <c r="F18" s="29"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="29"/>
-      <c r="J18" s="29"/>
-      <c r="K18" s="28"/>
-      <c r="L18" s="28"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" s="30"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="29"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="29"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="30"/>
-      <c r="B20" s="30"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="27"/>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="29"/>
-      <c r="F21" s="29"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29"/>
-      <c r="I21" s="29"/>
-      <c r="J21" s="29"/>
-      <c r="K21" s="28"/>
-      <c r="L21" s="28"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="30"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="29"/>
-      <c r="F22" s="29"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="29"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="28"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="30"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" s="30"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="29"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="28"/>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="27"/>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="29"/>
-      <c r="F25" s="29"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="29"/>
-      <c r="J25" s="29"/>
-      <c r="K25" s="28"/>
-      <c r="L25" s="28"/>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="30"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A27" s="30"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="29"/>
-      <c r="J27" s="29"/>
-      <c r="K27" s="28"/>
-      <c r="L27" s="28"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="30"/>
-      <c r="B28" s="30"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="29"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="27"/>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="30"/>
-      <c r="B30" s="30"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="29"/>
-      <c r="K30" s="28"/>
-      <c r="L30" s="28"/>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="30"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29"/>
-      <c r="I31" s="29"/>
-      <c r="J31" s="29"/>
-      <c r="K31" s="28"/>
-      <c r="L31" s="28"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="30"/>
-      <c r="B32" s="30"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A33" s="27"/>
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="29"/>
-      <c r="I33" s="29"/>
-      <c r="J33" s="29"/>
-      <c r="K33" s="28"/>
-      <c r="L33" s="28"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="30"/>
-      <c r="B34" s="30"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="29"/>
-      <c r="F34" s="29"/>
-      <c r="G34" s="29"/>
-      <c r="H34" s="29"/>
-      <c r="I34" s="29"/>
-      <c r="J34" s="29"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="28"/>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A35" s="30"/>
-      <c r="B35" s="30"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="27"/>
-      <c r="E35" s="29"/>
-      <c r="F35" s="29"/>
-      <c r="G35" s="29"/>
-      <c r="H35" s="29"/>
-      <c r="I35" s="29"/>
-      <c r="J35" s="29"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="28"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="30"/>
-      <c r="B36" s="30"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="29"/>
-      <c r="G36" s="29"/>
-      <c r="H36" s="29"/>
-      <c r="I36" s="29"/>
-      <c r="J36" s="29"/>
-      <c r="K36" s="28"/>
-      <c r="L36" s="28"/>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="27"/>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="29"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="30"/>
-      <c r="B38" s="30"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="29"/>
-      <c r="F38" s="29"/>
-      <c r="G38" s="29"/>
-      <c r="H38" s="29"/>
-      <c r="I38" s="29"/>
-      <c r="J38" s="29"/>
-      <c r="K38" s="28"/>
-      <c r="L38" s="28"/>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="30"/>
-      <c r="B39" s="30"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="27"/>
-      <c r="E39" s="29"/>
-      <c r="F39" s="29"/>
-      <c r="G39" s="29"/>
-      <c r="H39" s="29"/>
-      <c r="I39" s="29"/>
-      <c r="J39" s="29"/>
-      <c r="K39" s="28"/>
-      <c r="L39" s="28"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="30"/>
-      <c r="B40" s="30"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="28"/>
-      <c r="L40" s="28"/>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="27"/>
-      <c r="B41" s="27"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="27"/>
-      <c r="E41" s="29"/>
-      <c r="F41" s="29"/>
-      <c r="G41" s="29"/>
-      <c r="H41" s="29"/>
-      <c r="I41" s="29"/>
-      <c r="J41" s="29"/>
-      <c r="K41" s="28"/>
-      <c r="L41" s="28"/>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="30"/>
-      <c r="B42" s="30"/>
-      <c r="C42" s="27"/>
-      <c r="D42" s="27"/>
-      <c r="E42" s="29"/>
-      <c r="F42" s="29"/>
-      <c r="G42" s="29"/>
-      <c r="H42" s="29"/>
-      <c r="I42" s="29"/>
-      <c r="J42" s="29"/>
-      <c r="K42" s="28"/>
-      <c r="L42" s="28"/>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="30"/>
-      <c r="B43" s="30"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="29"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="28"/>
-      <c r="L43" s="28"/>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A44" s="30"/>
-      <c r="B44" s="30"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="27"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="29"/>
-      <c r="G44" s="29"/>
-      <c r="H44" s="29"/>
-      <c r="I44" s="29"/>
-      <c r="J44" s="29"/>
-      <c r="K44" s="28"/>
-      <c r="L44" s="28"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A45" s="27"/>
-      <c r="B45" s="27"/>
-      <c r="C45" s="27"/>
-      <c r="D45" s="27"/>
-      <c r="E45" s="29"/>
-      <c r="F45" s="29"/>
-      <c r="G45" s="29"/>
-      <c r="H45" s="29"/>
-      <c r="I45" s="29"/>
-      <c r="J45" s="29"/>
-      <c r="K45" s="28"/>
-      <c r="L45" s="28"/>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A46" s="30"/>
-      <c r="B46" s="30"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="28"/>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="30"/>
-      <c r="B47" s="30"/>
-      <c r="C47" s="27"/>
-      <c r="D47" s="27"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
-      <c r="G47" s="29"/>
-      <c r="H47" s="29"/>
-      <c r="I47" s="29"/>
-      <c r="J47" s="29"/>
-      <c r="K47" s="28"/>
-      <c r="L47" s="28"/>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A48" s="30"/>
-      <c r="B48" s="30"/>
-      <c r="C48" s="27"/>
-      <c r="D48" s="27"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="29"/>
-      <c r="I48" s="29"/>
-      <c r="J48" s="29"/>
-      <c r="K48" s="28"/>
-      <c r="L48" s="28"/>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" s="27"/>
-      <c r="B49" s="27"/>
-      <c r="C49" s="27"/>
-      <c r="D49" s="27"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="29"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="29"/>
-      <c r="K49" s="28"/>
-      <c r="L49" s="28"/>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="27"/>
-      <c r="B50" s="27"/>
-      <c r="C50" s="27"/>
-      <c r="D50" s="27"/>
-      <c r="E50" s="29"/>
-      <c r="F50" s="29"/>
-      <c r="G50" s="29"/>
-      <c r="H50" s="29"/>
-      <c r="I50" s="29"/>
-      <c r="J50" s="29"/>
-      <c r="K50" s="28"/>
-      <c r="L50" s="28"/>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="27"/>
-      <c r="B51" s="27"/>
-      <c r="C51" s="27"/>
-      <c r="D51" s="31"/>
-      <c r="E51" s="32"/>
-      <c r="F51" s="32"/>
-      <c r="G51" s="32"/>
-      <c r="H51" s="32"/>
-      <c r="I51" s="32"/>
-      <c r="J51" s="32"/>
-      <c r="K51" s="28"/>
-      <c r="L51" s="28"/>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" s="27"/>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
-      <c r="D52" s="31"/>
-      <c r="E52" s="32"/>
-      <c r="F52" s="32"/>
-      <c r="G52" s="32"/>
-      <c r="H52" s="32"/>
-      <c r="I52" s="32"/>
-      <c r="J52" s="32"/>
-      <c r="K52" s="28"/>
-      <c r="L52" s="28"/>
+      <c r="D14" s="47">
+        <v>0.03</v>
+      </c>
+      <c r="E14" s="47">
+        <v>0.17</v>
+      </c>
+      <c r="F14" s="47">
+        <v>1</v>
+      </c>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="75"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="26"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="27"/>
+      <c r="B15" s="27"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="75"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="26"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="27"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="75"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="25"/>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26"/>
+      <c r="I17" s="26"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="76"/>
+      <c r="L17" s="26"/>
+      <c r="M17" s="26"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" s="27"/>
+      <c r="B18" s="27"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="75"/>
+      <c r="L18" s="26"/>
+      <c r="M18" s="26"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" s="27"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="26"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="26"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="75"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="26"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" s="27"/>
+      <c r="B20" s="27"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="75"/>
+      <c r="L20" s="26"/>
+      <c r="M20" s="26"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" s="25"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="26"/>
+      <c r="K21" s="76"/>
+      <c r="L21" s="26"/>
+      <c r="M21" s="26"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" s="27"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="26"/>
+      <c r="K22" s="76"/>
+      <c r="L22" s="26"/>
+      <c r="M22" s="26"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" s="27"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="76"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" s="27"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="76"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="26"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" s="25"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="26"/>
+      <c r="K25" s="76"/>
+      <c r="L25" s="26"/>
+      <c r="M25" s="26"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" s="27"/>
+      <c r="B26" s="27"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
+      <c r="K26" s="76"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" s="27"/>
+      <c r="B27" s="27"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+      <c r="K27" s="76"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" s="27"/>
+      <c r="B28" s="27"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26"/>
+      <c r="K28" s="76"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" s="25"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="26"/>
+      <c r="K29" s="76"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="26"/>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" s="27"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
+      <c r="K30" s="76"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="26"/>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" s="27"/>
+      <c r="B31" s="27"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="26"/>
+      <c r="K31" s="76"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="26"/>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" s="27"/>
+      <c r="B32" s="27"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="26"/>
+      <c r="K32" s="76"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="26"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="25"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="26"/>
+      <c r="K33" s="76"/>
+      <c r="L33" s="26"/>
+      <c r="M33" s="26"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" s="27"/>
+      <c r="B34" s="27"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="26"/>
+      <c r="I34" s="26"/>
+      <c r="J34" s="26"/>
+      <c r="K34" s="76"/>
+      <c r="L34" s="26"/>
+      <c r="M34" s="26"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" s="27"/>
+      <c r="B35" s="27"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="26"/>
+      <c r="J35" s="26"/>
+      <c r="K35" s="76"/>
+      <c r="L35" s="26"/>
+      <c r="M35" s="26"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" s="27"/>
+      <c r="B36" s="27"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="26"/>
+      <c r="K36" s="76"/>
+      <c r="L36" s="26"/>
+      <c r="M36" s="26"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" s="25"/>
+      <c r="B37" s="25"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
+      <c r="K37" s="76"/>
+      <c r="L37" s="26"/>
+      <c r="M37" s="26"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" s="27"/>
+      <c r="B38" s="27"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="26"/>
+      <c r="J38" s="26"/>
+      <c r="K38" s="76"/>
+      <c r="L38" s="26"/>
+      <c r="M38" s="26"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" s="27"/>
+      <c r="B39" s="27"/>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="26"/>
+      <c r="K39" s="76"/>
+      <c r="L39" s="26"/>
+      <c r="M39" s="26"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" s="27"/>
+      <c r="B40" s="27"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="26"/>
+      <c r="J40" s="26"/>
+      <c r="K40" s="76"/>
+      <c r="L40" s="26"/>
+      <c r="M40" s="26"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" s="25"/>
+      <c r="B41" s="25"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="26"/>
+      <c r="K41" s="76"/>
+      <c r="L41" s="26"/>
+      <c r="M41" s="26"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" s="27"/>
+      <c r="B42" s="27"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="76"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="26"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" s="27"/>
+      <c r="B43" s="27"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="26"/>
+      <c r="I43" s="26"/>
+      <c r="J43" s="26"/>
+      <c r="K43" s="76"/>
+      <c r="L43" s="26"/>
+      <c r="M43" s="26"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" s="27"/>
+      <c r="B44" s="27"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="26"/>
+      <c r="G44" s="26"/>
+      <c r="H44" s="26"/>
+      <c r="I44" s="26"/>
+      <c r="J44" s="26"/>
+      <c r="K44" s="76"/>
+      <c r="L44" s="26"/>
+      <c r="M44" s="26"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" s="25"/>
+      <c r="B45" s="25"/>
+      <c r="C45" s="25"/>
+      <c r="D45" s="25"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="26"/>
+      <c r="H45" s="26"/>
+      <c r="I45" s="26"/>
+      <c r="J45" s="26"/>
+      <c r="K45" s="76"/>
+      <c r="L45" s="26"/>
+      <c r="M45" s="26"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" s="27"/>
+      <c r="B46" s="27"/>
+      <c r="C46" s="25"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="26"/>
+      <c r="H46" s="26"/>
+      <c r="I46" s="26"/>
+      <c r="J46" s="26"/>
+      <c r="K46" s="76"/>
+      <c r="L46" s="26"/>
+      <c r="M46" s="26"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" s="27"/>
+      <c r="B47" s="27"/>
+      <c r="C47" s="25"/>
+      <c r="D47" s="25"/>
+      <c r="E47" s="26"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="26"/>
+      <c r="H47" s="26"/>
+      <c r="I47" s="26"/>
+      <c r="J47" s="26"/>
+      <c r="K47" s="76"/>
+      <c r="L47" s="26"/>
+      <c r="M47" s="26"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" s="27"/>
+      <c r="B48" s="27"/>
+      <c r="C48" s="25"/>
+      <c r="D48" s="25"/>
+      <c r="E48" s="26"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="26"/>
+      <c r="H48" s="26"/>
+      <c r="I48" s="26"/>
+      <c r="J48" s="26"/>
+      <c r="K48" s="76"/>
+      <c r="L48" s="26"/>
+      <c r="M48" s="26"/>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" s="25"/>
+      <c r="B49" s="25"/>
+      <c r="C49" s="25"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="26"/>
+      <c r="G49" s="26"/>
+      <c r="H49" s="26"/>
+      <c r="I49" s="26"/>
+      <c r="J49" s="26"/>
+      <c r="L49" s="26"/>
+      <c r="M49" s="26"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" s="25"/>
+      <c r="B50" s="25"/>
+      <c r="C50" s="25"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="26"/>
+      <c r="F50" s="26"/>
+      <c r="G50" s="26"/>
+      <c r="H50" s="26"/>
+      <c r="I50" s="26"/>
+      <c r="J50" s="26"/>
+      <c r="L50" s="26"/>
+      <c r="M50" s="26"/>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" s="25"/>
+      <c r="B51" s="25"/>
+      <c r="C51" s="25"/>
+      <c r="D51" s="25"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="26"/>
+      <c r="G51" s="26"/>
+      <c r="H51" s="26"/>
+      <c r="I51" s="26"/>
+      <c r="J51" s="26"/>
+      <c r="L51" s="26"/>
+      <c r="M51" s="26"/>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" s="25"/>
+      <c r="B52" s="25"/>
+      <c r="C52" s="25"/>
+      <c r="D52" s="25"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="26"/>
+      <c r="G52" s="26"/>
+      <c r="H52" s="26"/>
+      <c r="I52" s="26"/>
+      <c r="J52" s="26"/>
+      <c r="L52" s="26"/>
+      <c r="M52" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/benchmarking/output/data.xlsx
+++ b/benchmarking/output/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F49F3ABE-5490-2440-869B-0F47643259FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83426C5-5F28-E141-A8E9-8C4C6B8165F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4280" yWindow="500" windowWidth="46920" windowHeight="26600" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="basic" sheetId="1" r:id="rId1"/>
@@ -7199,24 +7199,38 @@
       <c r="E20" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="K20" s="6"/>
-      <c r="L20" s="75"/>
+      <c r="F20" s="6">
+        <v>0.75838414629999995</v>
+      </c>
+      <c r="G20" s="6">
+        <v>0.82431402440000001</v>
+      </c>
+      <c r="H20" s="6">
+        <v>0.91101890269999997</v>
+      </c>
+      <c r="I20" s="6">
+        <v>5.2083333000000004E-3</v>
+      </c>
+      <c r="J20" s="6">
+        <v>0.16901408449999999</v>
+      </c>
+      <c r="K20" s="6">
+        <v>0.58367710129999995</v>
+      </c>
+      <c r="L20" s="75">
+        <v>0.27206442679999998</v>
+      </c>
       <c r="M20" s="26">
         <f>H20*1/3+I20*1/3+J20*1/3</f>
-        <v>0</v>
-      </c>
-      <c r="N20" s="26" t="e">
+        <v>0.36174710683333333</v>
+      </c>
+      <c r="N20" s="26">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>0.48268282581058747</v>
       </c>
       <c r="O20" s="12">
         <f>SUMPRODUCT(H20:J20,$D$26:$F$26)/SUM($D$26:$F$26)</f>
-        <v>0</v>
+        <v>0.16443471305901639</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.2">
@@ -7309,9 +7323,9 @@
         <f>MAX(M2:M23)</f>
         <v>0.44090356646666662</v>
       </c>
-      <c r="N25" s="51" t="e">
+      <c r="N25" s="51">
         <f>MAX(N2:N23)</f>
-        <v>#DIV/0!</v>
+        <v>0.55952529849253352</v>
       </c>
       <c r="O25" s="51">
         <f>MAX(O2:O23)</f>
@@ -7349,15 +7363,15 @@
       </c>
       <c r="M26" s="51">
         <f>MIN(M2:M20)</f>
-        <v>0</v>
-      </c>
-      <c r="N26" s="51" t="e">
+        <v>0.31121721976666666</v>
+      </c>
+      <c r="N26" s="51">
         <f>MIN(N2:N20)</f>
-        <v>#DIV/0!</v>
+        <v>0.14997136463523317</v>
       </c>
       <c r="O26" s="51">
         <f>MIN(O2:O20)</f>
-        <v>0</v>
+        <v>2.8877180972950819E-2</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.2">
@@ -7375,19 +7389,19 @@
       </c>
       <c r="L27" s="50">
         <f>AVERAGE(L2:L23)</f>
-        <v>0.38022704497857146</v>
+        <v>0.37301620376666667</v>
       </c>
       <c r="M27" s="51">
         <f>AVERAGE(M2:M23)</f>
-        <v>0.33532851900000005</v>
-      </c>
-      <c r="N27" s="51" t="e">
+        <v>0.35944499278888897</v>
+      </c>
+      <c r="N27" s="51">
         <f>AVERAGE(N2:N23)</f>
-        <v>#DIV/0!</v>
+        <v>0.35135493891108294</v>
       </c>
       <c r="O27" s="51">
         <f>AVERAGE(O2:O23)</f>
-        <v>0.15341104264945354</v>
+        <v>0.16437335685338797</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.2">
@@ -8128,24 +8142,38 @@
       <c r="D11" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="75"/>
+      <c r="E11" s="26">
+        <v>0.59413109760000005</v>
+      </c>
+      <c r="F11" s="26">
+        <v>0.80640243899999997</v>
+      </c>
+      <c r="G11" s="26">
+        <v>0.64545873669999998</v>
+      </c>
+      <c r="H11" s="26">
+        <v>0.33854166670000002</v>
+      </c>
+      <c r="I11" s="26">
+        <v>0.40845070420000001</v>
+      </c>
+      <c r="J11" s="26">
+        <v>0.58133493790000001</v>
+      </c>
+      <c r="K11" s="75">
+        <v>0.38967609759999999</v>
+      </c>
       <c r="L11" s="26">
         <f t="shared" ref="L11" si="5">G11*1/3+H11*1/3+I11*1/3</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="26" t="e">
+        <v>0.46415036919999997</v>
+      </c>
+      <c r="M11" s="26">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>0.16086131130629377</v>
       </c>
       <c r="N11" s="12">
         <f>SUMPRODUCT(G11:I11,$D$14:$F$14)/SUM($D$14:$F$14)</f>
-        <v>0</v>
+        <v>0.40447212470000005</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">

--- a/benchmarking/output/data.xlsx
+++ b/benchmarking/output/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83426C5-5F28-E141-A8E9-8C4C6B8165F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37788B9D-827A-EC4E-956A-E0912B1580A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4280" yWindow="500" windowWidth="46920" windowHeight="26600" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="basic" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,8 @@
     <sheet name="checking bias" sheetId="5" r:id="rId4"/>
     <sheet name="checking noise" sheetId="6" r:id="rId5"/>
     <sheet name="family of models" sheetId="7" r:id="rId6"/>
+    <sheet name="Meta-Learner Roberta" sheetId="8" r:id="rId7"/>
+    <sheet name="Meta-Learner Deberta" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="144">
   <si>
     <t>Model</t>
   </si>
@@ -370,15 +372,551 @@
   <si>
     <t>Relation classification + prediction f1_macro</t>
   </si>
+  <si>
+    <t>F1-Macro</t>
+  </si>
+  <si>
+    <t>Features</t>
+  </si>
+  <si>
+    <t>Distmult</t>
+  </si>
+  <si>
+    <t>Roberta</t>
+  </si>
+  <si>
+    <t>Deberta-v3</t>
+  </si>
+  <si>
+    <t>predictions from roberta and distmult</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Models</t>
+  </si>
+  <si>
+    <t>Single Model</t>
+  </si>
+  <si>
+    <t>Two Specialized models</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Distmult</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> classifies noRel/Rel and </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Roberta</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> classifies Support/Attack/Equivalent</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Distmult</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> classifies noRel/Rel and </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Deberta</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> classifies Support/Attack/Equivalent</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Roberta</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> classifies noRel/Rel and </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DistMult</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> classifies Support/Attack/Equivalent</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Deberta</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> classifies noRel/Rel and </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>DistMult</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> classifies Support/Attack/Equivalent</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Roberta and DistMult predictions are evaluated by a </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Random Forest Classifier</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Roberta and DistMult predictions are evaluated by a </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Support Vector Classifier</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Roberta and DistMult predictions are evaluated by a </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Decision Tree Classifier</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Roberta and DistMult predictions are evaluated by a </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AdaBoost Classifier</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Roberta and DistMult predictions are evaluated by a </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Gaussian Naive Bayes Classifier</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Roberta and DistMult predictions are evaluated by a </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>KNearest Neighbours Classifier</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Roberta and DistMult predictions are evaluated by a </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MultiLayer Perceptron Classifier</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Roberta and DistMult predictions are evaluated by a </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Gradient Boosting Classifier</t>
+    </r>
+  </si>
+  <si>
+    <t>Meta-Learner</t>
+  </si>
+  <si>
+    <t>text and predictions from roberta and distmult</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Roberta and DistMult predictions are evaluated by a </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">CNN </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>that also takes into account the textual features</t>
+    </r>
+  </si>
+  <si>
+    <t>Average of Models</t>
+  </si>
+  <si>
+    <t>Roberta and DistMult are averaged by their F1-macro score</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Deberta and DistMult predictions are evaluated by a </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Decision Tree Classifier</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Deberta and DistMult predictions are evaluated by a </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Random Forest Classifier</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Deberta and DistMult predictions are evaluated by a </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Support Vector Classifier</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Deberta and DistMult predictions are evaluated by a </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AdaBoost Classifier</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Deberta and DistMult predictions are evaluated by a </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Gaussian Naive Bayes Classifier</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Deberta and DistMult predictions are evaluated by a </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>KNearest Neighbours Classifier</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Deberta and DistMult predictions are evaluated by a </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MultiLayer Perceptron Classifier</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Deberta and DistMult predictions are evaluated by a </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Gradient Boosting Classifier</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Deberta and DistMult predictions are evaluated by a </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">CNN </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>that also takes into account the textual features</t>
+    </r>
+  </si>
+  <si>
+    <t>Deberta and DistMult are averaged by their F1-macro score</t>
+  </si>
+  <si>
+    <t>text and predictions from deberta and distmult</t>
+  </si>
+  <si>
+    <t>predictions from deberta and distmult</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000000"/>
+    <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -496,6 +1034,29 @@
       <color rgb="FFC00000"/>
       <name val="Calibri (Corpo)"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -577,7 +1138,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -655,11 +1216,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="89">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -888,13 +1458,13 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -919,6 +1489,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1270,13 +1861,13 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="80" t="s">
         <v>17</v>
       </c>
       <c r="B2" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="79" t="s">
+      <c r="C2" s="78" t="s">
         <v>29</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -1302,9 +1893,9 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A3" s="78"/>
+      <c r="A3" s="80"/>
       <c r="B3" s="81"/>
-      <c r="C3" s="80"/>
+      <c r="C3" s="79"/>
       <c r="D3" s="5" t="s">
         <v>24</v>
       </c>
@@ -1328,9 +1919,9 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="78"/>
+      <c r="A4" s="80"/>
       <c r="B4" s="81"/>
-      <c r="C4" s="80"/>
+      <c r="C4" s="79"/>
       <c r="D4" s="5" t="s">
         <v>25</v>
       </c>
@@ -1365,11 +1956,11 @@
       <c r="J5" s="6"/>
     </row>
     <row r="6" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="78" t="s">
+      <c r="A6" s="80" t="s">
         <v>18</v>
       </c>
       <c r="B6" s="81"/>
-      <c r="C6" s="79" t="s">
+      <c r="C6" s="78" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="5" t="s">
@@ -1395,9 +1986,9 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="78"/>
+      <c r="A7" s="80"/>
       <c r="B7" s="81"/>
-      <c r="C7" s="80"/>
+      <c r="C7" s="79"/>
       <c r="D7" s="5" t="s">
         <v>24</v>
       </c>
@@ -1421,9 +2012,9 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A8" s="78"/>
+      <c r="A8" s="80"/>
       <c r="B8" s="81"/>
-      <c r="C8" s="80"/>
+      <c r="C8" s="79"/>
       <c r="D8" s="5" t="s">
         <v>25</v>
       </c>
@@ -1458,11 +2049,11 @@
       <c r="J9" s="6"/>
     </row>
     <row r="10" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="78" t="s">
+      <c r="A10" s="80" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="81"/>
-      <c r="C10" s="79" t="s">
+      <c r="C10" s="78" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="5" t="s">
@@ -1488,9 +2079,9 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="78"/>
+      <c r="A11" s="80"/>
       <c r="B11" s="81"/>
-      <c r="C11" s="80"/>
+      <c r="C11" s="79"/>
       <c r="D11" s="5" t="s">
         <v>24</v>
       </c>
@@ -1514,9 +2105,9 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="78"/>
+      <c r="A12" s="80"/>
       <c r="B12" s="81"/>
-      <c r="C12" s="80"/>
+      <c r="C12" s="79"/>
       <c r="D12" s="5" t="s">
         <v>25</v>
       </c>
@@ -1551,11 +2142,11 @@
       <c r="J13" s="6"/>
     </row>
     <row r="14" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A14" s="78" t="s">
+      <c r="A14" s="80" t="s">
         <v>10</v>
       </c>
       <c r="B14" s="81"/>
-      <c r="C14" s="79" t="s">
+      <c r="C14" s="78" t="s">
         <v>32</v>
       </c>
       <c r="D14" s="5" t="s">
@@ -1581,9 +2172,9 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A15" s="78"/>
+      <c r="A15" s="80"/>
       <c r="B15" s="81"/>
-      <c r="C15" s="80"/>
+      <c r="C15" s="79"/>
       <c r="D15" s="5" t="s">
         <v>24</v>
       </c>
@@ -1607,9 +2198,9 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A16" s="78"/>
+      <c r="A16" s="80"/>
       <c r="B16" s="81"/>
-      <c r="C16" s="80"/>
+      <c r="C16" s="79"/>
       <c r="D16" s="5" t="s">
         <v>25</v>
       </c>
@@ -1644,11 +2235,11 @@
       <c r="J17" s="6"/>
     </row>
     <row r="18" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A18" s="78" t="s">
+      <c r="A18" s="80" t="s">
         <v>14</v>
       </c>
       <c r="B18" s="81"/>
-      <c r="C18" s="79" t="s">
+      <c r="C18" s="78" t="s">
         <v>33</v>
       </c>
       <c r="D18" s="5" t="s">
@@ -1674,9 +2265,9 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A19" s="78"/>
+      <c r="A19" s="80"/>
       <c r="B19" s="81"/>
-      <c r="C19" s="80"/>
+      <c r="C19" s="79"/>
       <c r="D19" s="5" t="s">
         <v>24</v>
       </c>
@@ -1700,9 +2291,9 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A20" s="78"/>
+      <c r="A20" s="80"/>
       <c r="B20" s="81"/>
-      <c r="C20" s="80"/>
+      <c r="C20" s="79"/>
       <c r="D20" s="5" t="s">
         <v>25</v>
       </c>
@@ -1737,11 +2328,11 @@
       <c r="J21" s="6"/>
     </row>
     <row r="22" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A22" s="78" t="s">
+      <c r="A22" s="80" t="s">
         <v>12</v>
       </c>
       <c r="B22" s="81"/>
-      <c r="C22" s="79" t="s">
+      <c r="C22" s="78" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="5" t="s">
@@ -1767,9 +2358,9 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A23" s="78"/>
+      <c r="A23" s="80"/>
       <c r="B23" s="81"/>
-      <c r="C23" s="80"/>
+      <c r="C23" s="79"/>
       <c r="D23" s="5" t="s">
         <v>24</v>
       </c>
@@ -1793,9 +2384,9 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A24" s="78"/>
+      <c r="A24" s="80"/>
       <c r="B24" s="81"/>
-      <c r="C24" s="80"/>
+      <c r="C24" s="79"/>
       <c r="D24" s="5" t="s">
         <v>25</v>
       </c>
@@ -1830,11 +2421,11 @@
       <c r="J25" s="6"/>
     </row>
     <row r="26" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A26" s="78" t="s">
+      <c r="A26" s="80" t="s">
         <v>15</v>
       </c>
       <c r="B26" s="81"/>
-      <c r="C26" s="79" t="s">
+      <c r="C26" s="78" t="s">
         <v>35</v>
       </c>
       <c r="D26" s="8" t="s">
@@ -1860,9 +2451,9 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A27" s="78"/>
+      <c r="A27" s="80"/>
       <c r="B27" s="81"/>
-      <c r="C27" s="80"/>
+      <c r="C27" s="79"/>
       <c r="D27" s="5" t="s">
         <v>24</v>
       </c>
@@ -1886,9 +2477,9 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A28" s="78"/>
+      <c r="A28" s="80"/>
       <c r="B28" s="81"/>
-      <c r="C28" s="80"/>
+      <c r="C28" s="79"/>
       <c r="D28" s="5" t="s">
         <v>25</v>
       </c>
@@ -1923,11 +2514,11 @@
       <c r="J29" s="6"/>
     </row>
     <row r="30" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A30" s="78" t="s">
+      <c r="A30" s="80" t="s">
         <v>11</v>
       </c>
       <c r="B30" s="81"/>
-      <c r="C30" s="79" t="s">
+      <c r="C30" s="78" t="s">
         <v>36</v>
       </c>
       <c r="D30" s="8" t="s">
@@ -1953,9 +2544,9 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A31" s="78"/>
+      <c r="A31" s="80"/>
       <c r="B31" s="81"/>
-      <c r="C31" s="80"/>
+      <c r="C31" s="79"/>
       <c r="D31" s="5" t="s">
         <v>24</v>
       </c>
@@ -1979,9 +2570,9 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A32" s="78"/>
+      <c r="A32" s="80"/>
       <c r="B32" s="81"/>
-      <c r="C32" s="80"/>
+      <c r="C32" s="79"/>
       <c r="D32" s="8" t="s">
         <v>25</v>
       </c>
@@ -2016,13 +2607,13 @@
       <c r="J33" s="6"/>
     </row>
     <row r="34" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A34" s="78" t="s">
+      <c r="A34" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="78" t="s">
+      <c r="B34" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="79" t="s">
+      <c r="C34" s="78" t="s">
         <v>29</v>
       </c>
       <c r="D34" s="5" t="s">
@@ -2048,9 +2639,9 @@
       </c>
     </row>
     <row r="35" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A35" s="78"/>
-      <c r="B35" s="78"/>
-      <c r="C35" s="80"/>
+      <c r="A35" s="80"/>
+      <c r="B35" s="80"/>
+      <c r="C35" s="79"/>
       <c r="D35" s="5" t="s">
         <v>24</v>
       </c>
@@ -2074,9 +2665,9 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A36" s="78"/>
-      <c r="B36" s="78"/>
-      <c r="C36" s="80"/>
+      <c r="A36" s="80"/>
+      <c r="B36" s="80"/>
+      <c r="C36" s="79"/>
       <c r="D36" s="5" t="s">
         <v>25</v>
       </c>
@@ -2101,7 +2692,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
-      <c r="B37" s="78"/>
+      <c r="B37" s="80"/>
       <c r="C37" s="7"/>
       <c r="E37" s="4"/>
       <c r="F37" s="6"/>
@@ -2111,11 +2702,11 @@
       <c r="J37" s="6"/>
     </row>
     <row r="38" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A38" s="78" t="s">
+      <c r="A38" s="80" t="s">
         <v>20</v>
       </c>
-      <c r="B38" s="78"/>
-      <c r="C38" s="79" t="s">
+      <c r="B38" s="80"/>
+      <c r="C38" s="78" t="s">
         <v>30</v>
       </c>
       <c r="D38" s="5" t="s">
@@ -2141,9 +2732,9 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A39" s="78"/>
-      <c r="B39" s="78"/>
-      <c r="C39" s="80"/>
+      <c r="A39" s="80"/>
+      <c r="B39" s="80"/>
+      <c r="C39" s="79"/>
       <c r="D39" s="8" t="s">
         <v>24</v>
       </c>
@@ -2167,9 +2758,9 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A40" s="78"/>
-      <c r="B40" s="78"/>
-      <c r="C40" s="80"/>
+      <c r="A40" s="80"/>
+      <c r="B40" s="80"/>
+      <c r="C40" s="79"/>
       <c r="D40" s="5" t="s">
         <v>25</v>
       </c>
@@ -2194,7 +2785,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
-      <c r="B41" s="78"/>
+      <c r="B41" s="80"/>
       <c r="C41" s="7"/>
       <c r="E41" s="4"/>
       <c r="F41" s="6"/>
@@ -2204,11 +2795,11 @@
       <c r="J41" s="6"/>
     </row>
     <row r="42" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A42" s="78" t="s">
+      <c r="A42" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="B42" s="78"/>
-      <c r="C42" s="79" t="s">
+      <c r="B42" s="80"/>
+      <c r="C42" s="78" t="s">
         <v>31</v>
       </c>
       <c r="D42" s="5" t="s">
@@ -2234,9 +2825,9 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A43" s="78"/>
-      <c r="B43" s="78"/>
-      <c r="C43" s="80"/>
+      <c r="A43" s="80"/>
+      <c r="B43" s="80"/>
+      <c r="C43" s="79"/>
       <c r="D43" s="5" t="s">
         <v>24</v>
       </c>
@@ -2260,9 +2851,9 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A44" s="78"/>
-      <c r="B44" s="78"/>
-      <c r="C44" s="80"/>
+      <c r="A44" s="80"/>
+      <c r="B44" s="80"/>
+      <c r="C44" s="79"/>
       <c r="D44" s="5" t="s">
         <v>25</v>
       </c>
@@ -2287,7 +2878,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
-      <c r="B45" s="78"/>
+      <c r="B45" s="80"/>
       <c r="C45" s="7"/>
       <c r="E45" s="4"/>
       <c r="F45" s="6"/>
@@ -2297,11 +2888,11 @@
       <c r="J45" s="6"/>
     </row>
     <row r="46" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A46" s="78" t="s">
+      <c r="A46" s="80" t="s">
         <v>16</v>
       </c>
-      <c r="B46" s="78"/>
-      <c r="C46" s="79" t="s">
+      <c r="B46" s="80"/>
+      <c r="C46" s="78" t="s">
         <v>35</v>
       </c>
       <c r="D46" s="5" t="s">
@@ -2327,9 +2918,9 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A47" s="78"/>
-      <c r="B47" s="78"/>
-      <c r="C47" s="80"/>
+      <c r="A47" s="80"/>
+      <c r="B47" s="80"/>
+      <c r="C47" s="79"/>
       <c r="D47" s="5" t="s">
         <v>24</v>
       </c>
@@ -2353,9 +2944,9 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A48" s="78"/>
-      <c r="B48" s="78"/>
-      <c r="C48" s="80"/>
+      <c r="A48" s="80"/>
+      <c r="B48" s="80"/>
+      <c r="C48" s="79"/>
       <c r="D48" s="5" t="s">
         <v>25</v>
       </c>
@@ -2433,6 +3024,16 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="C38:C40"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="C10:C12"/>
@@ -2449,16 +3050,6 @@
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="A14:A16"/>
     <mergeCell ref="A30:A32"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="C38:C40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2511,13 +3102,13 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="80" t="s">
         <v>40</v>
       </c>
       <c r="B2" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="79" t="s">
+      <c r="C2" s="78" t="s">
         <v>29</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -2543,9 +3134,9 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A3" s="78"/>
+      <c r="A3" s="80"/>
       <c r="B3" s="81"/>
-      <c r="C3" s="80"/>
+      <c r="C3" s="79"/>
       <c r="D3" s="5" t="s">
         <v>24</v>
       </c>
@@ -2569,9 +3160,9 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="78"/>
+      <c r="A4" s="80"/>
       <c r="B4" s="81"/>
-      <c r="C4" s="80"/>
+      <c r="C4" s="79"/>
       <c r="D4" s="5" t="s">
         <v>25</v>
       </c>
@@ -2606,11 +3197,11 @@
       <c r="J5" s="6"/>
     </row>
     <row r="6" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="78" t="s">
+      <c r="A6" s="80" t="s">
         <v>41</v>
       </c>
       <c r="B6" s="81"/>
-      <c r="C6" s="79" t="s">
+      <c r="C6" s="78" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="5" t="s">
@@ -2636,9 +3227,9 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="78"/>
+      <c r="A7" s="80"/>
       <c r="B7" s="81"/>
-      <c r="C7" s="80"/>
+      <c r="C7" s="79"/>
       <c r="D7" s="5" t="s">
         <v>24</v>
       </c>
@@ -2662,9 +3253,9 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A8" s="78"/>
+      <c r="A8" s="80"/>
       <c r="B8" s="81"/>
-      <c r="C8" s="80"/>
+      <c r="C8" s="79"/>
       <c r="D8" s="8" t="s">
         <v>25</v>
       </c>
@@ -2699,11 +3290,11 @@
       <c r="J9" s="6"/>
     </row>
     <row r="10" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="78" t="s">
+      <c r="A10" s="80" t="s">
         <v>42</v>
       </c>
       <c r="B10" s="81"/>
-      <c r="C10" s="79" t="s">
+      <c r="C10" s="78" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="5" t="s">
@@ -2729,9 +3320,9 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="78"/>
+      <c r="A11" s="80"/>
       <c r="B11" s="81"/>
-      <c r="C11" s="80"/>
+      <c r="C11" s="79"/>
       <c r="D11" s="5" t="s">
         <v>24</v>
       </c>
@@ -2755,9 +3346,9 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="78"/>
+      <c r="A12" s="80"/>
       <c r="B12" s="81"/>
-      <c r="C12" s="80"/>
+      <c r="C12" s="79"/>
       <c r="D12" s="8" t="s">
         <v>25</v>
       </c>
@@ -2792,11 +3383,11 @@
       <c r="J13" s="6"/>
     </row>
     <row r="14" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A14" s="78" t="s">
+      <c r="A14" s="80" t="s">
         <v>43</v>
       </c>
       <c r="B14" s="81"/>
-      <c r="C14" s="79" t="s">
+      <c r="C14" s="78" t="s">
         <v>32</v>
       </c>
       <c r="D14" s="5" t="s">
@@ -2822,9 +3413,9 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A15" s="78"/>
+      <c r="A15" s="80"/>
       <c r="B15" s="81"/>
-      <c r="C15" s="80"/>
+      <c r="C15" s="79"/>
       <c r="D15" s="5" t="s">
         <v>24</v>
       </c>
@@ -2848,9 +3439,9 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A16" s="78"/>
+      <c r="A16" s="80"/>
       <c r="B16" s="81"/>
-      <c r="C16" s="80"/>
+      <c r="C16" s="79"/>
       <c r="D16" s="8" t="s">
         <v>25</v>
       </c>
@@ -2885,11 +3476,11 @@
       <c r="J17" s="6"/>
     </row>
     <row r="18" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A18" s="78" t="s">
+      <c r="A18" s="80" t="s">
         <v>53</v>
       </c>
       <c r="B18" s="81"/>
-      <c r="C18" s="79" t="s">
+      <c r="C18" s="78" t="s">
         <v>33</v>
       </c>
       <c r="D18" s="5" t="s">
@@ -2915,9 +3506,9 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A19" s="78"/>
+      <c r="A19" s="80"/>
       <c r="B19" s="81"/>
-      <c r="C19" s="80"/>
+      <c r="C19" s="79"/>
       <c r="D19" s="5" t="s">
         <v>24</v>
       </c>
@@ -2941,9 +3532,9 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A20" s="78"/>
+      <c r="A20" s="80"/>
       <c r="B20" s="81"/>
-      <c r="C20" s="80"/>
+      <c r="C20" s="79"/>
       <c r="D20" s="8" t="s">
         <v>25</v>
       </c>
@@ -2978,11 +3569,11 @@
       <c r="J21" s="6"/>
     </row>
     <row r="22" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A22" s="78" t="s">
+      <c r="A22" s="80" t="s">
         <v>52</v>
       </c>
       <c r="B22" s="81"/>
-      <c r="C22" s="79" t="s">
+      <c r="C22" s="78" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="5" t="s">
@@ -3008,9 +3599,9 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A23" s="78"/>
+      <c r="A23" s="80"/>
       <c r="B23" s="81"/>
-      <c r="C23" s="80"/>
+      <c r="C23" s="79"/>
       <c r="D23" s="5" t="s">
         <v>24</v>
       </c>
@@ -3034,9 +3625,9 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A24" s="78"/>
+      <c r="A24" s="80"/>
       <c r="B24" s="81"/>
-      <c r="C24" s="80"/>
+      <c r="C24" s="79"/>
       <c r="D24" s="5" t="s">
         <v>25</v>
       </c>
@@ -3071,11 +3662,11 @@
       <c r="J25" s="6"/>
     </row>
     <row r="26" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A26" s="78" t="s">
+      <c r="A26" s="80" t="s">
         <v>44</v>
       </c>
       <c r="B26" s="81"/>
-      <c r="C26" s="79" t="s">
+      <c r="C26" s="78" t="s">
         <v>35</v>
       </c>
       <c r="D26" s="8" t="s">
@@ -3101,9 +3692,9 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A27" s="78"/>
+      <c r="A27" s="80"/>
       <c r="B27" s="81"/>
-      <c r="C27" s="80"/>
+      <c r="C27" s="79"/>
       <c r="D27" s="5" t="s">
         <v>24</v>
       </c>
@@ -3127,9 +3718,9 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A28" s="78"/>
+      <c r="A28" s="80"/>
       <c r="B28" s="81"/>
-      <c r="C28" s="80"/>
+      <c r="C28" s="79"/>
       <c r="D28" s="8" t="s">
         <v>25</v>
       </c>
@@ -3164,11 +3755,11 @@
       <c r="J29" s="6"/>
     </row>
     <row r="30" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A30" s="78" t="s">
+      <c r="A30" s="80" t="s">
         <v>45</v>
       </c>
       <c r="B30" s="81"/>
-      <c r="C30" s="79" t="s">
+      <c r="C30" s="78" t="s">
         <v>36</v>
       </c>
       <c r="D30" s="5" t="s">
@@ -3194,9 +3785,9 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A31" s="78"/>
+      <c r="A31" s="80"/>
       <c r="B31" s="81"/>
-      <c r="C31" s="80"/>
+      <c r="C31" s="79"/>
       <c r="D31" s="5" t="s">
         <v>24</v>
       </c>
@@ -3220,9 +3811,9 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A32" s="78"/>
+      <c r="A32" s="80"/>
       <c r="B32" s="81"/>
-      <c r="C32" s="80"/>
+      <c r="C32" s="79"/>
       <c r="D32" s="5" t="s">
         <v>25</v>
       </c>
@@ -3257,13 +3848,13 @@
       <c r="J33" s="6"/>
     </row>
     <row r="34" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A34" s="78" t="s">
+      <c r="A34" s="80" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="78" t="s">
+      <c r="B34" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="79" t="s">
+      <c r="C34" s="78" t="s">
         <v>29</v>
       </c>
       <c r="D34" s="5" t="s">
@@ -3289,9 +3880,9 @@
       </c>
     </row>
     <row r="35" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A35" s="78"/>
-      <c r="B35" s="78"/>
-      <c r="C35" s="80"/>
+      <c r="A35" s="80"/>
+      <c r="B35" s="80"/>
+      <c r="C35" s="79"/>
       <c r="D35" s="5" t="s">
         <v>24</v>
       </c>
@@ -3315,9 +3906,9 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A36" s="78"/>
-      <c r="B36" s="78"/>
-      <c r="C36" s="80"/>
+      <c r="A36" s="80"/>
+      <c r="B36" s="80"/>
+      <c r="C36" s="79"/>
       <c r="D36" s="5" t="s">
         <v>25</v>
       </c>
@@ -3342,7 +3933,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
-      <c r="B37" s="78"/>
+      <c r="B37" s="80"/>
       <c r="C37" s="7"/>
       <c r="E37" s="4"/>
       <c r="F37" s="6"/>
@@ -3352,11 +3943,11 @@
       <c r="J37" s="6"/>
     </row>
     <row r="38" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A38" s="78" t="s">
+      <c r="A38" s="80" t="s">
         <v>47</v>
       </c>
-      <c r="B38" s="78"/>
-      <c r="C38" s="79" t="s">
+      <c r="B38" s="80"/>
+      <c r="C38" s="78" t="s">
         <v>30</v>
       </c>
       <c r="D38" s="5" t="s">
@@ -3382,9 +3973,9 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A39" s="78"/>
-      <c r="B39" s="78"/>
-      <c r="C39" s="80"/>
+      <c r="A39" s="80"/>
+      <c r="B39" s="80"/>
+      <c r="C39" s="79"/>
       <c r="D39" s="5" t="s">
         <v>24</v>
       </c>
@@ -3408,9 +3999,9 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A40" s="78"/>
-      <c r="B40" s="78"/>
-      <c r="C40" s="80"/>
+      <c r="A40" s="80"/>
+      <c r="B40" s="80"/>
+      <c r="C40" s="79"/>
       <c r="D40" s="5" t="s">
         <v>25</v>
       </c>
@@ -3435,7 +4026,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
-      <c r="B41" s="78"/>
+      <c r="B41" s="80"/>
       <c r="C41" s="7"/>
       <c r="E41" s="4"/>
       <c r="F41" s="6"/>
@@ -3445,11 +4036,11 @@
       <c r="J41" s="6"/>
     </row>
     <row r="42" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A42" s="78" t="s">
+      <c r="A42" s="80" t="s">
         <v>48</v>
       </c>
-      <c r="B42" s="78"/>
-      <c r="C42" s="79" t="s">
+      <c r="B42" s="80"/>
+      <c r="C42" s="78" t="s">
         <v>31</v>
       </c>
       <c r="D42" s="5" t="s">
@@ -3475,9 +4066,9 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A43" s="78"/>
-      <c r="B43" s="78"/>
-      <c r="C43" s="80"/>
+      <c r="A43" s="80"/>
+      <c r="B43" s="80"/>
+      <c r="C43" s="79"/>
       <c r="D43" s="5" t="s">
         <v>24</v>
       </c>
@@ -3501,9 +4092,9 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A44" s="78"/>
-      <c r="B44" s="78"/>
-      <c r="C44" s="80"/>
+      <c r="A44" s="80"/>
+      <c r="B44" s="80"/>
+      <c r="C44" s="79"/>
       <c r="D44" s="5" t="s">
         <v>25</v>
       </c>
@@ -3528,7 +4119,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
-      <c r="B45" s="78"/>
+      <c r="B45" s="80"/>
       <c r="C45" s="7"/>
       <c r="E45" s="4"/>
       <c r="F45" s="6"/>
@@ -3538,11 +4129,11 @@
       <c r="J45" s="6"/>
     </row>
     <row r="46" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A46" s="78" t="s">
+      <c r="A46" s="80" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="78"/>
-      <c r="C46" s="79" t="s">
+      <c r="B46" s="80"/>
+      <c r="C46" s="78" t="s">
         <v>35</v>
       </c>
       <c r="D46" s="8" t="s">
@@ -3568,9 +4159,9 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A47" s="78"/>
-      <c r="B47" s="78"/>
-      <c r="C47" s="80"/>
+      <c r="A47" s="80"/>
+      <c r="B47" s="80"/>
+      <c r="C47" s="79"/>
       <c r="D47" s="8" t="s">
         <v>24</v>
       </c>
@@ -3594,9 +4185,9 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A48" s="78"/>
-      <c r="B48" s="78"/>
-      <c r="C48" s="80"/>
+      <c r="A48" s="80"/>
+      <c r="B48" s="80"/>
+      <c r="C48" s="79"/>
       <c r="D48" s="5" t="s">
         <v>25</v>
       </c>
@@ -3674,6 +4265,16 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="B34:B48"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="C46:C48"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B32"/>
     <mergeCell ref="C2:C4"/>
@@ -3690,16 +4291,6 @@
     <mergeCell ref="A26:A28"/>
     <mergeCell ref="C26:C28"/>
     <mergeCell ref="A30:A32"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="B34:B48"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="C46:C48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3764,10 +4355,10 @@
       <c r="A2" s="81" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="78" t="s">
+      <c r="B2" s="80" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="79" t="s">
+      <c r="C2" s="78" t="s">
         <v>29</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -3806,8 +4397,8 @@
     </row>
     <row r="3" spans="1:13" ht="20" x14ac:dyDescent="0.2">
       <c r="A3" s="81"/>
-      <c r="B3" s="78"/>
-      <c r="C3" s="80"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="79"/>
       <c r="D3" s="5" t="s">
         <v>24</v>
       </c>
@@ -3844,8 +4435,8 @@
     </row>
     <row r="4" spans="1:13" ht="20" x14ac:dyDescent="0.2">
       <c r="A4" s="81"/>
-      <c r="B4" s="78"/>
-      <c r="C4" s="80"/>
+      <c r="B4" s="80"/>
+      <c r="C4" s="79"/>
       <c r="D4" s="5" t="s">
         <v>25</v>
       </c>
@@ -3893,10 +4484,10 @@
     </row>
     <row r="6" spans="1:13" ht="20" x14ac:dyDescent="0.2">
       <c r="A6" s="81"/>
-      <c r="B6" s="78" t="s">
+      <c r="B6" s="80" t="s">
         <v>76</v>
       </c>
-      <c r="C6" s="79" t="s">
+      <c r="C6" s="78" t="s">
         <v>30</v>
       </c>
       <c r="D6" s="5" t="s">
@@ -3935,8 +4526,8 @@
     </row>
     <row r="7" spans="1:13" ht="20" x14ac:dyDescent="0.2">
       <c r="A7" s="81"/>
-      <c r="B7" s="78"/>
-      <c r="C7" s="80"/>
+      <c r="B7" s="80"/>
+      <c r="C7" s="79"/>
       <c r="D7" s="5" t="s">
         <v>24</v>
       </c>
@@ -3973,8 +4564,8 @@
     </row>
     <row r="8" spans="1:13" ht="20" x14ac:dyDescent="0.2">
       <c r="A8" s="81"/>
-      <c r="B8" s="78"/>
-      <c r="C8" s="80"/>
+      <c r="B8" s="80"/>
+      <c r="C8" s="79"/>
       <c r="D8" s="8" t="s">
         <v>25</v>
       </c>
@@ -4022,10 +4613,10 @@
     </row>
     <row r="10" spans="1:13" ht="20" x14ac:dyDescent="0.2">
       <c r="A10" s="81"/>
-      <c r="B10" s="78" t="s">
+      <c r="B10" s="80" t="s">
         <v>77</v>
       </c>
-      <c r="C10" s="79" t="s">
+      <c r="C10" s="78" t="s">
         <v>31</v>
       </c>
       <c r="D10" s="5" t="s">
@@ -4064,8 +4655,8 @@
     </row>
     <row r="11" spans="1:13" ht="20" x14ac:dyDescent="0.2">
       <c r="A11" s="81"/>
-      <c r="B11" s="78"/>
-      <c r="C11" s="80"/>
+      <c r="B11" s="80"/>
+      <c r="C11" s="79"/>
       <c r="D11" s="5" t="s">
         <v>24</v>
       </c>
@@ -4102,8 +4693,8 @@
     </row>
     <row r="12" spans="1:13" ht="20" x14ac:dyDescent="0.2">
       <c r="A12" s="81"/>
-      <c r="B12" s="78"/>
-      <c r="C12" s="80"/>
+      <c r="B12" s="80"/>
+      <c r="C12" s="79"/>
       <c r="D12" s="5" t="s">
         <v>25</v>
       </c>
@@ -4151,10 +4742,10 @@
     </row>
     <row r="14" spans="1:13" ht="20" x14ac:dyDescent="0.2">
       <c r="A14" s="81"/>
-      <c r="B14" s="78" t="s">
+      <c r="B14" s="80" t="s">
         <v>78</v>
       </c>
-      <c r="C14" s="79" t="s">
+      <c r="C14" s="78" t="s">
         <v>32</v>
       </c>
       <c r="D14" s="5" t="s">
@@ -4193,8 +4784,8 @@
     </row>
     <row r="15" spans="1:13" ht="20" x14ac:dyDescent="0.2">
       <c r="A15" s="81"/>
-      <c r="B15" s="78"/>
-      <c r="C15" s="80"/>
+      <c r="B15" s="80"/>
+      <c r="C15" s="79"/>
       <c r="D15" s="5" t="s">
         <v>24</v>
       </c>
@@ -4231,8 +4822,8 @@
     </row>
     <row r="16" spans="1:13" ht="20" x14ac:dyDescent="0.2">
       <c r="A16" s="81"/>
-      <c r="B16" s="78"/>
-      <c r="C16" s="80"/>
+      <c r="B16" s="80"/>
+      <c r="C16" s="79"/>
       <c r="D16" s="5" t="s">
         <v>25</v>
       </c>
@@ -4280,10 +4871,10 @@
     </row>
     <row r="18" spans="1:13" ht="20" x14ac:dyDescent="0.2">
       <c r="A18" s="81"/>
-      <c r="B18" s="78" t="s">
+      <c r="B18" s="80" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="79" t="s">
+      <c r="C18" s="78" t="s">
         <v>33</v>
       </c>
       <c r="D18" s="5" t="s">
@@ -4322,8 +4913,8 @@
     </row>
     <row r="19" spans="1:13" ht="20" x14ac:dyDescent="0.2">
       <c r="A19" s="81"/>
-      <c r="B19" s="78"/>
-      <c r="C19" s="80"/>
+      <c r="B19" s="80"/>
+      <c r="C19" s="79"/>
       <c r="D19" s="5" t="s">
         <v>24</v>
       </c>
@@ -4360,8 +4951,8 @@
     </row>
     <row r="20" spans="1:13" ht="20" x14ac:dyDescent="0.2">
       <c r="A20" s="81"/>
-      <c r="B20" s="78"/>
-      <c r="C20" s="80"/>
+      <c r="B20" s="80"/>
+      <c r="C20" s="79"/>
       <c r="D20" s="5" t="s">
         <v>25</v>
       </c>
@@ -4409,10 +5000,10 @@
     </row>
     <row r="22" spans="1:13" ht="20" x14ac:dyDescent="0.2">
       <c r="A22" s="81"/>
-      <c r="B22" s="78" t="s">
+      <c r="B22" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="79" t="s">
+      <c r="C22" s="78" t="s">
         <v>34</v>
       </c>
       <c r="D22" s="5" t="s">
@@ -4451,8 +5042,8 @@
     </row>
     <row r="23" spans="1:13" ht="20" x14ac:dyDescent="0.2">
       <c r="A23" s="81"/>
-      <c r="B23" s="78"/>
-      <c r="C23" s="80"/>
+      <c r="B23" s="80"/>
+      <c r="C23" s="79"/>
       <c r="D23" s="5" t="s">
         <v>24</v>
       </c>
@@ -4489,8 +5080,8 @@
     </row>
     <row r="24" spans="1:13" ht="20" x14ac:dyDescent="0.2">
       <c r="A24" s="81"/>
-      <c r="B24" s="78"/>
-      <c r="C24" s="80"/>
+      <c r="B24" s="80"/>
+      <c r="C24" s="79"/>
       <c r="D24" s="5" t="s">
         <v>25</v>
       </c>
@@ -4538,10 +5129,10 @@
     </row>
     <row r="26" spans="1:13" ht="20" x14ac:dyDescent="0.2">
       <c r="A26" s="81"/>
-      <c r="B26" s="78" t="s">
+      <c r="B26" s="80" t="s">
         <v>81</v>
       </c>
-      <c r="C26" s="79" t="s">
+      <c r="C26" s="78" t="s">
         <v>35</v>
       </c>
       <c r="D26" s="5" t="s">
@@ -4580,8 +5171,8 @@
     </row>
     <row r="27" spans="1:13" ht="20" x14ac:dyDescent="0.2">
       <c r="A27" s="81"/>
-      <c r="B27" s="78"/>
-      <c r="C27" s="80"/>
+      <c r="B27" s="80"/>
+      <c r="C27" s="79"/>
       <c r="D27" s="5" t="s">
         <v>24</v>
       </c>
@@ -4618,8 +5209,8 @@
     </row>
     <row r="28" spans="1:13" ht="20" x14ac:dyDescent="0.2">
       <c r="A28" s="81"/>
-      <c r="B28" s="78"/>
-      <c r="C28" s="80"/>
+      <c r="B28" s="80"/>
+      <c r="C28" s="79"/>
       <c r="D28" s="5" t="s">
         <v>25</v>
       </c>
@@ -4667,10 +5258,10 @@
     </row>
     <row r="30" spans="1:13" ht="20" x14ac:dyDescent="0.2">
       <c r="A30" s="81"/>
-      <c r="B30" s="78" t="s">
+      <c r="B30" s="80" t="s">
         <v>82</v>
       </c>
-      <c r="C30" s="79" t="s">
+      <c r="C30" s="78" t="s">
         <v>36</v>
       </c>
       <c r="D30" s="8" t="s">
@@ -4709,8 +5300,8 @@
     </row>
     <row r="31" spans="1:13" ht="20" x14ac:dyDescent="0.2">
       <c r="A31" s="81"/>
-      <c r="B31" s="78"/>
-      <c r="C31" s="80"/>
+      <c r="B31" s="80"/>
+      <c r="C31" s="79"/>
       <c r="D31" s="5" t="s">
         <v>24</v>
       </c>
@@ -4747,8 +5338,8 @@
     </row>
     <row r="32" spans="1:13" ht="20" x14ac:dyDescent="0.2">
       <c r="A32" s="81"/>
-      <c r="B32" s="78"/>
-      <c r="C32" s="80"/>
+      <c r="B32" s="80"/>
+      <c r="C32" s="79"/>
       <c r="D32" s="5" t="s">
         <v>25</v>
       </c>
@@ -4795,13 +5386,13 @@
       <c r="J33" s="6"/>
     </row>
     <row r="34" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A34" s="78" t="s">
+      <c r="A34" s="80" t="s">
         <v>51</v>
       </c>
-      <c r="B34" s="78" t="s">
+      <c r="B34" s="80" t="s">
         <v>83</v>
       </c>
-      <c r="C34" s="79" t="s">
+      <c r="C34" s="78" t="s">
         <v>29</v>
       </c>
       <c r="D34" s="5" t="s">
@@ -4839,9 +5430,9 @@
       </c>
     </row>
     <row r="35" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A35" s="78"/>
-      <c r="B35" s="78"/>
-      <c r="C35" s="80"/>
+      <c r="A35" s="80"/>
+      <c r="B35" s="80"/>
+      <c r="C35" s="79"/>
       <c r="D35" s="5" t="s">
         <v>24</v>
       </c>
@@ -4877,9 +5468,9 @@
       </c>
     </row>
     <row r="36" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A36" s="78"/>
-      <c r="B36" s="78"/>
-      <c r="C36" s="80"/>
+      <c r="A36" s="80"/>
+      <c r="B36" s="80"/>
+      <c r="C36" s="79"/>
       <c r="D36" s="5" t="s">
         <v>25</v>
       </c>
@@ -4915,7 +5506,7 @@
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A37" s="78"/>
+      <c r="A37" s="80"/>
       <c r="B37" s="4"/>
       <c r="C37" s="7"/>
       <c r="E37" s="4"/>
@@ -4926,11 +5517,11 @@
       <c r="J37" s="6"/>
     </row>
     <row r="38" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A38" s="78"/>
-      <c r="B38" s="78" t="s">
+      <c r="A38" s="80"/>
+      <c r="B38" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="C38" s="79" t="s">
+      <c r="C38" s="78" t="s">
         <v>30</v>
       </c>
       <c r="D38" s="5" t="s">
@@ -4968,9 +5559,9 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A39" s="78"/>
-      <c r="B39" s="78"/>
-      <c r="C39" s="80"/>
+      <c r="A39" s="80"/>
+      <c r="B39" s="80"/>
+      <c r="C39" s="79"/>
       <c r="D39" s="8" t="s">
         <v>24</v>
       </c>
@@ -5006,9 +5597,9 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A40" s="78"/>
-      <c r="B40" s="78"/>
-      <c r="C40" s="80"/>
+      <c r="A40" s="80"/>
+      <c r="B40" s="80"/>
+      <c r="C40" s="79"/>
       <c r="D40" s="5" t="s">
         <v>25</v>
       </c>
@@ -5044,7 +5635,7 @@
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A41" s="78"/>
+      <c r="A41" s="80"/>
       <c r="B41" s="4"/>
       <c r="C41" s="7"/>
       <c r="E41" s="4"/>
@@ -5055,11 +5646,11 @@
       <c r="J41" s="6"/>
     </row>
     <row r="42" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A42" s="78"/>
-      <c r="B42" s="78" t="s">
+      <c r="A42" s="80"/>
+      <c r="B42" s="80" t="s">
         <v>85</v>
       </c>
-      <c r="C42" s="79" t="s">
+      <c r="C42" s="78" t="s">
         <v>31</v>
       </c>
       <c r="D42" s="5" t="s">
@@ -5097,9 +5688,9 @@
       </c>
     </row>
     <row r="43" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A43" s="78"/>
-      <c r="B43" s="78"/>
-      <c r="C43" s="80"/>
+      <c r="A43" s="80"/>
+      <c r="B43" s="80"/>
+      <c r="C43" s="79"/>
       <c r="D43" s="5" t="s">
         <v>24</v>
       </c>
@@ -5135,9 +5726,9 @@
       </c>
     </row>
     <row r="44" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A44" s="78"/>
-      <c r="B44" s="78"/>
-      <c r="C44" s="80"/>
+      <c r="A44" s="80"/>
+      <c r="B44" s="80"/>
+      <c r="C44" s="79"/>
       <c r="D44" s="5" t="s">
         <v>25</v>
       </c>
@@ -5173,7 +5764,7 @@
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A45" s="78"/>
+      <c r="A45" s="80"/>
       <c r="B45" s="4"/>
       <c r="C45" s="7"/>
       <c r="E45" s="4"/>
@@ -5184,11 +5775,11 @@
       <c r="J45" s="6"/>
     </row>
     <row r="46" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A46" s="78"/>
-      <c r="B46" s="78" t="s">
+      <c r="A46" s="80"/>
+      <c r="B46" s="80" t="s">
         <v>86</v>
       </c>
-      <c r="C46" s="79" t="s">
+      <c r="C46" s="78" t="s">
         <v>35</v>
       </c>
       <c r="D46" s="8" t="s">
@@ -5226,9 +5817,9 @@
       </c>
     </row>
     <row r="47" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A47" s="78"/>
-      <c r="B47" s="78"/>
-      <c r="C47" s="80"/>
+      <c r="A47" s="80"/>
+      <c r="B47" s="80"/>
+      <c r="C47" s="79"/>
       <c r="D47" s="5" t="s">
         <v>24</v>
       </c>
@@ -5264,9 +5855,9 @@
       </c>
     </row>
     <row r="48" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A48" s="78"/>
-      <c r="B48" s="78"/>
-      <c r="C48" s="80"/>
+      <c r="A48" s="80"/>
+      <c r="B48" s="80"/>
+      <c r="C48" s="79"/>
       <c r="D48" s="5" t="s">
         <v>25</v>
       </c>
@@ -5417,16 +6008,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="A34:A48"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="B38:B40"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="C46:C48"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="A2:A32"/>
     <mergeCell ref="C2:C4"/>
@@ -5443,6 +6024,16 @@
     <mergeCell ref="B26:B28"/>
     <mergeCell ref="C26:C28"/>
     <mergeCell ref="B30:B32"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="A34:A48"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="B38:B40"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="C46:C48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5508,7 +6099,7 @@
       </c>
     </row>
     <row r="2" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A2" s="78" t="s">
+      <c r="A2" s="80" t="s">
         <v>76</v>
       </c>
       <c r="B2" s="82" t="s">
@@ -5555,8 +6146,8 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A3" s="78"/>
-      <c r="B3" s="78"/>
+      <c r="A3" s="80"/>
+      <c r="B3" s="80"/>
       <c r="C3" s="5" t="s">
         <v>24</v>
       </c>
@@ -5598,8 +6189,8 @@
       </c>
     </row>
     <row r="4" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="78"/>
-      <c r="B4" s="78"/>
+      <c r="A4" s="80"/>
+      <c r="B4" s="80"/>
       <c r="C4" s="5" t="s">
         <v>25</v>
       </c>
@@ -5654,10 +6245,10 @@
       <c r="M5" s="26"/>
     </row>
     <row r="6" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="78" t="s">
+      <c r="A6" s="80" t="s">
         <v>84</v>
       </c>
-      <c r="B6" s="78" t="s">
+      <c r="B6" s="80" t="s">
         <v>98</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -5701,8 +6292,8 @@
       </c>
     </row>
     <row r="7" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="78"/>
-      <c r="B7" s="78"/>
+      <c r="A7" s="80"/>
+      <c r="B7" s="80"/>
       <c r="C7" s="38" t="s">
         <v>24</v>
       </c>
@@ -5744,8 +6335,8 @@
       </c>
     </row>
     <row r="8" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A8" s="78"/>
-      <c r="B8" s="78"/>
+      <c r="A8" s="80"/>
+      <c r="B8" s="80"/>
       <c r="C8" s="5" t="s">
         <v>25</v>
       </c>
@@ -5800,10 +6391,10 @@
       <c r="M9" s="26"/>
     </row>
     <row r="10" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="78" t="s">
+      <c r="A10" s="80" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="78" t="s">
+      <c r="B10" s="80" t="s">
         <v>99</v>
       </c>
       <c r="C10" s="5" t="s">
@@ -5847,8 +6438,8 @@
       </c>
     </row>
     <row r="11" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="78"/>
-      <c r="B11" s="78"/>
+      <c r="A11" s="80"/>
+      <c r="B11" s="80"/>
       <c r="C11" s="5" t="s">
         <v>24</v>
       </c>
@@ -5890,8 +6481,8 @@
       </c>
     </row>
     <row r="12" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="78"/>
-      <c r="B12" s="78"/>
+      <c r="A12" s="80"/>
+      <c r="B12" s="80"/>
       <c r="C12" s="5" t="s">
         <v>25</v>
       </c>
@@ -6550,8 +7141,8 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A3" s="78"/>
-      <c r="B3" s="78"/>
+      <c r="A3" s="80"/>
+      <c r="B3" s="80"/>
       <c r="C3" s="81"/>
       <c r="D3" s="5" t="s">
         <v>24</v>
@@ -6594,8 +7185,8 @@
       </c>
     </row>
     <row r="4" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="78"/>
-      <c r="B4" s="78"/>
+      <c r="A4" s="80"/>
+      <c r="B4" s="80"/>
       <c r="C4" s="81"/>
       <c r="D4" s="5" t="s">
         <v>25</v>
@@ -6638,8 +7229,8 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="78"/>
-      <c r="B5" s="78"/>
+      <c r="A5" s="80"/>
+      <c r="B5" s="80"/>
       <c r="C5" s="21"/>
       <c r="E5" s="4"/>
       <c r="F5" s="6"/>
@@ -6653,8 +7244,8 @@
       <c r="N5" s="26"/>
     </row>
     <row r="6" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="78"/>
-      <c r="B6" s="78"/>
+      <c r="A6" s="80"/>
+      <c r="B6" s="80"/>
       <c r="C6" s="81">
         <v>10</v>
       </c>
@@ -6699,8 +7290,8 @@
       </c>
     </row>
     <row r="7" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="78"/>
-      <c r="B7" s="78"/>
+      <c r="A7" s="80"/>
+      <c r="B7" s="80"/>
       <c r="C7" s="81"/>
       <c r="D7" s="5" t="s">
         <v>24</v>
@@ -6743,8 +7334,8 @@
       </c>
     </row>
     <row r="8" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A8" s="78"/>
-      <c r="B8" s="78"/>
+      <c r="A8" s="80"/>
+      <c r="B8" s="80"/>
       <c r="C8" s="81"/>
       <c r="D8" s="5" t="s">
         <v>25</v>
@@ -6787,8 +7378,8 @@
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A9" s="78"/>
-      <c r="B9" s="78"/>
+      <c r="A9" s="80"/>
+      <c r="B9" s="80"/>
       <c r="C9" s="21"/>
       <c r="E9" s="4"/>
       <c r="F9" s="6"/>
@@ -6802,8 +7393,8 @@
       <c r="N9" s="26"/>
     </row>
     <row r="10" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="78"/>
-      <c r="B10" s="78"/>
+      <c r="A10" s="80"/>
+      <c r="B10" s="80"/>
       <c r="C10" s="81">
         <v>20</v>
       </c>
@@ -6848,8 +7439,8 @@
       </c>
     </row>
     <row r="11" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="78"/>
-      <c r="B11" s="78"/>
+      <c r="A11" s="80"/>
+      <c r="B11" s="80"/>
       <c r="C11" s="81"/>
       <c r="D11" s="5" t="s">
         <v>24</v>
@@ -6892,8 +7483,8 @@
       </c>
     </row>
     <row r="12" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="78"/>
-      <c r="B12" s="78"/>
+      <c r="A12" s="80"/>
+      <c r="B12" s="80"/>
       <c r="C12" s="81"/>
       <c r="D12" s="5" t="s">
         <v>25</v>
@@ -6936,8 +7527,8 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A13" s="78"/>
-      <c r="B13" s="78"/>
+      <c r="A13" s="80"/>
+      <c r="B13" s="80"/>
       <c r="C13" s="21"/>
       <c r="E13" s="4"/>
       <c r="F13" s="6"/>
@@ -6951,8 +7542,8 @@
       <c r="N13" s="26"/>
     </row>
     <row r="14" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A14" s="78"/>
-      <c r="B14" s="78"/>
+      <c r="A14" s="80"/>
+      <c r="B14" s="80"/>
       <c r="C14" s="81">
         <v>30</v>
       </c>
@@ -6997,8 +7588,8 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A15" s="78"/>
-      <c r="B15" s="78"/>
+      <c r="A15" s="80"/>
+      <c r="B15" s="80"/>
       <c r="C15" s="81"/>
       <c r="D15" s="5" t="s">
         <v>24</v>
@@ -7041,8 +7632,8 @@
       </c>
     </row>
     <row r="16" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A16" s="78"/>
-      <c r="B16" s="78"/>
+      <c r="A16" s="80"/>
+      <c r="B16" s="80"/>
       <c r="C16" s="81"/>
       <c r="D16" s="5" t="s">
         <v>25</v>
@@ -7085,8 +7676,8 @@
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A17" s="78"/>
-      <c r="B17" s="78"/>
+      <c r="A17" s="80"/>
+      <c r="B17" s="80"/>
       <c r="C17" s="23"/>
       <c r="E17" s="24"/>
       <c r="F17" s="19"/>
@@ -7100,8 +7691,8 @@
       <c r="N17" s="26"/>
     </row>
     <row r="18" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A18" s="78"/>
-      <c r="B18" s="78"/>
+      <c r="A18" s="80"/>
+      <c r="B18" s="80"/>
       <c r="C18" s="81">
         <v>100</v>
       </c>
@@ -7146,8 +7737,8 @@
       </c>
     </row>
     <row r="19" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A19" s="78"/>
-      <c r="B19" s="78"/>
+      <c r="A19" s="80"/>
+      <c r="B19" s="80"/>
       <c r="C19" s="81"/>
       <c r="D19" s="5" t="s">
         <v>24</v>
@@ -7190,8 +7781,8 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A20" s="78"/>
-      <c r="B20" s="78"/>
+      <c r="A20" s="80"/>
+      <c r="B20" s="80"/>
       <c r="C20" s="81"/>
       <c r="D20" s="5" t="s">
         <v>25</v>
@@ -8813,4 +9404,432 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025D3266-9124-624A-BC0F-EF159BDF8541}">
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="65.33203125" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="45" style="92" customWidth="1"/>
+    <col min="2" max="2" width="61.1640625" style="92" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53" style="92" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5" style="93" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="65.33203125" style="94"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="91" customFormat="1" ht="25" x14ac:dyDescent="0.2">
+      <c r="A1" s="89" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="89" t="s">
+        <v>112</v>
+      </c>
+      <c r="C1" s="89" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="90" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A2" s="92" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="92" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2" s="92" t="s">
+        <v>110</v>
+      </c>
+      <c r="D2" s="93">
+        <v>0.68325173248234505</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A3" s="92" t="s">
+        <v>127</v>
+      </c>
+      <c r="B3" s="92" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" s="92" t="s">
+        <v>110</v>
+      </c>
+      <c r="D3" s="93">
+        <v>0.68325173248234505</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A4" s="92" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="92" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="92" t="s">
+        <v>110</v>
+      </c>
+      <c r="D4" s="93">
+        <v>0.68325173248234505</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A5" s="92" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" s="92" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="92" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" s="93">
+        <v>0.68041836283516299</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A6" s="92" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="92" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" s="92" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" s="93">
+        <v>0.67742712096802804</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A7" s="92" t="s">
+        <v>127</v>
+      </c>
+      <c r="B7" s="92" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="92" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" s="93">
+        <v>0.65343720964277696</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A8" s="92" t="s">
+        <v>130</v>
+      </c>
+      <c r="B8" s="92" t="s">
+        <v>131</v>
+      </c>
+      <c r="D8" s="93">
+        <v>0.64949999999999997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A9" s="92" t="s">
+        <v>127</v>
+      </c>
+      <c r="B9" s="92" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="92" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" s="93">
+        <v>0.64262720538739304</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A10" s="92" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" s="92" t="s">
+        <v>129</v>
+      </c>
+      <c r="C10" s="92" t="s">
+        <v>128</v>
+      </c>
+      <c r="D10" s="93">
+        <v>0.63939999999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="22" x14ac:dyDescent="0.2">
+      <c r="A11" s="92" t="s">
+        <v>113</v>
+      </c>
+      <c r="B11" s="92" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11" s="93">
+        <v>0.60415152730396504</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="22" x14ac:dyDescent="0.2">
+      <c r="A12" s="92" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="95" t="s">
+        <v>108</v>
+      </c>
+      <c r="D12" s="93">
+        <v>0.603348181891603</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A13" s="92" t="s">
+        <v>114</v>
+      </c>
+      <c r="B13" s="92" t="s">
+        <v>115</v>
+      </c>
+      <c r="D13" s="93">
+        <v>0.57569693797857102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A14" s="92" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="92" t="s">
+        <v>123</v>
+      </c>
+      <c r="C14" s="92" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" s="93">
+        <v>0.57370283757216001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A15" s="92" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" s="92" t="s">
+        <v>117</v>
+      </c>
+      <c r="D15" s="93">
+        <v>0.51741735167898695</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D15">
+    <sortCondition descending="1" ref="D1:D15"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E37A00BD-B64F-384F-8AA4-A9588C0E9EEE}">
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="65.33203125" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="3" width="65.33203125" style="92"/>
+    <col min="4" max="4" width="65.33203125" style="93"/>
+    <col min="5" max="16384" width="65.33203125" style="94"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" s="91" customFormat="1" ht="25" x14ac:dyDescent="0.2">
+      <c r="A1" s="89" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="89" t="s">
+        <v>112</v>
+      </c>
+      <c r="C1" s="89" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="90" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A2" s="92" t="s">
+        <v>127</v>
+      </c>
+      <c r="B2" s="92" t="s">
+        <v>140</v>
+      </c>
+      <c r="C2" s="92" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2" s="93">
+        <v>0.73470000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A3" s="92" t="s">
+        <v>130</v>
+      </c>
+      <c r="B3" s="92" t="s">
+        <v>141</v>
+      </c>
+      <c r="D3" s="93">
+        <v>0.7097</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="22" x14ac:dyDescent="0.2">
+      <c r="A4" s="92" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" s="92" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="93">
+        <v>0.69406628387897396</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A5" s="92" t="s">
+        <v>127</v>
+      </c>
+      <c r="B5" s="92" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" s="92" t="s">
+        <v>143</v>
+      </c>
+      <c r="D5" s="93">
+        <v>0.665770082977021</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A6" s="92" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="92" t="s">
+        <v>135</v>
+      </c>
+      <c r="C6" s="92" t="s">
+        <v>143</v>
+      </c>
+      <c r="D6" s="93">
+        <v>0.65203403508906599</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A7" s="92" t="s">
+        <v>127</v>
+      </c>
+      <c r="B7" s="92" t="s">
+        <v>136</v>
+      </c>
+      <c r="C7" s="92" t="s">
+        <v>143</v>
+      </c>
+      <c r="D7" s="93">
+        <v>0.60864643260521401</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="22" x14ac:dyDescent="0.2">
+      <c r="A8" s="92" t="s">
+        <v>113</v>
+      </c>
+      <c r="B8" s="92" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" s="93">
+        <v>0.60415152730396504</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A9" s="92" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" s="92" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" s="93">
+        <v>0.59785011377850095</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A10" s="92" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" s="92" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" s="92" t="s">
+        <v>143</v>
+      </c>
+      <c r="D10" s="93">
+        <v>0.58596491228070102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A11" s="92" t="s">
+        <v>127</v>
+      </c>
+      <c r="B11" s="92" t="s">
+        <v>139</v>
+      </c>
+      <c r="C11" s="92" t="s">
+        <v>143</v>
+      </c>
+      <c r="D11" s="93">
+        <v>0.58596491228070102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A12" s="92" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="92" t="s">
+        <v>132</v>
+      </c>
+      <c r="C12" s="92" t="s">
+        <v>143</v>
+      </c>
+      <c r="D12" s="93">
+        <v>0.57994647302866398</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A13" s="92" t="s">
+        <v>127</v>
+      </c>
+      <c r="B13" s="92" t="s">
+        <v>138</v>
+      </c>
+      <c r="C13" s="92" t="s">
+        <v>143</v>
+      </c>
+      <c r="D13" s="93">
+        <v>0.579743455999432</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A14" s="92" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="92" t="s">
+        <v>137</v>
+      </c>
+      <c r="C14" s="92" t="s">
+        <v>143</v>
+      </c>
+      <c r="D14" s="93">
+        <v>0.57884998520905395</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A15" s="92" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" s="92" t="s">
+        <v>118</v>
+      </c>
+      <c r="D15" s="93">
+        <v>0.54874577477317199</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D18">
+    <sortCondition descending="1" ref="D1:D18"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/benchmarking/output/data.xlsx
+++ b/benchmarking/output/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37788B9D-827A-EC4E-956A-E0912B1580A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64F0270-B6F5-C045-8FFC-613BA3FCD10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4280" yWindow="500" windowWidth="46920" windowHeight="26600" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3920" yWindow="500" windowWidth="34480" windowHeight="19400" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="basic" sheetId="1" r:id="rId1"/>
@@ -109,9 +109,6 @@
   </si>
   <si>
     <t>Model Type</t>
-  </si>
-  <si>
-    <t>Transactional</t>
   </si>
   <si>
     <t>Semantic Matching</t>
@@ -906,6 +903,9 @@
   </si>
   <si>
     <t>predictions from deberta and distmult</t>
+  </si>
+  <si>
+    <t>Translational</t>
   </si>
 </sst>
 </file>
@@ -1458,13 +1458,34 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1489,27 +1510,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1833,10 +1833,10 @@
         <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>22</v>
@@ -1861,17 +1861,17 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="81" t="s">
+      <c r="B2" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="86" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="78" t="s">
-        <v>29</v>
-      </c>
       <c r="D2" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>7</v>
@@ -1893,11 +1893,11 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A3" s="80"/>
-      <c r="B3" s="81"/>
-      <c r="C3" s="79"/>
+      <c r="A3" s="85"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="87"/>
       <c r="D3" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>8</v>
@@ -1919,11 +1919,11 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="80"/>
-      <c r="B4" s="81"/>
-      <c r="C4" s="79"/>
+      <c r="A4" s="85"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="87"/>
       <c r="D4" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>9</v>
@@ -1946,7 +1946,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
-      <c r="B5" s="81"/>
+      <c r="B5" s="88"/>
       <c r="C5" s="7"/>
       <c r="E5" s="4"/>
       <c r="F5" s="6"/>
@@ -1956,15 +1956,15 @@
       <c r="J5" s="6"/>
     </row>
     <row r="6" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="85" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="81"/>
-      <c r="C6" s="78" t="s">
-        <v>30</v>
+      <c r="B6" s="88"/>
+      <c r="C6" s="86" t="s">
+        <v>29</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>7</v>
@@ -1986,11 +1986,11 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="80"/>
-      <c r="B7" s="81"/>
-      <c r="C7" s="79"/>
+      <c r="A7" s="85"/>
+      <c r="B7" s="88"/>
+      <c r="C7" s="87"/>
       <c r="D7" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>8</v>
@@ -2012,11 +2012,11 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A8" s="80"/>
-      <c r="B8" s="81"/>
-      <c r="C8" s="79"/>
+      <c r="A8" s="85"/>
+      <c r="B8" s="88"/>
+      <c r="C8" s="87"/>
       <c r="D8" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>9</v>
@@ -2039,7 +2039,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
-      <c r="B9" s="81"/>
+      <c r="B9" s="88"/>
       <c r="C9" s="7"/>
       <c r="E9" s="4"/>
       <c r="F9" s="6"/>
@@ -2049,15 +2049,15 @@
       <c r="J9" s="6"/>
     </row>
     <row r="10" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="80" t="s">
+      <c r="A10" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="81"/>
-      <c r="C10" s="78" t="s">
-        <v>31</v>
+      <c r="B10" s="88"/>
+      <c r="C10" s="86" t="s">
+        <v>30</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>7</v>
@@ -2079,11 +2079,11 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="80"/>
-      <c r="B11" s="81"/>
-      <c r="C11" s="79"/>
+      <c r="A11" s="85"/>
+      <c r="B11" s="88"/>
+      <c r="C11" s="87"/>
       <c r="D11" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>8</v>
@@ -2105,11 +2105,11 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="80"/>
-      <c r="B12" s="81"/>
-      <c r="C12" s="79"/>
+      <c r="A12" s="85"/>
+      <c r="B12" s="88"/>
+      <c r="C12" s="87"/>
       <c r="D12" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>9</v>
@@ -2132,7 +2132,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="4"/>
-      <c r="B13" s="81"/>
+      <c r="B13" s="88"/>
       <c r="C13" s="7"/>
       <c r="E13" s="4"/>
       <c r="F13" s="6"/>
@@ -2142,15 +2142,15 @@
       <c r="J13" s="6"/>
     </row>
     <row r="14" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A14" s="80" t="s">
+      <c r="A14" s="85" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="81"/>
-      <c r="C14" s="78" t="s">
-        <v>32</v>
+      <c r="B14" s="88"/>
+      <c r="C14" s="86" t="s">
+        <v>31</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>7</v>
@@ -2172,11 +2172,11 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A15" s="80"/>
-      <c r="B15" s="81"/>
-      <c r="C15" s="79"/>
+      <c r="A15" s="85"/>
+      <c r="B15" s="88"/>
+      <c r="C15" s="87"/>
       <c r="D15" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>8</v>
@@ -2198,11 +2198,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A16" s="80"/>
-      <c r="B16" s="81"/>
-      <c r="C16" s="79"/>
+      <c r="A16" s="85"/>
+      <c r="B16" s="88"/>
+      <c r="C16" s="87"/>
       <c r="D16" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>9</v>
@@ -2225,7 +2225,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
-      <c r="B17" s="81"/>
+      <c r="B17" s="88"/>
       <c r="C17" s="7"/>
       <c r="E17" s="4"/>
       <c r="F17" s="6"/>
@@ -2235,15 +2235,15 @@
       <c r="J17" s="6"/>
     </row>
     <row r="18" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A18" s="80" t="s">
+      <c r="A18" s="85" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="81"/>
-      <c r="C18" s="78" t="s">
-        <v>33</v>
+      <c r="B18" s="88"/>
+      <c r="C18" s="86" t="s">
+        <v>32</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>7</v>
@@ -2265,11 +2265,11 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A19" s="80"/>
-      <c r="B19" s="81"/>
-      <c r="C19" s="79"/>
+      <c r="A19" s="85"/>
+      <c r="B19" s="88"/>
+      <c r="C19" s="87"/>
       <c r="D19" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>8</v>
@@ -2291,11 +2291,11 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A20" s="80"/>
-      <c r="B20" s="81"/>
-      <c r="C20" s="79"/>
+      <c r="A20" s="85"/>
+      <c r="B20" s="88"/>
+      <c r="C20" s="87"/>
       <c r="D20" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>9</v>
@@ -2318,7 +2318,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
-      <c r="B21" s="81"/>
+      <c r="B21" s="88"/>
       <c r="C21" s="7"/>
       <c r="E21" s="4"/>
       <c r="F21" s="6"/>
@@ -2328,15 +2328,15 @@
       <c r="J21" s="6"/>
     </row>
     <row r="22" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A22" s="80" t="s">
+      <c r="A22" s="85" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="81"/>
-      <c r="C22" s="78" t="s">
-        <v>34</v>
+      <c r="B22" s="88"/>
+      <c r="C22" s="86" t="s">
+        <v>33</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>7</v>
@@ -2358,11 +2358,11 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A23" s="80"/>
-      <c r="B23" s="81"/>
-      <c r="C23" s="79"/>
+      <c r="A23" s="85"/>
+      <c r="B23" s="88"/>
+      <c r="C23" s="87"/>
       <c r="D23" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>8</v>
@@ -2384,11 +2384,11 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A24" s="80"/>
-      <c r="B24" s="81"/>
-      <c r="C24" s="79"/>
+      <c r="A24" s="85"/>
+      <c r="B24" s="88"/>
+      <c r="C24" s="87"/>
       <c r="D24" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>9</v>
@@ -2411,7 +2411,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="4"/>
-      <c r="B25" s="81"/>
+      <c r="B25" s="88"/>
       <c r="C25" s="7"/>
       <c r="E25" s="4"/>
       <c r="F25" s="6"/>
@@ -2421,15 +2421,15 @@
       <c r="J25" s="6"/>
     </row>
     <row r="26" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A26" s="80" t="s">
+      <c r="A26" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="81"/>
-      <c r="C26" s="78" t="s">
-        <v>35</v>
+      <c r="B26" s="88"/>
+      <c r="C26" s="86" t="s">
+        <v>34</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>7</v>
@@ -2451,11 +2451,11 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A27" s="80"/>
-      <c r="B27" s="81"/>
-      <c r="C27" s="79"/>
+      <c r="A27" s="85"/>
+      <c r="B27" s="88"/>
+      <c r="C27" s="87"/>
       <c r="D27" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>8</v>
@@ -2477,11 +2477,11 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A28" s="80"/>
-      <c r="B28" s="81"/>
-      <c r="C28" s="79"/>
+      <c r="A28" s="85"/>
+      <c r="B28" s="88"/>
+      <c r="C28" s="87"/>
       <c r="D28" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>9</v>
@@ -2504,7 +2504,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
-      <c r="B29" s="81"/>
+      <c r="B29" s="88"/>
       <c r="C29" s="7"/>
       <c r="E29" s="4"/>
       <c r="F29" s="6"/>
@@ -2514,15 +2514,15 @@
       <c r="J29" s="6"/>
     </row>
     <row r="30" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A30" s="80" t="s">
+      <c r="A30" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="B30" s="81"/>
-      <c r="C30" s="78" t="s">
-        <v>36</v>
+      <c r="B30" s="88"/>
+      <c r="C30" s="86" t="s">
+        <v>35</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>7</v>
@@ -2544,11 +2544,11 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A31" s="80"/>
-      <c r="B31" s="81"/>
-      <c r="C31" s="79"/>
+      <c r="A31" s="85"/>
+      <c r="B31" s="88"/>
+      <c r="C31" s="87"/>
       <c r="D31" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>8</v>
@@ -2570,11 +2570,11 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A32" s="80"/>
-      <c r="B32" s="81"/>
-      <c r="C32" s="79"/>
+      <c r="A32" s="85"/>
+      <c r="B32" s="88"/>
+      <c r="C32" s="87"/>
       <c r="D32" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>9</v>
@@ -2607,17 +2607,17 @@
       <c r="J33" s="6"/>
     </row>
     <row r="34" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A34" s="80" t="s">
+      <c r="A34" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="80" t="s">
-        <v>51</v>
-      </c>
-      <c r="C34" s="78" t="s">
-        <v>29</v>
+      <c r="B34" s="85" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" s="86" t="s">
+        <v>28</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>7</v>
@@ -2639,11 +2639,11 @@
       </c>
     </row>
     <row r="35" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A35" s="80"/>
-      <c r="B35" s="80"/>
-      <c r="C35" s="79"/>
+      <c r="A35" s="85"/>
+      <c r="B35" s="85"/>
+      <c r="C35" s="87"/>
       <c r="D35" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>8</v>
@@ -2665,11 +2665,11 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A36" s="80"/>
-      <c r="B36" s="80"/>
-      <c r="C36" s="79"/>
+      <c r="A36" s="85"/>
+      <c r="B36" s="85"/>
+      <c r="C36" s="87"/>
       <c r="D36" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>9</v>
@@ -2692,7 +2692,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
-      <c r="B37" s="80"/>
+      <c r="B37" s="85"/>
       <c r="C37" s="7"/>
       <c r="E37" s="4"/>
       <c r="F37" s="6"/>
@@ -2702,15 +2702,15 @@
       <c r="J37" s="6"/>
     </row>
     <row r="38" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A38" s="80" t="s">
+      <c r="A38" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="B38" s="80"/>
-      <c r="C38" s="78" t="s">
-        <v>30</v>
+      <c r="B38" s="85"/>
+      <c r="C38" s="86" t="s">
+        <v>29</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>7</v>
@@ -2732,11 +2732,11 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A39" s="80"/>
-      <c r="B39" s="80"/>
-      <c r="C39" s="79"/>
+      <c r="A39" s="85"/>
+      <c r="B39" s="85"/>
+      <c r="C39" s="87"/>
       <c r="D39" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>8</v>
@@ -2758,11 +2758,11 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A40" s="80"/>
-      <c r="B40" s="80"/>
-      <c r="C40" s="79"/>
+      <c r="A40" s="85"/>
+      <c r="B40" s="85"/>
+      <c r="C40" s="87"/>
       <c r="D40" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>9</v>
@@ -2785,7 +2785,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
-      <c r="B41" s="80"/>
+      <c r="B41" s="85"/>
       <c r="C41" s="7"/>
       <c r="E41" s="4"/>
       <c r="F41" s="6"/>
@@ -2795,15 +2795,15 @@
       <c r="J41" s="6"/>
     </row>
     <row r="42" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A42" s="80" t="s">
+      <c r="A42" s="85" t="s">
         <v>6</v>
       </c>
-      <c r="B42" s="80"/>
-      <c r="C42" s="78" t="s">
-        <v>31</v>
+      <c r="B42" s="85"/>
+      <c r="C42" s="86" t="s">
+        <v>30</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>7</v>
@@ -2825,11 +2825,11 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A43" s="80"/>
-      <c r="B43" s="80"/>
-      <c r="C43" s="79"/>
+      <c r="A43" s="85"/>
+      <c r="B43" s="85"/>
+      <c r="C43" s="87"/>
       <c r="D43" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>8</v>
@@ -2851,11 +2851,11 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A44" s="80"/>
-      <c r="B44" s="80"/>
-      <c r="C44" s="79"/>
+      <c r="A44" s="85"/>
+      <c r="B44" s="85"/>
+      <c r="C44" s="87"/>
       <c r="D44" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>9</v>
@@ -2878,7 +2878,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
-      <c r="B45" s="80"/>
+      <c r="B45" s="85"/>
       <c r="C45" s="7"/>
       <c r="E45" s="4"/>
       <c r="F45" s="6"/>
@@ -2888,15 +2888,15 @@
       <c r="J45" s="6"/>
     </row>
     <row r="46" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A46" s="80" t="s">
+      <c r="A46" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="B46" s="80"/>
-      <c r="C46" s="78" t="s">
-        <v>35</v>
+      <c r="B46" s="85"/>
+      <c r="C46" s="86" t="s">
+        <v>34</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>7</v>
@@ -2918,11 +2918,11 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A47" s="80"/>
-      <c r="B47" s="80"/>
-      <c r="C47" s="79"/>
+      <c r="A47" s="85"/>
+      <c r="B47" s="85"/>
+      <c r="C47" s="87"/>
       <c r="D47" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>8</v>
@@ -2944,11 +2944,11 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A48" s="80"/>
-      <c r="B48" s="80"/>
-      <c r="C48" s="79"/>
+      <c r="A48" s="85"/>
+      <c r="B48" s="85"/>
+      <c r="C48" s="87"/>
       <c r="D48" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>9</v>
@@ -2971,7 +2971,7 @@
     </row>
     <row r="51" spans="4:10" x14ac:dyDescent="0.2">
       <c r="E51" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F51" s="11">
         <f>MAX(F2:F48)</f>
@@ -2996,10 +2996,10 @@
     </row>
     <row r="52" spans="4:10" x14ac:dyDescent="0.2">
       <c r="D52" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E52" s="8" t="s">
         <v>37</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>38</v>
       </c>
       <c r="F52" s="11">
         <f>AVERAGE(F2:F48)</f>
@@ -3024,16 +3024,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="C38:C40"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="C10:C12"/>
@@ -3050,6 +3040,16 @@
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="A14:A16"/>
     <mergeCell ref="A30:A32"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="C38:C40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3071,13 +3071,13 @@
   <sheetData>
     <row r="1" spans="1:10" s="15" customFormat="1" ht="67" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>26</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>27</v>
       </c>
       <c r="D1" s="13" t="s">
         <v>22</v>
@@ -3102,17 +3102,17 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A2" s="80" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="81" t="s">
+      <c r="A2" s="85" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="86" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="78" t="s">
-        <v>29</v>
-      </c>
       <c r="D2" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>7</v>
@@ -3134,11 +3134,11 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A3" s="80"/>
-      <c r="B3" s="81"/>
-      <c r="C3" s="79"/>
+      <c r="A3" s="85"/>
+      <c r="B3" s="88"/>
+      <c r="C3" s="87"/>
       <c r="D3" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>8</v>
@@ -3160,11 +3160,11 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="80"/>
-      <c r="B4" s="81"/>
-      <c r="C4" s="79"/>
+      <c r="A4" s="85"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="87"/>
       <c r="D4" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>9</v>
@@ -3187,7 +3187,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
-      <c r="B5" s="81"/>
+      <c r="B5" s="88"/>
       <c r="C5" s="7"/>
       <c r="E5" s="4"/>
       <c r="F5" s="6"/>
@@ -3197,15 +3197,15 @@
       <c r="J5" s="6"/>
     </row>
     <row r="6" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="80" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="81"/>
-      <c r="C6" s="78" t="s">
-        <v>30</v>
+      <c r="A6" s="85" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="88"/>
+      <c r="C6" s="86" t="s">
+        <v>29</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>7</v>
@@ -3227,11 +3227,11 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="80"/>
-      <c r="B7" s="81"/>
-      <c r="C7" s="79"/>
+      <c r="A7" s="85"/>
+      <c r="B7" s="88"/>
+      <c r="C7" s="87"/>
       <c r="D7" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>8</v>
@@ -3253,11 +3253,11 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A8" s="80"/>
-      <c r="B8" s="81"/>
-      <c r="C8" s="79"/>
+      <c r="A8" s="85"/>
+      <c r="B8" s="88"/>
+      <c r="C8" s="87"/>
       <c r="D8" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>9</v>
@@ -3280,7 +3280,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
-      <c r="B9" s="81"/>
+      <c r="B9" s="88"/>
       <c r="C9" s="7"/>
       <c r="E9" s="4"/>
       <c r="F9" s="6"/>
@@ -3290,15 +3290,15 @@
       <c r="J9" s="6"/>
     </row>
     <row r="10" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="80" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="81"/>
-      <c r="C10" s="78" t="s">
-        <v>31</v>
+      <c r="A10" s="85" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="88"/>
+      <c r="C10" s="86" t="s">
+        <v>30</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>7</v>
@@ -3320,11 +3320,11 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="80"/>
-      <c r="B11" s="81"/>
-      <c r="C11" s="79"/>
+      <c r="A11" s="85"/>
+      <c r="B11" s="88"/>
+      <c r="C11" s="87"/>
       <c r="D11" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>8</v>
@@ -3346,11 +3346,11 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="80"/>
-      <c r="B12" s="81"/>
-      <c r="C12" s="79"/>
+      <c r="A12" s="85"/>
+      <c r="B12" s="88"/>
+      <c r="C12" s="87"/>
       <c r="D12" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>9</v>
@@ -3373,7 +3373,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="4"/>
-      <c r="B13" s="81"/>
+      <c r="B13" s="88"/>
       <c r="C13" s="7"/>
       <c r="E13" s="4"/>
       <c r="F13" s="6"/>
@@ -3383,15 +3383,15 @@
       <c r="J13" s="6"/>
     </row>
     <row r="14" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A14" s="80" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="81"/>
-      <c r="C14" s="78" t="s">
-        <v>32</v>
+      <c r="A14" s="85" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="88"/>
+      <c r="C14" s="86" t="s">
+        <v>31</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>7</v>
@@ -3413,11 +3413,11 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A15" s="80"/>
-      <c r="B15" s="81"/>
-      <c r="C15" s="79"/>
+      <c r="A15" s="85"/>
+      <c r="B15" s="88"/>
+      <c r="C15" s="87"/>
       <c r="D15" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>8</v>
@@ -3439,11 +3439,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A16" s="80"/>
-      <c r="B16" s="81"/>
-      <c r="C16" s="79"/>
+      <c r="A16" s="85"/>
+      <c r="B16" s="88"/>
+      <c r="C16" s="87"/>
       <c r="D16" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>9</v>
@@ -3466,7 +3466,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
-      <c r="B17" s="81"/>
+      <c r="B17" s="88"/>
       <c r="C17" s="7"/>
       <c r="E17" s="4"/>
       <c r="F17" s="6"/>
@@ -3476,15 +3476,15 @@
       <c r="J17" s="6"/>
     </row>
     <row r="18" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A18" s="80" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18" s="81"/>
-      <c r="C18" s="78" t="s">
-        <v>33</v>
+      <c r="A18" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="88"/>
+      <c r="C18" s="86" t="s">
+        <v>32</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>7</v>
@@ -3506,11 +3506,11 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A19" s="80"/>
-      <c r="B19" s="81"/>
-      <c r="C19" s="79"/>
+      <c r="A19" s="85"/>
+      <c r="B19" s="88"/>
+      <c r="C19" s="87"/>
       <c r="D19" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>8</v>
@@ -3532,11 +3532,11 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A20" s="80"/>
-      <c r="B20" s="81"/>
-      <c r="C20" s="79"/>
+      <c r="A20" s="85"/>
+      <c r="B20" s="88"/>
+      <c r="C20" s="87"/>
       <c r="D20" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>9</v>
@@ -3559,7 +3559,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
-      <c r="B21" s="81"/>
+      <c r="B21" s="88"/>
       <c r="C21" s="7"/>
       <c r="E21" s="4"/>
       <c r="F21" s="6"/>
@@ -3569,15 +3569,15 @@
       <c r="J21" s="6"/>
     </row>
     <row r="22" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A22" s="80" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="81"/>
-      <c r="C22" s="78" t="s">
-        <v>34</v>
+      <c r="A22" s="85" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="88"/>
+      <c r="C22" s="86" t="s">
+        <v>33</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>7</v>
@@ -3599,11 +3599,11 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A23" s="80"/>
-      <c r="B23" s="81"/>
-      <c r="C23" s="79"/>
+      <c r="A23" s="85"/>
+      <c r="B23" s="88"/>
+      <c r="C23" s="87"/>
       <c r="D23" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>8</v>
@@ -3625,11 +3625,11 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A24" s="80"/>
-      <c r="B24" s="81"/>
-      <c r="C24" s="79"/>
+      <c r="A24" s="85"/>
+      <c r="B24" s="88"/>
+      <c r="C24" s="87"/>
       <c r="D24" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>9</v>
@@ -3652,7 +3652,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="4"/>
-      <c r="B25" s="81"/>
+      <c r="B25" s="88"/>
       <c r="C25" s="7"/>
       <c r="E25" s="4"/>
       <c r="F25" s="6"/>
@@ -3662,15 +3662,15 @@
       <c r="J25" s="6"/>
     </row>
     <row r="26" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A26" s="80" t="s">
-        <v>44</v>
-      </c>
-      <c r="B26" s="81"/>
-      <c r="C26" s="78" t="s">
-        <v>35</v>
+      <c r="A26" s="85" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" s="88"/>
+      <c r="C26" s="86" t="s">
+        <v>34</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>7</v>
@@ -3692,11 +3692,11 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A27" s="80"/>
-      <c r="B27" s="81"/>
-      <c r="C27" s="79"/>
+      <c r="A27" s="85"/>
+      <c r="B27" s="88"/>
+      <c r="C27" s="87"/>
       <c r="D27" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>8</v>
@@ -3718,11 +3718,11 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A28" s="80"/>
-      <c r="B28" s="81"/>
-      <c r="C28" s="79"/>
+      <c r="A28" s="85"/>
+      <c r="B28" s="88"/>
+      <c r="C28" s="87"/>
       <c r="D28" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>9</v>
@@ -3745,7 +3745,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
-      <c r="B29" s="81"/>
+      <c r="B29" s="88"/>
       <c r="C29" s="7"/>
       <c r="E29" s="4"/>
       <c r="F29" s="6"/>
@@ -3755,15 +3755,15 @@
       <c r="J29" s="6"/>
     </row>
     <row r="30" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A30" s="80" t="s">
-        <v>45</v>
-      </c>
-      <c r="B30" s="81"/>
-      <c r="C30" s="78" t="s">
-        <v>36</v>
+      <c r="A30" s="85" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="88"/>
+      <c r="C30" s="86" t="s">
+        <v>35</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>7</v>
@@ -3785,11 +3785,11 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A31" s="80"/>
-      <c r="B31" s="81"/>
-      <c r="C31" s="79"/>
+      <c r="A31" s="85"/>
+      <c r="B31" s="88"/>
+      <c r="C31" s="87"/>
       <c r="D31" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>8</v>
@@ -3811,11 +3811,11 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A32" s="80"/>
-      <c r="B32" s="81"/>
-      <c r="C32" s="79"/>
+      <c r="A32" s="85"/>
+      <c r="B32" s="88"/>
+      <c r="C32" s="87"/>
       <c r="D32" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>9</v>
@@ -3848,17 +3848,17 @@
       <c r="J33" s="6"/>
     </row>
     <row r="34" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A34" s="80" t="s">
-        <v>46</v>
-      </c>
-      <c r="B34" s="80" t="s">
-        <v>51</v>
-      </c>
-      <c r="C34" s="78" t="s">
-        <v>29</v>
+      <c r="A34" s="85" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34" s="85" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" s="86" t="s">
+        <v>28</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>7</v>
@@ -3880,11 +3880,11 @@
       </c>
     </row>
     <row r="35" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A35" s="80"/>
-      <c r="B35" s="80"/>
-      <c r="C35" s="79"/>
+      <c r="A35" s="85"/>
+      <c r="B35" s="85"/>
+      <c r="C35" s="87"/>
       <c r="D35" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>8</v>
@@ -3906,11 +3906,11 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A36" s="80"/>
-      <c r="B36" s="80"/>
-      <c r="C36" s="79"/>
+      <c r="A36" s="85"/>
+      <c r="B36" s="85"/>
+      <c r="C36" s="87"/>
       <c r="D36" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>9</v>
@@ -3933,7 +3933,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
-      <c r="B37" s="80"/>
+      <c r="B37" s="85"/>
       <c r="C37" s="7"/>
       <c r="E37" s="4"/>
       <c r="F37" s="6"/>
@@ -3943,15 +3943,15 @@
       <c r="J37" s="6"/>
     </row>
     <row r="38" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A38" s="80" t="s">
-        <v>47</v>
-      </c>
-      <c r="B38" s="80"/>
-      <c r="C38" s="78" t="s">
-        <v>30</v>
+      <c r="A38" s="85" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" s="85"/>
+      <c r="C38" s="86" t="s">
+        <v>29</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>7</v>
@@ -3973,11 +3973,11 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A39" s="80"/>
-      <c r="B39" s="80"/>
-      <c r="C39" s="79"/>
+      <c r="A39" s="85"/>
+      <c r="B39" s="85"/>
+      <c r="C39" s="87"/>
       <c r="D39" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>8</v>
@@ -3999,11 +3999,11 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A40" s="80"/>
-      <c r="B40" s="80"/>
-      <c r="C40" s="79"/>
+      <c r="A40" s="85"/>
+      <c r="B40" s="85"/>
+      <c r="C40" s="87"/>
       <c r="D40" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>9</v>
@@ -4026,7 +4026,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
-      <c r="B41" s="80"/>
+      <c r="B41" s="85"/>
       <c r="C41" s="7"/>
       <c r="E41" s="4"/>
       <c r="F41" s="6"/>
@@ -4036,15 +4036,15 @@
       <c r="J41" s="6"/>
     </row>
     <row r="42" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A42" s="80" t="s">
-        <v>48</v>
-      </c>
-      <c r="B42" s="80"/>
-      <c r="C42" s="78" t="s">
-        <v>31</v>
+      <c r="A42" s="85" t="s">
+        <v>47</v>
+      </c>
+      <c r="B42" s="85"/>
+      <c r="C42" s="86" t="s">
+        <v>30</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>7</v>
@@ -4066,11 +4066,11 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A43" s="80"/>
-      <c r="B43" s="80"/>
-      <c r="C43" s="79"/>
+      <c r="A43" s="85"/>
+      <c r="B43" s="85"/>
+      <c r="C43" s="87"/>
       <c r="D43" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>8</v>
@@ -4092,11 +4092,11 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A44" s="80"/>
-      <c r="B44" s="80"/>
-      <c r="C44" s="79"/>
+      <c r="A44" s="85"/>
+      <c r="B44" s="85"/>
+      <c r="C44" s="87"/>
       <c r="D44" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>9</v>
@@ -4119,7 +4119,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
-      <c r="B45" s="80"/>
+      <c r="B45" s="85"/>
       <c r="C45" s="7"/>
       <c r="E45" s="4"/>
       <c r="F45" s="6"/>
@@ -4129,15 +4129,15 @@
       <c r="J45" s="6"/>
     </row>
     <row r="46" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A46" s="80" t="s">
-        <v>49</v>
-      </c>
-      <c r="B46" s="80"/>
-      <c r="C46" s="78" t="s">
-        <v>35</v>
+      <c r="A46" s="85" t="s">
+        <v>48</v>
+      </c>
+      <c r="B46" s="85"/>
+      <c r="C46" s="86" t="s">
+        <v>34</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>7</v>
@@ -4159,11 +4159,11 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A47" s="80"/>
-      <c r="B47" s="80"/>
-      <c r="C47" s="79"/>
+      <c r="A47" s="85"/>
+      <c r="B47" s="85"/>
+      <c r="C47" s="87"/>
       <c r="D47" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>8</v>
@@ -4185,11 +4185,11 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A48" s="80"/>
-      <c r="B48" s="80"/>
-      <c r="C48" s="79"/>
+      <c r="A48" s="85"/>
+      <c r="B48" s="85"/>
+      <c r="C48" s="87"/>
       <c r="D48" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>9</v>
@@ -4212,7 +4212,7 @@
     </row>
     <row r="51" spans="4:10" x14ac:dyDescent="0.2">
       <c r="E51" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F51" s="11">
         <f>MAX(F2:F48)</f>
@@ -4237,10 +4237,10 @@
     </row>
     <row r="52" spans="4:10" x14ac:dyDescent="0.2">
       <c r="D52" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E52" s="8" t="s">
         <v>37</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>38</v>
       </c>
       <c r="F52" s="11">
         <f>AVERAGE(F2:F48)</f>
@@ -4265,16 +4265,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="B34:B48"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="C46:C48"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B32"/>
     <mergeCell ref="C2:C4"/>
@@ -4291,6 +4281,16 @@
     <mergeCell ref="A26:A28"/>
     <mergeCell ref="C26:C28"/>
     <mergeCell ref="A30:A32"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="B34:B48"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="C46:C48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4312,13 +4312,13 @@
   <sheetData>
     <row r="1" spans="1:13" s="18" customFormat="1" ht="111" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>26</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>27</v>
       </c>
       <c r="D1" s="16" t="s">
         <v>22</v>
@@ -4342,27 +4342,27 @@
         <v>5</v>
       </c>
       <c r="K1" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="L1" s="29" t="s">
-        <v>56</v>
-      </c>
       <c r="M1" s="29" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A2" s="81" t="s">
+      <c r="A2" s="88" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="85" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="86" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="80" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" s="78" t="s">
-        <v>29</v>
-      </c>
       <c r="D2" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>7</v>
@@ -4396,11 +4396,11 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A3" s="81"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="79"/>
+      <c r="A3" s="88"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="87"/>
       <c r="D3" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>8</v>
@@ -4434,11 +4434,11 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="81"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="79"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="87"/>
       <c r="D4" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>9</v>
@@ -4472,7 +4472,7 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="81"/>
+      <c r="A5" s="88"/>
       <c r="B5" s="4"/>
       <c r="C5" s="7"/>
       <c r="E5" s="4"/>
@@ -4483,15 +4483,15 @@
       <c r="J5" s="6"/>
     </row>
     <row r="6" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="81"/>
-      <c r="B6" s="80" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" s="78" t="s">
-        <v>30</v>
+      <c r="A6" s="88"/>
+      <c r="B6" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="86" t="s">
+        <v>29</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>7</v>
@@ -4525,11 +4525,11 @@
       </c>
     </row>
     <row r="7" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="81"/>
-      <c r="B7" s="80"/>
-      <c r="C7" s="79"/>
+      <c r="A7" s="88"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="87"/>
       <c r="D7" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>8</v>
@@ -4563,11 +4563,11 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A8" s="81"/>
-      <c r="B8" s="80"/>
-      <c r="C8" s="79"/>
+      <c r="A8" s="88"/>
+      <c r="B8" s="85"/>
+      <c r="C8" s="87"/>
       <c r="D8" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E8" s="9" t="s">
         <v>9</v>
@@ -4601,7 +4601,7 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="81"/>
+      <c r="A9" s="88"/>
       <c r="B9" s="4"/>
       <c r="C9" s="7"/>
       <c r="E9" s="4"/>
@@ -4612,15 +4612,15 @@
       <c r="J9" s="6"/>
     </row>
     <row r="10" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="81"/>
-      <c r="B10" s="80" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" s="78" t="s">
-        <v>31</v>
+      <c r="A10" s="88"/>
+      <c r="B10" s="85" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" s="86" t="s">
+        <v>30</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>7</v>
@@ -4654,11 +4654,11 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="81"/>
-      <c r="B11" s="80"/>
-      <c r="C11" s="79"/>
+      <c r="A11" s="88"/>
+      <c r="B11" s="85"/>
+      <c r="C11" s="87"/>
       <c r="D11" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>8</v>
@@ -4692,11 +4692,11 @@
       </c>
     </row>
     <row r="12" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="81"/>
-      <c r="B12" s="80"/>
-      <c r="C12" s="79"/>
+      <c r="A12" s="88"/>
+      <c r="B12" s="85"/>
+      <c r="C12" s="87"/>
       <c r="D12" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>9</v>
@@ -4730,7 +4730,7 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="81"/>
+      <c r="A13" s="88"/>
       <c r="B13" s="4"/>
       <c r="C13" s="7"/>
       <c r="E13" s="4"/>
@@ -4741,15 +4741,15 @@
       <c r="J13" s="6"/>
     </row>
     <row r="14" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A14" s="81"/>
-      <c r="B14" s="80" t="s">
-        <v>78</v>
-      </c>
-      <c r="C14" s="78" t="s">
-        <v>32</v>
+      <c r="A14" s="88"/>
+      <c r="B14" s="85" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="86" t="s">
+        <v>31</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>7</v>
@@ -4783,11 +4783,11 @@
       </c>
     </row>
     <row r="15" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A15" s="81"/>
-      <c r="B15" s="80"/>
-      <c r="C15" s="79"/>
+      <c r="A15" s="88"/>
+      <c r="B15" s="85"/>
+      <c r="C15" s="87"/>
       <c r="D15" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>8</v>
@@ -4821,11 +4821,11 @@
       </c>
     </row>
     <row r="16" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A16" s="81"/>
-      <c r="B16" s="80"/>
-      <c r="C16" s="79"/>
+      <c r="A16" s="88"/>
+      <c r="B16" s="85"/>
+      <c r="C16" s="87"/>
       <c r="D16" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>9</v>
@@ -4859,7 +4859,7 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="81"/>
+      <c r="A17" s="88"/>
       <c r="B17" s="4"/>
       <c r="C17" s="7"/>
       <c r="E17" s="4"/>
@@ -4870,15 +4870,15 @@
       <c r="J17" s="6"/>
     </row>
     <row r="18" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A18" s="81"/>
-      <c r="B18" s="80" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" s="78" t="s">
-        <v>33</v>
+      <c r="A18" s="88"/>
+      <c r="B18" s="85" t="s">
+        <v>78</v>
+      </c>
+      <c r="C18" s="86" t="s">
+        <v>32</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>7</v>
@@ -4912,11 +4912,11 @@
       </c>
     </row>
     <row r="19" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A19" s="81"/>
-      <c r="B19" s="80"/>
-      <c r="C19" s="79"/>
+      <c r="A19" s="88"/>
+      <c r="B19" s="85"/>
+      <c r="C19" s="87"/>
       <c r="D19" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>8</v>
@@ -4950,11 +4950,11 @@
       </c>
     </row>
     <row r="20" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A20" s="81"/>
-      <c r="B20" s="80"/>
-      <c r="C20" s="79"/>
+      <c r="A20" s="88"/>
+      <c r="B20" s="85"/>
+      <c r="C20" s="87"/>
       <c r="D20" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>9</v>
@@ -4988,7 +4988,7 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="81"/>
+      <c r="A21" s="88"/>
       <c r="B21" s="4"/>
       <c r="C21" s="7"/>
       <c r="E21" s="4"/>
@@ -4999,15 +4999,15 @@
       <c r="J21" s="6"/>
     </row>
     <row r="22" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A22" s="81"/>
-      <c r="B22" s="80" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" s="78" t="s">
-        <v>34</v>
+      <c r="A22" s="88"/>
+      <c r="B22" s="85" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="86" t="s">
+        <v>33</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>7</v>
@@ -5041,11 +5041,11 @@
       </c>
     </row>
     <row r="23" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A23" s="81"/>
-      <c r="B23" s="80"/>
-      <c r="C23" s="79"/>
+      <c r="A23" s="88"/>
+      <c r="B23" s="85"/>
+      <c r="C23" s="87"/>
       <c r="D23" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>8</v>
@@ -5079,11 +5079,11 @@
       </c>
     </row>
     <row r="24" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A24" s="81"/>
-      <c r="B24" s="80"/>
-      <c r="C24" s="79"/>
+      <c r="A24" s="88"/>
+      <c r="B24" s="85"/>
+      <c r="C24" s="87"/>
       <c r="D24" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>9</v>
@@ -5117,7 +5117,7 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="81"/>
+      <c r="A25" s="88"/>
       <c r="B25" s="4"/>
       <c r="C25" s="7"/>
       <c r="E25" s="4"/>
@@ -5128,15 +5128,15 @@
       <c r="J25" s="6"/>
     </row>
     <row r="26" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A26" s="81"/>
-      <c r="B26" s="80" t="s">
-        <v>81</v>
-      </c>
-      <c r="C26" s="78" t="s">
-        <v>35</v>
+      <c r="A26" s="88"/>
+      <c r="B26" s="85" t="s">
+        <v>80</v>
+      </c>
+      <c r="C26" s="86" t="s">
+        <v>34</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>7</v>
@@ -5170,11 +5170,11 @@
       </c>
     </row>
     <row r="27" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A27" s="81"/>
-      <c r="B27" s="80"/>
-      <c r="C27" s="79"/>
+      <c r="A27" s="88"/>
+      <c r="B27" s="85"/>
+      <c r="C27" s="87"/>
       <c r="D27" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>8</v>
@@ -5208,11 +5208,11 @@
       </c>
     </row>
     <row r="28" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A28" s="81"/>
-      <c r="B28" s="80"/>
-      <c r="C28" s="79"/>
+      <c r="A28" s="88"/>
+      <c r="B28" s="85"/>
+      <c r="C28" s="87"/>
       <c r="D28" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>9</v>
@@ -5246,7 +5246,7 @@
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="81"/>
+      <c r="A29" s="88"/>
       <c r="B29" s="4"/>
       <c r="C29" s="7"/>
       <c r="E29" s="4"/>
@@ -5257,15 +5257,15 @@
       <c r="J29" s="6"/>
     </row>
     <row r="30" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A30" s="81"/>
-      <c r="B30" s="80" t="s">
-        <v>82</v>
-      </c>
-      <c r="C30" s="78" t="s">
-        <v>36</v>
+      <c r="A30" s="88"/>
+      <c r="B30" s="85" t="s">
+        <v>81</v>
+      </c>
+      <c r="C30" s="86" t="s">
+        <v>35</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>7</v>
@@ -5299,11 +5299,11 @@
       </c>
     </row>
     <row r="31" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A31" s="81"/>
-      <c r="B31" s="80"/>
-      <c r="C31" s="79"/>
+      <c r="A31" s="88"/>
+      <c r="B31" s="85"/>
+      <c r="C31" s="87"/>
       <c r="D31" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>8</v>
@@ -5337,11 +5337,11 @@
       </c>
     </row>
     <row r="32" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A32" s="81"/>
-      <c r="B32" s="80"/>
-      <c r="C32" s="79"/>
+      <c r="A32" s="88"/>
+      <c r="B32" s="85"/>
+      <c r="C32" s="87"/>
       <c r="D32" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>9</v>
@@ -5386,17 +5386,17 @@
       <c r="J33" s="6"/>
     </row>
     <row r="34" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A34" s="80" t="s">
-        <v>51</v>
-      </c>
-      <c r="B34" s="80" t="s">
-        <v>83</v>
-      </c>
-      <c r="C34" s="78" t="s">
-        <v>29</v>
+      <c r="A34" s="85" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34" s="85" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" s="86" t="s">
+        <v>28</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>7</v>
@@ -5430,11 +5430,11 @@
       </c>
     </row>
     <row r="35" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A35" s="80"/>
-      <c r="B35" s="80"/>
-      <c r="C35" s="79"/>
+      <c r="A35" s="85"/>
+      <c r="B35" s="85"/>
+      <c r="C35" s="87"/>
       <c r="D35" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>8</v>
@@ -5468,11 +5468,11 @@
       </c>
     </row>
     <row r="36" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A36" s="80"/>
-      <c r="B36" s="80"/>
-      <c r="C36" s="79"/>
+      <c r="A36" s="85"/>
+      <c r="B36" s="85"/>
+      <c r="C36" s="87"/>
       <c r="D36" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>9</v>
@@ -5506,7 +5506,7 @@
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A37" s="80"/>
+      <c r="A37" s="85"/>
       <c r="B37" s="4"/>
       <c r="C37" s="7"/>
       <c r="E37" s="4"/>
@@ -5517,15 +5517,15 @@
       <c r="J37" s="6"/>
     </row>
     <row r="38" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A38" s="80"/>
-      <c r="B38" s="80" t="s">
-        <v>84</v>
-      </c>
-      <c r="C38" s="78" t="s">
-        <v>30</v>
+      <c r="A38" s="85"/>
+      <c r="B38" s="85" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" s="86" t="s">
+        <v>29</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>7</v>
@@ -5559,11 +5559,11 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A39" s="80"/>
-      <c r="B39" s="80"/>
-      <c r="C39" s="79"/>
+      <c r="A39" s="85"/>
+      <c r="B39" s="85"/>
+      <c r="C39" s="87"/>
       <c r="D39" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>8</v>
@@ -5597,11 +5597,11 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A40" s="80"/>
-      <c r="B40" s="80"/>
-      <c r="C40" s="79"/>
+      <c r="A40" s="85"/>
+      <c r="B40" s="85"/>
+      <c r="C40" s="87"/>
       <c r="D40" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>9</v>
@@ -5635,7 +5635,7 @@
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A41" s="80"/>
+      <c r="A41" s="85"/>
       <c r="B41" s="4"/>
       <c r="C41" s="7"/>
       <c r="E41" s="4"/>
@@ -5646,15 +5646,15 @@
       <c r="J41" s="6"/>
     </row>
     <row r="42" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A42" s="80"/>
-      <c r="B42" s="80" t="s">
-        <v>85</v>
-      </c>
-      <c r="C42" s="78" t="s">
-        <v>31</v>
+      <c r="A42" s="85"/>
+      <c r="B42" s="85" t="s">
+        <v>84</v>
+      </c>
+      <c r="C42" s="86" t="s">
+        <v>30</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>7</v>
@@ -5688,11 +5688,11 @@
       </c>
     </row>
     <row r="43" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A43" s="80"/>
-      <c r="B43" s="80"/>
-      <c r="C43" s="79"/>
+      <c r="A43" s="85"/>
+      <c r="B43" s="85"/>
+      <c r="C43" s="87"/>
       <c r="D43" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>8</v>
@@ -5726,11 +5726,11 @@
       </c>
     </row>
     <row r="44" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A44" s="80"/>
-      <c r="B44" s="80"/>
-      <c r="C44" s="79"/>
+      <c r="A44" s="85"/>
+      <c r="B44" s="85"/>
+      <c r="C44" s="87"/>
       <c r="D44" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>9</v>
@@ -5764,7 +5764,7 @@
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A45" s="80"/>
+      <c r="A45" s="85"/>
       <c r="B45" s="4"/>
       <c r="C45" s="7"/>
       <c r="E45" s="4"/>
@@ -5775,15 +5775,15 @@
       <c r="J45" s="6"/>
     </row>
     <row r="46" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A46" s="80"/>
-      <c r="B46" s="80" t="s">
-        <v>86</v>
-      </c>
-      <c r="C46" s="78" t="s">
-        <v>35</v>
+      <c r="A46" s="85"/>
+      <c r="B46" s="85" t="s">
+        <v>85</v>
+      </c>
+      <c r="C46" s="86" t="s">
+        <v>34</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>7</v>
@@ -5817,11 +5817,11 @@
       </c>
     </row>
     <row r="47" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A47" s="80"/>
-      <c r="B47" s="80"/>
-      <c r="C47" s="79"/>
+      <c r="A47" s="85"/>
+      <c r="B47" s="85"/>
+      <c r="C47" s="87"/>
       <c r="D47" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>8</v>
@@ -5855,11 +5855,11 @@
       </c>
     </row>
     <row r="48" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A48" s="80"/>
-      <c r="B48" s="80"/>
-      <c r="C48" s="79"/>
+      <c r="A48" s="85"/>
+      <c r="B48" s="85"/>
+      <c r="C48" s="87"/>
       <c r="D48" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>9</v>
@@ -5894,7 +5894,7 @@
     </row>
     <row r="51" spans="4:13" x14ac:dyDescent="0.2">
       <c r="E51" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F51" s="11">
         <f>MAX(F2:F48)</f>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="52" spans="4:13" x14ac:dyDescent="0.2">
       <c r="D52" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E52" s="8" t="s">
         <v>37</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>38</v>
       </c>
       <c r="F52" s="11">
         <f>AVERAGE(F2:F48)</f>
@@ -5971,7 +5971,7 @@
     </row>
     <row r="53" spans="4:13" x14ac:dyDescent="0.2">
       <c r="E53" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F53" s="11">
         <f t="shared" ref="F53:L53" si="23">MIN(F2:F48)</f>
@@ -6008,6 +6008,16 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="A34:A48"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="B38:B40"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="C46:C48"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="A2:A32"/>
     <mergeCell ref="C2:C4"/>
@@ -6024,16 +6034,6 @@
     <mergeCell ref="B26:B28"/>
     <mergeCell ref="C26:C28"/>
     <mergeCell ref="B30:B32"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="A34:A48"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="B38:B40"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="C46:C48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6056,10 +6056,10 @@
   <sheetData>
     <row r="1" spans="1:14" s="74" customFormat="1" ht="89" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="68" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B1" s="68" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C1" s="68" t="s">
         <v>22</v>
@@ -6071,42 +6071,42 @@
         <v>3</v>
       </c>
       <c r="F1" s="69" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="70" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="70" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="70" t="s">
         <v>57</v>
-      </c>
-      <c r="G1" s="70" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="70" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="70" t="s">
-        <v>58</v>
       </c>
       <c r="J1" s="69" t="s">
         <v>5</v>
       </c>
       <c r="K1" s="71" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L1" s="72" t="s">
+        <v>101</v>
+      </c>
+      <c r="M1" s="72" t="s">
+        <v>71</v>
+      </c>
+      <c r="N1" s="73" t="s">
         <v>102</v>
       </c>
-      <c r="M1" s="72" t="s">
-        <v>72</v>
-      </c>
-      <c r="N1" s="73" t="s">
-        <v>103</v>
-      </c>
     </row>
     <row r="2" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A2" s="80" t="s">
-        <v>76</v>
-      </c>
-      <c r="B2" s="82" t="s">
-        <v>97</v>
+      <c r="A2" s="85" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="89" t="s">
+        <v>96</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>7</v>
@@ -6146,10 +6146,10 @@
       </c>
     </row>
     <row r="3" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A3" s="80"/>
-      <c r="B3" s="80"/>
+      <c r="A3" s="85"/>
+      <c r="B3" s="85"/>
       <c r="C3" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>8</v>
@@ -6189,10 +6189,10 @@
       </c>
     </row>
     <row r="4" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="80"/>
-      <c r="B4" s="80"/>
+      <c r="A4" s="85"/>
+      <c r="B4" s="85"/>
       <c r="C4" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>9</v>
@@ -6245,14 +6245,14 @@
       <c r="M5" s="26"/>
     </row>
     <row r="6" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="80" t="s">
-        <v>84</v>
-      </c>
-      <c r="B6" s="80" t="s">
-        <v>98</v>
+      <c r="A6" s="85" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="85" t="s">
+        <v>97</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>7</v>
@@ -6292,10 +6292,10 @@
       </c>
     </row>
     <row r="7" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="80"/>
-      <c r="B7" s="80"/>
+      <c r="A7" s="85"/>
+      <c r="B7" s="85"/>
       <c r="C7" s="38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7" s="39" t="s">
         <v>8</v>
@@ -6335,10 +6335,10 @@
       </c>
     </row>
     <row r="8" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A8" s="80"/>
-      <c r="B8" s="80"/>
+      <c r="A8" s="85"/>
+      <c r="B8" s="85"/>
       <c r="C8" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>9</v>
@@ -6391,14 +6391,14 @@
       <c r="M9" s="26"/>
     </row>
     <row r="10" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="80" t="s">
-        <v>86</v>
-      </c>
-      <c r="B10" s="80" t="s">
-        <v>99</v>
+      <c r="A10" s="85" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="85" t="s">
+        <v>98</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>7</v>
@@ -6438,10 +6438,10 @@
       </c>
     </row>
     <row r="11" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="80"/>
-      <c r="B11" s="80"/>
+      <c r="A11" s="85"/>
+      <c r="B11" s="85"/>
       <c r="C11" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>8</v>
@@ -6481,10 +6481,10 @@
       </c>
     </row>
     <row r="12" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="80"/>
-      <c r="B12" s="80"/>
+      <c r="A12" s="85"/>
+      <c r="B12" s="85"/>
       <c r="C12" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>9</v>
@@ -6546,7 +6546,7 @@
       <c r="H14" s="19"/>
       <c r="I14" s="19"/>
       <c r="J14" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K14" s="50">
         <f t="shared" ref="K14" si="1">MAX(K2:K12)</f>
@@ -6568,23 +6568,23 @@
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="22"/>
       <c r="B15" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="D15" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="E15" s="33" t="s">
         <v>91</v>
-      </c>
-      <c r="E15" s="33" t="s">
-        <v>92</v>
       </c>
       <c r="F15" s="19"/>
       <c r="G15" s="19"/>
       <c r="H15" s="19"/>
       <c r="I15" s="19"/>
       <c r="J15" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K15" s="50">
         <f t="shared" ref="K15" si="3">MIN(K2:K12)</f>
@@ -6606,7 +6606,7 @@
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="22"/>
       <c r="B16" s="31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C16" s="35">
         <f>1/38</f>
@@ -6625,7 +6625,7 @@
       <c r="H16" s="19"/>
       <c r="I16" s="19"/>
       <c r="J16" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K16" s="50">
         <f t="shared" ref="K16" si="5">AVERAGE(K2:K12)</f>
@@ -6660,16 +6660,16 @@
     <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18" s="22"/>
       <c r="B18" s="31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C18" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="E18" s="53" t="s">
         <v>91</v>
-      </c>
-      <c r="E18" s="53" t="s">
-        <v>92</v>
       </c>
       <c r="F18" s="19"/>
       <c r="G18" s="19"/>
@@ -6682,7 +6682,7 @@
     <row r="19" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A19" s="22"/>
       <c r="B19" s="31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C19" s="35">
         <f>1/34</f>
@@ -6720,16 +6720,16 @@
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="24"/>
       <c r="B21" s="31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C21" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="D21" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="E21" s="53" t="s">
         <v>91</v>
-      </c>
-      <c r="E21" s="53" t="s">
-        <v>92</v>
       </c>
       <c r="F21" s="19"/>
       <c r="G21" s="19"/>
@@ -6742,7 +6742,7 @@
     <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="22"/>
       <c r="B22" s="31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C22" s="35">
         <f>1/21</f>
@@ -7045,13 +7045,13 @@
   <sheetData>
     <row r="1" spans="1:15" s="67" customFormat="1" ht="89" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="61" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="61" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="61" t="s">
         <v>62</v>
-      </c>
-      <c r="B1" s="61" t="s">
-        <v>96</v>
-      </c>
-      <c r="C1" s="61" t="s">
-        <v>63</v>
       </c>
       <c r="D1" s="61" t="s">
         <v>22</v>
@@ -7063,45 +7063,45 @@
         <v>3</v>
       </c>
       <c r="G1" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="H1" s="63" t="s">
+        <v>59</v>
+      </c>
+      <c r="I1" s="63" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1" s="63" t="s">
         <v>57</v>
-      </c>
-      <c r="H1" s="63" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1" s="63" t="s">
-        <v>59</v>
-      </c>
-      <c r="J1" s="63" t="s">
-        <v>58</v>
       </c>
       <c r="K1" s="62" t="s">
         <v>5</v>
       </c>
       <c r="L1" s="64" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M1" s="65" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N1" s="65" t="s">
+        <v>71</v>
+      </c>
+      <c r="O1" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="O1" s="66" t="s">
-        <v>73</v>
-      </c>
     </row>
     <row r="2" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A2" s="82" t="s">
-        <v>84</v>
-      </c>
-      <c r="B2" s="82" t="s">
-        <v>98</v>
-      </c>
-      <c r="C2" s="83">
+      <c r="A2" s="89" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="89" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="90">
         <v>0</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>7</v>
@@ -7141,11 +7141,11 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A3" s="80"/>
-      <c r="B3" s="80"/>
-      <c r="C3" s="81"/>
+      <c r="A3" s="85"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="88"/>
       <c r="D3" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>8</v>
@@ -7185,11 +7185,11 @@
       </c>
     </row>
     <row r="4" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="80"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="81"/>
+      <c r="A4" s="85"/>
+      <c r="B4" s="85"/>
+      <c r="C4" s="88"/>
       <c r="D4" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>9</v>
@@ -7229,8 +7229,8 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="80"/>
-      <c r="B5" s="80"/>
+      <c r="A5" s="85"/>
+      <c r="B5" s="85"/>
       <c r="C5" s="21"/>
       <c r="E5" s="4"/>
       <c r="F5" s="6"/>
@@ -7244,13 +7244,13 @@
       <c r="N5" s="26"/>
     </row>
     <row r="6" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="80"/>
-      <c r="B6" s="80"/>
-      <c r="C6" s="81">
+      <c r="A6" s="85"/>
+      <c r="B6" s="85"/>
+      <c r="C6" s="88">
         <v>10</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>7</v>
@@ -7290,11 +7290,11 @@
       </c>
     </row>
     <row r="7" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="80"/>
-      <c r="B7" s="80"/>
-      <c r="C7" s="81"/>
+      <c r="A7" s="85"/>
+      <c r="B7" s="85"/>
+      <c r="C7" s="88"/>
       <c r="D7" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>8</v>
@@ -7334,11 +7334,11 @@
       </c>
     </row>
     <row r="8" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A8" s="80"/>
-      <c r="B8" s="80"/>
-      <c r="C8" s="81"/>
+      <c r="A8" s="85"/>
+      <c r="B8" s="85"/>
+      <c r="C8" s="88"/>
       <c r="D8" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>9</v>
@@ -7378,8 +7378,8 @@
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A9" s="80"/>
-      <c r="B9" s="80"/>
+      <c r="A9" s="85"/>
+      <c r="B9" s="85"/>
       <c r="C9" s="21"/>
       <c r="E9" s="4"/>
       <c r="F9" s="6"/>
@@ -7393,13 +7393,13 @@
       <c r="N9" s="26"/>
     </row>
     <row r="10" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="80"/>
-      <c r="B10" s="80"/>
-      <c r="C10" s="81">
+      <c r="A10" s="85"/>
+      <c r="B10" s="85"/>
+      <c r="C10" s="88">
         <v>20</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>7</v>
@@ -7439,11 +7439,11 @@
       </c>
     </row>
     <row r="11" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="80"/>
-      <c r="B11" s="80"/>
-      <c r="C11" s="81"/>
+      <c r="A11" s="85"/>
+      <c r="B11" s="85"/>
+      <c r="C11" s="88"/>
       <c r="D11" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>8</v>
@@ -7483,11 +7483,11 @@
       </c>
     </row>
     <row r="12" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="80"/>
-      <c r="B12" s="80"/>
-      <c r="C12" s="81"/>
+      <c r="A12" s="85"/>
+      <c r="B12" s="85"/>
+      <c r="C12" s="88"/>
       <c r="D12" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>9</v>
@@ -7527,8 +7527,8 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A13" s="80"/>
-      <c r="B13" s="80"/>
+      <c r="A13" s="85"/>
+      <c r="B13" s="85"/>
       <c r="C13" s="21"/>
       <c r="E13" s="4"/>
       <c r="F13" s="6"/>
@@ -7542,13 +7542,13 @@
       <c r="N13" s="26"/>
     </row>
     <row r="14" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A14" s="80"/>
-      <c r="B14" s="80"/>
-      <c r="C14" s="81">
+      <c r="A14" s="85"/>
+      <c r="B14" s="85"/>
+      <c r="C14" s="88">
         <v>30</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>7</v>
@@ -7588,11 +7588,11 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A15" s="80"/>
-      <c r="B15" s="80"/>
-      <c r="C15" s="81"/>
+      <c r="A15" s="85"/>
+      <c r="B15" s="85"/>
+      <c r="C15" s="88"/>
       <c r="D15" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>8</v>
@@ -7632,11 +7632,11 @@
       </c>
     </row>
     <row r="16" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A16" s="80"/>
-      <c r="B16" s="80"/>
-      <c r="C16" s="81"/>
+      <c r="A16" s="85"/>
+      <c r="B16" s="85"/>
+      <c r="C16" s="88"/>
       <c r="D16" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>9</v>
@@ -7676,8 +7676,8 @@
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A17" s="80"/>
-      <c r="B17" s="80"/>
+      <c r="A17" s="85"/>
+      <c r="B17" s="85"/>
       <c r="C17" s="23"/>
       <c r="E17" s="24"/>
       <c r="F17" s="19"/>
@@ -7691,13 +7691,13 @@
       <c r="N17" s="26"/>
     </row>
     <row r="18" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A18" s="80"/>
-      <c r="B18" s="80"/>
-      <c r="C18" s="81">
+      <c r="A18" s="85"/>
+      <c r="B18" s="85"/>
+      <c r="C18" s="88">
         <v>100</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>23</v>
+        <v>143</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>7</v>
@@ -7737,11 +7737,11 @@
       </c>
     </row>
     <row r="19" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A19" s="80"/>
-      <c r="B19" s="80"/>
-      <c r="C19" s="81"/>
+      <c r="A19" s="85"/>
+      <c r="B19" s="85"/>
+      <c r="C19" s="88"/>
       <c r="D19" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>8</v>
@@ -7781,11 +7781,11 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A20" s="80"/>
-      <c r="B20" s="80"/>
-      <c r="C20" s="81"/>
+      <c r="A20" s="85"/>
+      <c r="B20" s="85"/>
+      <c r="C20" s="88"/>
       <c r="D20" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>9</v>
@@ -7888,23 +7888,23 @@
       <c r="A25" s="24"/>
       <c r="B25" s="24"/>
       <c r="C25" s="31" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D25" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="E25" s="32" t="s">
+      <c r="F25" s="33" t="s">
         <v>91</v>
-      </c>
-      <c r="F25" s="33" t="s">
-        <v>92</v>
       </c>
       <c r="G25" s="19"/>
       <c r="H25" s="19"/>
       <c r="I25" s="19"/>
       <c r="J25" s="19"/>
       <c r="K25" s="20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L25" s="50">
         <f>MAX(L2:L23)</f>
@@ -7927,7 +7927,7 @@
       <c r="A26" s="22"/>
       <c r="B26" s="22"/>
       <c r="C26" s="31" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D26" s="35">
         <f>1/34</f>
@@ -7946,7 +7946,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="19"/>
       <c r="K26" s="20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L26" s="50">
         <f>MIN(L2:L20)</f>
@@ -7976,7 +7976,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="19"/>
       <c r="K27" s="20" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L27" s="50">
         <f>AVERAGE(L2:L23)</f>
@@ -8357,10 +8357,10 @@
   <sheetData>
     <row r="1" spans="1:14" s="60" customFormat="1" ht="89" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B1" s="54" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C1" s="55" t="s">
         <v>22</v>
@@ -8372,42 +8372,42 @@
         <v>3</v>
       </c>
       <c r="F1" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="56" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="56" t="s">
+        <v>58</v>
+      </c>
+      <c r="I1" s="56" t="s">
         <v>57</v>
-      </c>
-      <c r="G1" s="56" t="s">
-        <v>60</v>
-      </c>
-      <c r="H1" s="56" t="s">
-        <v>59</v>
-      </c>
-      <c r="I1" s="56" t="s">
-        <v>58</v>
       </c>
       <c r="J1" s="56" t="s">
         <v>5</v>
       </c>
       <c r="K1" s="57" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L1" s="58" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M1" s="58" t="s">
+        <v>71</v>
+      </c>
+      <c r="N1" s="59" t="s">
         <v>72</v>
       </c>
-      <c r="N1" s="59" t="s">
-        <v>73</v>
-      </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="85" t="s">
-        <v>84</v>
-      </c>
-      <c r="B2" s="88" t="s">
-        <v>98</v>
-      </c>
-      <c r="C2" s="85" t="s">
-        <v>23</v>
+      <c r="A2" s="92" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="95" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="92" t="s">
+        <v>143</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>7</v>
@@ -8447,11 +8447,11 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="86"/>
-      <c r="B3" s="84"/>
-      <c r="C3" s="86"/>
+      <c r="A3" s="93"/>
+      <c r="B3" s="91"/>
+      <c r="C3" s="93"/>
       <c r="D3" s="25" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E3" s="26">
         <v>0.82660060980000005</v>
@@ -8488,11 +8488,11 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="86"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="86"/>
+      <c r="A4" s="93"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="93"/>
       <c r="D4" s="25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E4" s="26">
         <v>0.61128048779999999</v>
@@ -8529,8 +8529,8 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="86"/>
-      <c r="B5" s="84"/>
+      <c r="A5" s="93"/>
+      <c r="B5" s="91"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
       <c r="E5" s="26"/>
@@ -8544,10 +8544,10 @@
       <c r="M5" s="26"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="86"/>
-      <c r="B6" s="84"/>
-      <c r="C6" s="87" t="s">
-        <v>65</v>
+      <c r="A6" s="93"/>
+      <c r="B6" s="91"/>
+      <c r="C6" s="94" t="s">
+        <v>64</v>
       </c>
       <c r="D6" s="25" t="s">
         <v>8</v>
@@ -8587,11 +8587,11 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="86"/>
-      <c r="B7" s="84"/>
-      <c r="C7" s="87"/>
+      <c r="A7" s="93"/>
+      <c r="B7" s="91"/>
+      <c r="C7" s="94"/>
       <c r="D7" s="25" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E7" s="26">
         <v>0.62080792679999997</v>
@@ -8628,11 +8628,11 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="86"/>
-      <c r="B8" s="84"/>
-      <c r="C8" s="87"/>
+      <c r="A8" s="93"/>
+      <c r="B8" s="91"/>
+      <c r="C8" s="94"/>
       <c r="D8" s="25" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E8" s="26">
         <v>0.61242378050000001</v>
@@ -8669,8 +8669,8 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="86"/>
-      <c r="B9" s="84"/>
+      <c r="A9" s="93"/>
+      <c r="B9" s="91"/>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
       <c r="E9" s="26"/>
@@ -8684,10 +8684,10 @@
       <c r="M9" s="26"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="86"/>
-      <c r="B10" s="84"/>
-      <c r="C10" s="84" t="s">
-        <v>66</v>
+      <c r="A10" s="93"/>
+      <c r="B10" s="91"/>
+      <c r="C10" s="91" t="s">
+        <v>65</v>
       </c>
       <c r="D10" s="25" t="s">
         <v>9</v>
@@ -8727,11 +8727,11 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="86"/>
-      <c r="B11" s="84"/>
-      <c r="C11" s="84"/>
+      <c r="A11" s="93"/>
+      <c r="B11" s="91"/>
+      <c r="C11" s="91"/>
       <c r="D11" s="25" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E11" s="26">
         <v>0.59413109760000005</v>
@@ -8786,16 +8786,16 @@
       <c r="A13" s="25"/>
       <c r="B13" s="25"/>
       <c r="C13" s="43" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D13" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="45" t="s">
         <v>90</v>
       </c>
-      <c r="E13" s="45" t="s">
+      <c r="F13" s="45" t="s">
         <v>91</v>
-      </c>
-      <c r="F13" s="45" t="s">
-        <v>92</v>
       </c>
       <c r="G13" s="26"/>
       <c r="H13" s="26"/>
@@ -8809,7 +8809,7 @@
       <c r="A14" s="27"/>
       <c r="B14" s="27"/>
       <c r="C14" s="46" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D14" s="47">
         <v>0.03</v>
@@ -9411,205 +9411,205 @@
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="65.33203125" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="45" style="92" customWidth="1"/>
-    <col min="2" max="2" width="61.1640625" style="92" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53" style="92" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5" style="93" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="65.33203125" style="94"/>
+    <col min="1" max="1" width="45" style="81" customWidth="1"/>
+    <col min="2" max="2" width="61.1640625" style="81" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53" style="81" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5" style="82" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="65.33203125" style="83"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="91" customFormat="1" ht="25" x14ac:dyDescent="0.2">
-      <c r="A1" s="89" t="s">
+    <row r="1" spans="1:4" s="80" customFormat="1" ht="25" x14ac:dyDescent="0.2">
+      <c r="A1" s="78" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="78" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="89" t="s">
+      <c r="C1" s="78" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" s="79" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A2" s="81" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="81" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="81" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="82">
+        <v>0.68325173248234505</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A3" s="81" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" s="81" t="s">
+        <v>121</v>
+      </c>
+      <c r="C3" s="81" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="82">
+        <v>0.68325173248234505</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A4" s="81" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="81" t="s">
+        <v>125</v>
+      </c>
+      <c r="C4" s="81" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="82">
+        <v>0.68325173248234505</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A5" s="81" t="s">
+        <v>126</v>
+      </c>
+      <c r="B5" s="81" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" s="81" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" s="82">
+        <v>0.68041836283516299</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A6" s="81" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="81" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="81" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6" s="82">
+        <v>0.67742712096802804</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A7" s="81" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="81" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="81" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7" s="82">
+        <v>0.65343720964277696</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A8" s="81" t="s">
+        <v>129</v>
+      </c>
+      <c r="B8" s="81" t="s">
+        <v>130</v>
+      </c>
+      <c r="D8" s="82">
+        <v>0.64949999999999997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A9" s="81" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9" s="81" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="81" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="82">
+        <v>0.64262720538739304</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A10" s="81" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="81" t="s">
+        <v>128</v>
+      </c>
+      <c r="C10" s="81" t="s">
+        <v>127</v>
+      </c>
+      <c r="D10" s="82">
+        <v>0.63939999999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="22" x14ac:dyDescent="0.2">
+      <c r="A11" s="81" t="s">
         <v>112</v>
       </c>
-      <c r="C1" s="89" t="s">
+      <c r="B11" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="90" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A2" s="92" t="s">
-        <v>127</v>
-      </c>
-      <c r="B2" s="92" t="s">
-        <v>119</v>
-      </c>
-      <c r="C2" s="92" t="s">
-        <v>110</v>
-      </c>
-      <c r="D2" s="93">
-        <v>0.68325173248234505</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A3" s="92" t="s">
-        <v>127</v>
-      </c>
-      <c r="B3" s="92" t="s">
+      <c r="D11" s="82">
+        <v>0.60415152730396504</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="22" x14ac:dyDescent="0.2">
+      <c r="A12" s="81" t="s">
+        <v>112</v>
+      </c>
+      <c r="B12" s="84" t="s">
+        <v>107</v>
+      </c>
+      <c r="D12" s="82">
+        <v>0.603348181891603</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A13" s="81" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13" s="81" t="s">
+        <v>114</v>
+      </c>
+      <c r="D13" s="82">
+        <v>0.57569693797857102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A14" s="81" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" s="81" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="92" t="s">
-        <v>110</v>
-      </c>
-      <c r="D3" s="93">
-        <v>0.68325173248234505</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A4" s="92" t="s">
-        <v>127</v>
-      </c>
-      <c r="B4" s="92" t="s">
-        <v>126</v>
-      </c>
-      <c r="C4" s="92" t="s">
-        <v>110</v>
-      </c>
-      <c r="D4" s="93">
-        <v>0.68325173248234505</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A5" s="92" t="s">
-        <v>127</v>
-      </c>
-      <c r="B5" s="92" t="s">
-        <v>121</v>
-      </c>
-      <c r="C5" s="92" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" s="93">
-        <v>0.68041836283516299</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A6" s="92" t="s">
-        <v>127</v>
-      </c>
-      <c r="B6" s="92" t="s">
-        <v>125</v>
-      </c>
-      <c r="C6" s="92" t="s">
-        <v>110</v>
-      </c>
-      <c r="D6" s="93">
-        <v>0.67742712096802804</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A7" s="92" t="s">
-        <v>127</v>
-      </c>
-      <c r="B7" s="92" t="s">
-        <v>120</v>
-      </c>
-      <c r="C7" s="92" t="s">
-        <v>110</v>
-      </c>
-      <c r="D7" s="93">
-        <v>0.65343720964277696</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A8" s="92" t="s">
-        <v>130</v>
-      </c>
-      <c r="B8" s="92" t="s">
-        <v>131</v>
-      </c>
-      <c r="D8" s="93">
-        <v>0.64949999999999997</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A9" s="92" t="s">
-        <v>127</v>
-      </c>
-      <c r="B9" s="92" t="s">
-        <v>124</v>
-      </c>
-      <c r="C9" s="92" t="s">
-        <v>110</v>
-      </c>
-      <c r="D9" s="93">
-        <v>0.64262720538739304</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A10" s="92" t="s">
-        <v>127</v>
-      </c>
-      <c r="B10" s="92" t="s">
-        <v>129</v>
-      </c>
-      <c r="C10" s="92" t="s">
-        <v>128</v>
-      </c>
-      <c r="D10" s="93">
-        <v>0.63939999999999997</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="22" x14ac:dyDescent="0.2">
-      <c r="A11" s="92" t="s">
+      <c r="C14" s="81" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" s="82">
+        <v>0.57370283757216001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A15" s="81" t="s">
         <v>113</v>
       </c>
-      <c r="B11" s="92" t="s">
-        <v>107</v>
-      </c>
-      <c r="D11" s="93">
-        <v>0.60415152730396504</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="22" x14ac:dyDescent="0.2">
-      <c r="A12" s="92" t="s">
-        <v>113</v>
-      </c>
-      <c r="B12" s="95" t="s">
-        <v>108</v>
-      </c>
-      <c r="D12" s="93">
-        <v>0.603348181891603</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A13" s="92" t="s">
-        <v>114</v>
-      </c>
-      <c r="B13" s="92" t="s">
-        <v>115</v>
-      </c>
-      <c r="D13" s="93">
-        <v>0.57569693797857102</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A14" s="92" t="s">
-        <v>127</v>
-      </c>
-      <c r="B14" s="92" t="s">
-        <v>123</v>
-      </c>
-      <c r="C14" s="92" t="s">
-        <v>110</v>
-      </c>
-      <c r="D14" s="93">
-        <v>0.57370283757216001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A15" s="92" t="s">
-        <v>114</v>
-      </c>
-      <c r="B15" s="92" t="s">
-        <v>117</v>
-      </c>
-      <c r="D15" s="93">
+      <c r="B15" s="81" t="s">
+        <v>116</v>
+      </c>
+      <c r="D15" s="82">
         <v>0.51741735167898695</v>
       </c>
     </row>
@@ -9626,203 +9626,203 @@
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="65.33203125" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="65.33203125" style="92"/>
-    <col min="4" max="4" width="65.33203125" style="93"/>
-    <col min="5" max="16384" width="65.33203125" style="94"/>
+    <col min="1" max="3" width="65.33203125" style="81"/>
+    <col min="4" max="4" width="65.33203125" style="82"/>
+    <col min="5" max="16384" width="65.33203125" style="83"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="91" customFormat="1" ht="25" x14ac:dyDescent="0.2">
-      <c r="A1" s="89" t="s">
+    <row r="1" spans="1:4" s="80" customFormat="1" ht="25" x14ac:dyDescent="0.2">
+      <c r="A1" s="78" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="78" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="89" t="s">
+      <c r="C1" s="78" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" s="79" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A2" s="81" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="81" t="s">
+        <v>139</v>
+      </c>
+      <c r="C2" s="81" t="s">
+        <v>141</v>
+      </c>
+      <c r="D2" s="82">
+        <v>0.73470000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A3" s="81" t="s">
+        <v>129</v>
+      </c>
+      <c r="B3" s="81" t="s">
+        <v>140</v>
+      </c>
+      <c r="D3" s="82">
+        <v>0.7097</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="22" x14ac:dyDescent="0.2">
+      <c r="A4" s="81" t="s">
         <v>112</v>
       </c>
-      <c r="C1" s="89" t="s">
+      <c r="B4" s="81" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" s="82">
+        <v>0.69406628387897396</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A5" s="81" t="s">
+        <v>126</v>
+      </c>
+      <c r="B5" s="81" t="s">
+        <v>133</v>
+      </c>
+      <c r="C5" s="81" t="s">
+        <v>142</v>
+      </c>
+      <c r="D5" s="82">
+        <v>0.665770082977021</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A6" s="81" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="81" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="81" t="s">
+        <v>142</v>
+      </c>
+      <c r="D6" s="82">
+        <v>0.65203403508906599</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A7" s="81" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="81" t="s">
+        <v>135</v>
+      </c>
+      <c r="C7" s="81" t="s">
+        <v>142</v>
+      </c>
+      <c r="D7" s="82">
+        <v>0.60864643260521401</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="22" x14ac:dyDescent="0.2">
+      <c r="A8" s="81" t="s">
+        <v>112</v>
+      </c>
+      <c r="B8" s="81" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="90" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A2" s="92" t="s">
-        <v>127</v>
-      </c>
-      <c r="B2" s="92" t="s">
-        <v>140</v>
-      </c>
-      <c r="C2" s="92" t="s">
+      <c r="D8" s="82">
+        <v>0.60415152730396504</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A9" s="81" t="s">
+        <v>113</v>
+      </c>
+      <c r="B9" s="81" t="s">
+        <v>115</v>
+      </c>
+      <c r="D9" s="82">
+        <v>0.59785011377850095</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A10" s="81" t="s">
+        <v>126</v>
+      </c>
+      <c r="B10" s="81" t="s">
+        <v>132</v>
+      </c>
+      <c r="C10" s="81" t="s">
         <v>142</v>
       </c>
-      <c r="D2" s="93">
-        <v>0.73470000000000002</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A3" s="92" t="s">
-        <v>130</v>
-      </c>
-      <c r="B3" s="92" t="s">
-        <v>141</v>
-      </c>
-      <c r="D3" s="93">
-        <v>0.7097</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="22" x14ac:dyDescent="0.2">
-      <c r="A4" s="92" t="s">
+      <c r="D10" s="82">
+        <v>0.58596491228070102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A11" s="81" t="s">
+        <v>126</v>
+      </c>
+      <c r="B11" s="81" t="s">
+        <v>138</v>
+      </c>
+      <c r="C11" s="81" t="s">
+        <v>142</v>
+      </c>
+      <c r="D11" s="82">
+        <v>0.58596491228070102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A12" s="81" t="s">
+        <v>126</v>
+      </c>
+      <c r="B12" s="81" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="81" t="s">
+        <v>142</v>
+      </c>
+      <c r="D12" s="82">
+        <v>0.57994647302866398</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A13" s="81" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="81" t="s">
+        <v>137</v>
+      </c>
+      <c r="C13" s="81" t="s">
+        <v>142</v>
+      </c>
+      <c r="D13" s="82">
+        <v>0.579743455999432</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A14" s="81" t="s">
+        <v>126</v>
+      </c>
+      <c r="B14" s="81" t="s">
+        <v>136</v>
+      </c>
+      <c r="C14" s="81" t="s">
+        <v>142</v>
+      </c>
+      <c r="D14" s="82">
+        <v>0.57884998520905395</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A15" s="81" t="s">
         <v>113</v>
       </c>
-      <c r="B4" s="92" t="s">
-        <v>109</v>
-      </c>
-      <c r="D4" s="93">
-        <v>0.69406628387897396</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A5" s="92" t="s">
-        <v>127</v>
-      </c>
-      <c r="B5" s="92" t="s">
-        <v>134</v>
-      </c>
-      <c r="C5" s="92" t="s">
-        <v>143</v>
-      </c>
-      <c r="D5" s="93">
-        <v>0.665770082977021</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A6" s="92" t="s">
-        <v>127</v>
-      </c>
-      <c r="B6" s="92" t="s">
-        <v>135</v>
-      </c>
-      <c r="C6" s="92" t="s">
-        <v>143</v>
-      </c>
-      <c r="D6" s="93">
-        <v>0.65203403508906599</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A7" s="92" t="s">
-        <v>127</v>
-      </c>
-      <c r="B7" s="92" t="s">
-        <v>136</v>
-      </c>
-      <c r="C7" s="92" t="s">
-        <v>143</v>
-      </c>
-      <c r="D7" s="93">
-        <v>0.60864643260521401</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="22" x14ac:dyDescent="0.2">
-      <c r="A8" s="92" t="s">
-        <v>113</v>
-      </c>
-      <c r="B8" s="92" t="s">
-        <v>107</v>
-      </c>
-      <c r="D8" s="93">
-        <v>0.60415152730396504</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A9" s="92" t="s">
-        <v>114</v>
-      </c>
-      <c r="B9" s="92" t="s">
-        <v>116</v>
-      </c>
-      <c r="D9" s="93">
-        <v>0.59785011377850095</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A10" s="92" t="s">
-        <v>127</v>
-      </c>
-      <c r="B10" s="92" t="s">
-        <v>133</v>
-      </c>
-      <c r="C10" s="92" t="s">
-        <v>143</v>
-      </c>
-      <c r="D10" s="93">
-        <v>0.58596491228070102</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A11" s="92" t="s">
-        <v>127</v>
-      </c>
-      <c r="B11" s="92" t="s">
-        <v>139</v>
-      </c>
-      <c r="C11" s="92" t="s">
-        <v>143</v>
-      </c>
-      <c r="D11" s="93">
-        <v>0.58596491228070102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A12" s="92" t="s">
-        <v>127</v>
-      </c>
-      <c r="B12" s="92" t="s">
-        <v>132</v>
-      </c>
-      <c r="C12" s="92" t="s">
-        <v>143</v>
-      </c>
-      <c r="D12" s="93">
-        <v>0.57994647302866398</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A13" s="92" t="s">
-        <v>127</v>
-      </c>
-      <c r="B13" s="92" t="s">
-        <v>138</v>
-      </c>
-      <c r="C13" s="92" t="s">
-        <v>143</v>
-      </c>
-      <c r="D13" s="93">
-        <v>0.579743455999432</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A14" s="92" t="s">
-        <v>127</v>
-      </c>
-      <c r="B14" s="92" t="s">
-        <v>137</v>
-      </c>
-      <c r="C14" s="92" t="s">
-        <v>143</v>
-      </c>
-      <c r="D14" s="93">
-        <v>0.57884998520905395</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A15" s="92" t="s">
-        <v>114</v>
-      </c>
-      <c r="B15" s="92" t="s">
-        <v>118</v>
-      </c>
-      <c r="D15" s="93">
+      <c r="B15" s="81" t="s">
+        <v>117</v>
+      </c>
+      <c r="D15" s="82">
         <v>0.54874577477317199</v>
       </c>
     </row>

--- a/benchmarking/output/data.xlsx
+++ b/benchmarking/output/data.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64F0270-B6F5-C045-8FFC-613BA3FCD10E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC837D66-E298-8F4D-982D-4E217F14A189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3920" yWindow="500" windowWidth="34480" windowHeight="19400" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3920" yWindow="500" windowWidth="34480" windowHeight="19400" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="basic" sheetId="1" r:id="rId1"/>
     <sheet name="special" sheetId="2" r:id="rId2"/>
     <sheet name="pretrained" sheetId="4" r:id="rId3"/>
-    <sheet name="checking bias" sheetId="5" r:id="rId4"/>
-    <sheet name="checking noise" sheetId="6" r:id="rId5"/>
-    <sheet name="family of models" sheetId="7" r:id="rId6"/>
-    <sheet name="Meta-Learner Roberta" sheetId="8" r:id="rId7"/>
-    <sheet name="Meta-Learner Deberta" sheetId="9" r:id="rId8"/>
+    <sheet name="pretrained - average" sheetId="10" r:id="rId4"/>
+    <sheet name="checking bias" sheetId="5" r:id="rId5"/>
+    <sheet name="checking noise" sheetId="6" r:id="rId6"/>
+    <sheet name="family of models" sheetId="7" r:id="rId7"/>
+    <sheet name="Meta-Learner Roberta" sheetId="8" r:id="rId8"/>
+    <sheet name="Meta-Learner Deberta" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="145">
   <si>
     <t>Model</t>
   </si>
@@ -346,15 +347,9 @@
     <t>Composition</t>
   </si>
   <si>
-    <t>year: 53%, support:38%, attack: 6,8%, equivalent:1,2%</t>
-  </si>
-  <si>
     <t>year: 59%, support: 34%, attack: 6%, equivalent: 1%</t>
   </si>
   <si>
-    <t>says: 38%, year:36%, support: 21%, attack:4%, equivalent:1%</t>
-  </si>
-  <si>
     <t>MAX=</t>
   </si>
   <si>
@@ -365,9 +360,6 @@
   </si>
   <si>
     <t>Weighted Average REL hits@1</t>
-  </si>
-  <si>
-    <t>Relation classification + prediction f1_macro</t>
   </si>
   <si>
     <t>F1-Macro</t>
@@ -907,6 +899,18 @@
   <si>
     <t>Translational</t>
   </si>
+  <si>
+    <t>support:17%, attack: 3%, equivalent:0.5%, type: 30%, speaker: 25,5%, year:24%</t>
+  </si>
+  <si>
+    <t>support: 25%, attack: 4%, equivalent: 1%, speaker: 36%, year: 34%</t>
+  </si>
+  <si>
+    <t>Average RC + RP</t>
+  </si>
+  <si>
+    <t>Average RC +RP</t>
+  </si>
 </sst>
 </file>
 
@@ -916,7 +920,7 @@
     <numFmt numFmtId="164" formatCode="0.000000"/>
     <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1008,34 +1012,6 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
-      <color rgb="FFC00000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFC00000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FFC00000"/>
-      <name val="Calibri (Corpo)"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color rgb="FFC00000"/>
-      <name val="Calibri (Corpo)"/>
-    </font>
-    <font>
-      <b/>
       <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1056,6 +1032,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri (Corpo)"/>
     </font>
   </fonts>
   <fills count="14">
@@ -1229,7 +1211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1343,12 +1325,6 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1370,15 +1346,6 @@
     <xf numFmtId="2" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1397,9 +1364,6 @@
     <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1414,9 +1378,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1437,9 +1398,6 @@
     <xf numFmtId="164" fontId="7" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1449,22 +1407,16 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="17" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="13" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1476,16 +1428,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1510,6 +1462,43 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="16" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1861,17 +1850,17 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A2" s="85" t="s">
+      <c r="A2" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="86" t="s">
+      <c r="C2" s="75" t="s">
         <v>28</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>7</v>
@@ -1893,9 +1882,9 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A3" s="85"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="87"/>
+      <c r="A3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="76"/>
       <c r="D3" s="5" t="s">
         <v>23</v>
       </c>
@@ -1919,9 +1908,9 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="85"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="87"/>
+      <c r="A4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="76"/>
       <c r="D4" s="5" t="s">
         <v>24</v>
       </c>
@@ -1946,7 +1935,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
-      <c r="B5" s="88"/>
+      <c r="B5" s="78"/>
       <c r="C5" s="7"/>
       <c r="E5" s="4"/>
       <c r="F5" s="6"/>
@@ -1956,15 +1945,15 @@
       <c r="J5" s="6"/>
     </row>
     <row r="6" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="85" t="s">
+      <c r="A6" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="88"/>
-      <c r="C6" s="86" t="s">
+      <c r="B6" s="78"/>
+      <c r="C6" s="75" t="s">
         <v>29</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>7</v>
@@ -1986,9 +1975,9 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="85"/>
-      <c r="B7" s="88"/>
-      <c r="C7" s="87"/>
+      <c r="A7" s="77"/>
+      <c r="B7" s="78"/>
+      <c r="C7" s="76"/>
       <c r="D7" s="5" t="s">
         <v>23</v>
       </c>
@@ -2012,9 +2001,9 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A8" s="85"/>
-      <c r="B8" s="88"/>
-      <c r="C8" s="87"/>
+      <c r="A8" s="77"/>
+      <c r="B8" s="78"/>
+      <c r="C8" s="76"/>
       <c r="D8" s="5" t="s">
         <v>24</v>
       </c>
@@ -2039,7 +2028,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
-      <c r="B9" s="88"/>
+      <c r="B9" s="78"/>
       <c r="C9" s="7"/>
       <c r="E9" s="4"/>
       <c r="F9" s="6"/>
@@ -2049,15 +2038,15 @@
       <c r="J9" s="6"/>
     </row>
     <row r="10" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="85" t="s">
+      <c r="A10" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="88"/>
-      <c r="C10" s="86" t="s">
+      <c r="B10" s="78"/>
+      <c r="C10" s="75" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>7</v>
@@ -2079,9 +2068,9 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="85"/>
-      <c r="B11" s="88"/>
-      <c r="C11" s="87"/>
+      <c r="A11" s="77"/>
+      <c r="B11" s="78"/>
+      <c r="C11" s="76"/>
       <c r="D11" s="5" t="s">
         <v>23</v>
       </c>
@@ -2105,9 +2094,9 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="85"/>
-      <c r="B12" s="88"/>
-      <c r="C12" s="87"/>
+      <c r="A12" s="77"/>
+      <c r="B12" s="78"/>
+      <c r="C12" s="76"/>
       <c r="D12" s="5" t="s">
         <v>24</v>
       </c>
@@ -2132,7 +2121,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="4"/>
-      <c r="B13" s="88"/>
+      <c r="B13" s="78"/>
       <c r="C13" s="7"/>
       <c r="E13" s="4"/>
       <c r="F13" s="6"/>
@@ -2142,15 +2131,15 @@
       <c r="J13" s="6"/>
     </row>
     <row r="14" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A14" s="85" t="s">
+      <c r="A14" s="77" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="88"/>
-      <c r="C14" s="86" t="s">
+      <c r="B14" s="78"/>
+      <c r="C14" s="75" t="s">
         <v>31</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>7</v>
@@ -2172,9 +2161,9 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A15" s="85"/>
-      <c r="B15" s="88"/>
-      <c r="C15" s="87"/>
+      <c r="A15" s="77"/>
+      <c r="B15" s="78"/>
+      <c r="C15" s="76"/>
       <c r="D15" s="5" t="s">
         <v>23</v>
       </c>
@@ -2198,9 +2187,9 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A16" s="85"/>
-      <c r="B16" s="88"/>
-      <c r="C16" s="87"/>
+      <c r="A16" s="77"/>
+      <c r="B16" s="78"/>
+      <c r="C16" s="76"/>
       <c r="D16" s="5" t="s">
         <v>24</v>
       </c>
@@ -2225,7 +2214,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
-      <c r="B17" s="88"/>
+      <c r="B17" s="78"/>
       <c r="C17" s="7"/>
       <c r="E17" s="4"/>
       <c r="F17" s="6"/>
@@ -2235,15 +2224,15 @@
       <c r="J17" s="6"/>
     </row>
     <row r="18" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A18" s="85" t="s">
+      <c r="A18" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="88"/>
-      <c r="C18" s="86" t="s">
+      <c r="B18" s="78"/>
+      <c r="C18" s="75" t="s">
         <v>32</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>7</v>
@@ -2265,9 +2254,9 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A19" s="85"/>
-      <c r="B19" s="88"/>
-      <c r="C19" s="87"/>
+      <c r="A19" s="77"/>
+      <c r="B19" s="78"/>
+      <c r="C19" s="76"/>
       <c r="D19" s="5" t="s">
         <v>23</v>
       </c>
@@ -2291,9 +2280,9 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A20" s="85"/>
-      <c r="B20" s="88"/>
-      <c r="C20" s="87"/>
+      <c r="A20" s="77"/>
+      <c r="B20" s="78"/>
+      <c r="C20" s="76"/>
       <c r="D20" s="5" t="s">
         <v>24</v>
       </c>
@@ -2318,7 +2307,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
-      <c r="B21" s="88"/>
+      <c r="B21" s="78"/>
       <c r="C21" s="7"/>
       <c r="E21" s="4"/>
       <c r="F21" s="6"/>
@@ -2328,15 +2317,15 @@
       <c r="J21" s="6"/>
     </row>
     <row r="22" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A22" s="85" t="s">
+      <c r="A22" s="77" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="88"/>
-      <c r="C22" s="86" t="s">
+      <c r="B22" s="78"/>
+      <c r="C22" s="75" t="s">
         <v>33</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>7</v>
@@ -2358,9 +2347,9 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A23" s="85"/>
-      <c r="B23" s="88"/>
-      <c r="C23" s="87"/>
+      <c r="A23" s="77"/>
+      <c r="B23" s="78"/>
+      <c r="C23" s="76"/>
       <c r="D23" s="5" t="s">
         <v>23</v>
       </c>
@@ -2384,9 +2373,9 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A24" s="85"/>
-      <c r="B24" s="88"/>
-      <c r="C24" s="87"/>
+      <c r="A24" s="77"/>
+      <c r="B24" s="78"/>
+      <c r="C24" s="76"/>
       <c r="D24" s="5" t="s">
         <v>24</v>
       </c>
@@ -2411,7 +2400,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="4"/>
-      <c r="B25" s="88"/>
+      <c r="B25" s="78"/>
       <c r="C25" s="7"/>
       <c r="E25" s="4"/>
       <c r="F25" s="6"/>
@@ -2421,15 +2410,15 @@
       <c r="J25" s="6"/>
     </row>
     <row r="26" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A26" s="85" t="s">
+      <c r="A26" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="88"/>
-      <c r="C26" s="86" t="s">
+      <c r="B26" s="78"/>
+      <c r="C26" s="75" t="s">
         <v>34</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>7</v>
@@ -2451,9 +2440,9 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A27" s="85"/>
-      <c r="B27" s="88"/>
-      <c r="C27" s="87"/>
+      <c r="A27" s="77"/>
+      <c r="B27" s="78"/>
+      <c r="C27" s="76"/>
       <c r="D27" s="5" t="s">
         <v>23</v>
       </c>
@@ -2477,9 +2466,9 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A28" s="85"/>
-      <c r="B28" s="88"/>
-      <c r="C28" s="87"/>
+      <c r="A28" s="77"/>
+      <c r="B28" s="78"/>
+      <c r="C28" s="76"/>
       <c r="D28" s="5" t="s">
         <v>24</v>
       </c>
@@ -2504,7 +2493,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
-      <c r="B29" s="88"/>
+      <c r="B29" s="78"/>
       <c r="C29" s="7"/>
       <c r="E29" s="4"/>
       <c r="F29" s="6"/>
@@ -2514,15 +2503,15 @@
       <c r="J29" s="6"/>
     </row>
     <row r="30" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A30" s="85" t="s">
+      <c r="A30" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="B30" s="88"/>
-      <c r="C30" s="86" t="s">
+      <c r="B30" s="78"/>
+      <c r="C30" s="75" t="s">
         <v>35</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>7</v>
@@ -2544,9 +2533,9 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A31" s="85"/>
-      <c r="B31" s="88"/>
-      <c r="C31" s="87"/>
+      <c r="A31" s="77"/>
+      <c r="B31" s="78"/>
+      <c r="C31" s="76"/>
       <c r="D31" s="5" t="s">
         <v>23</v>
       </c>
@@ -2570,9 +2559,9 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A32" s="85"/>
-      <c r="B32" s="88"/>
-      <c r="C32" s="87"/>
+      <c r="A32" s="77"/>
+      <c r="B32" s="78"/>
+      <c r="C32" s="76"/>
       <c r="D32" s="8" t="s">
         <v>24</v>
       </c>
@@ -2607,17 +2596,17 @@
       <c r="J33" s="6"/>
     </row>
     <row r="34" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A34" s="85" t="s">
+      <c r="A34" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="C34" s="86" t="s">
+      <c r="C34" s="75" t="s">
         <v>28</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>7</v>
@@ -2639,9 +2628,9 @@
       </c>
     </row>
     <row r="35" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A35" s="85"/>
-      <c r="B35" s="85"/>
-      <c r="C35" s="87"/>
+      <c r="A35" s="77"/>
+      <c r="B35" s="77"/>
+      <c r="C35" s="76"/>
       <c r="D35" s="5" t="s">
         <v>23</v>
       </c>
@@ -2665,9 +2654,9 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A36" s="85"/>
-      <c r="B36" s="85"/>
-      <c r="C36" s="87"/>
+      <c r="A36" s="77"/>
+      <c r="B36" s="77"/>
+      <c r="C36" s="76"/>
       <c r="D36" s="5" t="s">
         <v>24</v>
       </c>
@@ -2692,7 +2681,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
-      <c r="B37" s="85"/>
+      <c r="B37" s="77"/>
       <c r="C37" s="7"/>
       <c r="E37" s="4"/>
       <c r="F37" s="6"/>
@@ -2702,15 +2691,15 @@
       <c r="J37" s="6"/>
     </row>
     <row r="38" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A38" s="85" t="s">
+      <c r="A38" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="B38" s="85"/>
-      <c r="C38" s="86" t="s">
+      <c r="B38" s="77"/>
+      <c r="C38" s="75" t="s">
         <v>29</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>7</v>
@@ -2732,9 +2721,9 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A39" s="85"/>
-      <c r="B39" s="85"/>
-      <c r="C39" s="87"/>
+      <c r="A39" s="77"/>
+      <c r="B39" s="77"/>
+      <c r="C39" s="76"/>
       <c r="D39" s="8" t="s">
         <v>23</v>
       </c>
@@ -2758,9 +2747,9 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A40" s="85"/>
-      <c r="B40" s="85"/>
-      <c r="C40" s="87"/>
+      <c r="A40" s="77"/>
+      <c r="B40" s="77"/>
+      <c r="C40" s="76"/>
       <c r="D40" s="5" t="s">
         <v>24</v>
       </c>
@@ -2785,7 +2774,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
-      <c r="B41" s="85"/>
+      <c r="B41" s="77"/>
       <c r="C41" s="7"/>
       <c r="E41" s="4"/>
       <c r="F41" s="6"/>
@@ -2795,15 +2784,15 @@
       <c r="J41" s="6"/>
     </row>
     <row r="42" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A42" s="85" t="s">
+      <c r="A42" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="B42" s="85"/>
-      <c r="C42" s="86" t="s">
+      <c r="B42" s="77"/>
+      <c r="C42" s="75" t="s">
         <v>30</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>7</v>
@@ -2825,9 +2814,9 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A43" s="85"/>
-      <c r="B43" s="85"/>
-      <c r="C43" s="87"/>
+      <c r="A43" s="77"/>
+      <c r="B43" s="77"/>
+      <c r="C43" s="76"/>
       <c r="D43" s="5" t="s">
         <v>23</v>
       </c>
@@ -2851,9 +2840,9 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A44" s="85"/>
-      <c r="B44" s="85"/>
-      <c r="C44" s="87"/>
+      <c r="A44" s="77"/>
+      <c r="B44" s="77"/>
+      <c r="C44" s="76"/>
       <c r="D44" s="5" t="s">
         <v>24</v>
       </c>
@@ -2878,7 +2867,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
-      <c r="B45" s="85"/>
+      <c r="B45" s="77"/>
       <c r="C45" s="7"/>
       <c r="E45" s="4"/>
       <c r="F45" s="6"/>
@@ -2888,15 +2877,15 @@
       <c r="J45" s="6"/>
     </row>
     <row r="46" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A46" s="85" t="s">
+      <c r="A46" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="B46" s="85"/>
-      <c r="C46" s="86" t="s">
+      <c r="B46" s="77"/>
+      <c r="C46" s="75" t="s">
         <v>34</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>7</v>
@@ -2918,9 +2907,9 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A47" s="85"/>
-      <c r="B47" s="85"/>
-      <c r="C47" s="87"/>
+      <c r="A47" s="77"/>
+      <c r="B47" s="77"/>
+      <c r="C47" s="76"/>
       <c r="D47" s="5" t="s">
         <v>23</v>
       </c>
@@ -2944,9 +2933,9 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A48" s="85"/>
-      <c r="B48" s="85"/>
-      <c r="C48" s="87"/>
+      <c r="A48" s="77"/>
+      <c r="B48" s="77"/>
+      <c r="C48" s="76"/>
       <c r="D48" s="5" t="s">
         <v>24</v>
       </c>
@@ -3024,6 +3013,16 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C18:C20"/>
+    <mergeCell ref="C22:C24"/>
+    <mergeCell ref="C26:C28"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="C38:C40"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="C10:C12"/>
@@ -3040,16 +3039,6 @@
     <mergeCell ref="A42:A44"/>
     <mergeCell ref="A14:A16"/>
     <mergeCell ref="A30:A32"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="C22:C24"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="C38:C40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3102,17 +3091,17 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A2" s="85" t="s">
+      <c r="A2" s="77" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="86" t="s">
+      <c r="C2" s="75" t="s">
         <v>28</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>7</v>
@@ -3134,9 +3123,9 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A3" s="85"/>
-      <c r="B3" s="88"/>
-      <c r="C3" s="87"/>
+      <c r="A3" s="77"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="76"/>
       <c r="D3" s="5" t="s">
         <v>23</v>
       </c>
@@ -3160,9 +3149,9 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="85"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="87"/>
+      <c r="A4" s="77"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="76"/>
       <c r="D4" s="5" t="s">
         <v>24</v>
       </c>
@@ -3187,7 +3176,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
-      <c r="B5" s="88"/>
+      <c r="B5" s="78"/>
       <c r="C5" s="7"/>
       <c r="E5" s="4"/>
       <c r="F5" s="6"/>
@@ -3197,15 +3186,15 @@
       <c r="J5" s="6"/>
     </row>
     <row r="6" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="85" t="s">
+      <c r="A6" s="77" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="88"/>
-      <c r="C6" s="86" t="s">
+      <c r="B6" s="78"/>
+      <c r="C6" s="75" t="s">
         <v>29</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>7</v>
@@ -3227,9 +3216,9 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="85"/>
-      <c r="B7" s="88"/>
-      <c r="C7" s="87"/>
+      <c r="A7" s="77"/>
+      <c r="B7" s="78"/>
+      <c r="C7" s="76"/>
       <c r="D7" s="5" t="s">
         <v>23</v>
       </c>
@@ -3253,9 +3242,9 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A8" s="85"/>
-      <c r="B8" s="88"/>
-      <c r="C8" s="87"/>
+      <c r="A8" s="77"/>
+      <c r="B8" s="78"/>
+      <c r="C8" s="76"/>
       <c r="D8" s="8" t="s">
         <v>24</v>
       </c>
@@ -3280,7 +3269,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
-      <c r="B9" s="88"/>
+      <c r="B9" s="78"/>
       <c r="C9" s="7"/>
       <c r="E9" s="4"/>
       <c r="F9" s="6"/>
@@ -3290,15 +3279,15 @@
       <c r="J9" s="6"/>
     </row>
     <row r="10" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="85" t="s">
+      <c r="A10" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="88"/>
-      <c r="C10" s="86" t="s">
+      <c r="B10" s="78"/>
+      <c r="C10" s="75" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>7</v>
@@ -3320,9 +3309,9 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="85"/>
-      <c r="B11" s="88"/>
-      <c r="C11" s="87"/>
+      <c r="A11" s="77"/>
+      <c r="B11" s="78"/>
+      <c r="C11" s="76"/>
       <c r="D11" s="5" t="s">
         <v>23</v>
       </c>
@@ -3346,9 +3335,9 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="85"/>
-      <c r="B12" s="88"/>
-      <c r="C12" s="87"/>
+      <c r="A12" s="77"/>
+      <c r="B12" s="78"/>
+      <c r="C12" s="76"/>
       <c r="D12" s="8" t="s">
         <v>24</v>
       </c>
@@ -3373,7 +3362,7 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="4"/>
-      <c r="B13" s="88"/>
+      <c r="B13" s="78"/>
       <c r="C13" s="7"/>
       <c r="E13" s="4"/>
       <c r="F13" s="6"/>
@@ -3383,15 +3372,15 @@
       <c r="J13" s="6"/>
     </row>
     <row r="14" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A14" s="85" t="s">
+      <c r="A14" s="77" t="s">
         <v>42</v>
       </c>
-      <c r="B14" s="88"/>
-      <c r="C14" s="86" t="s">
+      <c r="B14" s="78"/>
+      <c r="C14" s="75" t="s">
         <v>31</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>7</v>
@@ -3413,9 +3402,9 @@
       </c>
     </row>
     <row r="15" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A15" s="85"/>
-      <c r="B15" s="88"/>
-      <c r="C15" s="87"/>
+      <c r="A15" s="77"/>
+      <c r="B15" s="78"/>
+      <c r="C15" s="76"/>
       <c r="D15" s="5" t="s">
         <v>23</v>
       </c>
@@ -3439,9 +3428,9 @@
       </c>
     </row>
     <row r="16" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A16" s="85"/>
-      <c r="B16" s="88"/>
-      <c r="C16" s="87"/>
+      <c r="A16" s="77"/>
+      <c r="B16" s="78"/>
+      <c r="C16" s="76"/>
       <c r="D16" s="8" t="s">
         <v>24</v>
       </c>
@@ -3466,7 +3455,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
-      <c r="B17" s="88"/>
+      <c r="B17" s="78"/>
       <c r="C17" s="7"/>
       <c r="E17" s="4"/>
       <c r="F17" s="6"/>
@@ -3476,15 +3465,15 @@
       <c r="J17" s="6"/>
     </row>
     <row r="18" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A18" s="85" t="s">
+      <c r="A18" s="77" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="88"/>
-      <c r="C18" s="86" t="s">
+      <c r="B18" s="78"/>
+      <c r="C18" s="75" t="s">
         <v>32</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>7</v>
@@ -3506,9 +3495,9 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A19" s="85"/>
-      <c r="B19" s="88"/>
-      <c r="C19" s="87"/>
+      <c r="A19" s="77"/>
+      <c r="B19" s="78"/>
+      <c r="C19" s="76"/>
       <c r="D19" s="5" t="s">
         <v>23</v>
       </c>
@@ -3532,9 +3521,9 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A20" s="85"/>
-      <c r="B20" s="88"/>
-      <c r="C20" s="87"/>
+      <c r="A20" s="77"/>
+      <c r="B20" s="78"/>
+      <c r="C20" s="76"/>
       <c r="D20" s="8" t="s">
         <v>24</v>
       </c>
@@ -3559,7 +3548,7 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" s="4"/>
-      <c r="B21" s="88"/>
+      <c r="B21" s="78"/>
       <c r="C21" s="7"/>
       <c r="E21" s="4"/>
       <c r="F21" s="6"/>
@@ -3569,15 +3558,15 @@
       <c r="J21" s="6"/>
     </row>
     <row r="22" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A22" s="85" t="s">
+      <c r="A22" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="B22" s="88"/>
-      <c r="C22" s="86" t="s">
+      <c r="B22" s="78"/>
+      <c r="C22" s="75" t="s">
         <v>33</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>7</v>
@@ -3599,9 +3588,9 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A23" s="85"/>
-      <c r="B23" s="88"/>
-      <c r="C23" s="87"/>
+      <c r="A23" s="77"/>
+      <c r="B23" s="78"/>
+      <c r="C23" s="76"/>
       <c r="D23" s="5" t="s">
         <v>23</v>
       </c>
@@ -3625,9 +3614,9 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A24" s="85"/>
-      <c r="B24" s="88"/>
-      <c r="C24" s="87"/>
+      <c r="A24" s="77"/>
+      <c r="B24" s="78"/>
+      <c r="C24" s="76"/>
       <c r="D24" s="5" t="s">
         <v>24</v>
       </c>
@@ -3652,7 +3641,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" s="4"/>
-      <c r="B25" s="88"/>
+      <c r="B25" s="78"/>
       <c r="C25" s="7"/>
       <c r="E25" s="4"/>
       <c r="F25" s="6"/>
@@ -3662,15 +3651,15 @@
       <c r="J25" s="6"/>
     </row>
     <row r="26" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A26" s="85" t="s">
+      <c r="A26" s="77" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="88"/>
-      <c r="C26" s="86" t="s">
+      <c r="B26" s="78"/>
+      <c r="C26" s="75" t="s">
         <v>34</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E26" s="9" t="s">
         <v>7</v>
@@ -3692,9 +3681,9 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A27" s="85"/>
-      <c r="B27" s="88"/>
-      <c r="C27" s="87"/>
+      <c r="A27" s="77"/>
+      <c r="B27" s="78"/>
+      <c r="C27" s="76"/>
       <c r="D27" s="5" t="s">
         <v>23</v>
       </c>
@@ -3718,9 +3707,9 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A28" s="85"/>
-      <c r="B28" s="88"/>
-      <c r="C28" s="87"/>
+      <c r="A28" s="77"/>
+      <c r="B28" s="78"/>
+      <c r="C28" s="76"/>
       <c r="D28" s="8" t="s">
         <v>24</v>
       </c>
@@ -3745,7 +3734,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" s="4"/>
-      <c r="B29" s="88"/>
+      <c r="B29" s="78"/>
       <c r="C29" s="7"/>
       <c r="E29" s="4"/>
       <c r="F29" s="6"/>
@@ -3755,15 +3744,15 @@
       <c r="J29" s="6"/>
     </row>
     <row r="30" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A30" s="85" t="s">
+      <c r="A30" s="77" t="s">
         <v>44</v>
       </c>
-      <c r="B30" s="88"/>
-      <c r="C30" s="86" t="s">
+      <c r="B30" s="78"/>
+      <c r="C30" s="75" t="s">
         <v>35</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>7</v>
@@ -3785,9 +3774,9 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A31" s="85"/>
-      <c r="B31" s="88"/>
-      <c r="C31" s="87"/>
+      <c r="A31" s="77"/>
+      <c r="B31" s="78"/>
+      <c r="C31" s="76"/>
       <c r="D31" s="5" t="s">
         <v>23</v>
       </c>
@@ -3811,9 +3800,9 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A32" s="85"/>
-      <c r="B32" s="88"/>
-      <c r="C32" s="87"/>
+      <c r="A32" s="77"/>
+      <c r="B32" s="78"/>
+      <c r="C32" s="76"/>
       <c r="D32" s="5" t="s">
         <v>24</v>
       </c>
@@ -3848,17 +3837,17 @@
       <c r="J33" s="6"/>
     </row>
     <row r="34" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A34" s="85" t="s">
+      <c r="A34" s="77" t="s">
         <v>45</v>
       </c>
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="C34" s="86" t="s">
+      <c r="C34" s="75" t="s">
         <v>28</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>7</v>
@@ -3880,9 +3869,9 @@
       </c>
     </row>
     <row r="35" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A35" s="85"/>
-      <c r="B35" s="85"/>
-      <c r="C35" s="87"/>
+      <c r="A35" s="77"/>
+      <c r="B35" s="77"/>
+      <c r="C35" s="76"/>
       <c r="D35" s="5" t="s">
         <v>23</v>
       </c>
@@ -3906,9 +3895,9 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A36" s="85"/>
-      <c r="B36" s="85"/>
-      <c r="C36" s="87"/>
+      <c r="A36" s="77"/>
+      <c r="B36" s="77"/>
+      <c r="C36" s="76"/>
       <c r="D36" s="5" t="s">
         <v>24</v>
       </c>
@@ -3933,7 +3922,7 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" s="4"/>
-      <c r="B37" s="85"/>
+      <c r="B37" s="77"/>
       <c r="C37" s="7"/>
       <c r="E37" s="4"/>
       <c r="F37" s="6"/>
@@ -3943,15 +3932,15 @@
       <c r="J37" s="6"/>
     </row>
     <row r="38" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A38" s="85" t="s">
+      <c r="A38" s="77" t="s">
         <v>46</v>
       </c>
-      <c r="B38" s="85"/>
-      <c r="C38" s="86" t="s">
+      <c r="B38" s="77"/>
+      <c r="C38" s="75" t="s">
         <v>29</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>7</v>
@@ -3973,9 +3962,9 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A39" s="85"/>
-      <c r="B39" s="85"/>
-      <c r="C39" s="87"/>
+      <c r="A39" s="77"/>
+      <c r="B39" s="77"/>
+      <c r="C39" s="76"/>
       <c r="D39" s="5" t="s">
         <v>23</v>
       </c>
@@ -3999,9 +3988,9 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A40" s="85"/>
-      <c r="B40" s="85"/>
-      <c r="C40" s="87"/>
+      <c r="A40" s="77"/>
+      <c r="B40" s="77"/>
+      <c r="C40" s="76"/>
       <c r="D40" s="5" t="s">
         <v>24</v>
       </c>
@@ -4026,7 +4015,7 @@
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" s="4"/>
-      <c r="B41" s="85"/>
+      <c r="B41" s="77"/>
       <c r="C41" s="7"/>
       <c r="E41" s="4"/>
       <c r="F41" s="6"/>
@@ -4036,15 +4025,15 @@
       <c r="J41" s="6"/>
     </row>
     <row r="42" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A42" s="85" t="s">
+      <c r="A42" s="77" t="s">
         <v>47</v>
       </c>
-      <c r="B42" s="85"/>
-      <c r="C42" s="86" t="s">
+      <c r="B42" s="77"/>
+      <c r="C42" s="75" t="s">
         <v>30</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>7</v>
@@ -4066,9 +4055,9 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A43" s="85"/>
-      <c r="B43" s="85"/>
-      <c r="C43" s="87"/>
+      <c r="A43" s="77"/>
+      <c r="B43" s="77"/>
+      <c r="C43" s="76"/>
       <c r="D43" s="5" t="s">
         <v>23</v>
       </c>
@@ -4092,9 +4081,9 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A44" s="85"/>
-      <c r="B44" s="85"/>
-      <c r="C44" s="87"/>
+      <c r="A44" s="77"/>
+      <c r="B44" s="77"/>
+      <c r="C44" s="76"/>
       <c r="D44" s="5" t="s">
         <v>24</v>
       </c>
@@ -4119,7 +4108,7 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="4"/>
-      <c r="B45" s="85"/>
+      <c r="B45" s="77"/>
       <c r="C45" s="7"/>
       <c r="E45" s="4"/>
       <c r="F45" s="6"/>
@@ -4129,15 +4118,15 @@
       <c r="J45" s="6"/>
     </row>
     <row r="46" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A46" s="85" t="s">
+      <c r="A46" s="77" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="85"/>
-      <c r="C46" s="86" t="s">
+      <c r="B46" s="77"/>
+      <c r="C46" s="75" t="s">
         <v>34</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>7</v>
@@ -4159,9 +4148,9 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A47" s="85"/>
-      <c r="B47" s="85"/>
-      <c r="C47" s="87"/>
+      <c r="A47" s="77"/>
+      <c r="B47" s="77"/>
+      <c r="C47" s="76"/>
       <c r="D47" s="8" t="s">
         <v>23</v>
       </c>
@@ -4185,9 +4174,9 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="20" x14ac:dyDescent="0.2">
-      <c r="A48" s="85"/>
-      <c r="B48" s="85"/>
-      <c r="C48" s="87"/>
+      <c r="A48" s="77"/>
+      <c r="B48" s="77"/>
+      <c r="C48" s="76"/>
       <c r="D48" s="5" t="s">
         <v>24</v>
       </c>
@@ -4265,6 +4254,16 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="B34:B48"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="C46:C48"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B32"/>
     <mergeCell ref="C2:C4"/>
@@ -4281,16 +4280,6 @@
     <mergeCell ref="A26:A28"/>
     <mergeCell ref="C26:C28"/>
     <mergeCell ref="A30:A32"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="B34:B48"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="C46:C48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4352,17 +4341,17 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A2" s="88" t="s">
+      <c r="A2" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="85" t="s">
+      <c r="B2" s="77" t="s">
         <v>74</v>
       </c>
-      <c r="C2" s="86" t="s">
+      <c r="C2" s="75" t="s">
         <v>28</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>7</v>
@@ -4396,9 +4385,9 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A3" s="88"/>
-      <c r="B3" s="85"/>
-      <c r="C3" s="87"/>
+      <c r="A3" s="78"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="76"/>
       <c r="D3" s="5" t="s">
         <v>23</v>
       </c>
@@ -4434,9 +4423,9 @@
       </c>
     </row>
     <row r="4" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="88"/>
-      <c r="B4" s="85"/>
-      <c r="C4" s="87"/>
+      <c r="A4" s="78"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="76"/>
       <c r="D4" s="5" t="s">
         <v>24</v>
       </c>
@@ -4472,7 +4461,7 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A5" s="88"/>
+      <c r="A5" s="78"/>
       <c r="B5" s="4"/>
       <c r="C5" s="7"/>
       <c r="E5" s="4"/>
@@ -4483,15 +4472,15 @@
       <c r="J5" s="6"/>
     </row>
     <row r="6" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="88"/>
-      <c r="B6" s="85" t="s">
+      <c r="A6" s="78"/>
+      <c r="B6" s="77" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="86" t="s">
+      <c r="C6" s="75" t="s">
         <v>29</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>7</v>
@@ -4525,9 +4514,9 @@
       </c>
     </row>
     <row r="7" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="88"/>
-      <c r="B7" s="85"/>
-      <c r="C7" s="87"/>
+      <c r="A7" s="78"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="76"/>
       <c r="D7" s="5" t="s">
         <v>23</v>
       </c>
@@ -4563,9 +4552,9 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A8" s="88"/>
-      <c r="B8" s="85"/>
-      <c r="C8" s="87"/>
+      <c r="A8" s="78"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="76"/>
       <c r="D8" s="8" t="s">
         <v>24</v>
       </c>
@@ -4601,7 +4590,7 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A9" s="88"/>
+      <c r="A9" s="78"/>
       <c r="B9" s="4"/>
       <c r="C9" s="7"/>
       <c r="E9" s="4"/>
@@ -4612,15 +4601,15 @@
       <c r="J9" s="6"/>
     </row>
     <row r="10" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="88"/>
-      <c r="B10" s="85" t="s">
+      <c r="A10" s="78"/>
+      <c r="B10" s="77" t="s">
         <v>76</v>
       </c>
-      <c r="C10" s="86" t="s">
+      <c r="C10" s="75" t="s">
         <v>30</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>7</v>
@@ -4654,9 +4643,9 @@
       </c>
     </row>
     <row r="11" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="88"/>
-      <c r="B11" s="85"/>
-      <c r="C11" s="87"/>
+      <c r="A11" s="78"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="76"/>
       <c r="D11" s="5" t="s">
         <v>23</v>
       </c>
@@ -4692,9 +4681,9 @@
       </c>
     </row>
     <row r="12" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="88"/>
-      <c r="B12" s="85"/>
-      <c r="C12" s="87"/>
+      <c r="A12" s="78"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="76"/>
       <c r="D12" s="5" t="s">
         <v>24</v>
       </c>
@@ -4730,7 +4719,7 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A13" s="88"/>
+      <c r="A13" s="78"/>
       <c r="B13" s="4"/>
       <c r="C13" s="7"/>
       <c r="E13" s="4"/>
@@ -4741,15 +4730,15 @@
       <c r="J13" s="6"/>
     </row>
     <row r="14" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A14" s="88"/>
-      <c r="B14" s="85" t="s">
+      <c r="A14" s="78"/>
+      <c r="B14" s="77" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="86" t="s">
+      <c r="C14" s="75" t="s">
         <v>31</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>7</v>
@@ -4783,9 +4772,9 @@
       </c>
     </row>
     <row r="15" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A15" s="88"/>
-      <c r="B15" s="85"/>
-      <c r="C15" s="87"/>
+      <c r="A15" s="78"/>
+      <c r="B15" s="77"/>
+      <c r="C15" s="76"/>
       <c r="D15" s="5" t="s">
         <v>23</v>
       </c>
@@ -4821,9 +4810,9 @@
       </c>
     </row>
     <row r="16" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A16" s="88"/>
-      <c r="B16" s="85"/>
-      <c r="C16" s="87"/>
+      <c r="A16" s="78"/>
+      <c r="B16" s="77"/>
+      <c r="C16" s="76"/>
       <c r="D16" s="5" t="s">
         <v>24</v>
       </c>
@@ -4859,7 +4848,7 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A17" s="88"/>
+      <c r="A17" s="78"/>
       <c r="B17" s="4"/>
       <c r="C17" s="7"/>
       <c r="E17" s="4"/>
@@ -4870,15 +4859,15 @@
       <c r="J17" s="6"/>
     </row>
     <row r="18" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A18" s="88"/>
-      <c r="B18" s="85" t="s">
+      <c r="A18" s="78"/>
+      <c r="B18" s="77" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="86" t="s">
+      <c r="C18" s="75" t="s">
         <v>32</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>7</v>
@@ -4912,9 +4901,9 @@
       </c>
     </row>
     <row r="19" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A19" s="88"/>
-      <c r="B19" s="85"/>
-      <c r="C19" s="87"/>
+      <c r="A19" s="78"/>
+      <c r="B19" s="77"/>
+      <c r="C19" s="76"/>
       <c r="D19" s="5" t="s">
         <v>23</v>
       </c>
@@ -4950,9 +4939,9 @@
       </c>
     </row>
     <row r="20" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A20" s="88"/>
-      <c r="B20" s="85"/>
-      <c r="C20" s="87"/>
+      <c r="A20" s="78"/>
+      <c r="B20" s="77"/>
+      <c r="C20" s="76"/>
       <c r="D20" s="5" t="s">
         <v>24</v>
       </c>
@@ -4988,7 +4977,7 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A21" s="88"/>
+      <c r="A21" s="78"/>
       <c r="B21" s="4"/>
       <c r="C21" s="7"/>
       <c r="E21" s="4"/>
@@ -4999,15 +4988,15 @@
       <c r="J21" s="6"/>
     </row>
     <row r="22" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A22" s="88"/>
-      <c r="B22" s="85" t="s">
+      <c r="A22" s="78"/>
+      <c r="B22" s="77" t="s">
         <v>79</v>
       </c>
-      <c r="C22" s="86" t="s">
+      <c r="C22" s="75" t="s">
         <v>33</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>7</v>
@@ -5041,9 +5030,9 @@
       </c>
     </row>
     <row r="23" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A23" s="88"/>
-      <c r="B23" s="85"/>
-      <c r="C23" s="87"/>
+      <c r="A23" s="78"/>
+      <c r="B23" s="77"/>
+      <c r="C23" s="76"/>
       <c r="D23" s="5" t="s">
         <v>23</v>
       </c>
@@ -5079,9 +5068,9 @@
       </c>
     </row>
     <row r="24" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A24" s="88"/>
-      <c r="B24" s="85"/>
-      <c r="C24" s="87"/>
+      <c r="A24" s="78"/>
+      <c r="B24" s="77"/>
+      <c r="C24" s="76"/>
       <c r="D24" s="5" t="s">
         <v>24</v>
       </c>
@@ -5117,7 +5106,7 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A25" s="88"/>
+      <c r="A25" s="78"/>
       <c r="B25" s="4"/>
       <c r="C25" s="7"/>
       <c r="E25" s="4"/>
@@ -5128,15 +5117,15 @@
       <c r="J25" s="6"/>
     </row>
     <row r="26" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A26" s="88"/>
-      <c r="B26" s="85" t="s">
+      <c r="A26" s="78"/>
+      <c r="B26" s="77" t="s">
         <v>80</v>
       </c>
-      <c r="C26" s="86" t="s">
+      <c r="C26" s="75" t="s">
         <v>34</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>7</v>
@@ -5170,9 +5159,9 @@
       </c>
     </row>
     <row r="27" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A27" s="88"/>
-      <c r="B27" s="85"/>
-      <c r="C27" s="87"/>
+      <c r="A27" s="78"/>
+      <c r="B27" s="77"/>
+      <c r="C27" s="76"/>
       <c r="D27" s="5" t="s">
         <v>23</v>
       </c>
@@ -5208,9 +5197,9 @@
       </c>
     </row>
     <row r="28" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A28" s="88"/>
-      <c r="B28" s="85"/>
-      <c r="C28" s="87"/>
+      <c r="A28" s="78"/>
+      <c r="B28" s="77"/>
+      <c r="C28" s="76"/>
       <c r="D28" s="5" t="s">
         <v>24</v>
       </c>
@@ -5246,7 +5235,7 @@
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A29" s="88"/>
+      <c r="A29" s="78"/>
       <c r="B29" s="4"/>
       <c r="C29" s="7"/>
       <c r="E29" s="4"/>
@@ -5257,15 +5246,15 @@
       <c r="J29" s="6"/>
     </row>
     <row r="30" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A30" s="88"/>
-      <c r="B30" s="85" t="s">
+      <c r="A30" s="78"/>
+      <c r="B30" s="77" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="86" t="s">
+      <c r="C30" s="75" t="s">
         <v>35</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>7</v>
@@ -5299,9 +5288,9 @@
       </c>
     </row>
     <row r="31" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A31" s="88"/>
-      <c r="B31" s="85"/>
-      <c r="C31" s="87"/>
+      <c r="A31" s="78"/>
+      <c r="B31" s="77"/>
+      <c r="C31" s="76"/>
       <c r="D31" s="5" t="s">
         <v>23</v>
       </c>
@@ -5337,9 +5326,9 @@
       </c>
     </row>
     <row r="32" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A32" s="88"/>
-      <c r="B32" s="85"/>
-      <c r="C32" s="87"/>
+      <c r="A32" s="78"/>
+      <c r="B32" s="77"/>
+      <c r="C32" s="76"/>
       <c r="D32" s="5" t="s">
         <v>24</v>
       </c>
@@ -5386,17 +5375,17 @@
       <c r="J33" s="6"/>
     </row>
     <row r="34" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A34" s="85" t="s">
+      <c r="A34" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="C34" s="86" t="s">
+      <c r="C34" s="75" t="s">
         <v>28</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>7</v>
@@ -5430,9 +5419,9 @@
       </c>
     </row>
     <row r="35" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A35" s="85"/>
-      <c r="B35" s="85"/>
-      <c r="C35" s="87"/>
+      <c r="A35" s="77"/>
+      <c r="B35" s="77"/>
+      <c r="C35" s="76"/>
       <c r="D35" s="5" t="s">
         <v>23</v>
       </c>
@@ -5468,9 +5457,9 @@
       </c>
     </row>
     <row r="36" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A36" s="85"/>
-      <c r="B36" s="85"/>
-      <c r="C36" s="87"/>
+      <c r="A36" s="77"/>
+      <c r="B36" s="77"/>
+      <c r="C36" s="76"/>
       <c r="D36" s="5" t="s">
         <v>24</v>
       </c>
@@ -5506,7 +5495,7 @@
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A37" s="85"/>
+      <c r="A37" s="77"/>
       <c r="B37" s="4"/>
       <c r="C37" s="7"/>
       <c r="E37" s="4"/>
@@ -5517,15 +5506,15 @@
       <c r="J37" s="6"/>
     </row>
     <row r="38" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A38" s="85"/>
-      <c r="B38" s="85" t="s">
+      <c r="A38" s="77"/>
+      <c r="B38" s="77" t="s">
         <v>83</v>
       </c>
-      <c r="C38" s="86" t="s">
+      <c r="C38" s="75" t="s">
         <v>29</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>7</v>
@@ -5559,9 +5548,9 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A39" s="85"/>
-      <c r="B39" s="85"/>
-      <c r="C39" s="87"/>
+      <c r="A39" s="77"/>
+      <c r="B39" s="77"/>
+      <c r="C39" s="76"/>
       <c r="D39" s="8" t="s">
         <v>23</v>
       </c>
@@ -5597,9 +5586,9 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A40" s="85"/>
-      <c r="B40" s="85"/>
-      <c r="C40" s="87"/>
+      <c r="A40" s="77"/>
+      <c r="B40" s="77"/>
+      <c r="C40" s="76"/>
       <c r="D40" s="5" t="s">
         <v>24</v>
       </c>
@@ -5635,7 +5624,7 @@
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A41" s="85"/>
+      <c r="A41" s="77"/>
       <c r="B41" s="4"/>
       <c r="C41" s="7"/>
       <c r="E41" s="4"/>
@@ -5646,15 +5635,15 @@
       <c r="J41" s="6"/>
     </row>
     <row r="42" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A42" s="85"/>
-      <c r="B42" s="85" t="s">
+      <c r="A42" s="77"/>
+      <c r="B42" s="77" t="s">
         <v>84</v>
       </c>
-      <c r="C42" s="86" t="s">
+      <c r="C42" s="75" t="s">
         <v>30</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>7</v>
@@ -5688,9 +5677,9 @@
       </c>
     </row>
     <row r="43" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A43" s="85"/>
-      <c r="B43" s="85"/>
-      <c r="C43" s="87"/>
+      <c r="A43" s="77"/>
+      <c r="B43" s="77"/>
+      <c r="C43" s="76"/>
       <c r="D43" s="5" t="s">
         <v>23</v>
       </c>
@@ -5726,9 +5715,9 @@
       </c>
     </row>
     <row r="44" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A44" s="85"/>
-      <c r="B44" s="85"/>
-      <c r="C44" s="87"/>
+      <c r="A44" s="77"/>
+      <c r="B44" s="77"/>
+      <c r="C44" s="76"/>
       <c r="D44" s="5" t="s">
         <v>24</v>
       </c>
@@ -5764,7 +5753,7 @@
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.2">
-      <c r="A45" s="85"/>
+      <c r="A45" s="77"/>
       <c r="B45" s="4"/>
       <c r="C45" s="7"/>
       <c r="E45" s="4"/>
@@ -5775,15 +5764,15 @@
       <c r="J45" s="6"/>
     </row>
     <row r="46" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A46" s="85"/>
-      <c r="B46" s="85" t="s">
+      <c r="A46" s="77"/>
+      <c r="B46" s="77" t="s">
         <v>85</v>
       </c>
-      <c r="C46" s="86" t="s">
+      <c r="C46" s="75" t="s">
         <v>34</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>7</v>
@@ -5817,9 +5806,9 @@
       </c>
     </row>
     <row r="47" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A47" s="85"/>
-      <c r="B47" s="85"/>
-      <c r="C47" s="87"/>
+      <c r="A47" s="77"/>
+      <c r="B47" s="77"/>
+      <c r="C47" s="76"/>
       <c r="D47" s="5" t="s">
         <v>23</v>
       </c>
@@ -5855,9 +5844,9 @@
       </c>
     </row>
     <row r="48" spans="1:13" ht="20" x14ac:dyDescent="0.2">
-      <c r="A48" s="85"/>
-      <c r="B48" s="85"/>
-      <c r="C48" s="87"/>
+      <c r="A48" s="77"/>
+      <c r="B48" s="77"/>
+      <c r="C48" s="76"/>
       <c r="D48" s="5" t="s">
         <v>24</v>
       </c>
@@ -6008,16 +5997,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="A34:A48"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="B38:B40"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="C46:C48"/>
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="A2:A32"/>
     <mergeCell ref="C2:C4"/>
@@ -6034,120 +6013,1658 @@
     <mergeCell ref="B26:B28"/>
     <mergeCell ref="C26:C28"/>
     <mergeCell ref="B30:B32"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="A34:A48"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="B38:B40"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="C46:C48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E75D5ADF-282B-7143-A056-3E023A2AE323}">
-  <dimension ref="A1:N44"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A12A09FB-0B35-7D40-BCF6-2631A2817EA3}">
+  <dimension ref="A1:L54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="42.83203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.83203125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="15" style="5" customWidth="1"/>
+    <col min="3" max="10" width="17.5" style="12" customWidth="1"/>
+    <col min="11" max="16384" width="8.83203125" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="18" customFormat="1" ht="111" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="29" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="J1" s="29" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A2" s="86" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="89" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="88">
+        <v>4.9161585399999999E-2</v>
+      </c>
+      <c r="D2" s="88">
+        <v>1.31478658E-2</v>
+      </c>
+      <c r="E2" s="88">
+        <v>0.71532012199999995</v>
+      </c>
+      <c r="F2" s="88">
+        <v>0.86194404820000003</v>
+      </c>
+      <c r="G2" s="88">
+        <v>0.73983099360000004</v>
+      </c>
+      <c r="H2" s="88">
+        <f>C2*1/5 +D2*1/5+E2*1/5+F2*1/5+G2*1/5</f>
+        <v>0.47588092300000001</v>
+      </c>
+      <c r="I2" s="88">
+        <f>E2*1/2+G2*1/2</f>
+        <v>0.72757555780000005</v>
+      </c>
+      <c r="J2" s="88">
+        <f>C2*1/3+D2*1/3+F2*1/3</f>
+        <v>0.30808449979999997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="40" x14ac:dyDescent="0.2">
+      <c r="A3" s="86" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="89" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="88">
+        <v>4.5385202100000001E-2</v>
+      </c>
+      <c r="D3" s="88">
+        <v>2.5171624699999999E-2</v>
+      </c>
+      <c r="E3" s="88">
+        <v>0.74942791760000005</v>
+      </c>
+      <c r="F3" s="88">
+        <v>0.85230850219999998</v>
+      </c>
+      <c r="G3" s="88">
+        <v>0.64946929639999995</v>
+      </c>
+      <c r="H3" s="88">
+        <f>C3*1/5 +D3*1/5+E3*1/5+F3*1/5+G3*1/5</f>
+        <v>0.46435250859999999</v>
+      </c>
+      <c r="I3" s="88">
+        <f>E3*1/2+G3*1/2</f>
+        <v>0.699448607</v>
+      </c>
+      <c r="J3" s="88">
+        <f>C3*1/3+D3*1/3+F3*1/3</f>
+        <v>0.30762177633333332</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A4" s="86" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" s="89" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="88">
+        <v>1.83066362E-2</v>
+      </c>
+      <c r="D4" s="88">
+        <v>9.1533181000000002E-3</v>
+      </c>
+      <c r="E4" s="88">
+        <v>0.74713958810000003</v>
+      </c>
+      <c r="F4" s="88">
+        <v>0.84097820459999995</v>
+      </c>
+      <c r="G4" s="88">
+        <v>0.65728491980000003</v>
+      </c>
+      <c r="H4" s="88">
+        <f>C4*1/5 +D4*1/5+E4*1/5+F4*1/5+G4*1/5</f>
+        <v>0.45457253335999998</v>
+      </c>
+      <c r="I4" s="88">
+        <f>E4*1/2+G4*1/2</f>
+        <v>0.70221225394999998</v>
+      </c>
+      <c r="J4" s="88">
+        <f>C4*1/3+D4*1/3+F4*1/3</f>
+        <v>0.28947938629999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A5" s="86" t="s">
+        <v>75</v>
+      </c>
+      <c r="B5" s="89" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="88">
+        <v>3.56598017E-2</v>
+      </c>
+      <c r="D5" s="88">
+        <v>1.14416476E-2</v>
+      </c>
+      <c r="E5" s="88">
+        <v>0.65484363079999997</v>
+      </c>
+      <c r="F5" s="88">
+        <v>0.75059192720000001</v>
+      </c>
+      <c r="G5" s="88">
+        <v>0.59952031800000005</v>
+      </c>
+      <c r="H5" s="88">
+        <f>C5*1/5 +D5*1/5+E5*1/5+F5*1/5+G5*1/5</f>
+        <v>0.41041146505999998</v>
+      </c>
+      <c r="I5" s="88">
+        <f>E5*1/2+G5*1/2</f>
+        <v>0.62718197440000001</v>
+      </c>
+      <c r="J5" s="88">
+        <f>C5*1/3+D5*1/3+F5*1/3</f>
+        <v>0.26589779216666665</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A6" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="89" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="88">
+        <v>1.3539282999999999E-2</v>
+      </c>
+      <c r="D6" s="88">
+        <v>7.437071E-3</v>
+      </c>
+      <c r="E6" s="88">
+        <v>0.68192219679999999</v>
+      </c>
+      <c r="F6" s="88">
+        <v>0.76195930150000002</v>
+      </c>
+      <c r="G6" s="88">
+        <v>0.65195960269999997</v>
+      </c>
+      <c r="H6" s="88">
+        <f>C6*1/5 +D6*1/5+E6*1/5+F6*1/5+G6*1/5</f>
+        <v>0.42336349099999998</v>
+      </c>
+      <c r="I6" s="88">
+        <f>E6*1/2+G6*1/2</f>
+        <v>0.66694089974999993</v>
+      </c>
+      <c r="J6" s="88">
+        <f>C6*1/3+D6*1/3+F6*1/3</f>
+        <v>0.26097855183333335</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A7" s="86" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="89" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="88">
+        <v>6.2929062000000001E-3</v>
+      </c>
+      <c r="D7" s="88">
+        <v>1.5064836E-2</v>
+      </c>
+      <c r="E7" s="88">
+        <v>0.65980167810000001</v>
+      </c>
+      <c r="F7" s="88">
+        <v>0.75336811260000003</v>
+      </c>
+      <c r="G7" s="88">
+        <v>0.59480806279999998</v>
+      </c>
+      <c r="H7" s="88">
+        <f>C7*1/5 +D7*1/5+E7*1/5+F7*1/5+G7*1/5</f>
+        <v>0.40586711914000001</v>
+      </c>
+      <c r="I7" s="88">
+        <f>E7*1/2+G7*1/2</f>
+        <v>0.62730487044999994</v>
+      </c>
+      <c r="J7" s="88">
+        <f>C7*1/3+D7*1/3+F7*1/3</f>
+        <v>0.25824195159999996</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A8" s="86" t="s">
+        <v>79</v>
+      </c>
+      <c r="B8" s="89" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="88">
+        <v>1.8688024399999999E-2</v>
+      </c>
+      <c r="D8" s="88">
+        <v>1.6209000800000001E-2</v>
+      </c>
+      <c r="E8" s="88">
+        <v>0.64340198319999997</v>
+      </c>
+      <c r="F8" s="88">
+        <v>0.73541693649999995</v>
+      </c>
+      <c r="G8" s="88">
+        <v>0.57155276239999997</v>
+      </c>
+      <c r="H8" s="88">
+        <f>C8*1/5 +D8*1/5+E8*1/5+F8*1/5+G8*1/5</f>
+        <v>0.39705374145999994</v>
+      </c>
+      <c r="I8" s="88">
+        <f>E8*1/2+G8*1/2</f>
+        <v>0.60747737280000003</v>
+      </c>
+      <c r="J8" s="88">
+        <f>C8*1/3+D8*1/3+F8*1/3</f>
+        <v>0.25677132056666668</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A9" s="86" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="89" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="88">
+        <v>1.5636918400000002E-2</v>
+      </c>
+      <c r="D9" s="88">
+        <v>6.2929062000000001E-3</v>
+      </c>
+      <c r="E9" s="88">
+        <v>0.77612509529999996</v>
+      </c>
+      <c r="F9" s="88">
+        <v>0.74139800369999997</v>
+      </c>
+      <c r="G9" s="88">
+        <v>0.74694543889999998</v>
+      </c>
+      <c r="H9" s="88">
+        <f>C9*1/5 +D9*1/5+E9*1/5+F9*1/5+G9*1/5</f>
+        <v>0.45727967249999996</v>
+      </c>
+      <c r="I9" s="88">
+        <f>E9*1/2+G9*1/2</f>
+        <v>0.76153526709999997</v>
+      </c>
+      <c r="J9" s="88">
+        <f>C9*1/3+D9*1/3+F9*1/3</f>
+        <v>0.2544426094333333</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A10" s="86" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="89" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="88">
+        <v>7.2408537E-3</v>
+      </c>
+      <c r="D10" s="88">
+        <v>9.3368902999999993E-3</v>
+      </c>
+      <c r="E10" s="88">
+        <v>0.72789634150000004</v>
+      </c>
+      <c r="F10" s="88">
+        <v>0.72569261240000005</v>
+      </c>
+      <c r="G10" s="88">
+        <v>0.68594619649999999</v>
+      </c>
+      <c r="H10" s="88">
+        <f>C10*1/5 +D10*1/5+E10*1/5+F10*1/5+G10*1/5</f>
+        <v>0.43122257887999998</v>
+      </c>
+      <c r="I10" s="88">
+        <f>E10*1/2+G10*1/2</f>
+        <v>0.70692126899999996</v>
+      </c>
+      <c r="J10" s="88">
+        <f>C10*1/3+D10*1/3+F10*1/3</f>
+        <v>0.24742345213333333</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A11" s="86" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="89" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="88">
+        <v>2.7841342500000001E-2</v>
+      </c>
+      <c r="D11" s="88">
+        <v>9.3440121999999997E-3</v>
+      </c>
+      <c r="E11" s="88">
+        <v>0.66628527839999996</v>
+      </c>
+      <c r="F11" s="88">
+        <v>0.68165094780000002</v>
+      </c>
+      <c r="G11" s="88">
+        <v>0.656536805</v>
+      </c>
+      <c r="H11" s="88">
+        <f>C11*1/5 +D11*1/5+E11*1/5+F11*1/5+G11*1/5</f>
+        <v>0.40833167718000002</v>
+      </c>
+      <c r="I11" s="88">
+        <f>E11*1/2+G11*1/2</f>
+        <v>0.66141104169999998</v>
+      </c>
+      <c r="J11" s="88">
+        <f>C11*1/3+D11*1/3+F11*1/3</f>
+        <v>0.23961210083333334</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A12" s="86" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="89" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="88">
+        <v>3.8901601799999998E-2</v>
+      </c>
+      <c r="D12" s="88">
+        <v>6.1022120000000001E-3</v>
+      </c>
+      <c r="E12" s="88">
+        <v>0.63958810070000005</v>
+      </c>
+      <c r="F12" s="88">
+        <v>0.6580912753</v>
+      </c>
+      <c r="G12" s="88">
+        <v>0.68471369510000002</v>
+      </c>
+      <c r="H12" s="88">
+        <f>C12*1/5 +D12*1/5+E12*1/5+F12*1/5+G12*1/5</f>
+        <v>0.40547937698000003</v>
+      </c>
+      <c r="I12" s="88">
+        <f>E12*1/2+G12*1/2</f>
+        <v>0.66215089790000004</v>
+      </c>
+      <c r="J12" s="88">
+        <f>C12*1/3+D12*1/3+F12*1/3</f>
+        <v>0.2343650297</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A13" s="86" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="89" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="88">
+        <v>5.7164629999999998E-4</v>
+      </c>
+      <c r="D13" s="88">
+        <v>5.1448170999999999E-3</v>
+      </c>
+      <c r="E13" s="88">
+        <v>0.77019817069999996</v>
+      </c>
+      <c r="F13" s="88">
+        <v>0.68990504159999999</v>
+      </c>
+      <c r="G13" s="88">
+        <v>0.82907810169999996</v>
+      </c>
+      <c r="H13" s="88">
+        <f>C13*1/5 +D13*1/5+E13*1/5+F13*1/5+G13*1/5</f>
+        <v>0.45897955547999991</v>
+      </c>
+      <c r="I13" s="88">
+        <f>E13*1/2+G13*1/2</f>
+        <v>0.79963813620000002</v>
+      </c>
+      <c r="J13" s="88">
+        <f>C13*1/3+D13*1/3+F13*1/3</f>
+        <v>0.231873835</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A14" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="89" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="88">
+        <v>4.3859648999999999E-3</v>
+      </c>
+      <c r="D14" s="88">
+        <v>3.8138830000000002E-4</v>
+      </c>
+      <c r="E14" s="88">
+        <v>0.81388253239999997</v>
+      </c>
+      <c r="F14" s="88">
+        <v>0.62862944050000003</v>
+      </c>
+      <c r="G14" s="88">
+        <v>0.64003247760000004</v>
+      </c>
+      <c r="H14" s="88">
+        <f>C14*1/5 +D14*1/5+E14*1/5+F14*1/5+G14*1/5</f>
+        <v>0.41746236073999998</v>
+      </c>
+      <c r="I14" s="88">
+        <f>E14*1/2+G14*1/2</f>
+        <v>0.726957505</v>
+      </c>
+      <c r="J14" s="88">
+        <f>C14*1/3+D14*1/3+F14*1/3</f>
+        <v>0.21113226456666667</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A15" s="86" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" s="89" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="88">
+        <v>5.7164629999999998E-4</v>
+      </c>
+      <c r="D15" s="88">
+        <v>4.7637195000000002E-3</v>
+      </c>
+      <c r="E15" s="88">
+        <v>0.60518292679999997</v>
+      </c>
+      <c r="F15" s="88">
+        <v>0.62701617990000003</v>
+      </c>
+      <c r="G15" s="88">
+        <v>0.68544860669999996</v>
+      </c>
+      <c r="H15" s="88">
+        <f>C15*1/5 +D15*1/5+E15*1/5+F15*1/5+G15*1/5</f>
+        <v>0.38459661583999999</v>
+      </c>
+      <c r="I15" s="88">
+        <f>E15*1/2+G15*1/2</f>
+        <v>0.64531576675000002</v>
+      </c>
+      <c r="J15" s="88">
+        <f>C15*1/3+D15*1/3+F15*1/3</f>
+        <v>0.21078384856666668</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A16" s="86" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="89" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="88">
+        <v>1.1814024399999999E-2</v>
+      </c>
+      <c r="D16" s="88">
+        <v>2.6676829000000001E-3</v>
+      </c>
+      <c r="E16" s="88">
+        <v>0.62461890239999995</v>
+      </c>
+      <c r="F16" s="88">
+        <v>0.61594775769999999</v>
+      </c>
+      <c r="G16" s="88">
+        <v>0.66839133620000002</v>
+      </c>
+      <c r="H16" s="88">
+        <f>C16*1/5 +D16*1/5+E16*1/5+F16*1/5+G16*1/5</f>
+        <v>0.38468794072000001</v>
+      </c>
+      <c r="I16" s="88">
+        <f>E16*1/2+G16*1/2</f>
+        <v>0.64650511929999999</v>
+      </c>
+      <c r="J16" s="88">
+        <f>C16*1/3+D16*1/3+F16*1/3</f>
+        <v>0.210143155</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A17" s="86" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="89" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="88">
+        <v>5.7208240000000004E-4</v>
+      </c>
+      <c r="D17" s="88">
+        <v>2.8604119000000001E-3</v>
+      </c>
+      <c r="E17" s="88">
+        <v>0.408085431</v>
+      </c>
+      <c r="F17" s="88">
+        <v>0.61558054129999995</v>
+      </c>
+      <c r="G17" s="88">
+        <v>0.64331702260000001</v>
+      </c>
+      <c r="H17" s="88">
+        <f>C17*1/5 +D17*1/5+E17*1/5+F17*1/5+G17*1/5</f>
+        <v>0.33408309784000001</v>
+      </c>
+      <c r="I17" s="88">
+        <f>E17*1/2+G17*1/2</f>
+        <v>0.52570122679999998</v>
+      </c>
+      <c r="J17" s="88">
+        <f>C17*1/3+D17*1/3+F17*1/3</f>
+        <v>0.20633767853333332</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A18" s="86" t="s">
+        <v>80</v>
+      </c>
+      <c r="B18" s="89" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="88">
+        <v>3.8138830000000002E-4</v>
+      </c>
+      <c r="D18" s="88">
+        <v>3.8138824999999999E-3</v>
+      </c>
+      <c r="E18" s="88">
+        <v>0.25896262399999997</v>
+      </c>
+      <c r="F18" s="88">
+        <v>0.58112698119999995</v>
+      </c>
+      <c r="G18" s="88">
+        <v>0.61473724439999999</v>
+      </c>
+      <c r="H18" s="88">
+        <f>C18*1/5 +D18*1/5+E18*1/5+F18*1/5+G18*1/5</f>
+        <v>0.29180442407999996</v>
+      </c>
+      <c r="I18" s="88">
+        <f>E18*1/2+G18*1/2</f>
+        <v>0.43684993419999996</v>
+      </c>
+      <c r="J18" s="88">
+        <f>C18*1/3+D18*1/3+F18*1/3</f>
+        <v>0.19510741733333331</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A19" s="86" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" s="89" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="88">
+        <v>3.8138830000000002E-4</v>
+      </c>
+      <c r="D19" s="88">
+        <v>2.6697177000000001E-3</v>
+      </c>
+      <c r="E19" s="88">
+        <v>0.79366895500000001</v>
+      </c>
+      <c r="F19" s="88">
+        <v>0.57090215860000004</v>
+      </c>
+      <c r="G19" s="88">
+        <v>0.58510193919999998</v>
+      </c>
+      <c r="H19" s="88">
+        <f>C19*1/5 +D19*1/5+E19*1/5+F19*1/5+G19*1/5</f>
+        <v>0.39054483175999999</v>
+      </c>
+      <c r="I19" s="88">
+        <f>E19*1/2+G19*1/2</f>
+        <v>0.68938544710000005</v>
+      </c>
+      <c r="J19" s="88">
+        <f>C19*1/3+D19*1/3+F19*1/3</f>
+        <v>0.19131775486666669</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A20" s="86" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="89" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="88">
+        <v>0</v>
+      </c>
+      <c r="D20" s="88">
+        <v>5.3394356000000002E-3</v>
+      </c>
+      <c r="E20" s="88">
+        <v>0.96948893970000005</v>
+      </c>
+      <c r="F20" s="88">
+        <v>0.54854145649999997</v>
+      </c>
+      <c r="G20" s="88">
+        <v>0.61895662200000001</v>
+      </c>
+      <c r="H20" s="88">
+        <f>C20*1/5 +D20*1/5+E20*1/5+F20*1/5+G20*1/5</f>
+        <v>0.42846529076000001</v>
+      </c>
+      <c r="I20" s="88">
+        <f>E20*1/2+G20*1/2</f>
+        <v>0.79422278084999998</v>
+      </c>
+      <c r="J20" s="88">
+        <f>C20*1/3+D20*1/3+F20*1/3</f>
+        <v>0.18462696403333334</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="40" x14ac:dyDescent="0.2">
+      <c r="A21" s="86" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="89" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="90">
+        <v>3.8138830000000002E-4</v>
+      </c>
+      <c r="D21" s="90">
+        <v>5.3394356000000002E-3</v>
+      </c>
+      <c r="E21" s="90">
+        <v>0.1487414188</v>
+      </c>
+      <c r="F21" s="90">
+        <v>0.53002011719999997</v>
+      </c>
+      <c r="G21" s="90">
+        <v>0.59878249289999996</v>
+      </c>
+      <c r="H21" s="88">
+        <f>C21*1/5 +D21*1/5+E21*1/5+F21*1/5+G21*1/5</f>
+        <v>0.25665297055999997</v>
+      </c>
+      <c r="I21" s="88">
+        <f>E21*1/2+G21*1/2</f>
+        <v>0.37376195584999999</v>
+      </c>
+      <c r="J21" s="88">
+        <f>C21*1/3+D21*1/3+F21*1/3</f>
+        <v>0.17858031369999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A22" s="86" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="89" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="88">
+        <v>1.75438596E-2</v>
+      </c>
+      <c r="D22" s="88">
+        <v>3.6231884E-3</v>
+      </c>
+      <c r="E22" s="88">
+        <v>0.26926010680000001</v>
+      </c>
+      <c r="F22" s="88">
+        <v>0.50990095319999995</v>
+      </c>
+      <c r="G22" s="88">
+        <v>0.49317243570000002</v>
+      </c>
+      <c r="H22" s="88">
+        <f>C22*1/5 +D22*1/5+E22*1/5+F22*1/5+G22*1/5</f>
+        <v>0.25870010873999999</v>
+      </c>
+      <c r="I22" s="88">
+        <f>E22*1/2+G22*1/2</f>
+        <v>0.38121627125000002</v>
+      </c>
+      <c r="J22" s="88">
+        <f>C22*1/3+D22*1/3+F22*1/3</f>
+        <v>0.17702266706666667</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A23" s="86" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="89" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="88">
+        <v>2.4009146299999999E-2</v>
+      </c>
+      <c r="D23" s="88">
+        <v>5.7164633999999999E-3</v>
+      </c>
+      <c r="E23" s="88">
+        <v>0.36547256099999997</v>
+      </c>
+      <c r="F23" s="88">
+        <v>0.49941951550000002</v>
+      </c>
+      <c r="G23" s="88">
+        <v>0.49771204279999998</v>
+      </c>
+      <c r="H23" s="88">
+        <f>C23*1/5 +D23*1/5+E23*1/5+F23*1/5+G23*1/5</f>
+        <v>0.27846594579999995</v>
+      </c>
+      <c r="I23" s="88">
+        <f>E23*1/2+G23*1/2</f>
+        <v>0.43159230189999997</v>
+      </c>
+      <c r="J23" s="88">
+        <f>C23*1/3+D23*1/3+F23*1/3</f>
+        <v>0.1763817084</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A24" s="86" t="s">
+        <v>84</v>
+      </c>
+      <c r="B24" s="89" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="88">
+        <v>5.7164629999999998E-4</v>
+      </c>
+      <c r="D24" s="88">
+        <v>2.0960366000000001E-3</v>
+      </c>
+      <c r="E24" s="88">
+        <v>0.16768292679999999</v>
+      </c>
+      <c r="F24" s="88">
+        <v>0.52153423170000002</v>
+      </c>
+      <c r="G24" s="88">
+        <v>0.53800463509999996</v>
+      </c>
+      <c r="H24" s="88">
+        <f>C24*1/5 +D24*1/5+E24*1/5+F24*1/5+G24*1/5</f>
+        <v>0.2459778953</v>
+      </c>
+      <c r="I24" s="88">
+        <f>E24*1/2+G24*1/2</f>
+        <v>0.35284378094999996</v>
+      </c>
+      <c r="J24" s="88">
+        <f>C24*1/3+D24*1/3+F24*1/3</f>
+        <v>0.17473397153333334</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A25" s="86" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" s="89" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="88">
+        <v>1.9069409999999999E-4</v>
+      </c>
+      <c r="D25" s="88">
+        <v>2.4790237000000001E-3</v>
+      </c>
+      <c r="E25" s="88">
+        <v>0.26735316549999999</v>
+      </c>
+      <c r="F25" s="88">
+        <v>0.51288884690000003</v>
+      </c>
+      <c r="G25" s="88">
+        <v>0.4966505316</v>
+      </c>
+      <c r="H25" s="88">
+        <f>C25*1/5 +D25*1/5+E25*1/5+F25*1/5+G25*1/5</f>
+        <v>0.25591245235999999</v>
+      </c>
+      <c r="I25" s="88">
+        <f>E25*1/2+G25*1/2</f>
+        <v>0.38200184854999997</v>
+      </c>
+      <c r="J25" s="88">
+        <f>C25*1/3+D25*1/3+F25*1/3</f>
+        <v>0.17185285489999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A26" s="86" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="89" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="88">
+        <v>0</v>
+      </c>
+      <c r="D26" s="88">
+        <v>2.6697178000000001E-3</v>
+      </c>
+      <c r="E26" s="88">
+        <v>0.31807780320000001</v>
+      </c>
+      <c r="F26" s="88">
+        <v>0.49853525259999998</v>
+      </c>
+      <c r="G26" s="88">
+        <v>0.49760901740000002</v>
+      </c>
+      <c r="H26" s="88">
+        <f>C26*1/5 +D26*1/5+E26*1/5+F26*1/5+G26*1/5</f>
+        <v>0.2633783582</v>
+      </c>
+      <c r="I26" s="88">
+        <f>E26*1/2+G26*1/2</f>
+        <v>0.40784341030000004</v>
+      </c>
+      <c r="J26" s="88">
+        <f>C26*1/3+D26*1/3+F26*1/3</f>
+        <v>0.16706832346666664</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A27" s="86" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="89" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="88">
+        <v>1.9069409999999999E-4</v>
+      </c>
+      <c r="D27" s="88">
+        <v>3.2418001E-3</v>
+      </c>
+      <c r="E27" s="88">
+        <v>0.29099923719999998</v>
+      </c>
+      <c r="F27" s="88">
+        <v>0.48040252360000002</v>
+      </c>
+      <c r="G27" s="88">
+        <v>0.47678633349999999</v>
+      </c>
+      <c r="H27" s="88">
+        <f>C27*1/5 +D27*1/5+E27*1/5+F27*1/5+G27*1/5</f>
+        <v>0.25032411769999996</v>
+      </c>
+      <c r="I27" s="88">
+        <f>E27*1/2+G27*1/2</f>
+        <v>0.38389278534999999</v>
+      </c>
+      <c r="J27" s="88">
+        <f>C27*1/3+D27*1/3+F27*1/3</f>
+        <v>0.16127833926666668</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A28" s="86" t="s">
+        <v>83</v>
+      </c>
+      <c r="B28" s="89" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="90">
+        <v>7.6219510000000005E-4</v>
+      </c>
+      <c r="D28" s="90">
+        <v>3.2393293000000001E-3</v>
+      </c>
+      <c r="E28" s="90">
+        <v>0.78048780490000003</v>
+      </c>
+      <c r="F28" s="90">
+        <v>0.47766805309999999</v>
+      </c>
+      <c r="G28" s="90">
+        <v>0.50378384080000005</v>
+      </c>
+      <c r="H28" s="88">
+        <f>C28*1/5 +D28*1/5+E28*1/5+F28*1/5+G28*1/5</f>
+        <v>0.35318824463999998</v>
+      </c>
+      <c r="I28" s="88">
+        <f>E28*1/2+G28*1/2</f>
+        <v>0.64213582285000004</v>
+      </c>
+      <c r="J28" s="88">
+        <f>C28*1/3+D28*1/3+F28*1/3</f>
+        <v>0.16055652583333335</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A29" s="86" t="s">
+        <v>85</v>
+      </c>
+      <c r="B29" s="89" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="88">
+        <v>3.8109759999999999E-4</v>
+      </c>
+      <c r="D29" s="88">
+        <v>3.4298781E-3</v>
+      </c>
+      <c r="E29" s="88">
+        <v>0.36775914630000001</v>
+      </c>
+      <c r="F29" s="88">
+        <v>0.47550582689999998</v>
+      </c>
+      <c r="G29" s="88">
+        <v>0.47833423320000001</v>
+      </c>
+      <c r="H29" s="88">
+        <f>C29*1/5 +D29*1/5+E29*1/5+F29*1/5+G29*1/5</f>
+        <v>0.26508203642</v>
+      </c>
+      <c r="I29" s="88">
+        <f>E29*1/2+G29*1/2</f>
+        <v>0.42304668975000004</v>
+      </c>
+      <c r="J29" s="88">
+        <f>C29*1/3+D29*1/3+F29*1/3</f>
+        <v>0.15977226753333335</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="B30" s="89" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="88">
+        <v>0</v>
+      </c>
+      <c r="D30" s="88">
+        <v>2.2883295000000001E-3</v>
+      </c>
+      <c r="E30" s="88">
+        <v>2.93668955E-2</v>
+      </c>
+      <c r="F30" s="88">
+        <v>0.47452555019999998</v>
+      </c>
+      <c r="G30" s="88">
+        <v>0.47974364320000001</v>
+      </c>
+      <c r="H30" s="88">
+        <f>C30*1/5 +D30*1/5+E30*1/5+F30*1/5+G30*1/5</f>
+        <v>0.19718488368000001</v>
+      </c>
+      <c r="I30" s="88">
+        <f>E30*1/2+G30*1/2</f>
+        <v>0.25455526935</v>
+      </c>
+      <c r="J30" s="88">
+        <f>C30*1/3+D30*1/3+F30*1/3</f>
+        <v>0.15893795990000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A31" s="86" t="s">
+        <v>82</v>
+      </c>
+      <c r="B31" s="89" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="88">
+        <v>0</v>
+      </c>
+      <c r="D31" s="88">
+        <v>1.06707317E-2</v>
+      </c>
+      <c r="E31" s="88">
+        <v>0.19740853659999999</v>
+      </c>
+      <c r="F31" s="88">
+        <v>0.44089801090000003</v>
+      </c>
+      <c r="G31" s="88">
+        <v>0.35974137750000001</v>
+      </c>
+      <c r="H31" s="88">
+        <f>C31*1/5 +D31*1/5+E31*1/5+F31*1/5+G31*1/5</f>
+        <v>0.20174373134000001</v>
+      </c>
+      <c r="I31" s="88">
+        <f>E31*1/2+G31*1/2</f>
+        <v>0.27857495705000002</v>
+      </c>
+      <c r="J31" s="88">
+        <f>C31*1/3+D31*1/3+F31*1/3</f>
+        <v>0.1505229142</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A32" s="86" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="89" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="90">
+        <v>0</v>
+      </c>
+      <c r="D32" s="90">
+        <v>2.2865854E-3</v>
+      </c>
+      <c r="E32" s="90">
+        <v>1</v>
+      </c>
+      <c r="F32" s="90">
+        <v>0.448357271</v>
+      </c>
+      <c r="G32" s="90">
+        <v>0.4793704064</v>
+      </c>
+      <c r="H32" s="88">
+        <f>C32*1/5 +D32*1/5+E32*1/5+F32*1/5+G32*1/5</f>
+        <v>0.38600285256</v>
+      </c>
+      <c r="I32" s="88">
+        <f>E32*1/2+G32*1/2</f>
+        <v>0.73968520319999997</v>
+      </c>
+      <c r="J32" s="88">
+        <f>C32*1/3+D32*1/3+F32*1/3</f>
+        <v>0.1502146188</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A33" s="86" t="s">
+        <v>78</v>
+      </c>
+      <c r="B33" s="89" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="88">
+        <v>3.8138830000000002E-4</v>
+      </c>
+      <c r="D33" s="88">
+        <v>4.1952708000000003E-3</v>
+      </c>
+      <c r="E33" s="88">
+        <v>2.7078565999999998E-2</v>
+      </c>
+      <c r="F33" s="88">
+        <v>0.40992652470000002</v>
+      </c>
+      <c r="G33" s="88">
+        <v>0.38954129339999999</v>
+      </c>
+      <c r="H33" s="88">
+        <f>C33*1/5 +D33*1/5+E33*1/5+F33*1/5+G33*1/5</f>
+        <v>0.16622460863999999</v>
+      </c>
+      <c r="I33" s="88">
+        <f>E33*1/2+G33*1/2</f>
+        <v>0.20830992970000001</v>
+      </c>
+      <c r="J33" s="88">
+        <f>C33*1/3+D33*1/3+F33*1/3</f>
+        <v>0.13816772793333332</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A34" s="86" t="s">
+        <v>84</v>
+      </c>
+      <c r="B34" s="89" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="88">
+        <v>7.6219510000000005E-4</v>
+      </c>
+      <c r="D34" s="88">
+        <v>4.3826220000000001E-3</v>
+      </c>
+      <c r="E34" s="88">
+        <v>0.25609756099999997</v>
+      </c>
+      <c r="F34" s="88">
+        <v>0.3903245058</v>
+      </c>
+      <c r="G34" s="88">
+        <v>0.35050324440000002</v>
+      </c>
+      <c r="H34" s="88">
+        <f>C34*1/5 +D34*1/5+E34*1/5+F34*1/5+G34*1/5</f>
+        <v>0.20041402565999999</v>
+      </c>
+      <c r="I34" s="88">
+        <f>E34*1/2+G34*1/2</f>
+        <v>0.30330040270000003</v>
+      </c>
+      <c r="J34" s="88">
+        <f>C34*1/3+D34*1/3+F34*1/3</f>
+        <v>0.13182310763333333</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="40" x14ac:dyDescent="0.2">
+      <c r="A35" s="86" t="s">
+        <v>81</v>
+      </c>
+      <c r="B35" s="89" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="88">
+        <v>9.5347059999999998E-4</v>
+      </c>
+      <c r="D35" s="88">
+        <v>4.5766590999999999E-3</v>
+      </c>
+      <c r="E35" s="88">
+        <v>0.15331807780000001</v>
+      </c>
+      <c r="F35" s="88">
+        <v>0.37985365679999999</v>
+      </c>
+      <c r="G35" s="88">
+        <v>0.36610513039999998</v>
+      </c>
+      <c r="H35" s="88">
+        <f>C35*1/5 +D35*1/5+E35*1/5+F35*1/5+G35*1/5</f>
+        <v>0.18096139894000002</v>
+      </c>
+      <c r="I35" s="88">
+        <f>E35*1/2+G35*1/2</f>
+        <v>0.25971160409999999</v>
+      </c>
+      <c r="J35" s="88">
+        <f>C35*1/3+D35*1/3+F35*1/3</f>
+        <v>0.12846126216666667</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A36" s="86" t="s">
+        <v>79</v>
+      </c>
+      <c r="B36" s="89" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="88">
+        <v>5.7208240000000004E-4</v>
+      </c>
+      <c r="D36" s="88">
+        <v>2.4790237000000001E-3</v>
+      </c>
+      <c r="E36" s="88">
+        <v>0.14492753620000001</v>
+      </c>
+      <c r="F36" s="88">
+        <v>0.36882205509999999</v>
+      </c>
+      <c r="G36" s="88">
+        <v>0.36333761959999999</v>
+      </c>
+      <c r="H36" s="88">
+        <f>C36*1/5 +D36*1/5+E36*1/5+F36*1/5+G36*1/5</f>
+        <v>0.17602766340000001</v>
+      </c>
+      <c r="I36" s="88">
+        <f>E36*1/2+G36*1/2</f>
+        <v>0.25413257789999999</v>
+      </c>
+      <c r="J36" s="88">
+        <f>C36*1/3+D36*1/3+F36*1/3</f>
+        <v>0.1239577204</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="20" x14ac:dyDescent="0.2">
+      <c r="A37" s="86" t="s">
+        <v>77</v>
+      </c>
+      <c r="B37" s="89" t="s">
+        <v>9</v>
+      </c>
+      <c r="C37" s="88">
+        <v>3.8138830000000002E-4</v>
+      </c>
+      <c r="D37" s="88">
+        <v>3.2418001E-3</v>
+      </c>
+      <c r="E37" s="88">
+        <v>2.8604119000000001E-2</v>
+      </c>
+      <c r="F37" s="88">
+        <v>0.30229342920000002</v>
+      </c>
+      <c r="G37" s="88">
+        <v>0.19462933560000001</v>
+      </c>
+      <c r="H37" s="88">
+        <f>C37*1/5 +D37*1/5+E37*1/5+F37*1/5+G37*1/5</f>
+        <v>0.10583001444000001</v>
+      </c>
+      <c r="I37" s="88">
+        <f>E37*1/2+G37*1/2</f>
+        <v>0.11161672730000001</v>
+      </c>
+      <c r="J37" s="88">
+        <f>C37*1/3+D37*1/3+F37*1/3</f>
+        <v>0.10197220586666668</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" s="86"/>
+      <c r="B38" s="89"/>
+      <c r="C38" s="90"/>
+      <c r="D38" s="90"/>
+      <c r="E38" s="90"/>
+      <c r="F38" s="90"/>
+      <c r="G38" s="90"/>
+      <c r="H38" s="88"/>
+      <c r="I38" s="88"/>
+      <c r="J38" s="88"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A39" s="86"/>
+      <c r="B39" s="89"/>
+      <c r="C39" s="90"/>
+      <c r="D39" s="90"/>
+      <c r="E39" s="90"/>
+      <c r="F39" s="90"/>
+      <c r="G39" s="90"/>
+      <c r="H39" s="88"/>
+      <c r="I39" s="88"/>
+      <c r="J39" s="88"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A40" s="86"/>
+      <c r="B40" s="89"/>
+      <c r="C40" s="90"/>
+      <c r="D40" s="90"/>
+      <c r="E40" s="90"/>
+      <c r="F40" s="90"/>
+      <c r="G40" s="90"/>
+      <c r="H40" s="88"/>
+      <c r="I40" s="88"/>
+      <c r="J40" s="88"/>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A41" s="86"/>
+      <c r="B41" s="89"/>
+      <c r="C41" s="90"/>
+      <c r="D41" s="90"/>
+      <c r="E41" s="90"/>
+      <c r="F41" s="90"/>
+      <c r="G41" s="90"/>
+      <c r="H41" s="88"/>
+      <c r="I41" s="88"/>
+      <c r="J41" s="88"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A42" s="86"/>
+      <c r="B42" s="89"/>
+      <c r="C42" s="90"/>
+      <c r="D42" s="90"/>
+      <c r="E42" s="90"/>
+      <c r="F42" s="90"/>
+      <c r="G42" s="90"/>
+      <c r="H42" s="88"/>
+      <c r="I42" s="88"/>
+      <c r="J42" s="88"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A43" s="86"/>
+      <c r="B43" s="89"/>
+      <c r="C43" s="90"/>
+      <c r="D43" s="90"/>
+      <c r="E43" s="90"/>
+      <c r="F43" s="90"/>
+      <c r="G43" s="90"/>
+      <c r="H43" s="88"/>
+      <c r="I43" s="88"/>
+      <c r="J43" s="88"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A44" s="86"/>
+      <c r="B44" s="89"/>
+      <c r="C44" s="90"/>
+      <c r="D44" s="90"/>
+      <c r="E44" s="90"/>
+      <c r="F44" s="90"/>
+      <c r="G44" s="90"/>
+      <c r="H44" s="88"/>
+      <c r="I44" s="88"/>
+      <c r="J44" s="88"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A45" s="4"/>
+      <c r="B45" s="89"/>
+      <c r="C45" s="90"/>
+      <c r="D45" s="90"/>
+      <c r="E45" s="90"/>
+      <c r="F45" s="90"/>
+      <c r="G45" s="90"/>
+      <c r="H45" s="88"/>
+      <c r="I45" s="88"/>
+      <c r="J45" s="88"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A46" s="86"/>
+      <c r="B46" s="89"/>
+      <c r="C46" s="90"/>
+      <c r="D46" s="90"/>
+      <c r="E46" s="90"/>
+      <c r="F46" s="90"/>
+      <c r="G46" s="90"/>
+      <c r="H46" s="88"/>
+      <c r="I46" s="88"/>
+      <c r="J46" s="88"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A47" s="86"/>
+      <c r="B47" s="89"/>
+      <c r="C47" s="90"/>
+      <c r="D47" s="90"/>
+      <c r="E47" s="90"/>
+      <c r="F47" s="90"/>
+      <c r="G47" s="90"/>
+      <c r="H47" s="88"/>
+      <c r="I47" s="88"/>
+      <c r="J47" s="88"/>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A48" s="86"/>
+      <c r="B48" s="89"/>
+      <c r="C48" s="90"/>
+      <c r="D48" s="90"/>
+      <c r="E48" s="90"/>
+      <c r="F48" s="90"/>
+      <c r="G48" s="90"/>
+      <c r="H48" s="88"/>
+      <c r="I48" s="88"/>
+      <c r="J48" s="88"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A49" s="87"/>
+      <c r="B49" s="87"/>
+      <c r="C49" s="88"/>
+      <c r="D49" s="88"/>
+      <c r="E49" s="88"/>
+      <c r="F49" s="88"/>
+      <c r="G49" s="88"/>
+      <c r="H49" s="88"/>
+      <c r="I49" s="88"/>
+      <c r="J49" s="88"/>
+      <c r="K49" s="87"/>
+      <c r="L49" s="87"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A50" s="87"/>
+      <c r="B50" s="87"/>
+      <c r="C50" s="88"/>
+      <c r="D50" s="88"/>
+      <c r="E50" s="88"/>
+      <c r="F50" s="88"/>
+      <c r="G50" s="88"/>
+      <c r="H50" s="88"/>
+      <c r="I50" s="88"/>
+      <c r="J50" s="88"/>
+      <c r="K50" s="87"/>
+      <c r="L50" s="87"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A51" s="87"/>
+      <c r="B51" s="87"/>
+      <c r="C51" s="88"/>
+      <c r="D51" s="88"/>
+      <c r="E51" s="88"/>
+      <c r="F51" s="88"/>
+      <c r="G51" s="88"/>
+      <c r="H51" s="88"/>
+      <c r="I51" s="88"/>
+      <c r="J51" s="88"/>
+      <c r="K51" s="87"/>
+      <c r="L51" s="87"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A52" s="87"/>
+      <c r="B52" s="87"/>
+      <c r="C52" s="88"/>
+      <c r="D52" s="88"/>
+      <c r="E52" s="88"/>
+      <c r="F52" s="88"/>
+      <c r="G52" s="88"/>
+      <c r="H52" s="88"/>
+      <c r="I52" s="88"/>
+      <c r="J52" s="88"/>
+      <c r="K52" s="87"/>
+      <c r="L52" s="87"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A53" s="87"/>
+      <c r="B53" s="87"/>
+      <c r="C53" s="88"/>
+      <c r="D53" s="88"/>
+      <c r="E53" s="88"/>
+      <c r="F53" s="88"/>
+      <c r="G53" s="88"/>
+      <c r="H53" s="88"/>
+      <c r="I53" s="88"/>
+      <c r="J53" s="88"/>
+      <c r="K53" s="87"/>
+      <c r="L53" s="87"/>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A54" s="87"/>
+      <c r="B54" s="87"/>
+      <c r="C54" s="88"/>
+      <c r="D54" s="88"/>
+      <c r="E54" s="88"/>
+      <c r="F54" s="88"/>
+      <c r="G54" s="88"/>
+      <c r="H54" s="88"/>
+      <c r="I54" s="88"/>
+      <c r="J54" s="88"/>
+      <c r="K54" s="87"/>
+      <c r="L54" s="87"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J54">
+    <sortCondition descending="1" ref="J1:J54"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E75D5ADF-282B-7143-A056-3E023A2AE323}">
+  <dimension ref="A1:O44"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="45.6640625" style="5" customWidth="1"/>
     <col min="2" max="2" width="42.83203125" style="5" customWidth="1"/>
     <col min="3" max="3" width="22" style="5" customWidth="1"/>
     <col min="4" max="4" width="12.5" style="5" customWidth="1"/>
     <col min="5" max="10" width="18" style="12" customWidth="1"/>
-    <col min="11" max="11" width="18" style="48" customWidth="1"/>
+    <col min="11" max="11" width="19.5" style="5" bestFit="1" customWidth="1"/>
     <col min="12" max="14" width="18" style="12" customWidth="1"/>
-    <col min="15" max="16384" width="8.83203125" style="5"/>
+    <col min="16" max="16384" width="8.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="74" customFormat="1" ht="89" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="68" t="s">
+    <row r="1" spans="1:15" s="66" customFormat="1" ht="67" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="68" t="s">
+      <c r="B1" s="61" t="s">
         <v>95</v>
       </c>
-      <c r="C1" s="68" t="s">
+      <c r="C1" s="61" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="68" t="s">
+      <c r="D1" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="69" t="s">
+      <c r="E1" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="69" t="s">
+      <c r="F1" s="62" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="70" t="s">
+      <c r="G1" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="H1" s="70" t="s">
+      <c r="H1" s="63" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="70" t="s">
+      <c r="I1" s="63" t="s">
         <v>57</v>
       </c>
-      <c r="J1" s="69" t="s">
+      <c r="J1" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="71" t="s">
-        <v>103</v>
-      </c>
-      <c r="L1" s="72" t="s">
-        <v>101</v>
-      </c>
-      <c r="M1" s="72" t="s">
+      <c r="K1" s="91" t="s">
+        <v>143</v>
+      </c>
+      <c r="L1" s="64" t="s">
+        <v>99</v>
+      </c>
+      <c r="M1" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="N1" s="73" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A2" s="85" t="s">
-        <v>75</v>
-      </c>
-      <c r="B2" s="89" t="s">
-        <v>96</v>
+      <c r="N1" s="65" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="20" x14ac:dyDescent="0.2">
+      <c r="A2" s="77" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="79" t="s">
+        <v>141</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="6">
-        <v>0.65484363079999997</v>
+        <v>0.74942791760000005</v>
       </c>
       <c r="F2" s="6">
-        <v>0.83790999239999997</v>
+        <v>0.93745232649999999</v>
       </c>
       <c r="G2" s="6">
-        <v>0.71204430090000004</v>
+        <v>0.8227964928</v>
       </c>
       <c r="H2" s="6">
-        <v>0.40625</v>
+        <v>0.453125</v>
       </c>
       <c r="I2" s="6">
-        <v>0.2535211268</v>
+        <v>0.11267605629999999</v>
       </c>
       <c r="J2" s="6">
-        <v>0.59952031800000005</v>
-      </c>
-      <c r="K2" s="48">
-        <v>0.35202662579999999</v>
-      </c>
-      <c r="L2" s="26">
+        <v>0.64946929639999995</v>
+      </c>
+      <c r="K2" s="5">
+        <f>SUM(E2,J2)/2</f>
+        <v>0.699448607</v>
+      </c>
+      <c r="L2" s="39">
         <f>SUM(E2:J2)/6</f>
-        <v>0.57734822815000009</v>
+        <v>0.62082451493333335</v>
       </c>
       <c r="M2" s="26">
         <f>STDEV(E2:J2)</f>
-        <v>0.21291838776787708</v>
+        <v>0.29824258344639348</v>
       </c>
       <c r="N2" s="12">
         <f>SUMPRODUCT(G2:I2,$C$16:$E$16)/SUM($C$16:$E$16)</f>
-        <v>0.28781759565756021</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A3" s="85"/>
-      <c r="B3" s="85"/>
+        <v>0.17757764115573771</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="20" x14ac:dyDescent="0.2">
+      <c r="A3" s="77"/>
+      <c r="B3" s="77"/>
       <c r="C3" s="5" t="s">
         <v>23</v>
       </c>
@@ -6155,42 +7672,43 @@
         <v>8</v>
       </c>
       <c r="E3" s="6">
-        <v>0.31807780320000001</v>
+        <v>0.15331807780000001</v>
       </c>
       <c r="F3" s="6">
-        <v>0.70289855069999996</v>
+        <v>0.93592677349999998</v>
       </c>
       <c r="G3" s="6">
-        <v>0.31379787720000002</v>
+        <v>1.01522843E-2</v>
       </c>
       <c r="H3" s="6">
-        <v>0.32552083329999998</v>
+        <v>0.98958333330000003</v>
       </c>
       <c r="I3" s="6">
-        <v>0.40845070420000001</v>
+        <v>0</v>
       </c>
       <c r="J3" s="6">
-        <v>0.49760901740000002</v>
-      </c>
-      <c r="K3" s="48">
-        <v>0.30946887969999998</v>
+        <v>0.36610513039999998</v>
+      </c>
+      <c r="K3" s="5">
+        <f>SUM(E3,J3)/2</f>
+        <v>0.25971160409999999</v>
       </c>
       <c r="L3" s="26">
-        <f t="shared" ref="L3:L12" si="0">SUM(E3:J3)/6</f>
-        <v>0.42772579766666663</v>
+        <f>SUM(E3:J3)/6</f>
+        <v>0.40918093321666665</v>
       </c>
       <c r="M3" s="26">
         <f>STDEV(E3:J3)</f>
-        <v>0.15259314934426299</v>
+        <v>0.44906622019761899</v>
       </c>
       <c r="N3" s="12">
         <f>SUMPRODUCT(G3:I3,$C$16:$E$16)/SUM($C$16:$E$16)</f>
-        <v>0.39386213045140961</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="85"/>
-      <c r="B4" s="85"/>
+        <v>0.13814240589344262</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="20" x14ac:dyDescent="0.2">
+      <c r="A4" s="77"/>
+      <c r="B4" s="77"/>
       <c r="C4" s="5" t="s">
         <v>24</v>
       </c>
@@ -6198,13 +7716,13 @@
         <v>9</v>
       </c>
       <c r="E4" s="6">
-        <v>0.96948893970000005</v>
+        <v>0.1487414188</v>
       </c>
       <c r="F4" s="6">
         <v>0.97330282229999998</v>
       </c>
       <c r="G4" s="6">
-        <v>0.99584679279999999</v>
+        <v>2.7688048E-3</v>
       </c>
       <c r="H4" s="6">
         <v>0.99739583330000003</v>
@@ -6213,25 +7731,26 @@
         <v>1.4084507E-2</v>
       </c>
       <c r="J4" s="6">
-        <v>0.61895662200000001</v>
-      </c>
-      <c r="K4" s="48">
-        <v>0.21538406309999999</v>
+        <v>0.59878249289999996</v>
+      </c>
+      <c r="K4" s="5">
+        <f>SUM(E4,J4)/2</f>
+        <v>0.37376195584999999</v>
       </c>
       <c r="L4" s="26">
-        <f t="shared" si="0"/>
-        <v>0.76151258618333351</v>
-      </c>
-      <c r="M4" s="26">
+        <f>SUM(E4:J4)/6</f>
+        <v>0.45584597985000003</v>
+      </c>
+      <c r="M4" s="39">
         <f>STDEV(E4:J4)</f>
-        <v>0.39436876926890008</v>
+        <v>0.46394267128526467</v>
       </c>
       <c r="N4" s="12">
         <f>SUMPRODUCT(G4:I4,$C$16:$E$16)/SUM($C$16:$E$16)</f>
-        <v>0.18338927612931832</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+        <v>0.15082504339754099</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="D5" s="4"/>
@@ -6244,15 +7763,15 @@
       <c r="L5" s="26"/>
       <c r="M5" s="26"/>
     </row>
-    <row r="6" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="85" t="s">
+    <row r="6" spans="1:15" ht="20" x14ac:dyDescent="0.2">
+      <c r="A6" s="77" t="s">
         <v>83</v>
       </c>
-      <c r="B6" s="85" t="s">
-        <v>97</v>
+      <c r="B6" s="77" t="s">
+        <v>96</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>7</v>
@@ -6275,11 +7794,12 @@
       <c r="J6" s="6">
         <v>0.68544860669999996</v>
       </c>
-      <c r="K6" s="48">
-        <v>0.29145481309999999</v>
+      <c r="K6" s="5">
+        <f>SUM(E6,J6)/2</f>
+        <v>0.64531576675000002</v>
       </c>
       <c r="L6" s="26">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="L3:L12" si="0">SUM(E6:J6)/6</f>
         <v>0.56237986523333339</v>
       </c>
       <c r="M6" s="26">
@@ -6291,52 +7811,54 @@
         <v>0.15905989481147539</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="85"/>
-      <c r="B7" s="85"/>
-      <c r="C7" s="38" t="s">
+    <row r="7" spans="1:15" s="87" customFormat="1" ht="20" x14ac:dyDescent="0.2">
+      <c r="A7" s="77"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D7" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="40">
+      <c r="E7" s="90">
         <v>0.71532012199999995</v>
       </c>
-      <c r="F7" s="40">
+      <c r="F7" s="90">
         <v>0.88452743899999997</v>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="90">
         <v>0.82664822500000001</v>
       </c>
-      <c r="H7" s="40">
+      <c r="H7" s="90">
         <v>0.20572916669999999</v>
       </c>
-      <c r="I7" s="40">
+      <c r="I7" s="90">
         <v>7.0422535199999997E-2</v>
       </c>
-      <c r="J7" s="40">
+      <c r="J7" s="90">
         <v>0.73983099360000004</v>
       </c>
-      <c r="K7" s="49">
-        <v>0.60415152729999999</v>
-      </c>
-      <c r="L7" s="41">
+      <c r="K7" s="38">
+        <f>SUM(E7,J7)/2</f>
+        <v>0.72757555780000005</v>
+      </c>
+      <c r="L7" s="92">
         <f>SUM(E7:J7)/6</f>
         <v>0.57374641358333334</v>
       </c>
-      <c r="M7" s="41">
+      <c r="M7" s="92">
         <f>STDEV(E7:J7)</f>
         <v>0.34552655329669091</v>
       </c>
-      <c r="N7" s="42">
+      <c r="N7" s="88">
         <f>SUMPRODUCT(G7:I7,$C$19:$E$19)/SUM($C$19:$E$19)</f>
         <v>0.10787245163360654</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A8" s="85"/>
-      <c r="B8" s="85"/>
+      <c r="O7" s="93"/>
+    </row>
+    <row r="8" spans="1:15" ht="20" x14ac:dyDescent="0.2">
+      <c r="A8" s="77"/>
+      <c r="B8" s="77"/>
       <c r="C8" s="5" t="s">
         <v>24</v>
       </c>
@@ -6361,8 +7883,9 @@
       <c r="J8" s="6">
         <v>0.50378384080000005</v>
       </c>
-      <c r="K8" s="48">
-        <v>0.322335392</v>
+      <c r="K8" s="5">
+        <f>SUM(E8,J8)/2</f>
+        <v>0.64213582285000004</v>
       </c>
       <c r="L8" s="26">
         <f>SUM(E8:J8)/6</f>
@@ -6377,7 +7900,7 @@
         <v>0.12909648446311475</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
       <c r="B9" s="4"/>
       <c r="D9" s="4"/>
@@ -6390,56 +7913,57 @@
       <c r="L9" s="26"/>
       <c r="M9" s="26"/>
     </row>
-    <row r="10" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="85" t="s">
-        <v>85</v>
-      </c>
-      <c r="B10" s="85" t="s">
-        <v>98</v>
+    <row r="10" spans="1:15" ht="20" x14ac:dyDescent="0.2">
+      <c r="A10" s="77" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="77" t="s">
+        <v>142</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E10" s="6">
-        <v>0.77019817069999996</v>
+        <v>0.74713958810000003</v>
       </c>
       <c r="F10" s="6">
-        <v>0.96989329270000002</v>
+        <v>0.90999237219999995</v>
       </c>
       <c r="G10" s="6">
-        <v>0.91240202859999997</v>
+        <v>0.83848638669999997</v>
       </c>
       <c r="H10" s="6">
-        <v>0.109375</v>
+        <v>0.34114583329999998</v>
       </c>
       <c r="I10" s="6">
-        <v>0</v>
+        <v>0.1549295775</v>
       </c>
       <c r="J10" s="6">
-        <v>0.82907810169999996</v>
-      </c>
-      <c r="K10" s="48">
-        <v>0.27578664860000002</v>
+        <v>0.65728491980000003</v>
+      </c>
+      <c r="K10" s="5">
+        <f>SUM(E10,J10)/2</f>
+        <v>0.70221225394999998</v>
       </c>
       <c r="L10" s="26">
         <f t="shared" si="0"/>
-        <v>0.59849109894999997</v>
+        <v>0.60816311293333336</v>
       </c>
       <c r="M10" s="26">
         <f>STDEV(E10:J10)</f>
-        <v>0.42814938967063176</v>
-      </c>
-      <c r="N10" s="12">
+        <v>0.29752176055268348</v>
+      </c>
+      <c r="N10" s="40">
         <f>SUMPRODUCT(G10:I10, $C$22:$E$22)/SUM($C$22:$E$22)</f>
-        <v>5.4554890957798155E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="85"/>
-      <c r="B11" s="85"/>
+        <v>0.21221355914186049</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="20" x14ac:dyDescent="0.2">
+      <c r="A11" s="77"/>
+      <c r="B11" s="77"/>
       <c r="C11" s="5" t="s">
         <v>23</v>
       </c>
@@ -6447,42 +7971,43 @@
         <v>8</v>
       </c>
       <c r="E11" s="6">
-        <v>0.36775914630000001</v>
+        <v>0.65980167810000001</v>
       </c>
       <c r="F11" s="6">
-        <v>0.64481707320000003</v>
+        <v>0.85621662850000002</v>
       </c>
       <c r="G11" s="6">
-        <v>0.3785154449</v>
+        <v>0.77480387630000003</v>
       </c>
       <c r="H11" s="6">
-        <v>0.31510416670000002</v>
+        <v>0.12239583330000001</v>
       </c>
       <c r="I11" s="6">
-        <v>0.32394366200000002</v>
+        <v>5.6338028200000001E-2</v>
       </c>
       <c r="J11" s="6">
-        <v>0.47833423320000001</v>
-      </c>
-      <c r="K11" s="48">
-        <v>0.30020344319999998</v>
+        <v>0.59480806279999998</v>
+      </c>
+      <c r="K11" s="5">
+        <f>SUM(E11,J11)/2</f>
+        <v>0.62730487044999994</v>
       </c>
       <c r="L11" s="26">
         <f t="shared" si="0"/>
-        <v>0.41807895438333337</v>
+        <v>0.51072735120000001</v>
       </c>
       <c r="M11" s="26">
         <f>STDEV(E11:J11)</f>
-        <v>0.12538220582562706</v>
+        <v>0.33931195012640925</v>
       </c>
       <c r="N11" s="12">
         <f>SUMPRODUCT(G11:I11, $C$22:$E$22)/SUM($C$22:$E$22)</f>
-        <v>0.32424327420458715</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="85"/>
-      <c r="B12" s="85"/>
+        <v>9.1417939206976745E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="20" x14ac:dyDescent="0.2">
+      <c r="A12" s="77"/>
+      <c r="B12" s="77"/>
       <c r="C12" s="5" t="s">
         <v>24</v>
       </c>
@@ -6490,40 +8015,41 @@
         <v>9</v>
       </c>
       <c r="E12" s="6">
-        <v>1</v>
+        <v>0.25896262399999997</v>
       </c>
       <c r="F12" s="6">
-        <v>1</v>
+        <v>0.96109839819999998</v>
       </c>
       <c r="G12" s="6">
-        <v>1</v>
+        <v>0.1647438856</v>
       </c>
       <c r="H12" s="6">
-        <v>1</v>
+        <v>0.8359375</v>
       </c>
       <c r="I12" s="6">
-        <v>1</v>
+        <v>1.4084507E-2</v>
       </c>
       <c r="J12" s="6">
-        <v>0.4793704064</v>
-      </c>
-      <c r="K12" s="48">
-        <v>0.29891920059999999</v>
+        <v>0.61473724439999999</v>
+      </c>
+      <c r="K12" s="5">
+        <f>SUM(E12,J12)/2</f>
+        <v>0.43684993419999996</v>
       </c>
       <c r="L12" s="26">
         <f t="shared" si="0"/>
-        <v>0.9132284010666667</v>
+        <v>0.47492735986666673</v>
       </c>
       <c r="M12" s="26">
         <f>STDEV(E12:J12)</f>
-        <v>0.21254614155209578</v>
+        <v>0.38508910488114606</v>
       </c>
       <c r="N12" s="12">
         <f>SUMPRODUCT(G12:I12, $C$22:$E$22)/SUM($C$22:$E$22)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+        <v>0.17802995149147285</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="D13" s="4"/>
@@ -6536,7 +8062,7 @@
       <c r="L13" s="26"/>
       <c r="M13" s="26"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="22"/>
       <c r="B14" s="22"/>
       <c r="D14" s="24"/>
@@ -6546,26 +8072,26 @@
       <c r="H14" s="19"/>
       <c r="I14" s="19"/>
       <c r="J14" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="K14" s="50">
+        <v>97</v>
+      </c>
+      <c r="K14" s="37">
         <f t="shared" ref="K14" si="1">MAX(K2:K12)</f>
-        <v>0.60415152729999999</v>
+        <v>0.72757555780000005</v>
       </c>
       <c r="L14" s="37">
         <f>MAX(L2:L12)</f>
-        <v>0.9132284010666667</v>
+        <v>0.62082451493333335</v>
       </c>
       <c r="M14" s="37">
         <f t="shared" ref="M14:N14" si="2">MAX(M2:M12)</f>
-        <v>0.42814938967063176</v>
+        <v>0.46394267128526467</v>
       </c>
       <c r="N14" s="37">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+        <v>0.21221355914186049</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="22"/>
       <c r="B15" s="31" t="s">
         <v>88</v>
@@ -6586,69 +8112,69 @@
       <c r="J15" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="K15" s="50">
+      <c r="K15" s="37">
         <f t="shared" ref="K15" si="3">MIN(K2:K12)</f>
-        <v>0.21538406309999999</v>
+        <v>0.25971160409999999</v>
       </c>
       <c r="L15" s="37">
         <f>MIN(L2:L12)</f>
-        <v>0.41807895438333337</v>
+        <v>0.40918093321666665</v>
       </c>
       <c r="M15" s="37">
         <f t="shared" ref="M15:N15" si="4">MIN(M2:M12)</f>
-        <v>0.12538220582562706</v>
+        <v>0.27171777170155592</v>
       </c>
       <c r="N15" s="37">
         <f t="shared" si="4"/>
-        <v>5.4554890957798155E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+        <v>9.1417939206976745E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="22"/>
       <c r="B16" s="31" t="s">
         <v>92</v>
       </c>
       <c r="C16" s="35">
-        <f>1/38</f>
-        <v>2.6315789473684209E-2</v>
+        <f>1/17</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="D16" s="36">
-        <f>1/6.8</f>
-        <v>0.14705882352941177</v>
+        <f>1/3</f>
+        <v>0.33333333333333331</v>
       </c>
       <c r="E16" s="36">
-        <f>1/1.2</f>
-        <v>0.83333333333333337</v>
+        <f>1/0.5</f>
+        <v>2</v>
       </c>
       <c r="F16" s="19"/>
       <c r="G16" s="19"/>
       <c r="H16" s="19"/>
       <c r="I16" s="19"/>
       <c r="J16" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="K16" s="50">
+        <v>98</v>
+      </c>
+      <c r="K16" s="37">
         <f t="shared" ref="K16" si="5">AVERAGE(K2:K12)</f>
-        <v>0.32997006593333333</v>
+        <v>0.56825737477222216</v>
       </c>
       <c r="L16" s="37">
         <f>AVERAGE(L2:L12)</f>
-        <v>0.59634948413703703</v>
+        <v>0.52782550475925927</v>
       </c>
       <c r="M16" s="37">
         <f t="shared" ref="M16:N16" si="6">AVERAGE(M2:M12)</f>
-        <v>0.28206663277159816</v>
+        <v>0.36064621577827832</v>
       </c>
       <c r="N16" s="37">
         <f t="shared" si="6"/>
-        <v>0.29332177758987449</v>
+        <v>0.14935948568835869</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17" s="24"/>
       <c r="B17" s="24"/>
       <c r="D17" s="24"/>
-      <c r="E17" s="52"/>
+      <c r="E17" s="47"/>
       <c r="F17" s="19"/>
       <c r="G17" s="19"/>
       <c r="H17" s="19"/>
@@ -6668,7 +8194,7 @@
       <c r="D18" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="E18" s="53" t="s">
+      <c r="E18" s="48" t="s">
         <v>91</v>
       </c>
       <c r="F18" s="19"/>
@@ -6708,7 +8234,7 @@
       <c r="A20" s="22"/>
       <c r="B20" s="22"/>
       <c r="D20" s="24"/>
-      <c r="E20" s="52"/>
+      <c r="E20" s="47"/>
       <c r="F20" s="19"/>
       <c r="G20" s="19"/>
       <c r="H20" s="19"/>
@@ -6728,7 +8254,7 @@
       <c r="D21" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="E21" s="53" t="s">
+      <c r="E21" s="48" t="s">
         <v>91</v>
       </c>
       <c r="F21" s="19"/>
@@ -6745,8 +8271,8 @@
         <v>92</v>
       </c>
       <c r="C22" s="35">
-        <f>1/21</f>
-        <v>4.7619047619047616E-2</v>
+        <f>1/25</f>
+        <v>0.04</v>
       </c>
       <c r="D22" s="36">
         <f>1/4</f>
@@ -7027,7 +8553,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB030C74-5D3D-4140-98C1-A6779936EBBB}">
   <dimension ref="A1:O52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="19" x14ac:dyDescent="0.2"/>
@@ -7038,70 +8564,70 @@
     <col min="4" max="4" width="19.5" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.83203125" style="5" customWidth="1"/>
     <col min="6" max="11" width="19.1640625" style="12" customWidth="1"/>
-    <col min="12" max="12" width="19.1640625" style="48" customWidth="1"/>
+    <col min="12" max="12" width="21" style="95" customWidth="1"/>
     <col min="13" max="15" width="19.1640625" style="12" customWidth="1"/>
     <col min="16" max="16384" width="8.83203125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="67" customFormat="1" ht="89" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="61" t="s">
+    <row r="1" spans="1:15" s="60" customFormat="1" ht="67" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="55" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="55" t="s">
         <v>95</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="C1" s="55" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="61" t="s">
+      <c r="D1" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="61" t="s">
+      <c r="E1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="F1" s="62" t="s">
+      <c r="F1" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="62" t="s">
+      <c r="G1" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="H1" s="63" t="s">
+      <c r="H1" s="57" t="s">
         <v>59</v>
       </c>
-      <c r="I1" s="63" t="s">
+      <c r="I1" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="J1" s="63" t="s">
+      <c r="J1" s="57" t="s">
         <v>57</v>
       </c>
-      <c r="K1" s="62" t="s">
+      <c r="K1" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="64" t="s">
-        <v>103</v>
-      </c>
-      <c r="M1" s="65" t="s">
+      <c r="L1" s="94" t="s">
+        <v>144</v>
+      </c>
+      <c r="M1" s="58" t="s">
         <v>73</v>
       </c>
-      <c r="N1" s="65" t="s">
+      <c r="N1" s="58" t="s">
         <v>71</v>
       </c>
-      <c r="O1" s="66" t="s">
+      <c r="O1" s="59" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A2" s="89" t="s">
+      <c r="A2" s="79" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="89" t="s">
-        <v>97</v>
-      </c>
-      <c r="C2" s="90">
+      <c r="B2" s="79" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" s="80">
         <v>0</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>7</v>
@@ -7124,8 +8650,9 @@
       <c r="K2" s="6">
         <v>0.68544860669999996</v>
       </c>
-      <c r="L2" s="48">
-        <v>0.29145481309999999</v>
+      <c r="L2" s="95">
+        <f>SUM(F2,K2)/2</f>
+        <v>0.64531576675000002</v>
       </c>
       <c r="M2" s="26">
         <f>H2*1/3+I2*1/3+J2*1/3</f>
@@ -7141,9 +8668,9 @@
       </c>
     </row>
     <row r="3" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A3" s="85"/>
-      <c r="B3" s="85"/>
-      <c r="C3" s="88"/>
+      <c r="A3" s="77"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="78"/>
       <c r="D3" s="5" t="s">
         <v>23</v>
       </c>
@@ -7168,15 +8695,16 @@
       <c r="K3" s="19">
         <v>0.73983099360000004</v>
       </c>
-      <c r="L3" s="76">
-        <v>0.60415152729999999</v>
+      <c r="L3" s="95">
+        <f t="shared" ref="L3:L4" si="0">SUM(F3,K3)/2</f>
+        <v>0.72757555780000005</v>
       </c>
       <c r="M3" s="26">
         <f>H3*1/3+I3*1/3+J3*1/3</f>
         <v>0.36759997563333335</v>
       </c>
       <c r="N3" s="26">
-        <f t="shared" ref="N3:N4" si="0">STDEV(H3:J3)</f>
+        <f t="shared" ref="N3:N4" si="1">STDEV(H3:J3)</f>
         <v>0.40326287030536323</v>
       </c>
       <c r="O3" s="12">
@@ -7185,9 +8713,9 @@
       </c>
     </row>
     <row r="4" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A4" s="85"/>
-      <c r="B4" s="85"/>
-      <c r="C4" s="88"/>
+      <c r="A4" s="77"/>
+      <c r="B4" s="77"/>
+      <c r="C4" s="78"/>
       <c r="D4" s="5" t="s">
         <v>24</v>
       </c>
@@ -7212,15 +8740,16 @@
       <c r="K4" s="26">
         <v>0.50378384080000005</v>
       </c>
-      <c r="L4" s="48">
-        <v>0.322335392</v>
+      <c r="L4" s="95">
+        <f t="shared" si="0"/>
+        <v>0.64213582285000004</v>
       </c>
       <c r="M4" s="26">
         <f>H4*1/3+I4*1/3+J4*1/3</f>
         <v>0.35560836976666665</v>
       </c>
       <c r="N4" s="26">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.51010668146346583</v>
       </c>
       <c r="O4" s="12">
@@ -7229,8 +8758,8 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="85"/>
-      <c r="B5" s="85"/>
+      <c r="A5" s="77"/>
+      <c r="B5" s="77"/>
       <c r="C5" s="21"/>
       <c r="E5" s="4"/>
       <c r="F5" s="6"/>
@@ -7239,18 +8768,18 @@
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
       <c r="K5" s="6"/>
-      <c r="L5" s="75"/>
+      <c r="L5" s="97"/>
       <c r="M5" s="26"/>
       <c r="N5" s="26"/>
     </row>
     <row r="6" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A6" s="85"/>
-      <c r="B6" s="85"/>
-      <c r="C6" s="88">
+      <c r="A6" s="77"/>
+      <c r="B6" s="77"/>
+      <c r="C6" s="78">
         <v>10</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>7</v>
@@ -7273,8 +8802,9 @@
       <c r="K6" s="19">
         <v>0.73476295459999996</v>
       </c>
-      <c r="L6" s="76">
-        <v>0.31354534789999999</v>
+      <c r="L6" s="95">
+        <f>SUM(F6,K6)/2</f>
+        <v>0.7031284284999999</v>
       </c>
       <c r="M6" s="26">
         <f>H6*1/3+I6*1/3+J6*1/3</f>
@@ -7290,9 +8820,9 @@
       </c>
     </row>
     <row r="7" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A7" s="85"/>
-      <c r="B7" s="85"/>
-      <c r="C7" s="88"/>
+      <c r="A7" s="77"/>
+      <c r="B7" s="77"/>
+      <c r="C7" s="78"/>
       <c r="D7" s="5" t="s">
         <v>23</v>
       </c>
@@ -7317,15 +8847,16 @@
       <c r="K7" s="26">
         <v>0.70778481859999998</v>
       </c>
-      <c r="L7" s="48">
-        <v>0.60222457630000004</v>
+      <c r="L7" s="95">
+        <f t="shared" ref="L7:L8" si="2">SUM(F7,K7)/2</f>
+        <v>0.70583600685000003</v>
       </c>
       <c r="M7" s="26">
         <f>H7*1/3+I7*1/3+J7*1/3</f>
         <v>0.44090356646666662</v>
       </c>
       <c r="N7" s="26">
-        <f t="shared" ref="N7:N8" si="1">STDEV(H7:J7)</f>
+        <f t="shared" ref="N7:N8" si="3">STDEV(H7:J7)</f>
         <v>0.31896485779988359</v>
       </c>
       <c r="O7" s="12">
@@ -7334,9 +8865,9 @@
       </c>
     </row>
     <row r="8" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A8" s="85"/>
-      <c r="B8" s="85"/>
-      <c r="C8" s="88"/>
+      <c r="A8" s="77"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="78"/>
       <c r="D8" s="5" t="s">
         <v>24</v>
       </c>
@@ -7361,15 +8892,16 @@
       <c r="K8" s="6">
         <v>0.46718656149999999</v>
       </c>
-      <c r="L8" s="75">
-        <v>0.27905481360000001</v>
+      <c r="L8" s="95">
+        <f t="shared" si="2"/>
+        <v>0.34982803684999997</v>
       </c>
       <c r="M8" s="26">
         <f>H8*1/3+I8*1/3+J8*1/3</f>
         <v>0.31121721976666666</v>
       </c>
       <c r="N8" s="26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.1625942445289115</v>
       </c>
       <c r="O8" s="12">
@@ -7378,8 +8910,8 @@
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A9" s="85"/>
-      <c r="B9" s="85"/>
+      <c r="A9" s="77"/>
+      <c r="B9" s="77"/>
       <c r="C9" s="21"/>
       <c r="E9" s="4"/>
       <c r="F9" s="6"/>
@@ -7388,23 +8920,23 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
       <c r="K9" s="6"/>
-      <c r="L9" s="75"/>
+      <c r="L9" s="97"/>
       <c r="M9" s="26"/>
       <c r="N9" s="26"/>
     </row>
     <row r="10" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A10" s="85"/>
-      <c r="B10" s="85"/>
-      <c r="C10" s="88">
+      <c r="A10" s="77"/>
+      <c r="B10" s="77"/>
+      <c r="C10" s="78">
         <v>20</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="77">
+      <c r="F10" s="67">
         <v>0.59908536590000006</v>
       </c>
       <c r="G10" s="26">
@@ -7422,15 +8954,16 @@
       <c r="K10" s="26">
         <v>0.68091049619999999</v>
       </c>
-      <c r="L10" s="48">
-        <v>0.26234870690000001</v>
+      <c r="L10" s="95">
+        <f>SUM(F10,K10)/2</f>
+        <v>0.63999793105000002</v>
       </c>
       <c r="M10" s="26">
         <f>H10*1/3+I10*1/3+J10*1/3</f>
         <v>0.35593631086666666</v>
       </c>
       <c r="N10" s="26">
-        <f t="shared" ref="N10:N20" si="2">STDEV(H10:J10)</f>
+        <f t="shared" ref="N10:N20" si="4">STDEV(H10:J10)</f>
         <v>0.30821125459200288</v>
       </c>
       <c r="O10" s="12">
@@ -7439,9 +8972,9 @@
       </c>
     </row>
     <row r="11" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A11" s="85"/>
-      <c r="B11" s="85"/>
-      <c r="C11" s="88"/>
+      <c r="A11" s="77"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="78"/>
       <c r="D11" s="5" t="s">
         <v>23</v>
       </c>
@@ -7466,15 +8999,16 @@
       <c r="K11" s="6">
         <v>0.77931160200000005</v>
       </c>
-      <c r="L11" s="75">
-        <v>0.59928654589999997</v>
+      <c r="L11" s="95">
+        <f t="shared" ref="L11:L12" si="5">SUM(F11,K11)/2</f>
+        <v>0.74560092295000002</v>
       </c>
       <c r="M11" s="26">
         <f>H11*1/3+I11*1/3+J11*1/3</f>
         <v>0.39560690466666665</v>
       </c>
       <c r="N11" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.36727687312398277</v>
       </c>
       <c r="O11" s="12">
@@ -7483,9 +9017,9 @@
       </c>
     </row>
     <row r="12" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A12" s="85"/>
-      <c r="B12" s="85"/>
-      <c r="C12" s="88"/>
+      <c r="A12" s="77"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="78"/>
       <c r="D12" s="5" t="s">
         <v>24</v>
       </c>
@@ -7510,15 +9044,16 @@
       <c r="K12" s="19">
         <v>0.49644469029999999</v>
       </c>
-      <c r="L12" s="76">
-        <v>0.30310681719999999</v>
+      <c r="L12" s="95">
+        <f t="shared" si="5"/>
+        <v>0.45877874760000004</v>
       </c>
       <c r="M12" s="26">
         <f>H12*1/3+I12*1/3+J12*1/3</f>
         <v>0.34218283953333334</v>
       </c>
       <c r="N12" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.14997136463523317</v>
       </c>
       <c r="O12" s="12">
@@ -7527,8 +9062,8 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A13" s="85"/>
-      <c r="B13" s="85"/>
+      <c r="A13" s="77"/>
+      <c r="B13" s="77"/>
       <c r="C13" s="21"/>
       <c r="E13" s="4"/>
       <c r="F13" s="6"/>
@@ -7537,18 +9072,18 @@
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
-      <c r="L13" s="75"/>
+      <c r="L13" s="97"/>
       <c r="M13" s="26"/>
       <c r="N13" s="26"/>
     </row>
     <row r="14" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A14" s="85"/>
-      <c r="B14" s="85"/>
-      <c r="C14" s="88">
+      <c r="A14" s="77"/>
+      <c r="B14" s="77"/>
+      <c r="C14" s="78">
         <v>30</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>7</v>
@@ -7571,15 +9106,16 @@
       <c r="K14" s="26">
         <v>0.71088839550000005</v>
       </c>
-      <c r="L14" s="48">
-        <v>0.31843601970000002</v>
+      <c r="L14" s="95">
+        <f>SUM(F14,K14)/2</f>
+        <v>0.66432377090000005</v>
       </c>
       <c r="M14" s="26">
         <f>H14*1/3+I14*1/3+J14*1/3</f>
         <v>0.36790393796666665</v>
       </c>
       <c r="N14" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.289732121091618</v>
       </c>
       <c r="O14" s="12">
@@ -7588,9 +9124,9 @@
       </c>
     </row>
     <row r="15" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A15" s="85"/>
-      <c r="B15" s="85"/>
-      <c r="C15" s="88"/>
+      <c r="A15" s="77"/>
+      <c r="B15" s="77"/>
+      <c r="C15" s="78"/>
       <c r="D15" s="5" t="s">
         <v>23</v>
       </c>
@@ -7615,15 +9151,16 @@
       <c r="K15" s="26">
         <v>0.7951218136</v>
       </c>
-      <c r="L15" s="48">
-        <v>0.55517741580000002</v>
+      <c r="L15" s="95">
+        <f t="shared" ref="L15:L16" si="6">SUM(F15,K15)/2</f>
+        <v>0.74950450434999993</v>
       </c>
       <c r="M15" s="26">
         <f>H15*1/3+I15*1/3+J15*1/3</f>
         <v>0.32681134159999997</v>
       </c>
       <c r="N15" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.44346139019273595</v>
       </c>
       <c r="O15" s="12">
@@ -7632,9 +9169,9 @@
       </c>
     </row>
     <row r="16" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A16" s="85"/>
-      <c r="B16" s="85"/>
-      <c r="C16" s="88"/>
+      <c r="A16" s="77"/>
+      <c r="B16" s="77"/>
+      <c r="C16" s="78"/>
       <c r="D16" s="5" t="s">
         <v>24</v>
       </c>
@@ -7659,15 +9196,16 @@
       <c r="K16" s="26">
         <v>0.36442804410000001</v>
       </c>
-      <c r="L16" s="48">
-        <v>0.15361280429999999</v>
+      <c r="L16" s="95">
+        <f t="shared" si="6"/>
+        <v>0.25424146105000001</v>
       </c>
       <c r="M16" s="26">
         <f>H16*1/3+I16*1/3+J16*1/3</f>
         <v>0.33052303029999996</v>
       </c>
       <c r="N16" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.55952529849253352</v>
       </c>
       <c r="O16" s="12">
@@ -7676,8 +9214,8 @@
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A17" s="85"/>
-      <c r="B17" s="85"/>
+      <c r="A17" s="77"/>
+      <c r="B17" s="77"/>
       <c r="C17" s="23"/>
       <c r="E17" s="24"/>
       <c r="F17" s="19"/>
@@ -7686,18 +9224,18 @@
       <c r="I17" s="19"/>
       <c r="J17" s="19"/>
       <c r="K17" s="19"/>
-      <c r="L17" s="76"/>
+      <c r="L17" s="96"/>
       <c r="M17" s="26"/>
       <c r="N17" s="26"/>
     </row>
     <row r="18" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A18" s="85"/>
-      <c r="B18" s="85"/>
-      <c r="C18" s="88">
+      <c r="A18" s="77"/>
+      <c r="B18" s="77"/>
+      <c r="C18" s="78">
         <v>100</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>7</v>
@@ -7720,15 +9258,16 @@
       <c r="K18" s="6">
         <v>0.56211542520000002</v>
       </c>
-      <c r="L18" s="75">
-        <v>0.27215055560000001</v>
+      <c r="L18" s="95">
+        <f>SUM(F18,K18)/2</f>
+        <v>0.49523454185000004</v>
       </c>
       <c r="M18" s="26">
         <f>H18*1/3+I18*1/3+J18*1/3</f>
         <v>0.33127474313333333</v>
       </c>
       <c r="N18" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.15453424775938834</v>
       </c>
       <c r="O18" s="12">
@@ -7737,9 +9276,9 @@
       </c>
     </row>
     <row r="19" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A19" s="85"/>
-      <c r="B19" s="85"/>
-      <c r="C19" s="88"/>
+      <c r="A19" s="77"/>
+      <c r="B19" s="77"/>
+      <c r="C19" s="78"/>
       <c r="D19" s="5" t="s">
         <v>23</v>
       </c>
@@ -7764,15 +9303,16 @@
       <c r="K19" s="6">
         <v>0.70333462499999999</v>
       </c>
-      <c r="L19" s="75">
-        <v>0.44629329410000002</v>
+      <c r="L19" s="95">
+        <f t="shared" ref="L19:L20" si="7">SUM(F19,K19)/2</f>
+        <v>0.73066883690000006</v>
       </c>
       <c r="M19" s="26">
         <f>H19*1/3+I19*1/3+J19*1/3</f>
         <v>0.31852956430000001</v>
       </c>
       <c r="N19" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.51165153732277202</v>
       </c>
       <c r="O19" s="12">
@@ -7781,9 +9321,9 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="20" x14ac:dyDescent="0.2">
-      <c r="A20" s="85"/>
-      <c r="B20" s="85"/>
-      <c r="C20" s="88"/>
+      <c r="A20" s="77"/>
+      <c r="B20" s="77"/>
+      <c r="C20" s="78"/>
       <c r="D20" s="5" t="s">
         <v>24</v>
       </c>
@@ -7808,15 +9348,16 @@
       <c r="K20" s="6">
         <v>0.58367710129999995</v>
       </c>
-      <c r="L20" s="75">
-        <v>0.27206442679999998</v>
+      <c r="L20" s="95">
+        <f t="shared" si="7"/>
+        <v>0.67103062379999989</v>
       </c>
       <c r="M20" s="26">
         <f>H20*1/3+I20*1/3+J20*1/3</f>
         <v>0.36174710683333333</v>
       </c>
       <c r="N20" s="26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.48268282581058747</v>
       </c>
       <c r="O20" s="12">
@@ -7835,7 +9376,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="19"/>
       <c r="K21" s="19"/>
-      <c r="L21" s="76"/>
+      <c r="L21" s="96"/>
       <c r="M21" s="26"/>
       <c r="N21" s="26"/>
     </row>
@@ -7850,7 +9391,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="19"/>
       <c r="K22" s="19"/>
-      <c r="L22" s="76"/>
+      <c r="L22" s="96"/>
       <c r="M22" s="26"/>
       <c r="N22" s="26"/>
     </row>
@@ -7865,7 +9406,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="19"/>
       <c r="K23" s="19"/>
-      <c r="L23" s="76"/>
+      <c r="L23" s="96"/>
       <c r="M23" s="26"/>
       <c r="N23" s="26"/>
     </row>
@@ -7880,7 +9421,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="19"/>
       <c r="K24" s="19"/>
-      <c r="L24" s="76"/>
+      <c r="L24" s="96"/>
       <c r="M24" s="26"/>
       <c r="N24" s="26"/>
     </row>
@@ -7904,21 +9445,21 @@
       <c r="I25" s="19"/>
       <c r="J25" s="19"/>
       <c r="K25" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="L25" s="50">
+        <v>97</v>
+      </c>
+      <c r="L25" s="46">
         <f>MAX(L2:L23)</f>
-        <v>0.60415152729999999</v>
-      </c>
-      <c r="M25" s="51">
+        <v>0.74950450434999993</v>
+      </c>
+      <c r="M25" s="46">
         <f>MAX(M2:M23)</f>
         <v>0.44090356646666662</v>
       </c>
-      <c r="N25" s="51">
+      <c r="N25" s="46">
         <f>MAX(N2:N23)</f>
         <v>0.55952529849253352</v>
       </c>
-      <c r="O25" s="51">
+      <c r="O25" s="46">
         <f>MAX(O2:O23)</f>
         <v>0.30787586147131152</v>
       </c>
@@ -7948,19 +9489,19 @@
       <c r="K26" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="L26" s="50">
+      <c r="L26" s="46">
         <f>MIN(L2:L20)</f>
-        <v>0.15361280429999999</v>
-      </c>
-      <c r="M26" s="51">
+        <v>0.25424146105000001</v>
+      </c>
+      <c r="M26" s="46">
         <f>MIN(M2:M20)</f>
         <v>0.31121721976666666</v>
       </c>
-      <c r="N26" s="51">
+      <c r="N26" s="46">
         <f>MIN(N2:N20)</f>
         <v>0.14997136463523317</v>
       </c>
-      <c r="O26" s="51">
+      <c r="O26" s="46">
         <f>MIN(O2:O20)</f>
         <v>2.8877180972950819E-2</v>
       </c>
@@ -7976,21 +9517,21 @@
       <c r="I27" s="19"/>
       <c r="J27" s="19"/>
       <c r="K27" s="20" t="s">
-        <v>100</v>
-      </c>
-      <c r="L27" s="50">
+        <v>98</v>
+      </c>
+      <c r="L27" s="46">
         <f>AVERAGE(L2:L23)</f>
-        <v>0.37301620376666667</v>
-      </c>
-      <c r="M27" s="51">
+        <v>0.6122133973366668</v>
+      </c>
+      <c r="M27" s="46">
         <f>AVERAGE(M2:M23)</f>
         <v>0.35944499278888897</v>
       </c>
-      <c r="N27" s="51">
+      <c r="N27" s="46">
         <f>AVERAGE(N2:N23)</f>
         <v>0.35135493891108294</v>
       </c>
-      <c r="O27" s="51">
+      <c r="O27" s="46">
         <f>AVERAGE(O2:O23)</f>
         <v>0.16437335685338797</v>
       </c>
@@ -8006,7 +9547,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="19"/>
       <c r="K28" s="19"/>
-      <c r="L28" s="76"/>
+      <c r="L28" s="96"/>
       <c r="M28" s="26"/>
       <c r="N28" s="26"/>
     </row>
@@ -8021,7 +9562,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="19"/>
       <c r="K29" s="19"/>
-      <c r="L29" s="76"/>
+      <c r="L29" s="96"/>
       <c r="M29" s="26"/>
       <c r="N29" s="26"/>
     </row>
@@ -8036,7 +9577,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="19"/>
       <c r="K30" s="19"/>
-      <c r="L30" s="76"/>
+      <c r="L30" s="96"/>
       <c r="M30" s="26"/>
       <c r="N30" s="26"/>
     </row>
@@ -8051,7 +9592,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="19"/>
       <c r="K31" s="19"/>
-      <c r="L31" s="76"/>
+      <c r="L31" s="96"/>
       <c r="M31" s="26"/>
       <c r="N31" s="26"/>
     </row>
@@ -8066,7 +9607,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="19"/>
       <c r="K32" s="19"/>
-      <c r="L32" s="76"/>
+      <c r="L32" s="96"/>
       <c r="M32" s="26"/>
       <c r="N32" s="26"/>
     </row>
@@ -8081,7 +9622,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="19"/>
       <c r="K33" s="19"/>
-      <c r="L33" s="76"/>
+      <c r="L33" s="96"/>
       <c r="M33" s="26"/>
       <c r="N33" s="26"/>
     </row>
@@ -8096,7 +9637,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="19"/>
       <c r="K34" s="19"/>
-      <c r="L34" s="76"/>
+      <c r="L34" s="96"/>
       <c r="M34" s="26"/>
       <c r="N34" s="26"/>
     </row>
@@ -8111,7 +9652,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="19"/>
       <c r="K35" s="19"/>
-      <c r="L35" s="76"/>
+      <c r="L35" s="96"/>
       <c r="M35" s="26"/>
       <c r="N35" s="26"/>
     </row>
@@ -8126,7 +9667,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="19"/>
       <c r="K36" s="19"/>
-      <c r="L36" s="76"/>
+      <c r="L36" s="96"/>
       <c r="M36" s="26"/>
       <c r="N36" s="26"/>
     </row>
@@ -8141,7 +9682,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="19"/>
       <c r="K37" s="19"/>
-      <c r="L37" s="76"/>
+      <c r="L37" s="96"/>
       <c r="M37" s="26"/>
       <c r="N37" s="26"/>
     </row>
@@ -8156,7 +9697,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="19"/>
       <c r="K38" s="19"/>
-      <c r="L38" s="76"/>
+      <c r="L38" s="96"/>
       <c r="M38" s="26"/>
       <c r="N38" s="26"/>
     </row>
@@ -8171,7 +9712,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="19"/>
       <c r="K39" s="19"/>
-      <c r="L39" s="76"/>
+      <c r="L39" s="96"/>
       <c r="M39" s="26"/>
       <c r="N39" s="26"/>
     </row>
@@ -8186,7 +9727,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="19"/>
       <c r="K40" s="19"/>
-      <c r="L40" s="76"/>
+      <c r="L40" s="96"/>
       <c r="M40" s="26"/>
       <c r="N40" s="26"/>
     </row>
@@ -8201,7 +9742,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="19"/>
       <c r="K41" s="19"/>
-      <c r="L41" s="76"/>
+      <c r="L41" s="96"/>
       <c r="M41" s="26"/>
       <c r="N41" s="26"/>
     </row>
@@ -8216,7 +9757,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="19"/>
       <c r="K42" s="19"/>
-      <c r="L42" s="76"/>
+      <c r="L42" s="96"/>
       <c r="M42" s="26"/>
       <c r="N42" s="26"/>
     </row>
@@ -8231,7 +9772,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="19"/>
       <c r="K43" s="19"/>
-      <c r="L43" s="76"/>
+      <c r="L43" s="96"/>
       <c r="M43" s="26"/>
       <c r="N43" s="26"/>
     </row>
@@ -8246,7 +9787,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="19"/>
       <c r="K44" s="19"/>
-      <c r="L44" s="76"/>
+      <c r="L44" s="96"/>
       <c r="M44" s="26"/>
       <c r="N44" s="26"/>
     </row>
@@ -8261,7 +9802,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="19"/>
       <c r="K45" s="19"/>
-      <c r="L45" s="76"/>
+      <c r="L45" s="96"/>
       <c r="M45" s="26"/>
       <c r="N45" s="26"/>
     </row>
@@ -8276,7 +9817,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="19"/>
       <c r="K46" s="19"/>
-      <c r="L46" s="76"/>
+      <c r="L46" s="96"/>
       <c r="M46" s="26"/>
       <c r="N46" s="26"/>
     </row>
@@ -8291,7 +9832,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="19"/>
       <c r="K47" s="19"/>
-      <c r="L47" s="76"/>
+      <c r="L47" s="96"/>
       <c r="M47" s="26"/>
       <c r="N47" s="26"/>
     </row>
@@ -8306,7 +9847,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="19"/>
       <c r="K48" s="19"/>
-      <c r="L48" s="76"/>
+      <c r="L48" s="96"/>
       <c r="M48" s="26"/>
       <c r="N48" s="26"/>
     </row>
@@ -8340,7 +9881,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C64FDBF-6E58-8148-821B-47274FA4A935}">
   <dimension ref="A1:N52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
@@ -8350,64 +9891,64 @@
     <col min="3" max="3" width="21.5" style="28" customWidth="1"/>
     <col min="4" max="4" width="14.6640625" style="28" customWidth="1"/>
     <col min="5" max="10" width="17.5" style="12" customWidth="1"/>
-    <col min="11" max="11" width="17.5" style="48" customWidth="1"/>
+    <col min="11" max="11" width="17.5" style="95" customWidth="1"/>
     <col min="12" max="14" width="17.5" style="12" customWidth="1"/>
     <col min="15" max="16384" width="10.83203125" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="60" customFormat="1" ht="89" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
+    <row r="1" spans="1:14" s="54" customFormat="1" ht="89" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="49" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="49" t="s">
         <v>95</v>
       </c>
-      <c r="C1" s="55" t="s">
+      <c r="C1" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="55" t="s">
+      <c r="D1" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="56" t="s">
+      <c r="E1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="56" t="s">
+      <c r="F1" s="51" t="s">
         <v>56</v>
       </c>
-      <c r="G1" s="56" t="s">
+      <c r="G1" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="H1" s="56" t="s">
+      <c r="H1" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="56" t="s">
+      <c r="I1" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="J1" s="56" t="s">
+      <c r="J1" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="57" t="s">
-        <v>103</v>
-      </c>
-      <c r="L1" s="58" t="s">
+      <c r="K1" s="98" t="s">
+        <v>143</v>
+      </c>
+      <c r="L1" s="52" t="s">
         <v>73</v>
       </c>
-      <c r="M1" s="58" t="s">
+      <c r="M1" s="52" t="s">
         <v>71</v>
       </c>
-      <c r="N1" s="59" t="s">
+      <c r="N1" s="53" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="82" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="95" t="s">
-        <v>97</v>
-      </c>
-      <c r="C2" s="92" t="s">
-        <v>143</v>
+      <c r="B2" s="85" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" s="82" t="s">
+        <v>140</v>
       </c>
       <c r="D2" s="25" t="s">
         <v>7</v>
@@ -8430,8 +9971,9 @@
       <c r="J2" s="6">
         <v>0.68544860669999996</v>
       </c>
-      <c r="K2" s="48">
-        <v>0.29145481309999999</v>
+      <c r="K2" s="95">
+        <f>SUM(E2,J2)/2</f>
+        <v>0.64531576675000002</v>
       </c>
       <c r="L2" s="26">
         <f>G2*1/3+H2*1/3+I2*1/3</f>
@@ -8447,9 +9989,9 @@
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="93"/>
-      <c r="B3" s="91"/>
-      <c r="C3" s="93"/>
+      <c r="A3" s="83"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="83"/>
       <c r="D3" s="25" t="s">
         <v>66</v>
       </c>
@@ -8471,8 +10013,9 @@
       <c r="J3" s="26">
         <v>0.86995045729999998</v>
       </c>
-      <c r="K3" s="48">
-        <v>0.19871618520000001</v>
+      <c r="K3" s="95">
+        <f>SUM(E3,J3)/2</f>
+        <v>0.84827553355000007</v>
       </c>
       <c r="L3" s="26">
         <f t="shared" ref="L3:L4" si="0">G3*1/3+H3*1/3+I3*1/3</f>
@@ -8488,9 +10031,9 @@
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="93"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="93"/>
+      <c r="A4" s="83"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="83"/>
       <c r="D4" s="25" t="s">
         <v>67</v>
       </c>
@@ -8512,8 +10055,9 @@
       <c r="J4" s="26">
         <v>0.50006826780000002</v>
       </c>
-      <c r="K4" s="48">
-        <v>0.42822100460000001</v>
+      <c r="K4" s="95">
+        <f>SUM(E4,J4)/2</f>
+        <v>0.55567437779999995</v>
       </c>
       <c r="L4" s="26">
         <f t="shared" si="0"/>
@@ -8529,8 +10073,8 @@
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="93"/>
-      <c r="B5" s="91"/>
+      <c r="A5" s="83"/>
+      <c r="B5" s="81"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
       <c r="E5" s="26"/>
@@ -8539,14 +10083,14 @@
       <c r="H5" s="26"/>
       <c r="I5" s="26"/>
       <c r="J5" s="26"/>
-      <c r="K5" s="75"/>
+      <c r="K5" s="97"/>
       <c r="L5" s="26"/>
       <c r="M5" s="26"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="93"/>
-      <c r="B6" s="91"/>
-      <c r="C6" s="94" t="s">
+      <c r="A6" s="83"/>
+      <c r="B6" s="81"/>
+      <c r="C6" s="84" t="s">
         <v>64</v>
       </c>
       <c r="D6" s="25" t="s">
@@ -8570,8 +10114,9 @@
       <c r="J6" s="6">
         <v>0.73983099360000004</v>
       </c>
-      <c r="K6" s="48">
-        <v>0.60415152729999999</v>
+      <c r="K6" s="95">
+        <f>SUM(E6,J6)/2</f>
+        <v>0.72757555780000005</v>
       </c>
       <c r="L6" s="26">
         <f>G6*1/3+H6*1/3+I6*1/3</f>
@@ -8587,9 +10132,9 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="93"/>
-      <c r="B7" s="91"/>
-      <c r="C7" s="94"/>
+      <c r="A7" s="83"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="84"/>
       <c r="D7" s="25" t="s">
         <v>68</v>
       </c>
@@ -8611,8 +10156,9 @@
       <c r="J7" s="26">
         <v>0.64483064459999995</v>
       </c>
-      <c r="K7" s="75">
-        <v>0.48987603270000002</v>
+      <c r="K7" s="95">
+        <f>SUM(E7,J7)/2</f>
+        <v>0.6328192856999999</v>
       </c>
       <c r="L7" s="26">
         <f t="shared" ref="L7:L8" si="2">G7*1/3+H7*1/3+I7*1/3</f>
@@ -8628,9 +10174,9 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="93"/>
-      <c r="B8" s="91"/>
-      <c r="C8" s="94"/>
+      <c r="A8" s="83"/>
+      <c r="B8" s="81"/>
+      <c r="C8" s="84"/>
       <c r="D8" s="25" t="s">
         <v>69</v>
       </c>
@@ -8652,8 +10198,9 @@
       <c r="J8" s="26">
         <v>0.63692361819999999</v>
       </c>
-      <c r="K8" s="75">
-        <v>0.52219947680000001</v>
+      <c r="K8" s="95">
+        <f>SUM(E8,J8)/2</f>
+        <v>0.62467369934999994</v>
       </c>
       <c r="L8" s="26">
         <f t="shared" si="2"/>
@@ -8669,8 +10216,8 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="93"/>
-      <c r="B9" s="91"/>
+      <c r="A9" s="83"/>
+      <c r="B9" s="81"/>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
       <c r="E9" s="26"/>
@@ -8679,14 +10226,14 @@
       <c r="H9" s="26"/>
       <c r="I9" s="26"/>
       <c r="J9" s="26"/>
-      <c r="K9" s="75"/>
+      <c r="K9" s="97"/>
       <c r="L9" s="26"/>
       <c r="M9" s="26"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="93"/>
-      <c r="B10" s="91"/>
-      <c r="C10" s="91" t="s">
+      <c r="A10" s="83"/>
+      <c r="B10" s="81"/>
+      <c r="C10" s="81" t="s">
         <v>65</v>
       </c>
       <c r="D10" s="25" t="s">
@@ -8710,8 +10257,9 @@
       <c r="J10" s="6">
         <v>0.50378384080000005</v>
       </c>
-      <c r="K10" s="48">
-        <v>0.322335392</v>
+      <c r="K10" s="95">
+        <f>SUM(E10,J10)/2</f>
+        <v>0.64213582285000004</v>
       </c>
       <c r="L10" s="26">
         <f>G10*1/3+H10*1/3+I10*1/3</f>
@@ -8727,9 +10275,9 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="93"/>
-      <c r="B11" s="91"/>
-      <c r="C11" s="91"/>
+      <c r="A11" s="83"/>
+      <c r="B11" s="81"/>
+      <c r="C11" s="81"/>
       <c r="D11" s="25" t="s">
         <v>70</v>
       </c>
@@ -8751,8 +10299,9 @@
       <c r="J11" s="26">
         <v>0.58133493790000001</v>
       </c>
-      <c r="K11" s="75">
-        <v>0.38967609759999999</v>
+      <c r="K11" s="95">
+        <f>SUM(E11,J11)/2</f>
+        <v>0.58773301774999998</v>
       </c>
       <c r="L11" s="26">
         <f t="shared" ref="L11" si="5">G11*1/3+H11*1/3+I11*1/3</f>
@@ -8778,53 +10327,52 @@
       <c r="H12" s="26"/>
       <c r="I12" s="26"/>
       <c r="J12" s="26"/>
-      <c r="K12" s="75"/>
       <c r="L12" s="26"/>
       <c r="M12" s="26"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="25"/>
       <c r="B13" s="25"/>
-      <c r="C13" s="43" t="s">
+      <c r="C13" s="41" t="s">
         <v>93</v>
       </c>
-      <c r="D13" s="44" t="s">
+      <c r="D13" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="E13" s="45" t="s">
+      <c r="E13" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="F13" s="45" t="s">
+      <c r="F13" s="43" t="s">
         <v>91</v>
       </c>
       <c r="G13" s="26"/>
       <c r="H13" s="26"/>
       <c r="I13" s="26"/>
       <c r="J13" s="26"/>
-      <c r="K13" s="75"/>
+      <c r="K13" s="97"/>
       <c r="L13" s="26"/>
       <c r="M13" s="26"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="27"/>
       <c r="B14" s="27"/>
-      <c r="C14" s="46" t="s">
+      <c r="C14" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="47">
+      <c r="D14" s="45">
         <v>0.03</v>
       </c>
-      <c r="E14" s="47">
+      <c r="E14" s="45">
         <v>0.17</v>
       </c>
-      <c r="F14" s="47">
+      <c r="F14" s="45">
         <v>1</v>
       </c>
       <c r="G14" s="26"/>
       <c r="H14" s="26"/>
       <c r="I14" s="26"/>
       <c r="J14" s="26"/>
-      <c r="K14" s="75"/>
+      <c r="K14" s="97"/>
       <c r="L14" s="26"/>
       <c r="M14" s="26"/>
     </row>
@@ -8839,7 +10387,7 @@
       <c r="H15" s="26"/>
       <c r="I15" s="26"/>
       <c r="J15" s="26"/>
-      <c r="K15" s="75"/>
+      <c r="K15" s="97"/>
       <c r="L15" s="26"/>
       <c r="M15" s="26"/>
     </row>
@@ -8854,7 +10402,7 @@
       <c r="H16" s="26"/>
       <c r="I16" s="26"/>
       <c r="J16" s="26"/>
-      <c r="K16" s="75"/>
+      <c r="K16" s="97"/>
       <c r="L16" s="26"/>
       <c r="M16" s="26"/>
     </row>
@@ -8869,7 +10417,7 @@
       <c r="H17" s="26"/>
       <c r="I17" s="26"/>
       <c r="J17" s="26"/>
-      <c r="K17" s="76"/>
+      <c r="K17" s="96"/>
       <c r="L17" s="26"/>
       <c r="M17" s="26"/>
     </row>
@@ -8884,7 +10432,7 @@
       <c r="H18" s="26"/>
       <c r="I18" s="26"/>
       <c r="J18" s="26"/>
-      <c r="K18" s="75"/>
+      <c r="K18" s="97"/>
       <c r="L18" s="26"/>
       <c r="M18" s="26"/>
     </row>
@@ -8899,7 +10447,7 @@
       <c r="H19" s="26"/>
       <c r="I19" s="26"/>
       <c r="J19" s="26"/>
-      <c r="K19" s="75"/>
+      <c r="K19" s="97"/>
       <c r="L19" s="26"/>
       <c r="M19" s="26"/>
     </row>
@@ -8914,7 +10462,7 @@
       <c r="H20" s="26"/>
       <c r="I20" s="26"/>
       <c r="J20" s="26"/>
-      <c r="K20" s="75"/>
+      <c r="K20" s="97"/>
       <c r="L20" s="26"/>
       <c r="M20" s="26"/>
     </row>
@@ -8929,7 +10477,7 @@
       <c r="H21" s="26"/>
       <c r="I21" s="26"/>
       <c r="J21" s="26"/>
-      <c r="K21" s="76"/>
+      <c r="K21" s="96"/>
       <c r="L21" s="26"/>
       <c r="M21" s="26"/>
     </row>
@@ -8944,7 +10492,7 @@
       <c r="H22" s="26"/>
       <c r="I22" s="26"/>
       <c r="J22" s="26"/>
-      <c r="K22" s="76"/>
+      <c r="K22" s="96"/>
       <c r="L22" s="26"/>
       <c r="M22" s="26"/>
     </row>
@@ -8959,7 +10507,7 @@
       <c r="H23" s="26"/>
       <c r="I23" s="26"/>
       <c r="J23" s="26"/>
-      <c r="K23" s="76"/>
+      <c r="K23" s="96"/>
       <c r="L23" s="26"/>
       <c r="M23" s="26"/>
     </row>
@@ -8974,7 +10522,7 @@
       <c r="H24" s="26"/>
       <c r="I24" s="26"/>
       <c r="J24" s="26"/>
-      <c r="K24" s="76"/>
+      <c r="K24" s="96"/>
       <c r="L24" s="26"/>
       <c r="M24" s="26"/>
     </row>
@@ -8989,7 +10537,7 @@
       <c r="H25" s="26"/>
       <c r="I25" s="26"/>
       <c r="J25" s="26"/>
-      <c r="K25" s="76"/>
+      <c r="K25" s="96"/>
       <c r="L25" s="26"/>
       <c r="M25" s="26"/>
     </row>
@@ -9004,7 +10552,7 @@
       <c r="H26" s="26"/>
       <c r="I26" s="26"/>
       <c r="J26" s="26"/>
-      <c r="K26" s="76"/>
+      <c r="K26" s="96"/>
       <c r="L26" s="26"/>
       <c r="M26" s="26"/>
     </row>
@@ -9019,7 +10567,7 @@
       <c r="H27" s="26"/>
       <c r="I27" s="26"/>
       <c r="J27" s="26"/>
-      <c r="K27" s="76"/>
+      <c r="K27" s="96"/>
       <c r="L27" s="26"/>
       <c r="M27" s="26"/>
     </row>
@@ -9034,7 +10582,7 @@
       <c r="H28" s="26"/>
       <c r="I28" s="26"/>
       <c r="J28" s="26"/>
-      <c r="K28" s="76"/>
+      <c r="K28" s="96"/>
       <c r="L28" s="26"/>
       <c r="M28" s="26"/>
     </row>
@@ -9049,7 +10597,7 @@
       <c r="H29" s="26"/>
       <c r="I29" s="26"/>
       <c r="J29" s="26"/>
-      <c r="K29" s="76"/>
+      <c r="K29" s="96"/>
       <c r="L29" s="26"/>
       <c r="M29" s="26"/>
     </row>
@@ -9064,7 +10612,7 @@
       <c r="H30" s="26"/>
       <c r="I30" s="26"/>
       <c r="J30" s="26"/>
-      <c r="K30" s="76"/>
+      <c r="K30" s="96"/>
       <c r="L30" s="26"/>
       <c r="M30" s="26"/>
     </row>
@@ -9079,7 +10627,7 @@
       <c r="H31" s="26"/>
       <c r="I31" s="26"/>
       <c r="J31" s="26"/>
-      <c r="K31" s="76"/>
+      <c r="K31" s="96"/>
       <c r="L31" s="26"/>
       <c r="M31" s="26"/>
     </row>
@@ -9094,7 +10642,7 @@
       <c r="H32" s="26"/>
       <c r="I32" s="26"/>
       <c r="J32" s="26"/>
-      <c r="K32" s="76"/>
+      <c r="K32" s="96"/>
       <c r="L32" s="26"/>
       <c r="M32" s="26"/>
     </row>
@@ -9109,7 +10657,7 @@
       <c r="H33" s="26"/>
       <c r="I33" s="26"/>
       <c r="J33" s="26"/>
-      <c r="K33" s="76"/>
+      <c r="K33" s="96"/>
       <c r="L33" s="26"/>
       <c r="M33" s="26"/>
     </row>
@@ -9124,7 +10672,7 @@
       <c r="H34" s="26"/>
       <c r="I34" s="26"/>
       <c r="J34" s="26"/>
-      <c r="K34" s="76"/>
+      <c r="K34" s="96"/>
       <c r="L34" s="26"/>
       <c r="M34" s="26"/>
     </row>
@@ -9139,7 +10687,7 @@
       <c r="H35" s="26"/>
       <c r="I35" s="26"/>
       <c r="J35" s="26"/>
-      <c r="K35" s="76"/>
+      <c r="K35" s="96"/>
       <c r="L35" s="26"/>
       <c r="M35" s="26"/>
     </row>
@@ -9154,7 +10702,7 @@
       <c r="H36" s="26"/>
       <c r="I36" s="26"/>
       <c r="J36" s="26"/>
-      <c r="K36" s="76"/>
+      <c r="K36" s="96"/>
       <c r="L36" s="26"/>
       <c r="M36" s="26"/>
     </row>
@@ -9169,7 +10717,7 @@
       <c r="H37" s="26"/>
       <c r="I37" s="26"/>
       <c r="J37" s="26"/>
-      <c r="K37" s="76"/>
+      <c r="K37" s="96"/>
       <c r="L37" s="26"/>
       <c r="M37" s="26"/>
     </row>
@@ -9184,7 +10732,7 @@
       <c r="H38" s="26"/>
       <c r="I38" s="26"/>
       <c r="J38" s="26"/>
-      <c r="K38" s="76"/>
+      <c r="K38" s="96"/>
       <c r="L38" s="26"/>
       <c r="M38" s="26"/>
     </row>
@@ -9199,7 +10747,7 @@
       <c r="H39" s="26"/>
       <c r="I39" s="26"/>
       <c r="J39" s="26"/>
-      <c r="K39" s="76"/>
+      <c r="K39" s="96"/>
       <c r="L39" s="26"/>
       <c r="M39" s="26"/>
     </row>
@@ -9214,7 +10762,7 @@
       <c r="H40" s="26"/>
       <c r="I40" s="26"/>
       <c r="J40" s="26"/>
-      <c r="K40" s="76"/>
+      <c r="K40" s="96"/>
       <c r="L40" s="26"/>
       <c r="M40" s="26"/>
     </row>
@@ -9229,7 +10777,7 @@
       <c r="H41" s="26"/>
       <c r="I41" s="26"/>
       <c r="J41" s="26"/>
-      <c r="K41" s="76"/>
+      <c r="K41" s="96"/>
       <c r="L41" s="26"/>
       <c r="M41" s="26"/>
     </row>
@@ -9244,7 +10792,7 @@
       <c r="H42" s="26"/>
       <c r="I42" s="26"/>
       <c r="J42" s="26"/>
-      <c r="K42" s="76"/>
+      <c r="K42" s="96"/>
       <c r="L42" s="26"/>
       <c r="M42" s="26"/>
     </row>
@@ -9259,7 +10807,7 @@
       <c r="H43" s="26"/>
       <c r="I43" s="26"/>
       <c r="J43" s="26"/>
-      <c r="K43" s="76"/>
+      <c r="K43" s="96"/>
       <c r="L43" s="26"/>
       <c r="M43" s="26"/>
     </row>
@@ -9274,7 +10822,7 @@
       <c r="H44" s="26"/>
       <c r="I44" s="26"/>
       <c r="J44" s="26"/>
-      <c r="K44" s="76"/>
+      <c r="K44" s="96"/>
       <c r="L44" s="26"/>
       <c r="M44" s="26"/>
     </row>
@@ -9289,7 +10837,7 @@
       <c r="H45" s="26"/>
       <c r="I45" s="26"/>
       <c r="J45" s="26"/>
-      <c r="K45" s="76"/>
+      <c r="K45" s="96"/>
       <c r="L45" s="26"/>
       <c r="M45" s="26"/>
     </row>
@@ -9304,7 +10852,7 @@
       <c r="H46" s="26"/>
       <c r="I46" s="26"/>
       <c r="J46" s="26"/>
-      <c r="K46" s="76"/>
+      <c r="K46" s="96"/>
       <c r="L46" s="26"/>
       <c r="M46" s="26"/>
     </row>
@@ -9319,7 +10867,7 @@
       <c r="H47" s="26"/>
       <c r="I47" s="26"/>
       <c r="J47" s="26"/>
-      <c r="K47" s="76"/>
+      <c r="K47" s="96"/>
       <c r="L47" s="26"/>
       <c r="M47" s="26"/>
     </row>
@@ -9334,7 +10882,7 @@
       <c r="H48" s="26"/>
       <c r="I48" s="26"/>
       <c r="J48" s="26"/>
-      <c r="K48" s="76"/>
+      <c r="K48" s="96"/>
       <c r="L48" s="26"/>
       <c r="M48" s="26"/>
     </row>
@@ -9406,210 +10954,210 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{025D3266-9124-624A-BC0F-EF159BDF8541}">
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="65.33203125" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="45" style="81" customWidth="1"/>
-    <col min="2" max="2" width="61.1640625" style="81" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53" style="81" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5" style="82" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="65.33203125" style="83"/>
+    <col min="1" max="1" width="45" style="71" customWidth="1"/>
+    <col min="2" max="2" width="61.1640625" style="71" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53" style="71" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5" style="72" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="65.33203125" style="73"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="80" customFormat="1" ht="25" x14ac:dyDescent="0.2">
-      <c r="A1" s="78" t="s">
+    <row r="1" spans="1:4" s="70" customFormat="1" ht="25" x14ac:dyDescent="0.2">
+      <c r="A1" s="68" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="68" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1" s="69" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A2" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="71" t="s">
+        <v>115</v>
+      </c>
+      <c r="C2" s="71" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="72">
+        <v>0.68325173248234505</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A3" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="B3" s="71" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" s="71" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="72">
+        <v>0.68325173248234505</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A4" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="B4" s="71" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" s="71" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="72">
+        <v>0.68325173248234505</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A5" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="B5" s="71" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" s="71" t="s">
+        <v>106</v>
+      </c>
+      <c r="D5" s="72">
+        <v>0.68041836283516299</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A6" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" s="71" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="71" t="s">
+        <v>106</v>
+      </c>
+      <c r="D6" s="72">
+        <v>0.67742712096802804</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A7" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" s="71" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7" s="71" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="72">
+        <v>0.65343720964277696</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A8" s="71" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8" s="71" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="72">
+        <v>0.64949999999999997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A9" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="B9" s="71" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" s="71" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" s="72">
+        <v>0.64262720538739304</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A10" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="71" t="s">
+        <v>125</v>
+      </c>
+      <c r="C10" s="71" t="s">
+        <v>124</v>
+      </c>
+      <c r="D10" s="72">
+        <v>0.63939999999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="22" x14ac:dyDescent="0.2">
+      <c r="A11" s="71" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" s="71" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" s="72">
+        <v>0.60415152730396504</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="22" x14ac:dyDescent="0.2">
+      <c r="A12" s="71" t="s">
+        <v>109</v>
+      </c>
+      <c r="B12" s="74" t="s">
+        <v>104</v>
+      </c>
+      <c r="D12" s="72">
+        <v>0.603348181891603</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A13" s="71" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="78" t="s">
+      <c r="B13" s="71" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="78" t="s">
-        <v>105</v>
-      </c>
-      <c r="D1" s="79" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A2" s="81" t="s">
-        <v>126</v>
-      </c>
-      <c r="B2" s="81" t="s">
-        <v>118</v>
-      </c>
-      <c r="C2" s="81" t="s">
-        <v>109</v>
-      </c>
-      <c r="D2" s="82">
-        <v>0.68325173248234505</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A3" s="81" t="s">
-        <v>126</v>
-      </c>
-      <c r="B3" s="81" t="s">
-        <v>121</v>
-      </c>
-      <c r="C3" s="81" t="s">
-        <v>109</v>
-      </c>
-      <c r="D3" s="82">
-        <v>0.68325173248234505</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A4" s="81" t="s">
-        <v>126</v>
-      </c>
-      <c r="B4" s="81" t="s">
-        <v>125</v>
-      </c>
-      <c r="C4" s="81" t="s">
-        <v>109</v>
-      </c>
-      <c r="D4" s="82">
-        <v>0.68325173248234505</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A5" s="81" t="s">
-        <v>126</v>
-      </c>
-      <c r="B5" s="81" t="s">
-        <v>120</v>
-      </c>
-      <c r="C5" s="81" t="s">
-        <v>109</v>
-      </c>
-      <c r="D5" s="82">
-        <v>0.68041836283516299</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A6" s="81" t="s">
-        <v>126</v>
-      </c>
-      <c r="B6" s="81" t="s">
-        <v>124</v>
-      </c>
-      <c r="C6" s="81" t="s">
-        <v>109</v>
-      </c>
-      <c r="D6" s="82">
-        <v>0.67742712096802804</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A7" s="81" t="s">
-        <v>126</v>
-      </c>
-      <c r="B7" s="81" t="s">
+      <c r="D13" s="72">
+        <v>0.57569693797857102</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A14" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="B14" s="71" t="s">
         <v>119</v>
       </c>
-      <c r="C7" s="81" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" s="82">
-        <v>0.65343720964277696</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A8" s="81" t="s">
-        <v>129</v>
-      </c>
-      <c r="B8" s="81" t="s">
-        <v>130</v>
-      </c>
-      <c r="D8" s="82">
-        <v>0.64949999999999997</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A9" s="81" t="s">
-        <v>126</v>
-      </c>
-      <c r="B9" s="81" t="s">
-        <v>123</v>
-      </c>
-      <c r="C9" s="81" t="s">
-        <v>109</v>
-      </c>
-      <c r="D9" s="82">
-        <v>0.64262720538739304</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A10" s="81" t="s">
-        <v>126</v>
-      </c>
-      <c r="B10" s="81" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10" s="81" t="s">
-        <v>127</v>
-      </c>
-      <c r="D10" s="82">
-        <v>0.63939999999999997</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="22" x14ac:dyDescent="0.2">
-      <c r="A11" s="81" t="s">
-        <v>112</v>
-      </c>
-      <c r="B11" s="81" t="s">
+      <c r="C14" s="71" t="s">
         <v>106</v>
       </c>
-      <c r="D11" s="82">
-        <v>0.60415152730396504</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="22" x14ac:dyDescent="0.2">
-      <c r="A12" s="81" t="s">
-        <v>112</v>
-      </c>
-      <c r="B12" s="84" t="s">
-        <v>107</v>
-      </c>
-      <c r="D12" s="82">
-        <v>0.603348181891603</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A13" s="81" t="s">
+      <c r="D14" s="72">
+        <v>0.57370283757216001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A15" s="71" t="s">
+        <v>110</v>
+      </c>
+      <c r="B15" s="71" t="s">
         <v>113</v>
       </c>
-      <c r="B13" s="81" t="s">
-        <v>114</v>
-      </c>
-      <c r="D13" s="82">
-        <v>0.57569693797857102</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A14" s="81" t="s">
-        <v>126</v>
-      </c>
-      <c r="B14" s="81" t="s">
-        <v>122</v>
-      </c>
-      <c r="C14" s="81" t="s">
-        <v>109</v>
-      </c>
-      <c r="D14" s="82">
-        <v>0.57370283757216001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A15" s="81" t="s">
-        <v>113</v>
-      </c>
-      <c r="B15" s="81" t="s">
-        <v>116</v>
-      </c>
-      <c r="D15" s="82">
+      <c r="D15" s="72">
         <v>0.51741735167898695</v>
       </c>
     </row>
@@ -9621,208 +11169,208 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E37A00BD-B64F-384F-8AA4-A9588C0E9EEE}">
   <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="65.33203125" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="65.33203125" style="81"/>
-    <col min="4" max="4" width="65.33203125" style="82"/>
-    <col min="5" max="16384" width="65.33203125" style="83"/>
+    <col min="1" max="3" width="65.33203125" style="71"/>
+    <col min="4" max="4" width="65.33203125" style="72"/>
+    <col min="5" max="16384" width="65.33203125" style="73"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="80" customFormat="1" ht="25" x14ac:dyDescent="0.2">
-      <c r="A1" s="78" t="s">
+    <row r="1" spans="1:4" s="70" customFormat="1" ht="25" x14ac:dyDescent="0.2">
+      <c r="A1" s="68" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="68" t="s">
+        <v>108</v>
+      </c>
+      <c r="C1" s="68" t="s">
+        <v>102</v>
+      </c>
+      <c r="D1" s="69" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A2" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="71" t="s">
+        <v>136</v>
+      </c>
+      <c r="C2" s="71" t="s">
+        <v>138</v>
+      </c>
+      <c r="D2" s="72">
+        <v>0.73470000000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A3" s="71" t="s">
+        <v>126</v>
+      </c>
+      <c r="B3" s="71" t="s">
+        <v>137</v>
+      </c>
+      <c r="D3" s="72">
+        <v>0.7097</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="22" x14ac:dyDescent="0.2">
+      <c r="A4" s="71" t="s">
+        <v>109</v>
+      </c>
+      <c r="B4" s="71" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="72">
+        <v>0.69406628387897396</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A5" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="B5" s="71" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5" s="71" t="s">
+        <v>139</v>
+      </c>
+      <c r="D5" s="72">
+        <v>0.665770082977021</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A6" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" s="71" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="71" t="s">
+        <v>139</v>
+      </c>
+      <c r="D6" s="72">
+        <v>0.65203403508906599</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A7" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="B7" s="71" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="71" t="s">
+        <v>139</v>
+      </c>
+      <c r="D7" s="72">
+        <v>0.60864643260521401</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="22" x14ac:dyDescent="0.2">
+      <c r="A8" s="71" t="s">
+        <v>109</v>
+      </c>
+      <c r="B8" s="71" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" s="72">
+        <v>0.60415152730396504</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A9" s="71" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="78" t="s">
-        <v>111</v>
-      </c>
-      <c r="C1" s="78" t="s">
-        <v>105</v>
-      </c>
-      <c r="D1" s="79" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A2" s="81" t="s">
-        <v>126</v>
-      </c>
-      <c r="B2" s="81" t="s">
+      <c r="B9" s="71" t="s">
+        <v>112</v>
+      </c>
+      <c r="D9" s="72">
+        <v>0.59785011377850095</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A10" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="B10" s="71" t="s">
+        <v>129</v>
+      </c>
+      <c r="C10" s="71" t="s">
         <v>139</v>
       </c>
-      <c r="C2" s="81" t="s">
-        <v>141</v>
-      </c>
-      <c r="D2" s="82">
-        <v>0.73470000000000002</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A3" s="81" t="s">
-        <v>129</v>
-      </c>
-      <c r="B3" s="81" t="s">
-        <v>140</v>
-      </c>
-      <c r="D3" s="82">
-        <v>0.7097</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="22" x14ac:dyDescent="0.2">
-      <c r="A4" s="81" t="s">
-        <v>112</v>
-      </c>
-      <c r="B4" s="81" t="s">
-        <v>108</v>
-      </c>
-      <c r="D4" s="82">
-        <v>0.69406628387897396</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A5" s="81" t="s">
-        <v>126</v>
-      </c>
-      <c r="B5" s="81" t="s">
+      <c r="D10" s="72">
+        <v>0.58596491228070102</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A11" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="B11" s="71" t="s">
+        <v>135</v>
+      </c>
+      <c r="C11" s="71" t="s">
+        <v>139</v>
+      </c>
+      <c r="D11" s="72">
+        <v>0.58596491228070102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A12" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="B12" s="71" t="s">
+        <v>128</v>
+      </c>
+      <c r="C12" s="71" t="s">
+        <v>139</v>
+      </c>
+      <c r="D12" s="72">
+        <v>0.57994647302866398</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A13" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="B13" s="71" t="s">
+        <v>134</v>
+      </c>
+      <c r="C13" s="71" t="s">
+        <v>139</v>
+      </c>
+      <c r="D13" s="72">
+        <v>0.579743455999432</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="44" x14ac:dyDescent="0.2">
+      <c r="A14" s="71" t="s">
+        <v>123</v>
+      </c>
+      <c r="B14" s="71" t="s">
         <v>133</v>
       </c>
-      <c r="C5" s="81" t="s">
-        <v>142</v>
-      </c>
-      <c r="D5" s="82">
-        <v>0.665770082977021</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A6" s="81" t="s">
-        <v>126</v>
-      </c>
-      <c r="B6" s="81" t="s">
-        <v>134</v>
-      </c>
-      <c r="C6" s="81" t="s">
-        <v>142</v>
-      </c>
-      <c r="D6" s="82">
-        <v>0.65203403508906599</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A7" s="81" t="s">
-        <v>126</v>
-      </c>
-      <c r="B7" s="81" t="s">
-        <v>135</v>
-      </c>
-      <c r="C7" s="81" t="s">
-        <v>142</v>
-      </c>
-      <c r="D7" s="82">
-        <v>0.60864643260521401</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="22" x14ac:dyDescent="0.2">
-      <c r="A8" s="81" t="s">
-        <v>112</v>
-      </c>
-      <c r="B8" s="81" t="s">
-        <v>106</v>
-      </c>
-      <c r="D8" s="82">
-        <v>0.60415152730396504</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A9" s="81" t="s">
-        <v>113</v>
-      </c>
-      <c r="B9" s="81" t="s">
-        <v>115</v>
-      </c>
-      <c r="D9" s="82">
-        <v>0.59785011377850095</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A10" s="81" t="s">
-        <v>126</v>
-      </c>
-      <c r="B10" s="81" t="s">
-        <v>132</v>
-      </c>
-      <c r="C10" s="81" t="s">
-        <v>142</v>
-      </c>
-      <c r="D10" s="82">
-        <v>0.58596491228070102</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A11" s="81" t="s">
-        <v>126</v>
-      </c>
-      <c r="B11" s="81" t="s">
-        <v>138</v>
-      </c>
-      <c r="C11" s="81" t="s">
-        <v>142</v>
-      </c>
-      <c r="D11" s="82">
-        <v>0.58596491228070102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A12" s="81" t="s">
-        <v>126</v>
-      </c>
-      <c r="B12" s="81" t="s">
-        <v>131</v>
-      </c>
-      <c r="C12" s="81" t="s">
-        <v>142</v>
-      </c>
-      <c r="D12" s="82">
-        <v>0.57994647302866398</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A13" s="81" t="s">
-        <v>126</v>
-      </c>
-      <c r="B13" s="81" t="s">
-        <v>137</v>
-      </c>
-      <c r="C13" s="81" t="s">
-        <v>142</v>
-      </c>
-      <c r="D13" s="82">
-        <v>0.579743455999432</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A14" s="81" t="s">
-        <v>126</v>
-      </c>
-      <c r="B14" s="81" t="s">
-        <v>136</v>
-      </c>
-      <c r="C14" s="81" t="s">
-        <v>142</v>
-      </c>
-      <c r="D14" s="82">
+      <c r="C14" s="71" t="s">
+        <v>139</v>
+      </c>
+      <c r="D14" s="72">
         <v>0.57884998520905395</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="44" x14ac:dyDescent="0.2">
-      <c r="A15" s="81" t="s">
-        <v>113</v>
-      </c>
-      <c r="B15" s="81" t="s">
-        <v>117</v>
-      </c>
-      <c r="D15" s="82">
+      <c r="A15" s="71" t="s">
+        <v>110</v>
+      </c>
+      <c r="B15" s="71" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" s="72">
         <v>0.54874577477317199</v>
       </c>
     </row>
